--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19991059-8505-304B-BEB9-177AAD27E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD685E8-FE59-9A42-B143-6C5FC2D5FC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="СПРАВОЧНИК -1" sheetId="1" r:id="rId1"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD685E8-FE59-9A42-B143-6C5FC2D5FC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E9DCE1-FC9C-3346-8A6A-D0F926B10CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="СПРАВОЧНИК -1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Итоговый расчет с монтажом" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$AA$214</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2177,13 +2177,13 @@
     <t>(n_imp_vert*height + n_imp_hor*width)/1000 * qty</t>
   </si>
   <si>
-    <t>P_SP * qty</t>
-  </si>
-  <si>
     <t>4 * qty</t>
   </si>
   <si>
     <t>2 * n_sash * qty</t>
+  </si>
+  <si>
+    <t>4 * n_frame_rect * qty или 4 * qty</t>
   </si>
 </sst>
 </file>
@@ -11814,7 +11814,7 @@
         <v>0</v>
       </c>
       <c r="O179" s="11" t="s">
-        <v>474</v>
+        <v>23</v>
       </c>
       <c r="Q179" s="11"/>
       <c r="R179" s="11"/>
@@ -11870,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="O180" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q180" s="11"/>
       <c r="R180" s="11"/>
@@ -12093,8 +12093,8 @@
       <c r="N184" s="11">
         <v>0</v>
       </c>
-      <c r="O184" s="11" t="s">
-        <v>711</v>
+      <c r="O184" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="Q184" s="11"/>
       <c r="R184" s="11"/>
@@ -12261,8 +12261,8 @@
       <c r="N187" s="11">
         <v>0</v>
       </c>
-      <c r="O187" t="s">
-        <v>712</v>
+      <c r="O187" s="11" t="s">
+        <v>713</v>
       </c>
       <c r="Q187" s="11"/>
       <c r="R187" s="11"/>
@@ -12425,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="O190" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="Q190" s="11"/>
       <c r="R190" s="11"/>
@@ -12537,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="O192" s="11" t="s">
-        <v>711</v>
+        <v>225</v>
       </c>
       <c r="Q192" s="11"/>
       <c r="R192" s="11"/>
@@ -12593,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="O193" s="11" t="s">
-        <v>711</v>
+        <v>225</v>
       </c>
       <c r="Q193" s="11"/>
       <c r="R193" s="11"/>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q201" s="11"/>
       <c r="R201" s="11"/>
@@ -13099,7 +13099,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q202" s="11"/>
       <c r="R202" s="11"/>
@@ -13273,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q205" s="11"/>
       <c r="R205" s="11"/>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q206" s="11"/>
       <c r="R206" s="11"/>
@@ -13505,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q209" s="11"/>
       <c r="R209" s="11"/>
@@ -13563,7 +13563,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q210" s="11"/>
       <c r="R210" s="11"/>
@@ -13737,7 +13737,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q213" s="11"/>
       <c r="R213" s="11"/>
@@ -13795,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="O214" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q214" s="11"/>
       <c r="R214" s="11"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F538A70-E4F5-E741-B46D-12752863A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A008742F-C133-7A4E-8935-F4BF1EF8F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15918,7 +15918,6 @@
       <c r="N568" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA214" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A008742F-C133-7A4E-8935-F4BF1EF8F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E599377-048B-3A45-82DC-F93C40FFF636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,6 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$AA$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'СПРАВОЧНИК -3'!$A$1:$Q$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2846" uniqueCount="710">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -1157,9 +1158,6 @@
     <t>Периметр одной створки</t>
   </si>
   <si>
-    <t>2*(sash_width + sash_height)/1000</t>
-  </si>
-  <si>
     <t>Штапик общий (глух+створка+фрамуга)</t>
   </si>
   <si>
@@ -2072,9 +2070,6 @@
     <t>Длина профиля по ширине изделия</t>
   </si>
   <si>
-    <t>SW/1000 * N_sash</t>
-  </si>
-  <si>
     <t>Расход порога</t>
   </si>
   <si>
@@ -2118,9 +2113,6 @@
   </si>
   <si>
     <t>Сухари для 4 углов рамы</t>
-  </si>
-  <si>
-    <t>N_nodes_42</t>
   </si>
   <si>
     <t>Для крепления усилителей</t>
@@ -8012,22 +8004,22 @@
         <v>16</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G112" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H112" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I112" s="24" t="s">
         <v>48</v>
@@ -8046,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P112" s="11"/>
       <c r="Q112" s="11"/>
@@ -8068,22 +8060,22 @@
         <v>16</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G113" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H113" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I113" s="24" t="s">
         <v>48</v>
@@ -8102,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="O113" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P113" s="11"/>
       <c r="Q113" s="11"/>
@@ -8124,22 +8116,22 @@
         <v>16</v>
       </c>
       <c r="C114" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E114" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D114" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E114" s="11" t="s">
+      <c r="F114" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="F114" s="11" t="s">
+      <c r="G114" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H114" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G114" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H114" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I114" s="24" t="s">
         <v>48</v>
@@ -8158,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P114" s="11"/>
       <c r="Q114" s="11"/>
@@ -8180,22 +8172,22 @@
         <v>16</v>
       </c>
       <c r="C115" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E115" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D115" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F115" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G115" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H115" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G115" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H115" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I115" s="24" t="s">
         <v>48</v>
@@ -8214,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P115" s="11"/>
       <c r="Q115" s="11"/>
@@ -8236,22 +8228,22 @@
         <v>16</v>
       </c>
       <c r="C116" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E116" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="F116" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="G116" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H116" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="G116" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H116" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I116" s="24" t="s">
         <v>48</v>
@@ -8270,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P116" s="11"/>
       <c r="Q116" s="11"/>
@@ -8292,22 +8284,22 @@
         <v>16</v>
       </c>
       <c r="C117" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E117" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="F117" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E117" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="F117" s="11" t="s">
-        <v>560</v>
-      </c>
       <c r="G117" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H117" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I117" s="24" t="s">
         <v>48</v>
@@ -8326,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="O117" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P117" s="11"/>
       <c r="Q117" s="11"/>
@@ -8348,22 +8340,22 @@
         <v>16</v>
       </c>
       <c r="C118" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E118" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E118" s="11" t="s">
+      <c r="F118" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="G118" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H118" s="21" t="s">
         <v>575</v>
-      </c>
-      <c r="G118" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H118" s="21" t="s">
-        <v>576</v>
       </c>
       <c r="I118" s="24" t="s">
         <v>48</v>
@@ -8382,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P118" s="11"/>
       <c r="Q118" s="11"/>
@@ -8404,22 +8396,22 @@
         <v>16</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E119" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D119" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E119" s="11" t="s">
+      <c r="F119" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G119" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H119" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F119" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G119" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H119" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I119" s="24" t="s">
         <v>48</v>
@@ -8438,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="O119" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P119" s="11"/>
       <c r="Q119" s="11"/>
@@ -8460,22 +8452,22 @@
         <v>101</v>
       </c>
       <c r="C120" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D120" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G120" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H120" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I120" s="24" t="s">
         <v>48</v>
@@ -8494,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="O120" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P120" s="11"/>
       <c r="Q120" s="11"/>
@@ -8516,22 +8508,22 @@
         <v>101</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G121" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H121" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I121" s="24" t="s">
         <v>48</v>
@@ -8550,7 +8542,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P121" s="11"/>
       <c r="Q121" s="11"/>
@@ -8572,22 +8564,22 @@
         <v>101</v>
       </c>
       <c r="C122" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E122" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D122" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E122" s="11" t="s">
+      <c r="F122" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="F122" s="11" t="s">
+      <c r="G122" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H122" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G122" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H122" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I122" s="24" t="s">
         <v>48</v>
@@ -8606,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P122" s="11"/>
       <c r="Q122" s="11"/>
@@ -8628,22 +8620,22 @@
         <v>101</v>
       </c>
       <c r="C123" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E123" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D123" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F123" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G123" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H123" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G123" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H123" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I123" s="24" t="s">
         <v>48</v>
@@ -8662,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="O123" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P123" s="11"/>
       <c r="Q123" s="11"/>
@@ -8684,22 +8676,22 @@
         <v>101</v>
       </c>
       <c r="C124" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E124" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="F124" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="G124" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H124" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="G124" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H124" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I124" s="24" t="s">
         <v>48</v>
@@ -8718,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P124" s="11"/>
       <c r="Q124" s="11"/>
@@ -8740,22 +8732,22 @@
         <v>101</v>
       </c>
       <c r="C125" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E125" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="F125" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E125" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>560</v>
-      </c>
       <c r="G125" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H125" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I125" s="24" t="s">
         <v>48</v>
@@ -8774,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P125" s="11"/>
       <c r="Q125" s="11"/>
@@ -8796,22 +8788,22 @@
         <v>101</v>
       </c>
       <c r="C126" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E126" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D126" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E126" s="11" t="s">
+      <c r="F126" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="F126" s="11" t="s">
+      <c r="G126" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H126" s="21" t="s">
         <v>575</v>
-      </c>
-      <c r="G126" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H126" s="21" t="s">
-        <v>576</v>
       </c>
       <c r="I126" s="24" t="s">
         <v>48</v>
@@ -8830,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="O126" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P126" s="11"/>
       <c r="Q126" s="11"/>
@@ -8852,22 +8844,22 @@
         <v>101</v>
       </c>
       <c r="C127" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E127" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E127" s="11" t="s">
+      <c r="F127" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G127" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H127" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F127" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G127" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H127" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I127" s="24" t="s">
         <v>48</v>
@@ -8886,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="O127" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P127" s="11"/>
       <c r="Q127" s="11"/>
@@ -8908,22 +8900,22 @@
         <v>120</v>
       </c>
       <c r="C128" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D128" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E128" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G128" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H128" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I128" s="24" t="s">
         <v>48</v>
@@ -8942,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P128" s="11"/>
       <c r="Q128" s="11"/>
@@ -8964,22 +8956,22 @@
         <v>120</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G129" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H129" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I129" s="24" t="s">
         <v>48</v>
@@ -8998,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="O129" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P129" s="11"/>
       <c r="Q129" s="11"/>
@@ -9020,22 +9012,22 @@
         <v>120</v>
       </c>
       <c r="C130" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E130" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D130" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E130" s="11" t="s">
+      <c r="F130" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="G130" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H130" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G130" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H130" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I130" s="24" t="s">
         <v>48</v>
@@ -9054,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="O130" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P130" s="11"/>
       <c r="Q130" s="11"/>
@@ -9076,22 +9068,22 @@
         <v>120</v>
       </c>
       <c r="C131" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E131" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D131" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E131" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F131" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G131" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H131" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G131" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H131" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I131" s="24" t="s">
         <v>48</v>
@@ -9110,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P131" s="11"/>
       <c r="Q131" s="11"/>
@@ -9132,22 +9124,22 @@
         <v>120</v>
       </c>
       <c r="C132" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E132" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="F132" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="G132" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H132" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="G132" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H132" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I132" s="24" t="s">
         <v>48</v>
@@ -9166,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P132" s="11"/>
       <c r="Q132" s="11"/>
@@ -9188,22 +9180,22 @@
         <v>120</v>
       </c>
       <c r="C133" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E133" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="F133" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E133" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="F133" s="11" t="s">
-        <v>560</v>
-      </c>
       <c r="G133" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H133" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I133" s="24" t="s">
         <v>48</v>
@@ -9222,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P133" s="11"/>
       <c r="Q133" s="11"/>
@@ -9244,22 +9236,22 @@
         <v>120</v>
       </c>
       <c r="C134" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E134" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D134" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E134" s="11" t="s">
+      <c r="F134" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="F134" s="11" t="s">
+      <c r="G134" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H134" s="21" t="s">
         <v>575</v>
-      </c>
-      <c r="G134" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H134" s="21" t="s">
-        <v>576</v>
       </c>
       <c r="I134" s="24" t="s">
         <v>48</v>
@@ -9278,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P134" s="11"/>
       <c r="Q134" s="11"/>
@@ -9300,22 +9292,22 @@
         <v>120</v>
       </c>
       <c r="C135" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E135" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D135" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E135" s="11" t="s">
+      <c r="F135" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G135" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H135" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F135" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G135" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H135" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I135" s="24" t="s">
         <v>48</v>
@@ -9334,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P135" s="11"/>
       <c r="Q135" s="11"/>
@@ -9356,22 +9348,22 @@
         <v>120</v>
       </c>
       <c r="C136" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D136" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="D136" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E136" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G136" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H136" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I136" s="24" t="s">
         <v>48</v>
@@ -9390,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P136" s="11"/>
       <c r="Q136" s="11"/>
@@ -9412,22 +9404,22 @@
         <v>120</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E137" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G137" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H137" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I137" s="24" t="s">
         <v>48</v>
@@ -9446,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P137" s="11"/>
       <c r="Q137" s="11"/>
@@ -9468,22 +9460,22 @@
         <v>120</v>
       </c>
       <c r="C138" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E138" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D138" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E138" s="11" t="s">
+      <c r="F138" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="F138" s="11" t="s">
+      <c r="G138" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H138" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G138" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H138" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I138" s="24" t="s">
         <v>48</v>
@@ -9502,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P138" s="11"/>
       <c r="Q138" s="11"/>
@@ -9524,22 +9516,22 @@
         <v>120</v>
       </c>
       <c r="C139" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E139" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D139" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E139" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F139" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G139" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H139" s="21" t="s">
         <v>564</v>
-      </c>
-      <c r="G139" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H139" s="21" t="s">
-        <v>565</v>
       </c>
       <c r="I139" s="24" t="s">
         <v>48</v>
@@ -9558,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P139" s="11"/>
       <c r="Q139" s="11"/>
@@ -9580,22 +9572,22 @@
         <v>120</v>
       </c>
       <c r="C140" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E140" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D140" s="11" t="s">
+      <c r="F140" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E140" s="11" t="s">
+      <c r="G140" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H140" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F140" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="G140" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H140" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I140" s="24" t="s">
         <v>48</v>
@@ -9614,7 +9606,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P140" s="11"/>
       <c r="Q140" s="11"/>
@@ -9636,22 +9628,22 @@
         <v>120</v>
       </c>
       <c r="C141" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E141" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="F141" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="E141" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="F141" s="11" t="s">
-        <v>560</v>
-      </c>
       <c r="G141" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H141" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I141" s="24" t="s">
         <v>48</v>
@@ -9670,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P141" s="11"/>
       <c r="Q141" s="11"/>
@@ -9692,22 +9684,22 @@
         <v>120</v>
       </c>
       <c r="C142" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E142" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D142" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E142" s="11" t="s">
+      <c r="F142" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="F142" s="11" t="s">
+      <c r="G142" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H142" s="21" t="s">
         <v>575</v>
-      </c>
-      <c r="G142" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H142" s="21" t="s">
-        <v>576</v>
       </c>
       <c r="I142" s="24" t="s">
         <v>48</v>
@@ -9726,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P142" s="11"/>
       <c r="Q142" s="11"/>
@@ -9748,22 +9740,22 @@
         <v>120</v>
       </c>
       <c r="C143" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E143" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D143" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E143" s="11" t="s">
+      <c r="F143" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G143" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H143" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F143" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G143" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H143" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I143" s="24" t="s">
         <v>48</v>
@@ -9782,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P143" s="11"/>
       <c r="Q143" s="11"/>
@@ -9804,22 +9796,22 @@
         <v>16</v>
       </c>
       <c r="C144" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E144" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="D144" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E144" s="11" t="s">
+      <c r="F144" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G144" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H144" s="21" t="s">
         <v>581</v>
-      </c>
-      <c r="F144" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G144" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H144" s="21" t="s">
-        <v>582</v>
       </c>
       <c r="I144" s="24" t="s">
         <v>48</v>
@@ -9838,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P144" s="11"/>
       <c r="Q144" s="11"/>
@@ -9860,22 +9852,22 @@
         <v>16</v>
       </c>
       <c r="C145" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E145" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="D145" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E145" s="11" t="s">
-        <v>584</v>
-      </c>
       <c r="F145" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G145" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H145" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I145" s="24" t="s">
         <v>48</v>
@@ -9894,7 +9886,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P145" s="11"/>
       <c r="Q145" s="11"/>
@@ -9916,22 +9908,22 @@
         <v>120</v>
       </c>
       <c r="C146" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E146" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="D146" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E146" s="11" t="s">
+      <c r="F146" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="G146" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H146" s="21" t="s">
         <v>581</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="G146" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H146" s="21" t="s">
-        <v>582</v>
       </c>
       <c r="I146" s="24" t="s">
         <v>48</v>
@@ -9950,7 +9942,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P146" s="11"/>
       <c r="Q146" s="11"/>
@@ -9972,22 +9964,22 @@
         <v>120</v>
       </c>
       <c r="C147" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E147" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="D147" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E147" s="11" t="s">
-        <v>584</v>
-      </c>
       <c r="F147" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G147" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H147" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I147" s="24" t="s">
         <v>48</v>
@@ -10006,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P147" s="11"/>
       <c r="Q147" s="11"/>
@@ -10023,22 +10015,22 @@
     </row>
     <row r="148" spans="1:27" s="38" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B148" s="35" t="s">
         <v>101</v>
       </c>
       <c r="C148" s="35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D148" s="35" t="s">
         <v>172</v>
       </c>
       <c r="E148" s="35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G148" s="36" t="s">
         <v>21</v>
@@ -10063,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Q148" s="35"/>
       <c r="R148" s="35"/>
@@ -10079,7 +10071,7 @@
     </row>
     <row r="149" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>101</v>
@@ -10088,13 +10080,13 @@
         <v>214</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E149" s="11" t="s">
         <v>216</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G149" s="24" t="s">
         <v>21</v>
@@ -10119,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="Q149" s="11"/>
       <c r="R149" s="11"/>
@@ -10135,19 +10127,19 @@
     </row>
     <row r="150" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D150" s="11" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F150" s="11" t="s">
         <v>123</v>
@@ -10156,7 +10148,7 @@
         <v>21</v>
       </c>
       <c r="H150" s="21" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I150" s="24" t="s">
         <v>21</v>
@@ -10175,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q150" s="11"/>
       <c r="R150" s="11"/>
@@ -10191,28 +10183,28 @@
     </row>
     <row r="151" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C151" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D151" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="D151" s="11" t="s">
+      <c r="E151" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="F151" s="11" t="s">
         <v>447</v>
-      </c>
-      <c r="E151" s="11" t="s">
-        <v>449</v>
-      </c>
-      <c r="F151" s="11" t="s">
-        <v>448</v>
       </c>
       <c r="G151" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H151" s="21" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I151" s="24" t="s">
         <v>21</v>
@@ -10231,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="Q151" s="11"/>
       <c r="R151" s="11"/>
@@ -10247,28 +10239,28 @@
     </row>
     <row r="152" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C152" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D152" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="E152" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="F152" s="11" t="s">
         <v>452</v>
-      </c>
-      <c r="E152" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>453</v>
       </c>
       <c r="G152" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H152" s="21" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I152" s="24" t="s">
         <v>21</v>
@@ -10287,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="Q152" s="11"/>
       <c r="R152" s="11"/>
@@ -10303,19 +10295,19 @@
     </row>
     <row r="153" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D153" s="11" t="s">
         <v>156</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F153" s="11" t="s">
         <v>130</v>
@@ -10324,7 +10316,7 @@
         <v>21</v>
       </c>
       <c r="H153" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I153" s="24" t="s">
         <v>21</v>
@@ -10343,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="Q153" s="11"/>
       <c r="R153" s="11"/>
@@ -10359,19 +10351,19 @@
     </row>
     <row r="154" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C154" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D154" s="11" t="s">
+      <c r="E154" s="11" t="s">
         <v>461</v>
-      </c>
-      <c r="E154" s="11" t="s">
-        <v>462</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>130</v>
@@ -10380,7 +10372,7 @@
         <v>21</v>
       </c>
       <c r="H154" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I154" s="24" t="s">
         <v>21</v>
@@ -10399,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="Q154" s="11"/>
       <c r="R154" s="11"/>
@@ -10415,28 +10407,28 @@
     </row>
     <row r="155" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C155" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="D155" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D155" s="11" t="s">
+      <c r="E155" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="F155" s="11" t="s">
         <v>465</v>
-      </c>
-      <c r="E155" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="F155" s="11" t="s">
-        <v>466</v>
       </c>
       <c r="G155" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H155" s="21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I155" s="24" t="s">
         <v>21</v>
@@ -10455,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="Q155" s="11"/>
       <c r="R155" s="11"/>
@@ -10471,22 +10463,22 @@
     </row>
     <row r="156" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C156" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D156" s="11" t="s">
         <v>469</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>470</v>
       </c>
       <c r="E156" s="11" t="s">
         <v>287</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G156" s="24" t="s">
         <v>21</v>
@@ -10511,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="Q156" s="11"/>
       <c r="R156" s="11"/>
@@ -10527,7 +10519,7 @@
     </row>
     <row r="157" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>101</v>
@@ -10542,13 +10534,13 @@
         <v>186</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G157" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H157" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I157" s="24" t="s">
         <v>21</v>
@@ -10567,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="11" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="Q157" s="11"/>
       <c r="R157" s="11"/>
@@ -10583,13 +10575,13 @@
     </row>
     <row r="158" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D158" s="11" t="s">
         <v>62</v>
@@ -10623,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q158" s="11"/>
       <c r="R158" s="11"/>
@@ -10639,16 +10631,16 @@
     </row>
     <row r="159" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C159" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D159" s="11" t="s">
         <v>476</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>477</v>
       </c>
       <c r="E159" s="11" t="s">
         <v>189</v>
@@ -10679,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="Q159" s="11"/>
       <c r="R159" s="11"/>
@@ -10695,13 +10687,13 @@
     </row>
     <row r="160" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D160" s="11" t="s">
         <v>62</v>
@@ -10735,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="11" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="Q160" s="11"/>
       <c r="R160" s="11"/>
@@ -10751,7 +10743,7 @@
     </row>
     <row r="161" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>101</v>
@@ -10760,10 +10752,10 @@
         <v>195</v>
       </c>
       <c r="D161" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E161" s="11" t="s">
         <v>479</v>
-      </c>
-      <c r="E161" s="11" t="s">
-        <v>480</v>
       </c>
       <c r="F161" s="11" t="s">
         <v>200</v>
@@ -10791,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="Q161" s="11"/>
       <c r="R161" s="11"/>
@@ -10807,7 +10799,7 @@
     </row>
     <row r="162" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>101</v>
@@ -10819,7 +10811,7 @@
         <v>52</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F162" s="11" t="s">
         <v>200</v>
@@ -10847,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="Q162" s="11"/>
       <c r="R162" s="11"/>
@@ -10863,22 +10855,22 @@
     </row>
     <row r="163" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C163" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D163" s="11" t="s">
         <v>482</v>
-      </c>
-      <c r="D163" s="11" t="s">
-        <v>483</v>
       </c>
       <c r="E163" s="11" t="s">
         <v>197</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G163" s="24" t="s">
         <v>48</v>
@@ -10919,13 +10911,13 @@
     </row>
     <row r="164" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D164" s="11" t="s">
         <v>62</v>
@@ -10934,7 +10926,7 @@
         <v>199</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G164" s="24" t="s">
         <v>48</v>
@@ -10975,22 +10967,22 @@
     </row>
     <row r="165" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D165" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="E165" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="E165" s="11" t="s">
-        <v>486</v>
-      </c>
       <c r="F165" s="11" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G165" s="24" t="s">
         <v>21</v>
@@ -11015,7 +11007,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q165" s="11"/>
       <c r="R165" s="11"/>
@@ -11031,22 +11023,22 @@
     </row>
     <row r="166" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C166" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="D166" s="11" t="s">
         <v>487</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>488</v>
       </c>
       <c r="E166" s="11" t="s">
         <v>224</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G166" s="24" t="s">
         <v>21</v>
@@ -11071,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q166" s="11"/>
       <c r="R166" s="11"/>
@@ -11087,13 +11079,13 @@
     </row>
     <row r="167" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D167" s="11" t="s">
         <v>93</v>
@@ -11102,7 +11094,7 @@
         <v>203</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G167" s="24" t="s">
         <v>21</v>
@@ -11127,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q167" s="11"/>
       <c r="R167" s="11"/>
@@ -11143,7 +11135,7 @@
     </row>
     <row r="168" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>101</v>
@@ -11158,7 +11150,7 @@
         <v>90</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G168" s="24" t="s">
         <v>21</v>
@@ -11199,13 +11191,13 @@
     </row>
     <row r="169" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D169" s="11" t="s">
         <v>97</v>
@@ -11214,7 +11206,7 @@
         <v>98</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G169" s="24" t="s">
         <v>21</v>
@@ -11239,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q169" s="11"/>
       <c r="R169" s="11"/>
@@ -11255,28 +11247,28 @@
     </row>
     <row r="170" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C170" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="D170" s="11" t="s">
         <v>493</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>494</v>
       </c>
       <c r="E170" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F170" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G170" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H170" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I170" s="24" t="s">
         <v>48</v>
@@ -11295,7 +11287,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q170" s="11"/>
       <c r="R170" s="11"/>
@@ -11311,13 +11303,13 @@
     </row>
     <row r="171" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D171" s="11" t="s">
         <v>236</v>
@@ -11326,13 +11318,13 @@
         <v>111</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G171" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H171" s="21" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I171" s="24" t="s">
         <v>48</v>
@@ -11367,28 +11359,28 @@
     </row>
     <row r="172" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C172" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="D172" s="11" t="s">
         <v>502</v>
-      </c>
-      <c r="D172" s="11" t="s">
-        <v>503</v>
       </c>
       <c r="E172" s="11" t="s">
         <v>269</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G172" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H172" s="21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I172" s="24" t="s">
         <v>48</v>
@@ -11423,28 +11415,28 @@
     </row>
     <row r="173" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C173" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D173" s="11" t="s">
         <v>505</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>506</v>
       </c>
       <c r="E173" s="11" t="s">
         <v>118</v>
       </c>
       <c r="F173" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G173" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H173" s="21" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I173" s="24" t="s">
         <v>119</v>
@@ -11479,28 +11471,28 @@
     </row>
     <row r="174" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C174" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="D174" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="D174" s="11" t="s">
-        <v>509</v>
       </c>
       <c r="E174" s="11" t="s">
         <v>247</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G174" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H174" s="21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I174" s="24" t="s">
         <v>119</v>
@@ -11535,13 +11527,13 @@
     </row>
     <row r="175" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D175" s="11" t="s">
         <v>106</v>
@@ -11550,13 +11542,13 @@
         <v>313</v>
       </c>
       <c r="F175" s="11" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G175" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H175" s="21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I175" s="24" t="s">
         <v>48</v>
@@ -11591,28 +11583,28 @@
     </row>
     <row r="176" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D176" s="11" t="s">
         <v>168</v>
       </c>
       <c r="E176" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G176" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H176" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I176" s="24" t="s">
         <v>119</v>
@@ -11647,25 +11639,25 @@
     </row>
     <row r="177" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C177" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="E177" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="E177" s="11" t="s">
-        <v>518</v>
-      </c>
       <c r="F177" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G177" s="24" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H177" s="21">
         <v>230</v>
@@ -11703,28 +11695,28 @@
     </row>
     <row r="178" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C178" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="D178" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="E178" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="E178" s="11" t="s">
-        <v>521</v>
-      </c>
       <c r="F178" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G178" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H178" s="21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I178" s="24" t="s">
         <v>21</v>
@@ -11743,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="O178" s="11" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="Q178" s="11"/>
       <c r="R178" s="11"/>
@@ -11759,7 +11751,7 @@
     </row>
     <row r="179" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>16</v>
@@ -11768,19 +11760,19 @@
         <v>151</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E179" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G179" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H179" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I179" s="24" t="s">
         <v>21</v>
@@ -11815,28 +11807,28 @@
     </row>
     <row r="180" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B180" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C180" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>525</v>
-      </c>
-      <c r="D180" s="11" t="s">
-        <v>526</v>
       </c>
       <c r="E180" s="11" t="s">
         <v>157</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G180" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H180" s="21" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I180" s="24" t="s">
         <v>21</v>
@@ -11855,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="O180" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="Q180" s="11"/>
       <c r="R180" s="11"/>
@@ -11871,28 +11863,28 @@
     </row>
     <row r="181" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B181" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E181" s="11" t="s">
         <v>160</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G181" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H181" s="21" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I181" s="24" t="s">
         <v>21</v>
@@ -11911,7 +11903,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="Q181" s="11"/>
       <c r="R181" s="11"/>
@@ -11927,7 +11919,7 @@
     </row>
     <row r="182" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B182" s="17" t="s">
         <v>16</v>
@@ -11936,19 +11928,19 @@
         <v>24</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E182" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G182" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H182" s="21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I182" s="24" t="s">
         <v>21</v>
@@ -11967,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="O182" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="Q182" s="11"/>
       <c r="R182" s="11"/>
@@ -11983,7 +11975,7 @@
     </row>
     <row r="183" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B183" s="17" t="s">
         <v>16</v>
@@ -11992,19 +11984,19 @@
         <v>29</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E183" s="11" t="s">
         <v>31</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G183" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H183" s="21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I183" s="24" t="s">
         <v>21</v>
@@ -12023,7 +12015,7 @@
         <v>0</v>
       </c>
       <c r="O183" s="11" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="Q183" s="11"/>
       <c r="R183" s="11"/>
@@ -12039,7 +12031,7 @@
     </row>
     <row r="184" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B184" s="17" t="s">
         <v>16</v>
@@ -12048,13 +12040,13 @@
         <v>39</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E184" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G184" s="24" t="s">
         <v>21</v>
@@ -12095,7 +12087,7 @@
     </row>
     <row r="185" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B185" s="17" t="s">
         <v>16</v>
@@ -12104,13 +12096,13 @@
         <v>214</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E185" s="11" t="s">
         <v>216</v>
       </c>
       <c r="F185" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G185" s="24" t="s">
         <v>21</v>
@@ -12151,13 +12143,13 @@
     </row>
     <row r="186" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B186" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D186" s="11" t="s">
         <v>52</v>
@@ -12166,7 +12158,7 @@
         <v>53</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G186" s="24" t="s">
         <v>48</v>
@@ -12207,7 +12199,7 @@
     </row>
     <row r="187" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B187" s="17" t="s">
         <v>16</v>
@@ -12216,13 +12208,13 @@
         <v>335</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E187" s="11" t="s">
         <v>336</v>
       </c>
       <c r="F187" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G187" s="24" t="s">
         <v>48</v>
@@ -12247,7 +12239,7 @@
         <v>0</v>
       </c>
       <c r="O187" s="11" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="Q187" s="11"/>
       <c r="R187" s="11"/>
@@ -12258,7 +12250,7 @@
     </row>
     <row r="188" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B188" s="17" t="s">
         <v>16</v>
@@ -12267,13 +12259,13 @@
         <v>337</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E188" s="11" t="s">
         <v>338</v>
       </c>
       <c r="F188" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G188" s="24" t="s">
         <v>48</v>
@@ -12314,7 +12306,7 @@
     </row>
     <row r="189" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B189" s="17" t="s">
         <v>16</v>
@@ -12323,13 +12315,13 @@
         <v>339</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E189" s="11" t="s">
         <v>63</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G189" s="24" t="s">
         <v>48</v>
@@ -12370,22 +12362,22 @@
     </row>
     <row r="190" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B190" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C190" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="D190" s="11" t="s">
         <v>539</v>
-      </c>
-      <c r="D190" s="11" t="s">
-        <v>540</v>
       </c>
       <c r="E190" s="11" t="s">
         <v>80</v>
       </c>
       <c r="F190" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G190" s="24" t="s">
         <v>48</v>
@@ -12426,22 +12418,22 @@
     </row>
     <row r="191" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B191" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E191" s="11" t="s">
         <v>224</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G191" s="24" t="s">
         <v>21</v>
@@ -12466,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="O191" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q191" s="11"/>
       <c r="R191" s="11"/>
@@ -12482,13 +12474,13 @@
     </row>
     <row r="192" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B192" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D192" s="11" t="s">
         <v>93</v>
@@ -12497,7 +12489,7 @@
         <v>94</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G192" s="24" t="s">
         <v>21</v>
@@ -12538,22 +12530,22 @@
     </row>
     <row r="193" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B193" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C193" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="D193" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="D193" s="11" t="s">
-        <v>544</v>
       </c>
       <c r="E193" s="11" t="s">
         <v>98</v>
       </c>
       <c r="F193" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G193" s="24" t="s">
         <v>21</v>
@@ -12594,28 +12586,28 @@
     </row>
     <row r="194" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B194" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C194" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="E194" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="D194" s="11" t="s">
+      <c r="F194" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="G194" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H194" s="21" t="s">
         <v>494</v>
-      </c>
-      <c r="E194" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="F194" s="11" t="s">
-        <v>653</v>
-      </c>
-      <c r="G194" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H194" s="21" t="s">
-        <v>495</v>
       </c>
       <c r="I194" s="24" t="s">
         <v>48</v>
@@ -12634,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="O194" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q194" s="11"/>
       <c r="R194" s="11"/>
@@ -12650,13 +12642,13 @@
     </row>
     <row r="195" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B195" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D195" s="11" t="s">
         <v>236</v>
@@ -12665,13 +12657,13 @@
         <v>237</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G195" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H195" s="21" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I195" s="24" t="s">
         <v>48</v>
@@ -12706,28 +12698,28 @@
     </row>
     <row r="196" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B196" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C196" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="D196" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="D196" s="11" t="s">
-        <v>549</v>
       </c>
       <c r="E196" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G196" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H196" s="21" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I196" s="24" t="s">
         <v>48</v>
@@ -12762,28 +12754,28 @@
     </row>
     <row r="197" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B197" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E197" s="11" t="s">
         <v>244</v>
       </c>
       <c r="F197" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G197" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H197" s="21" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I197" s="24" t="s">
         <v>48</v>
@@ -12818,28 +12810,28 @@
     </row>
     <row r="198" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B198" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C198" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="D198" s="11" t="s">
+      <c r="E198" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="E198" s="11" t="s">
-        <v>555</v>
-      </c>
       <c r="F198" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G198" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H198" s="21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I198" s="24" t="s">
         <v>119</v>
@@ -12874,28 +12866,28 @@
     </row>
     <row r="199" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B199" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C199" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D199" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="D199" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E199" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G199" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H199" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I199" s="24" t="s">
         <v>48</v>
@@ -12914,7 +12906,7 @@
         <v>0</v>
       </c>
       <c r="O199" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q199" s="11"/>
       <c r="R199" s="11"/>
@@ -12930,28 +12922,28 @@
     </row>
     <row r="200" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B200" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E200" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G200" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H200" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I200" s="24" t="s">
         <v>48</v>
@@ -12970,7 +12962,7 @@
         <v>0</v>
       </c>
       <c r="O200" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q200" s="11"/>
       <c r="R200" s="11"/>
@@ -12986,28 +12978,28 @@
     </row>
     <row r="201" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B201" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C201" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E201" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D201" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E201" s="11" t="s">
-        <v>563</v>
-      </c>
       <c r="F201" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G201" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H201" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I201" s="24" t="s">
         <v>48</v>
@@ -13026,7 +13018,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q201" s="11"/>
       <c r="R201" s="11"/>
@@ -13034,7 +13026,7 @@
       <c r="T201" s="11"/>
       <c r="U201" s="11"/>
       <c r="V201" s="15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="W201" s="11"/>
       <c r="X201" s="11"/>
@@ -13044,28 +13036,28 @@
     </row>
     <row r="202" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B202" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C202" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E202" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D202" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E202" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F202" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G202" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H202" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I202" s="24" t="s">
         <v>48</v>
@@ -13084,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q202" s="11"/>
       <c r="R202" s="11"/>
@@ -13092,7 +13084,7 @@
       <c r="T202" s="11"/>
       <c r="U202" s="11"/>
       <c r="V202" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W202" s="11"/>
       <c r="X202" s="11"/>
@@ -13102,28 +13094,28 @@
     </row>
     <row r="203" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C203" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E203" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D203" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E203" s="11" t="s">
+      <c r="F203" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="G203" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H203" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F203" s="11" t="s">
-        <v>653</v>
-      </c>
-      <c r="G203" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H203" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I203" s="24" t="s">
         <v>48</v>
@@ -13142,7 +13134,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q203" s="11"/>
       <c r="R203" s="11"/>
@@ -13150,7 +13142,7 @@
       <c r="T203" s="11"/>
       <c r="U203" s="11"/>
       <c r="V203" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W203" s="11"/>
       <c r="X203" s="11"/>
@@ -13160,28 +13152,28 @@
     </row>
     <row r="204" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C204" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E204" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D204" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E204" s="11" t="s">
-        <v>572</v>
-      </c>
       <c r="F204" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G204" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H204" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I204" s="24" t="s">
         <v>48</v>
@@ -13200,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q204" s="11"/>
       <c r="R204" s="11"/>
@@ -13208,7 +13200,7 @@
       <c r="T204" s="11"/>
       <c r="U204" s="11"/>
       <c r="V204" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W204" s="11"/>
       <c r="X204" s="11"/>
@@ -13218,28 +13210,28 @@
     </row>
     <row r="205" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C205" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E205" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D205" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E205" s="11" t="s">
-        <v>574</v>
-      </c>
       <c r="F205" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G205" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H205" s="21" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I205" s="24" t="s">
         <v>48</v>
@@ -13258,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q205" s="11"/>
       <c r="R205" s="11"/>
@@ -13266,7 +13258,7 @@
       <c r="T205" s="11"/>
       <c r="U205" s="11"/>
       <c r="V205" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W205" s="11"/>
       <c r="X205" s="11"/>
@@ -13276,28 +13268,28 @@
     </row>
     <row r="206" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C206" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E206" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D206" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E206" s="11" t="s">
+      <c r="F206" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="G206" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H206" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F206" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="G206" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H206" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I206" s="24" t="s">
         <v>48</v>
@@ -13316,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q206" s="11"/>
       <c r="R206" s="11"/>
@@ -13324,7 +13316,7 @@
       <c r="T206" s="11"/>
       <c r="U206" s="11"/>
       <c r="V206" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W206" s="11"/>
       <c r="X206" s="11"/>
@@ -13334,28 +13326,28 @@
     </row>
     <row r="207" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C207" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D207" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="D207" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E207" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F207" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G207" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H207" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I207" s="24" t="s">
         <v>48</v>
@@ -13374,7 +13366,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q207" s="11"/>
       <c r="R207" s="11"/>
@@ -13382,7 +13374,7 @@
       <c r="T207" s="11"/>
       <c r="U207" s="11"/>
       <c r="V207" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W207" s="11"/>
       <c r="X207" s="11"/>
@@ -13392,28 +13384,28 @@
     </row>
     <row r="208" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E208" s="11" t="s">
         <v>229</v>
       </c>
       <c r="F208" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G208" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H208" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I208" s="24" t="s">
         <v>48</v>
@@ -13432,7 +13424,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q208" s="11"/>
       <c r="R208" s="11"/>
@@ -13440,7 +13432,7 @@
       <c r="T208" s="11"/>
       <c r="U208" s="11"/>
       <c r="V208" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W208" s="11"/>
       <c r="X208" s="11"/>
@@ -13450,28 +13442,28 @@
     </row>
     <row r="209" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C209" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E209" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="D209" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E209" s="11" t="s">
-        <v>563</v>
-      </c>
       <c r="F209" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G209" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H209" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I209" s="24" t="s">
         <v>48</v>
@@ -13490,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q209" s="11"/>
       <c r="R209" s="11"/>
@@ -13498,7 +13490,7 @@
       <c r="T209" s="11"/>
       <c r="U209" s="11"/>
       <c r="V209" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W209" s="11"/>
       <c r="X209" s="11"/>
@@ -13508,28 +13500,28 @@
     </row>
     <row r="210" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C210" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E210" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D210" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E210" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="F210" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G210" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H210" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I210" s="24" t="s">
         <v>48</v>
@@ -13548,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q210" s="11"/>
       <c r="R210" s="11"/>
@@ -13556,7 +13548,7 @@
       <c r="T210" s="11"/>
       <c r="U210" s="11"/>
       <c r="V210" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W210" s="11"/>
       <c r="X210" s="11"/>
@@ -13566,28 +13558,28 @@
     </row>
     <row r="211" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C211" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E211" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D211" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E211" s="11" t="s">
+      <c r="F211" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="G211" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H211" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F211" s="11" t="s">
-        <v>653</v>
-      </c>
-      <c r="G211" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H211" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="I211" s="24" t="s">
         <v>48</v>
@@ -13606,7 +13598,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q211" s="11"/>
       <c r="R211" s="11"/>
@@ -13614,7 +13606,7 @@
       <c r="T211" s="11"/>
       <c r="U211" s="11"/>
       <c r="V211" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W211" s="11"/>
       <c r="X211" s="11"/>
@@ -13624,28 +13616,28 @@
     </row>
     <row r="212" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C212" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E212" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="D212" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E212" s="11" t="s">
-        <v>572</v>
-      </c>
       <c r="F212" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G212" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H212" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I212" s="24" t="s">
         <v>48</v>
@@ -13664,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q212" s="11"/>
       <c r="R212" s="11"/>
@@ -13672,7 +13664,7 @@
       <c r="T212" s="11"/>
       <c r="U212" s="11"/>
       <c r="V212" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W212" s="11"/>
       <c r="X212" s="11"/>
@@ -13682,28 +13674,28 @@
     </row>
     <row r="213" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B213" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C213" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E213" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D213" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E213" s="11" t="s">
-        <v>574</v>
-      </c>
       <c r="F213" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G213" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H213" s="21" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I213" s="24" t="s">
         <v>48</v>
@@ -13722,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q213" s="11"/>
       <c r="R213" s="11"/>
@@ -13730,7 +13722,7 @@
       <c r="T213" s="11"/>
       <c r="U213" s="11"/>
       <c r="V213" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W213" s="11"/>
       <c r="X213" s="11"/>
@@ -13740,28 +13732,28 @@
     </row>
     <row r="214" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C214" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E214" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D214" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E214" s="11" t="s">
+      <c r="F214" t="s">
+        <v>659</v>
+      </c>
+      <c r="G214" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H214" s="21" t="s">
         <v>578</v>
-      </c>
-      <c r="F214" t="s">
-        <v>660</v>
-      </c>
-      <c r="G214" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H214" s="21" t="s">
-        <v>579</v>
       </c>
       <c r="I214" s="24" t="s">
         <v>48</v>
@@ -13780,7 +13772,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q214" s="11"/>
       <c r="R214" s="11"/>
@@ -13788,7 +13780,7 @@
       <c r="T214" s="11"/>
       <c r="U214" s="11"/>
       <c r="V214" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="215" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -15944,10 +15936,10 @@
         <v>343</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>345</v>
@@ -15968,16 +15960,16 @@
         <v>350</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>248</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="O1" s="1"/>
     </row>
@@ -15989,7 +15981,7 @@
         <v>9000</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D2" s="23">
         <f>2248</f>
@@ -16008,7 +16000,7 @@
         <v>10000</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J2" s="7">
         <v>10000</v>
@@ -16035,7 +16027,7 @@
         <v>14000</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D3" s="23">
         <f>4588</f>
@@ -16066,7 +16058,7 @@
         <v>12977</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="N3" s="18">
         <v>0</v>
@@ -16081,11 +16073,11 @@
         <v>12000</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D4" s="23"/>
       <c r="I4" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="J4">
         <v>12000</v>
@@ -16108,7 +16100,7 @@
         <v>15000</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J5">
         <v>15000</v>
@@ -16124,7 +16116,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B6" s="9">
         <v>4000</v>
@@ -16142,7 +16134,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B7" s="9">
         <v>6000</v>
@@ -16150,15 +16142,15 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="K7" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B8" s="9">
         <v>6000</v>
@@ -16174,7 +16166,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B9" s="9">
         <v>8500</v>
@@ -16241,16 +16233,16 @@
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -16268,16 +16260,16 @@
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -16298,13 +16290,13 @@
         <v>110</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -16325,13 +16317,13 @@
         <v>256</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>672</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -16349,16 +16341,16 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -16376,16 +16368,16 @@
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -16406,13 +16398,13 @@
         <v>18</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -16433,13 +16425,13 @@
         <v>243</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -16457,16 +16449,16 @@
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -16487,13 +16479,13 @@
         <v>311</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -16514,13 +16506,13 @@
         <v>117</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -16541,13 +16533,13 @@
         <v>271</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -16565,16 +16557,16 @@
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>676</v>
+        <v>23</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -16592,16 +16584,16 @@
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="11" t="s">
-        <v>183</v>
+        <v>460</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>371</v>
+        <v>705</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -16619,16 +16611,16 @@
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -16646,16 +16638,16 @@
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>360</v>
+        <v>706</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -16673,16 +16665,16 @@
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>360</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -16703,13 +16695,13 @@
         <v>114</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -16727,16 +16719,16 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -16754,16 +16746,16 @@
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -16784,13 +16776,13 @@
         <v>196</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -16808,16 +16800,16 @@
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -16838,13 +16830,13 @@
         <v>215</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -16865,13 +16857,13 @@
         <v>219</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -16889,16 +16881,16 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -16916,16 +16908,16 @@
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -16943,16 +16935,16 @@
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -16970,16 +16962,16 @@
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -16997,16 +16989,16 @@
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>692</v>
+        <v>191</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -17024,16 +17016,16 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -17051,16 +17043,16 @@
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -17078,16 +17070,16 @@
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="11" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -17105,16 +17097,16 @@
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>608</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -17135,13 +17127,13 @@
         <v>142</v>
       </c>
       <c r="B35" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>610</v>
-      </c>
       <c r="D35" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
@@ -17162,13 +17154,13 @@
         <v>302</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>612</v>
-      </c>
       <c r="D36" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -17186,16 +17178,16 @@
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
@@ -17213,16 +17205,16 @@
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
@@ -17240,16 +17232,16 @@
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
@@ -17270,13 +17262,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>360</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -17297,13 +17289,13 @@
         <v>202</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
@@ -17321,16 +17313,16 @@
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -17351,13 +17343,13 @@
         <v>45</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -17375,16 +17367,16 @@
     </row>
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="11" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -17405,13 +17397,13 @@
         <v>40</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -17429,16 +17421,16 @@
     </row>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B46" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>620</v>
-      </c>
       <c r="D46" s="7" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -17455,6 +17447,15 @@
       <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -33637,6 +33638,7 @@
       <c r="Q998" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q46" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33653,68 +33655,68 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="C1" s="26" t="s">
         <v>430</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="28" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
@@ -33761,58 +33763,58 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" t="s">
         <v>380</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>381</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>382</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>383</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>384</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>385</v>
-      </c>
-      <c r="G2" t="s">
-        <v>386</v>
       </c>
       <c r="H2" t="s">
         <v>342</v>
       </c>
       <c r="I2" t="s">
+        <v>386</v>
+      </c>
+      <c r="J2" t="s">
         <v>387</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>388</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>389</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>390</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>391</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>392</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>393</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>394</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>395</v>
-      </c>
-      <c r="R2" t="s">
-        <v>396</v>
       </c>
       <c r="S2" t="s">
         <v>344</v>
@@ -33829,7 +33831,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -33838,22 +33840,22 @@
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H3" t="s">
         <v>351</v>
       </c>
       <c r="I3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J3">
         <v>1500</v>
@@ -33897,7 +33899,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -33906,22 +33908,22 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H4" t="s">
         <v>351</v>
       </c>
       <c r="I4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J4">
         <v>1500</v>
@@ -33965,7 +33967,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -33974,22 +33976,22 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H5" t="s">
         <v>351</v>
       </c>
       <c r="I5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J5">
         <v>1500</v>
@@ -34033,7 +34035,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -34042,22 +34044,22 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H6" t="s">
         <v>351</v>
       </c>
       <c r="I6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J6">
         <v>1500</v>
@@ -34101,7 +34103,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -34110,22 +34112,22 @@
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H7" t="s">
         <v>351</v>
       </c>
       <c r="I7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J7">
         <v>1500</v>
@@ -34169,7 +34171,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -34178,22 +34180,22 @@
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H8" t="s">
         <v>351</v>
       </c>
       <c r="I8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J8">
         <v>1500</v>
@@ -34237,7 +34239,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -34246,22 +34248,22 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H9" t="s">
         <v>351</v>
       </c>
       <c r="I9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J9">
         <v>1500</v>
@@ -34305,7 +34307,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -34314,22 +34316,22 @@
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F10" t="s">
         <v>101</v>
       </c>
       <c r="G10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H10" t="s">
         <v>351</v>
       </c>
       <c r="I10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J10">
         <v>3050</v>
@@ -34386,7 +34388,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
@@ -34495,7 +34497,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B15">
         <v>23.64</v>
@@ -34511,7 +34513,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B17">
         <v>11.82</v>
@@ -34519,7 +34521,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -34535,7 +34537,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -34551,7 +34553,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -34559,7 +34561,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -34567,7 +34569,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -34583,7 +34585,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -34601,7 +34603,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -34619,25 +34621,25 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" t="s">
         <v>410</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>411</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>412</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>413</v>
-      </c>
-      <c r="M1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.15">
@@ -35595,27 +35597,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" t="s">
         <v>415</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>416</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>417</v>
-      </c>
-      <c r="D1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B2">
         <v>9000</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D2">
         <v>78507</v>
@@ -35629,7 +35631,7 @@
         <v>4000</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D3">
         <v>34892</v>
@@ -35643,7 +35645,7 @@
         <v>2000</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D4">
         <v>17446</v>
@@ -35657,7 +35659,7 @@
         <v>10000</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D5">
         <v>87230.000000000015</v>
@@ -35671,7 +35673,7 @@
         <v>10000</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D6">
         <v>87230.000000000015</v>
@@ -35679,13 +35681,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" t="s">
         <v>421</v>
       </c>
-      <c r="B7" t="s">
-        <v>422</v>
-      </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D7">
         <v>555189</v>
@@ -35693,7 +35695,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D8">
         <v>602345.79999999993</v>
@@ -35701,7 +35703,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D9">
         <v>1462839.8</v>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E599377-048B-3A45-82DC-F93C40FFF636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37CBD06-CCE8-A442-9AB1-FAC375B70B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="СПРАВОЧНИК -1" sheetId="1" r:id="rId1"/>
@@ -2637,7 +2637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA568"/>
@@ -2715,7 +2715,7 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
         <v>15</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>15</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>15</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>15</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:25" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>15</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>15</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
         <v>100</v>
       </c>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P19" s="11"/>
     </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
         <v>100</v>
       </c>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
         <v>100</v>
       </c>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="P21" s="11"/>
     </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>100</v>
       </c>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="P22" s="11"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
         <v>100</v>
       </c>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="P23" s="11"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
         <v>15</v>
       </c>
@@ -3737,7 +3737,7 @@
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
     </row>
-    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
         <v>15</v>
       </c>
@@ -3786,7 +3786,7 @@
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
     </row>
-    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
         <v>15</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="S26" s="11"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
         <v>15</v>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="S27" s="11"/>
       <c r="T27" s="11"/>
     </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>15</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
         <v>15</v>
       </c>
@@ -3982,7 +3982,7 @@
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
     </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>15</v>
       </c>
@@ -4031,7 +4031,7 @@
       <c r="S30" s="11"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>15</v>
       </c>
@@ -4080,7 +4080,7 @@
       <c r="S31" s="11"/>
       <c r="T31" s="11"/>
     </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>15</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="S32" s="11"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>15</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="S33" s="11"/>
       <c r="T33" s="11"/>
     </row>
-    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="S34" s="11"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>15</v>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="S35" s="11"/>
       <c r="T35" s="11"/>
     </row>
-    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>100</v>
       </c>
@@ -4325,7 +4325,7 @@
       <c r="S36" s="11"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>100</v>
       </c>
@@ -4423,7 +4423,7 @@
       <c r="S38" s="11"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
         <v>100</v>
       </c>
@@ -4472,7 +4472,7 @@
       <c r="S39" s="11"/>
       <c r="T39" s="11"/>
     </row>
-    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
         <v>100</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="S40" s="11"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7" t="s">
         <v>100</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
     </row>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7" t="s">
         <v>100</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="S42" s="11"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
         <v>100</v>
       </c>
@@ -4668,7 +4668,7 @@
       <c r="S43" s="11"/>
       <c r="T43" s="11"/>
     </row>
-    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
         <v>100</v>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="S44" s="11"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7" t="s">
         <v>100</v>
       </c>
@@ -4766,7 +4766,7 @@
       <c r="S45" s="11"/>
       <c r="T45" s="11"/>
     </row>
-    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7" t="s">
         <v>100</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="S46" s="11"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7" t="s">
         <v>100</v>
       </c>
@@ -4864,7 +4864,7 @@
       <c r="S47" s="11"/>
       <c r="T47" s="11"/>
     </row>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7" t="s">
         <v>100</v>
       </c>
@@ -4913,7 +4913,7 @@
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
     </row>
-    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7" t="s">
         <v>100</v>
       </c>
@@ -4962,7 +4962,7 @@
       <c r="S49" s="11"/>
       <c r="T49" s="11"/>
     </row>
-    <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7" t="s">
         <v>100</v>
       </c>
@@ -5011,7 +5011,7 @@
       <c r="S50" s="11"/>
       <c r="T50" s="11"/>
     </row>
-    <row r="51" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="7" t="s">
         <v>100</v>
       </c>
@@ -5060,7 +5060,7 @@
       <c r="S51" s="11"/>
       <c r="T51" s="11"/>
     </row>
-    <row r="52" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="7" t="s">
         <v>100</v>
       </c>
@@ -5109,7 +5109,7 @@
       <c r="S52" s="11"/>
       <c r="T52" s="11"/>
     </row>
-    <row r="53" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="7" t="s">
         <v>100</v>
       </c>
@@ -5158,7 +5158,7 @@
       <c r="S53" s="11"/>
       <c r="T53" s="11"/>
     </row>
-    <row r="54" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="7" t="s">
         <v>100</v>
       </c>
@@ -5207,7 +5207,7 @@
       <c r="S54" s="11"/>
       <c r="T54" s="11"/>
     </row>
-    <row r="55" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="7" t="s">
         <v>100</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="S55" s="11"/>
       <c r="T55" s="11"/>
     </row>
-    <row r="56" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="7" t="s">
         <v>100</v>
       </c>
@@ -5305,7 +5305,7 @@
       <c r="S56" s="11"/>
       <c r="T56" s="11"/>
     </row>
-    <row r="57" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="7" t="s">
         <v>100</v>
       </c>
@@ -5354,7 +5354,7 @@
       <c r="S57" s="11"/>
       <c r="T57" s="11"/>
     </row>
-    <row r="58" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="7" t="s">
         <v>100</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="S58" s="11"/>
       <c r="T58" s="11"/>
     </row>
-    <row r="59" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="7" t="s">
         <v>100</v>
       </c>
@@ -5452,7 +5452,7 @@
       <c r="S59" s="11"/>
       <c r="T59" s="11"/>
     </row>
-    <row r="60" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7" t="s">
         <v>100</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="S60" s="11"/>
       <c r="T60" s="11"/>
     </row>
-    <row r="61" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="7" t="s">
         <v>100</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="S61" s="11"/>
       <c r="T61" s="11"/>
     </row>
-    <row r="62" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="7" t="s">
         <v>100</v>
       </c>
@@ -5599,7 +5599,7 @@
       <c r="S62" s="11"/>
       <c r="T62" s="11"/>
     </row>
-    <row r="63" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="7" t="s">
         <v>100</v>
       </c>
@@ -5648,7 +5648,7 @@
       <c r="S63" s="11"/>
       <c r="T63" s="11"/>
     </row>
-    <row r="64" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="7" t="s">
         <v>100</v>
       </c>
@@ -5697,7 +5697,7 @@
       <c r="S64" s="11"/>
       <c r="T64" s="11"/>
     </row>
-    <row r="65" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="7" t="s">
         <v>100</v>
       </c>
@@ -5746,7 +5746,7 @@
       <c r="S65" s="11"/>
       <c r="T65" s="11"/>
     </row>
-    <row r="66" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="7" t="s">
         <v>100</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="S66" s="11"/>
       <c r="T66" s="11"/>
     </row>
-    <row r="67" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="7" t="s">
         <v>100</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
     </row>
-    <row r="68" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="7" t="s">
         <v>100</v>
       </c>
@@ -5893,7 +5893,7 @@
       <c r="S68" s="11"/>
       <c r="T68" s="11"/>
     </row>
-    <row r="69" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="7" t="s">
         <v>100</v>
       </c>
@@ -5942,7 +5942,7 @@
       <c r="S69" s="11"/>
       <c r="T69" s="11"/>
     </row>
-    <row r="70" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="7" t="s">
         <v>100</v>
       </c>
@@ -5991,7 +5991,7 @@
       <c r="S70" s="6"/>
       <c r="T70" s="6"/>
     </row>
-    <row r="71" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="7" t="s">
         <v>100</v>
       </c>
@@ -6040,7 +6040,7 @@
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
     </row>
-    <row r="72" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="7" t="s">
         <v>100</v>
       </c>
@@ -6089,7 +6089,7 @@
       <c r="S72" s="11"/>
       <c r="T72" s="11"/>
     </row>
-    <row r="73" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="7" t="s">
         <v>100</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="S73" s="11"/>
       <c r="T73" s="11"/>
     </row>
-    <row r="74" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7" t="s">
         <v>100</v>
       </c>
@@ -6187,7 +6187,7 @@
       <c r="S74" s="11"/>
       <c r="T74" s="11"/>
     </row>
-    <row r="75" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="7" t="s">
         <v>100</v>
       </c>
@@ -6236,7 +6236,7 @@
       <c r="S75" s="11"/>
       <c r="T75" s="11"/>
     </row>
-    <row r="76" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="7" t="s">
         <v>100</v>
       </c>
@@ -6285,7 +6285,7 @@
       <c r="S76" s="11"/>
       <c r="T76" s="11"/>
     </row>
-    <row r="77" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="7" t="s">
         <v>100</v>
       </c>
@@ -6334,7 +6334,7 @@
       <c r="S77" s="11"/>
       <c r="T77" s="11"/>
     </row>
-    <row r="78" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="7" t="s">
         <v>100</v>
       </c>
@@ -6383,7 +6383,7 @@
       <c r="S78" s="11"/>
       <c r="T78" s="11"/>
     </row>
-    <row r="79" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="7" t="s">
         <v>100</v>
       </c>
@@ -6432,7 +6432,7 @@
       <c r="S79" s="11"/>
       <c r="T79" s="11"/>
     </row>
-    <row r="80" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="7" t="s">
         <v>100</v>
       </c>
@@ -6481,7 +6481,7 @@
       <c r="S80" s="11"/>
       <c r="T80" s="11"/>
     </row>
-    <row r="81" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="7" t="s">
         <v>100</v>
       </c>
@@ -6530,7 +6530,7 @@
       <c r="S81" s="11"/>
       <c r="T81" s="11"/>
     </row>
-    <row r="82" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="7" t="s">
         <v>100</v>
       </c>
@@ -6579,7 +6579,7 @@
       <c r="S82" s="11"/>
       <c r="T82" s="11"/>
     </row>
-    <row r="83" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="7" t="s">
         <v>100</v>
       </c>
@@ -6628,7 +6628,7 @@
       <c r="S83" s="11"/>
       <c r="T83" s="11"/>
     </row>
-    <row r="84" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="7" t="s">
         <v>100</v>
       </c>
@@ -6677,7 +6677,7 @@
       <c r="S84" s="11"/>
       <c r="T84" s="11"/>
     </row>
-    <row r="85" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="7" t="s">
         <v>100</v>
       </c>
@@ -6726,7 +6726,7 @@
       <c r="S85" s="11"/>
       <c r="T85" s="11"/>
     </row>
-    <row r="86" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="7" t="s">
         <v>100</v>
       </c>
@@ -6775,7 +6775,7 @@
       <c r="S86" s="11"/>
       <c r="T86" s="11"/>
     </row>
-    <row r="87" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="7" t="s">
         <v>100</v>
       </c>
@@ -6824,7 +6824,7 @@
       <c r="S87" s="11"/>
       <c r="T87" s="11"/>
     </row>
-    <row r="88" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="7" t="s">
         <v>100</v>
       </c>
@@ -6873,7 +6873,7 @@
       <c r="S88" s="11"/>
       <c r="T88" s="11"/>
     </row>
-    <row r="89" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="7" t="s">
         <v>100</v>
       </c>
@@ -6922,7 +6922,7 @@
       <c r="S89" s="11"/>
       <c r="T89" s="11"/>
     </row>
-    <row r="90" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="7" t="s">
         <v>100</v>
       </c>
@@ -6971,7 +6971,7 @@
       <c r="S90" s="11"/>
       <c r="T90" s="11"/>
     </row>
-    <row r="91" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="7" t="s">
         <v>100</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="S91" s="11"/>
       <c r="T91" s="11"/>
     </row>
-    <row r="92" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="7" t="s">
         <v>100</v>
       </c>
@@ -7070,7 +7070,7 @@
       <c r="T92" s="6"/>
       <c r="U92" s="6"/>
     </row>
-    <row r="93" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="7" t="s">
         <v>100</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="T93" s="11"/>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="7" t="s">
         <v>100</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="T94" s="11"/>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="7" t="s">
         <v>100</v>
       </c>
@@ -7217,7 +7217,7 @@
       <c r="T95" s="11"/>
       <c r="U95" s="11"/>
     </row>
-    <row r="96" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:21" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="7" t="s">
         <v>100</v>
       </c>
@@ -7267,7 +7267,7 @@
       <c r="T96" s="11"/>
       <c r="U96" s="11"/>
     </row>
-    <row r="97" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="7" t="s">
         <v>100</v>
       </c>
@@ -7316,7 +7316,7 @@
       <c r="T97" s="11"/>
       <c r="U97" s="11"/>
     </row>
-    <row r="98" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="7" t="s">
         <v>100</v>
       </c>
@@ -7365,7 +7365,7 @@
       <c r="T98" s="11"/>
       <c r="U98" s="11"/>
     </row>
-    <row r="99" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="7" t="s">
         <v>100</v>
       </c>
@@ -7414,7 +7414,7 @@
       <c r="T99" s="11"/>
       <c r="U99" s="11"/>
     </row>
-    <row r="100" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="7" t="s">
         <v>100</v>
       </c>
@@ -7464,7 +7464,7 @@
       <c r="T100" s="11"/>
       <c r="U100" s="11"/>
     </row>
-    <row r="101" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="7" t="s">
         <v>100</v>
       </c>
@@ -7514,7 +7514,7 @@
       <c r="T101" s="11"/>
       <c r="U101" s="11"/>
     </row>
-    <row r="102" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="7" t="s">
         <v>100</v>
       </c>
@@ -7564,7 +7564,7 @@
       <c r="T102" s="11"/>
       <c r="U102" s="11"/>
     </row>
-    <row r="103" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="7" t="s">
         <v>100</v>
       </c>
@@ -7614,7 +7614,7 @@
       <c r="T103" s="11"/>
       <c r="U103" s="11"/>
     </row>
-    <row r="104" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="7" t="s">
         <v>100</v>
       </c>
@@ -7664,7 +7664,7 @@
       <c r="T104" s="11"/>
       <c r="U104" s="11"/>
     </row>
-    <row r="105" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="7" t="s">
         <v>100</v>
       </c>
@@ -7714,7 +7714,7 @@
       <c r="T105" s="11"/>
       <c r="U105" s="11"/>
     </row>
-    <row r="106" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="7" t="s">
         <v>100</v>
       </c>
@@ -7764,7 +7764,7 @@
       <c r="T106" s="11"/>
       <c r="U106" s="11"/>
     </row>
-    <row r="107" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="7" t="s">
         <v>100</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="T107" s="11"/>
       <c r="U107" s="11"/>
     </row>
-    <row r="108" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="7" t="s">
         <v>100</v>
       </c>
@@ -7864,7 +7864,7 @@
       <c r="T108" s="11"/>
       <c r="U108" s="11"/>
     </row>
-    <row r="109" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="7" t="s">
         <v>100</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="7" t="s">
         <v>100</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="7" t="s">
         <v>100</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="112" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="11" t="s">
         <v>100</v>
       </c>
@@ -8052,7 +8052,7 @@
       <c r="Y112" s="11"/>
       <c r="Z112" s="11"/>
     </row>
-    <row r="113" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="11" t="s">
         <v>100</v>
       </c>
@@ -8108,7 +8108,7 @@
       <c r="Y113" s="11"/>
       <c r="Z113" s="11"/>
     </row>
-    <row r="114" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="11" t="s">
         <v>100</v>
       </c>
@@ -8164,7 +8164,7 @@
       <c r="Y114" s="11"/>
       <c r="Z114" s="11"/>
     </row>
-    <row r="115" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="11" t="s">
         <v>100</v>
       </c>
@@ -8220,7 +8220,7 @@
       <c r="Y115" s="11"/>
       <c r="Z115" s="11"/>
     </row>
-    <row r="116" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="11" t="s">
         <v>100</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="Y116" s="11"/>
       <c r="Z116" s="11"/>
     </row>
-    <row r="117" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="11" t="s">
         <v>100</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="Y117" s="11"/>
       <c r="Z117" s="11"/>
     </row>
-    <row r="118" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="11" t="s">
         <v>100</v>
       </c>
@@ -8388,7 +8388,7 @@
       <c r="Y118" s="11"/>
       <c r="Z118" s="11"/>
     </row>
-    <row r="119" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="11" t="s">
         <v>100</v>
       </c>
@@ -8444,7 +8444,7 @@
       <c r="Y119" s="11"/>
       <c r="Z119" s="11"/>
     </row>
-    <row r="120" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="11" t="s">
         <v>100</v>
       </c>
@@ -8500,7 +8500,7 @@
       <c r="Y120" s="11"/>
       <c r="Z120" s="11"/>
     </row>
-    <row r="121" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="11" t="s">
         <v>100</v>
       </c>
@@ -8556,7 +8556,7 @@
       <c r="Y121" s="11"/>
       <c r="Z121" s="11"/>
     </row>
-    <row r="122" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="11" t="s">
         <v>100</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="Y122" s="11"/>
       <c r="Z122" s="11"/>
     </row>
-    <row r="123" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="11" t="s">
         <v>100</v>
       </c>
@@ -8668,7 +8668,7 @@
       <c r="Y123" s="11"/>
       <c r="Z123" s="11"/>
     </row>
-    <row r="124" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="11" t="s">
         <v>100</v>
       </c>
@@ -8724,7 +8724,7 @@
       <c r="Y124" s="11"/>
       <c r="Z124" s="11"/>
     </row>
-    <row r="125" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="11" t="s">
         <v>100</v>
       </c>
@@ -8780,7 +8780,7 @@
       <c r="Y125" s="11"/>
       <c r="Z125" s="11"/>
     </row>
-    <row r="126" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="11" t="s">
         <v>100</v>
       </c>
@@ -8836,7 +8836,7 @@
       <c r="Y126" s="11"/>
       <c r="Z126" s="11"/>
     </row>
-    <row r="127" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="11" t="s">
         <v>100</v>
       </c>
@@ -8892,7 +8892,7 @@
       <c r="Y127" s="11"/>
       <c r="Z127" s="11"/>
     </row>
-    <row r="128" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="11" t="s">
         <v>100</v>
       </c>
@@ -8948,7 +8948,7 @@
       <c r="Y128" s="11"/>
       <c r="Z128" s="11"/>
     </row>
-    <row r="129" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="11" t="s">
         <v>100</v>
       </c>
@@ -9004,7 +9004,7 @@
       <c r="Y129" s="11"/>
       <c r="Z129" s="11"/>
     </row>
-    <row r="130" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="11" t="s">
         <v>100</v>
       </c>
@@ -9060,7 +9060,7 @@
       <c r="Y130" s="11"/>
       <c r="Z130" s="11"/>
     </row>
-    <row r="131" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="11" t="s">
         <v>100</v>
       </c>
@@ -9116,7 +9116,7 @@
       <c r="Y131" s="11"/>
       <c r="Z131" s="11"/>
     </row>
-    <row r="132" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="11" t="s">
         <v>100</v>
       </c>
@@ -9172,7 +9172,7 @@
       <c r="Y132" s="11"/>
       <c r="Z132" s="11"/>
     </row>
-    <row r="133" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="11" t="s">
         <v>100</v>
       </c>
@@ -9228,7 +9228,7 @@
       <c r="Y133" s="11"/>
       <c r="Z133" s="11"/>
     </row>
-    <row r="134" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="11" t="s">
         <v>100</v>
       </c>
@@ -9284,7 +9284,7 @@
       <c r="Y134" s="11"/>
       <c r="Z134" s="11"/>
     </row>
-    <row r="135" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="11" t="s">
         <v>100</v>
       </c>
@@ -9340,7 +9340,7 @@
       <c r="Y135" s="11"/>
       <c r="Z135" s="11"/>
     </row>
-    <row r="136" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="11" t="s">
         <v>100</v>
       </c>
@@ -9396,7 +9396,7 @@
       <c r="Y136" s="11"/>
       <c r="Z136" s="11"/>
     </row>
-    <row r="137" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="11" t="s">
         <v>100</v>
       </c>
@@ -9452,7 +9452,7 @@
       <c r="Y137" s="11"/>
       <c r="Z137" s="11"/>
     </row>
-    <row r="138" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="11" t="s">
         <v>100</v>
       </c>
@@ -9508,7 +9508,7 @@
       <c r="Y138" s="11"/>
       <c r="Z138" s="11"/>
     </row>
-    <row r="139" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="11" t="s">
         <v>100</v>
       </c>
@@ -9564,7 +9564,7 @@
       <c r="Y139" s="11"/>
       <c r="Z139" s="11"/>
     </row>
-    <row r="140" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="11" t="s">
         <v>100</v>
       </c>
@@ -9620,7 +9620,7 @@
       <c r="Y140" s="11"/>
       <c r="Z140" s="11"/>
     </row>
-    <row r="141" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="11" t="s">
         <v>100</v>
       </c>
@@ -9676,7 +9676,7 @@
       <c r="Y141" s="11"/>
       <c r="Z141" s="11"/>
     </row>
-    <row r="142" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="11" t="s">
         <v>100</v>
       </c>
@@ -9732,7 +9732,7 @@
       <c r="Y142" s="11"/>
       <c r="Z142" s="11"/>
     </row>
-    <row r="143" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="11" t="s">
         <v>100</v>
       </c>
@@ -9788,7 +9788,7 @@
       <c r="Y143" s="11"/>
       <c r="Z143" s="11"/>
     </row>
-    <row r="144" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="11" t="s">
         <v>15</v>
       </c>
@@ -9844,7 +9844,7 @@
       <c r="Y144" s="11"/>
       <c r="Z144" s="11"/>
     </row>
-    <row r="145" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="11" t="s">
         <v>15</v>
       </c>
@@ -9900,7 +9900,7 @@
       <c r="Y145" s="11"/>
       <c r="Z145" s="11"/>
     </row>
-    <row r="146" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="11" t="s">
         <v>15</v>
       </c>
@@ -9956,7 +9956,7 @@
       <c r="Y146" s="11"/>
       <c r="Z146" s="11"/>
     </row>
-    <row r="147" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="11" t="s">
         <v>15</v>
       </c>
@@ -10013,7 +10013,7 @@
       <c r="Z147" s="1"/>
       <c r="AA147" s="1"/>
     </row>
-    <row r="148" spans="1:27" s="38" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:27" s="38" customFormat="1" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="35" t="s">
         <v>438</v>
       </c>
@@ -10069,7 +10069,7 @@
       <c r="Z148" s="11"/>
       <c r="AA148" s="11"/>
     </row>
-    <row r="149" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="11" t="s">
         <v>438</v>
       </c>
@@ -10125,7 +10125,7 @@
       <c r="Z149" s="11"/>
       <c r="AA149" s="11"/>
     </row>
-    <row r="150" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="11" t="s">
         <v>438</v>
       </c>
@@ -10181,7 +10181,7 @@
       <c r="Z150" s="11"/>
       <c r="AA150" s="11"/>
     </row>
-    <row r="151" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="11" t="s">
         <v>438</v>
       </c>
@@ -10237,7 +10237,7 @@
       <c r="Z151" s="11"/>
       <c r="AA151" s="11"/>
     </row>
-    <row r="152" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="11" t="s">
         <v>438</v>
       </c>
@@ -10293,7 +10293,7 @@
       <c r="Z152" s="11"/>
       <c r="AA152" s="11"/>
     </row>
-    <row r="153" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="11" t="s">
         <v>438</v>
       </c>
@@ -10349,7 +10349,7 @@
       <c r="Z153" s="11"/>
       <c r="AA153" s="11"/>
     </row>
-    <row r="154" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="11" t="s">
         <v>438</v>
       </c>
@@ -10405,7 +10405,7 @@
       <c r="Z154" s="11"/>
       <c r="AA154" s="11"/>
     </row>
-    <row r="155" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="11" t="s">
         <v>438</v>
       </c>
@@ -10461,7 +10461,7 @@
       <c r="Z155" s="11"/>
       <c r="AA155" s="11"/>
     </row>
-    <row r="156" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="11" t="s">
         <v>438</v>
       </c>
@@ -10517,7 +10517,7 @@
       <c r="Z156" s="11"/>
       <c r="AA156" s="11"/>
     </row>
-    <row r="157" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="11" t="s">
         <v>438</v>
       </c>
@@ -10573,7 +10573,7 @@
       <c r="Z157" s="11"/>
       <c r="AA157" s="11"/>
     </row>
-    <row r="158" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="11" t="s">
         <v>438</v>
       </c>
@@ -10629,7 +10629,7 @@
       <c r="Z158" s="11"/>
       <c r="AA158" s="11"/>
     </row>
-    <row r="159" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="11" t="s">
         <v>438</v>
       </c>
@@ -10685,7 +10685,7 @@
       <c r="Z159" s="11"/>
       <c r="AA159" s="11"/>
     </row>
-    <row r="160" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="11" t="s">
         <v>438</v>
       </c>
@@ -10741,7 +10741,7 @@
       <c r="Z160" s="11"/>
       <c r="AA160" s="11"/>
     </row>
-    <row r="161" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="11" t="s">
         <v>438</v>
       </c>
@@ -10797,7 +10797,7 @@
       <c r="Z161" s="11"/>
       <c r="AA161" s="11"/>
     </row>
-    <row r="162" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="11" t="s">
         <v>438</v>
       </c>
@@ -10853,7 +10853,7 @@
       <c r="Z162" s="11"/>
       <c r="AA162" s="11"/>
     </row>
-    <row r="163" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="11" t="s">
         <v>438</v>
       </c>
@@ -10909,7 +10909,7 @@
       <c r="Z163" s="11"/>
       <c r="AA163" s="11"/>
     </row>
-    <row r="164" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="11" t="s">
         <v>438</v>
       </c>
@@ -10965,7 +10965,7 @@
       <c r="Z164" s="11"/>
       <c r="AA164" s="11"/>
     </row>
-    <row r="165" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="11" t="s">
         <v>438</v>
       </c>
@@ -11021,7 +11021,7 @@
       <c r="Z165" s="11"/>
       <c r="AA165" s="11"/>
     </row>
-    <row r="166" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="11" t="s">
         <v>438</v>
       </c>
@@ -11077,7 +11077,7 @@
       <c r="Z166" s="11"/>
       <c r="AA166" s="11"/>
     </row>
-    <row r="167" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="11" t="s">
         <v>438</v>
       </c>
@@ -11133,7 +11133,7 @@
       <c r="Z167" s="11"/>
       <c r="AA167" s="11"/>
     </row>
-    <row r="168" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="11" t="s">
         <v>438</v>
       </c>
@@ -11189,7 +11189,7 @@
       <c r="Z168" s="11"/>
       <c r="AA168" s="11"/>
     </row>
-    <row r="169" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="11" t="s">
         <v>438</v>
       </c>
@@ -11245,7 +11245,7 @@
       <c r="Z169" s="11"/>
       <c r="AA169" s="11"/>
     </row>
-    <row r="170" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="11" t="s">
         <v>438</v>
       </c>
@@ -11301,7 +11301,7 @@
       <c r="Z170" s="11"/>
       <c r="AA170" s="11"/>
     </row>
-    <row r="171" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="11" t="s">
         <v>438</v>
       </c>
@@ -11357,7 +11357,7 @@
       <c r="Z171" s="11"/>
       <c r="AA171" s="11"/>
     </row>
-    <row r="172" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="11" t="s">
         <v>438</v>
       </c>
@@ -11413,7 +11413,7 @@
       <c r="Z172" s="11"/>
       <c r="AA172" s="11"/>
     </row>
-    <row r="173" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="11" t="s">
         <v>438</v>
       </c>
@@ -11469,7 +11469,7 @@
       <c r="Z173" s="11"/>
       <c r="AA173" s="11"/>
     </row>
-    <row r="174" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="11" t="s">
         <v>438</v>
       </c>
@@ -11525,7 +11525,7 @@
       <c r="Z174" s="11"/>
       <c r="AA174" s="11"/>
     </row>
-    <row r="175" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="11" t="s">
         <v>438</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="Z175" s="11"/>
       <c r="AA175" s="11"/>
     </row>
-    <row r="176" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="11" t="s">
         <v>438</v>
       </c>
@@ -11637,7 +11637,7 @@
       <c r="Z176" s="11"/>
       <c r="AA176" s="11"/>
     </row>
-    <row r="177" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="11" t="s">
         <v>438</v>
       </c>
@@ -11693,7 +11693,7 @@
       <c r="Z177" s="11"/>
       <c r="AA177" s="11"/>
     </row>
-    <row r="178" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="11" t="s">
         <v>438</v>
       </c>
@@ -11749,7 +11749,7 @@
       <c r="Z178" s="11"/>
       <c r="AA178" s="11"/>
     </row>
-    <row r="179" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="11" t="s">
         <v>438</v>
       </c>
@@ -11805,7 +11805,7 @@
       <c r="Z179" s="11"/>
       <c r="AA179" s="11"/>
     </row>
-    <row r="180" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
         <v>438</v>
       </c>
@@ -11917,7 +11917,7 @@
       <c r="Z181" s="11"/>
       <c r="AA181" s="11"/>
     </row>
-    <row r="182" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="11" t="s">
         <v>438</v>
       </c>
@@ -11973,7 +11973,7 @@
       <c r="Z182" s="11"/>
       <c r="AA182" s="11"/>
     </row>
-    <row r="183" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
         <v>438</v>
       </c>
@@ -12029,7 +12029,7 @@
       <c r="Z183" s="11"/>
       <c r="AA183" s="11"/>
     </row>
-    <row r="184" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="11" t="s">
         <v>438</v>
       </c>
@@ -12085,7 +12085,7 @@
       <c r="Z184" s="11"/>
       <c r="AA184" s="11"/>
     </row>
-    <row r="185" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
         <v>438</v>
       </c>
@@ -12141,7 +12141,7 @@
       <c r="Z185" s="11"/>
       <c r="AA185" s="11"/>
     </row>
-    <row r="186" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="11" t="s">
         <v>438</v>
       </c>
@@ -12197,7 +12197,7 @@
       <c r="Z186" s="11"/>
       <c r="AA186" s="11"/>
     </row>
-    <row r="187" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="11" t="s">
         <v>438</v>
       </c>
@@ -12248,7 +12248,7 @@
       <c r="U187" s="11"/>
       <c r="V187" s="11"/>
     </row>
-    <row r="188" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="11" t="s">
         <v>438</v>
       </c>
@@ -12304,7 +12304,7 @@
       <c r="Z188" s="11"/>
       <c r="AA188" s="11"/>
     </row>
-    <row r="189" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="11" t="s">
         <v>438</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="Z189" s="11"/>
       <c r="AA189" s="11"/>
     </row>
-    <row r="190" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
         <v>438</v>
       </c>
@@ -12416,7 +12416,7 @@
       <c r="Z190" s="11"/>
       <c r="AA190" s="11"/>
     </row>
-    <row r="191" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="11" t="s">
         <v>438</v>
       </c>
@@ -12472,7 +12472,7 @@
       <c r="Z191" s="11"/>
       <c r="AA191" s="11"/>
     </row>
-    <row r="192" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
         <v>438</v>
       </c>
@@ -12528,7 +12528,7 @@
       <c r="Z192" s="11"/>
       <c r="AA192" s="11"/>
     </row>
-    <row r="193" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="11" t="s">
         <v>438</v>
       </c>
@@ -12584,7 +12584,7 @@
       <c r="Z193" s="11"/>
       <c r="AA193" s="11"/>
     </row>
-    <row r="194" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="11" t="s">
         <v>438</v>
       </c>
@@ -12640,7 +12640,7 @@
       <c r="Z194" s="11"/>
       <c r="AA194" s="11"/>
     </row>
-    <row r="195" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="11" t="s">
         <v>438</v>
       </c>
@@ -12696,7 +12696,7 @@
       <c r="Z195" s="11"/>
       <c r="AA195" s="11"/>
     </row>
-    <row r="196" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="11" t="s">
         <v>438</v>
       </c>
@@ -12752,7 +12752,7 @@
       <c r="Z196" s="11"/>
       <c r="AA196" s="11"/>
     </row>
-    <row r="197" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="11" t="s">
         <v>438</v>
       </c>
@@ -12808,7 +12808,7 @@
       <c r="Z197" s="11"/>
       <c r="AA197" s="11"/>
     </row>
-    <row r="198" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="11" t="s">
         <v>438</v>
       </c>
@@ -12864,7 +12864,7 @@
       <c r="Z198" s="11"/>
       <c r="AA198" s="11"/>
     </row>
-    <row r="199" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="11" t="s">
         <v>438</v>
       </c>
@@ -12920,7 +12920,7 @@
       <c r="Z199" s="11"/>
       <c r="AA199" s="11"/>
     </row>
-    <row r="200" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="11" t="s">
         <v>438</v>
       </c>
@@ -12976,7 +12976,7 @@
       <c r="Z200" s="15"/>
       <c r="AA200" s="11"/>
     </row>
-    <row r="201" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="11" t="s">
         <v>438</v>
       </c>
@@ -13034,7 +13034,7 @@
       <c r="Z201" s="11"/>
       <c r="AA201" s="11"/>
     </row>
-    <row r="202" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
         <v>438</v>
       </c>
@@ -13092,7 +13092,7 @@
       <c r="Z202" s="11"/>
       <c r="AA202" s="11"/>
     </row>
-    <row r="203" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="11" t="s">
         <v>438</v>
       </c>
@@ -13150,7 +13150,7 @@
       <c r="Z203" s="11"/>
       <c r="AA203" s="11"/>
     </row>
-    <row r="204" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="11" t="s">
         <v>438</v>
       </c>
@@ -13208,7 +13208,7 @@
       <c r="Z204" s="11"/>
       <c r="AA204" s="11"/>
     </row>
-    <row r="205" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="11" t="s">
         <v>438</v>
       </c>
@@ -13266,7 +13266,7 @@
       <c r="Z205" s="11"/>
       <c r="AA205" s="11"/>
     </row>
-    <row r="206" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="11" t="s">
         <v>438</v>
       </c>
@@ -13324,7 +13324,7 @@
       <c r="Z206" s="11"/>
       <c r="AA206" s="11"/>
     </row>
-    <row r="207" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="11" t="s">
         <v>438</v>
       </c>
@@ -13382,7 +13382,7 @@
       <c r="Z207" s="11"/>
       <c r="AA207" s="11"/>
     </row>
-    <row r="208" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="11" t="s">
         <v>438</v>
       </c>
@@ -13440,7 +13440,7 @@
       <c r="Z208" s="11"/>
       <c r="AA208" s="11"/>
     </row>
-    <row r="209" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="11" t="s">
         <v>438</v>
       </c>
@@ -13498,7 +13498,7 @@
       <c r="Z209" s="11"/>
       <c r="AA209" s="11"/>
     </row>
-    <row r="210" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="11" t="s">
         <v>438</v>
       </c>
@@ -13556,7 +13556,7 @@
       <c r="Z210" s="11"/>
       <c r="AA210" s="11"/>
     </row>
-    <row r="211" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="11" t="s">
         <v>438</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="Z211" s="11"/>
       <c r="AA211" s="11"/>
     </row>
-    <row r="212" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="11" t="s">
         <v>438</v>
       </c>
@@ -13672,7 +13672,7 @@
       <c r="Z212" s="11"/>
       <c r="AA212" s="11"/>
     </row>
-    <row r="213" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="11" t="s">
         <v>438</v>
       </c>
@@ -13730,7 +13730,7 @@
       <c r="Z213" s="11"/>
       <c r="AA213" s="11"/>
     </row>
-    <row r="214" spans="1:27" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:27" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="11" t="s">
         <v>438</v>
       </c>
@@ -15910,6 +15910,13 @@
       <c r="N568" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA214" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="2-00-2116-60-9016"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26847E5-B4D2-2847-9028-E9364F2F3490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A5809D1-7C6A-5740-822E-8049BC0B6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="835">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -2446,6 +2446,129 @@
   </si>
   <si>
     <t>Сухарь на створку</t>
+  </si>
+  <si>
+    <t>45 Рама компланарной двери RAL 7024 мат</t>
+  </si>
+  <si>
+    <t>45 Створка компланарной двери Н/О RAL 7024 мат</t>
+  </si>
+  <si>
+    <t>2*(sash_width + sash_height)/1000 * (n_sash_active if 'n_sash_active' in globals() else (n_sash if 'n_sash' in globals() else 1)) * qty</t>
+  </si>
+  <si>
+    <t>45 Штульп компланарной двери RAL 9016</t>
+  </si>
+  <si>
+    <t>2 186</t>
+  </si>
+  <si>
+    <t>45 Рама RAL 7024 мат</t>
+  </si>
+  <si>
+    <t>2-00-2160-60-7024-</t>
+  </si>
+  <si>
+    <t>45 Импост RAL 7024 мат</t>
+  </si>
+  <si>
+    <t>2-00-2163-60-7024-</t>
+  </si>
+  <si>
+    <t>(((center if 'center' in globals() else 0) + (top if 'top' in globals() else 0))/1000) * qty</t>
+  </si>
+  <si>
+    <t>Руит Штапик 10,7 мм RAL 7024 мат</t>
+  </si>
+  <si>
+    <t>(((1 if (center if 'center' in globals() else 0) else 0) + (1 if (top if 'top' in globals() else 0) else 0)) * qty)</t>
+  </si>
+  <si>
+    <t>Сухарь (фиксатор)</t>
+  </si>
+  <si>
+    <t>(n_sash if 'n_sash' in globals() and n_sash else 1) * qty</t>
+  </si>
+  <si>
+    <t>math.ceil(((2*(width + height)/1000) * qty) / (pack_size if 'pack_size' in globals() else 250))</t>
+  </si>
+  <si>
+    <t>hinges_per_sash * (n_sash if 'n_sash' in globals() and n_sash else 1) * qty</t>
+  </si>
+  <si>
+    <t>Дверная нажимная ручка (T-MZS70) Ral 9016 (LCNH01)</t>
+  </si>
+  <si>
+    <t>Дверная нажимная ручка</t>
+  </si>
+  <si>
+    <t>2-10-1417-00-9016</t>
+  </si>
+  <si>
+    <t>4 092</t>
+  </si>
+  <si>
+    <t>Замок язычковый 153/30 KALE без барели</t>
+  </si>
+  <si>
+    <t>Замок язычковый</t>
+  </si>
+  <si>
+    <t>2-22-1414-00-5330</t>
+  </si>
+  <si>
+    <t>Ответная планка (С Коробом Под Замок 3096.00) универсальная</t>
+  </si>
+  <si>
+    <t>Ответная планка универсальная</t>
+  </si>
+  <si>
+    <t>Доводчик Elementis 604, с низкотемпературным маслом Черный RAL 9005 мат</t>
+  </si>
+  <si>
+    <t>Доводчик (closer)</t>
+  </si>
+  <si>
+    <t>2-22-2443-00-9005-</t>
+  </si>
+  <si>
+    <t>13 025</t>
+  </si>
+  <si>
+    <t>45 Адаптер порога 45С Компланарная (2102)</t>
+  </si>
+  <si>
+    <t>2-22-0025-00-4500</t>
+  </si>
+  <si>
+    <t>Профиль поворота 90°</t>
+  </si>
+  <si>
+    <t>Петля дверная 3-секц.</t>
+  </si>
+  <si>
+    <t>Ручка дверная офисная АРД-02 1000мм (Ral 9016) (упак.8шт)</t>
+  </si>
+  <si>
+    <t>Ручка дверная офисная (упак.)</t>
+  </si>
+  <si>
+    <t>2-10-1200А-00-9016</t>
+  </si>
+  <si>
+    <t>math.ceil((door_count * qty) / (pack_size if 'pack_size' in globals() else 8))</t>
+  </si>
+  <si>
+    <t>2-22-2443-00-9006</t>
+  </si>
+  <si>
+    <t>Фиксатор пассивной створки накладной 220*2*8 мм ELEMENTIS с ответной планкой RAL 9016</t>
+  </si>
+  <si>
+    <t>45- (2118) Крышка Штульпа Компланарной двери верх/низ 45 (EPDM, 10)</t>
+  </si>
+  <si>
+    <t>Доводчик Elementis 604, с низкотемпературным маслом Серебро RAL9006</t>
   </si>
 </sst>
 </file>
@@ -2609,7 +2732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2696,6 +2819,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2915,7 +3041,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z568"/>
+  <dimension ref="A1:Z563"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -14531,446 +14657,2863 @@
       <c r="U214" s="10"/>
     </row>
     <row r="215" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D215" s="7"/>
+      <c r="A215" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>142</v>
+      </c>
       <c r="F215" s="10"/>
-      <c r="G215" s="7"/>
-      <c r="L215" s="7"/>
-      <c r="N215" s="12"/>
-      <c r="P215" s="10"/>
+      <c r="G215" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H215" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="I215" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J215" s="10"/>
+      <c r="K215" s="10">
+        <v>6</v>
+      </c>
+      <c r="L215" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M215" s="10">
+        <v>0</v>
+      </c>
+      <c r="N215" s="10">
+        <v>0</v>
+      </c>
+      <c r="O215" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="P215" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q215" s="10"/>
+      <c r="R215" s="10"/>
+      <c r="S215" s="10"/>
+      <c r="T215" s="10"/>
+      <c r="U215" s="10"/>
+      <c r="V215" s="10"/>
     </row>
     <row r="216" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D216" s="7"/>
-      <c r="G216" s="7"/>
-      <c r="L216" s="7"/>
-      <c r="N216" s="12"/>
+      <c r="A216" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F216" s="10"/>
+      <c r="G216" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H216" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="I216" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J216" s="10"/>
+      <c r="K216" s="10">
+        <v>6</v>
+      </c>
+      <c r="L216" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M216" s="10">
+        <v>0</v>
+      </c>
+      <c r="N216" s="10">
+        <v>0</v>
+      </c>
+      <c r="O216" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P216" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q216" s="10"/>
+      <c r="R216" s="10"/>
+      <c r="S216" s="10"/>
+      <c r="T216" s="10"/>
+      <c r="U216" s="10"/>
+      <c r="V216" s="10"/>
     </row>
     <row r="217" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D217" s="7"/>
-      <c r="G217" s="7"/>
-      <c r="L217" s="7"/>
-      <c r="N217" s="12"/>
+      <c r="A217" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>795</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F217" s="10"/>
+      <c r="G217" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H217" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="I217" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J217" s="10"/>
+      <c r="K217" s="10">
+        <v>6</v>
+      </c>
+      <c r="L217" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M217" s="10">
+        <v>0</v>
+      </c>
+      <c r="N217" s="10">
+        <v>0</v>
+      </c>
+      <c r="O217" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="P217" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q217" s="10"/>
+      <c r="R217" s="10"/>
+      <c r="S217" s="10"/>
+      <c r="T217" s="10"/>
+      <c r="U217" s="10"/>
+      <c r="V217" s="10"/>
     </row>
     <row r="218" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D218" s="7"/>
-      <c r="G218" s="7"/>
-      <c r="L218" s="7"/>
-      <c r="N218" s="12"/>
+      <c r="A218" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C218" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F218" s="10"/>
+      <c r="G218" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H218" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="I218" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J218" s="10"/>
+      <c r="K218" s="10">
+        <v>6</v>
+      </c>
+      <c r="L218" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M218" s="10">
+        <v>0</v>
+      </c>
+      <c r="N218" s="10">
+        <v>0</v>
+      </c>
+      <c r="O218" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="P218" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q218" s="10"/>
+      <c r="R218" s="10"/>
+      <c r="S218" s="10"/>
+      <c r="T218" s="10"/>
+      <c r="U218" s="10"/>
+      <c r="V218" s="10"/>
     </row>
     <row r="219" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D219" s="7"/>
-      <c r="G219" s="7"/>
-      <c r="L219" s="7"/>
-      <c r="N219" s="12"/>
+      <c r="A219" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="F219" s="10"/>
+      <c r="G219" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H219" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="I219" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J219" s="10"/>
+      <c r="K219" s="10">
+        <v>6</v>
+      </c>
+      <c r="L219" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M219" s="10">
+        <v>0</v>
+      </c>
+      <c r="N219" s="10">
+        <v>0</v>
+      </c>
+      <c r="O219" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P219" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q219" s="10"/>
+      <c r="R219" s="10"/>
+      <c r="S219" s="10"/>
+      <c r="T219" s="10"/>
+      <c r="U219" s="10"/>
+      <c r="V219" s="10"/>
     </row>
     <row r="220" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D220" s="7"/>
-      <c r="G220" s="7"/>
-      <c r="L220" s="7"/>
-      <c r="N220" s="12"/>
+      <c r="A220" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="F220" s="10"/>
+      <c r="G220" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H220" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="I220" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J220" s="10"/>
+      <c r="K220" s="10">
+        <v>6</v>
+      </c>
+      <c r="L220" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M220" s="10">
+        <v>0</v>
+      </c>
+      <c r="N220" s="10">
+        <v>0</v>
+      </c>
+      <c r="O220" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="P220" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="Q220" s="10"/>
+      <c r="R220" s="10"/>
+      <c r="S220" s="10"/>
+      <c r="T220" s="10"/>
+      <c r="U220" s="10"/>
+      <c r="V220" s="10"/>
     </row>
     <row r="221" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D221" s="7"/>
-      <c r="G221" s="7"/>
-      <c r="L221" s="7"/>
-      <c r="N221" s="12"/>
+      <c r="A221" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F221" s="10"/>
+      <c r="G221" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H221" s="19">
+        <v>810</v>
+      </c>
+      <c r="I221" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J221" s="10"/>
+      <c r="K221" s="10">
+        <v>6</v>
+      </c>
+      <c r="L221" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M221" s="10">
+        <v>0</v>
+      </c>
+      <c r="N221" s="10">
+        <v>0</v>
+      </c>
+      <c r="O221" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P221" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q221" s="10"/>
+      <c r="R221" s="10"/>
+      <c r="S221" s="10"/>
+      <c r="T221" s="10"/>
+      <c r="U221" s="10"/>
+      <c r="V221" s="10"/>
     </row>
     <row r="222" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D222" s="7"/>
-      <c r="G222" s="7"/>
-      <c r="L222" s="7"/>
-      <c r="N222" s="12"/>
+      <c r="A222" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F222" s="10"/>
+      <c r="G222" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H222" s="19">
+        <v>384</v>
+      </c>
+      <c r="I222" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J222" s="10"/>
+      <c r="K222" s="10">
+        <v>6</v>
+      </c>
+      <c r="L222" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M222" s="10">
+        <v>0</v>
+      </c>
+      <c r="N222" s="10">
+        <v>0</v>
+      </c>
+      <c r="O222" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P222" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q222" s="10"/>
+      <c r="R222" s="10"/>
+      <c r="S222" s="10"/>
+      <c r="T222" s="10"/>
+      <c r="U222" s="10"/>
+      <c r="V222" s="10"/>
     </row>
     <row r="223" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D223" s="7"/>
-      <c r="G223" s="7"/>
-      <c r="L223" s="7"/>
-      <c r="N223" s="12"/>
+      <c r="A223" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E223" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F223" s="10"/>
+      <c r="G223" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H223" s="19">
+        <v>161</v>
+      </c>
+      <c r="I223" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J223" s="10"/>
+      <c r="K223" s="10">
+        <v>1</v>
+      </c>
+      <c r="L223" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M223" s="10">
+        <v>0</v>
+      </c>
+      <c r="N223" s="10">
+        <v>0</v>
+      </c>
+      <c r="O223" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="P223" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q223" s="10"/>
+      <c r="R223" s="10"/>
+      <c r="S223" s="10"/>
+      <c r="T223" s="10"/>
+      <c r="U223" s="10"/>
+      <c r="V223" s="10"/>
     </row>
     <row r="224" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D224" s="7"/>
-      <c r="G224" s="7"/>
-      <c r="L224" s="7"/>
-      <c r="N224" s="12"/>
-    </row>
-    <row r="225" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D225" s="7"/>
-      <c r="G225" s="7"/>
-      <c r="L225" s="7"/>
-      <c r="N225" s="12"/>
-    </row>
-    <row r="226" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D226" s="7"/>
-      <c r="G226" s="7"/>
-      <c r="L226" s="7"/>
-      <c r="N226" s="12"/>
-    </row>
-    <row r="227" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D227" s="7"/>
-      <c r="G227" s="7"/>
-      <c r="L227" s="7"/>
-      <c r="N227" s="12"/>
-    </row>
-    <row r="228" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D228" s="7"/>
-      <c r="G228" s="7"/>
-      <c r="L228" s="7"/>
-      <c r="N228" s="12"/>
-    </row>
-    <row r="229" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D229" s="7"/>
-      <c r="G229" s="7"/>
-      <c r="L229" s="7"/>
-      <c r="N229" s="12"/>
-    </row>
-    <row r="230" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D230" s="7"/>
-      <c r="G230" s="7"/>
-      <c r="L230" s="7"/>
-      <c r="N230" s="12"/>
-    </row>
-    <row r="231" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D231" s="7"/>
-      <c r="G231" s="7"/>
-      <c r="L231" s="7"/>
-      <c r="N231" s="12"/>
-    </row>
-    <row r="232" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D232" s="7"/>
-      <c r="G232" s="7"/>
-      <c r="L232" s="7"/>
-      <c r="N232" s="12"/>
-    </row>
-    <row r="233" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D233" s="7"/>
-      <c r="G233" s="7"/>
-      <c r="L233" s="7"/>
-      <c r="N233" s="12"/>
-    </row>
-    <row r="234" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D234" s="7"/>
-      <c r="G234" s="7"/>
-      <c r="L234" s="7"/>
-      <c r="N234" s="12"/>
-    </row>
-    <row r="235" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D235" s="7"/>
-      <c r="G235" s="7"/>
-      <c r="L235" s="7"/>
-      <c r="N235" s="12"/>
-    </row>
-    <row r="236" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D236" s="7"/>
-      <c r="G236" s="7"/>
-      <c r="L236" s="7"/>
-      <c r="N236" s="12"/>
-    </row>
-    <row r="237" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D237" s="7"/>
-      <c r="G237" s="7"/>
-      <c r="L237" s="7"/>
-      <c r="N237" s="12"/>
-    </row>
-    <row r="238" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D238" s="7"/>
-      <c r="G238" s="7"/>
-      <c r="L238" s="7"/>
-      <c r="N238" s="12"/>
-    </row>
-    <row r="239" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D239" s="7"/>
-      <c r="G239" s="7"/>
-      <c r="L239" s="7"/>
-      <c r="N239" s="12"/>
-    </row>
-    <row r="240" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D240" s="7"/>
-      <c r="G240" s="7"/>
-      <c r="L240" s="7"/>
-      <c r="N240" s="12"/>
-    </row>
-    <row r="241" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D241" s="7"/>
-      <c r="G241" s="7"/>
-      <c r="L241" s="7"/>
-      <c r="N241" s="12"/>
-    </row>
-    <row r="242" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D242" s="7"/>
-      <c r="G242" s="7"/>
-      <c r="L242" s="7"/>
-      <c r="N242" s="12"/>
-    </row>
-    <row r="243" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D243" s="7"/>
-      <c r="G243" s="7"/>
-      <c r="L243" s="7"/>
-      <c r="N243" s="12"/>
-    </row>
-    <row r="244" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D244" s="7"/>
-      <c r="G244" s="7"/>
-      <c r="L244" s="7"/>
-      <c r="N244" s="12"/>
-    </row>
-    <row r="245" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D245" s="7"/>
-      <c r="G245" s="7"/>
-      <c r="L245" s="7"/>
-      <c r="N245" s="12"/>
-    </row>
-    <row r="246" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D246" s="7"/>
-      <c r="G246" s="7"/>
-      <c r="L246" s="7"/>
-      <c r="N246" s="12"/>
-    </row>
-    <row r="247" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D247" s="7"/>
-      <c r="G247" s="7"/>
-      <c r="L247" s="7"/>
-      <c r="N247" s="12"/>
-    </row>
-    <row r="248" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D248" s="7"/>
-      <c r="G248" s="7"/>
-      <c r="L248" s="7"/>
-      <c r="N248" s="12"/>
-    </row>
-    <row r="249" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D249" s="7"/>
-      <c r="G249" s="7"/>
-      <c r="L249" s="7"/>
-      <c r="N249" s="12"/>
-    </row>
-    <row r="250" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D250" s="7"/>
-      <c r="G250" s="7"/>
-      <c r="L250" s="7"/>
-      <c r="N250" s="12"/>
-    </row>
-    <row r="251" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D251" s="7"/>
-      <c r="G251" s="7"/>
-      <c r="L251" s="7"/>
-      <c r="N251" s="12"/>
-    </row>
-    <row r="252" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D252" s="7"/>
-      <c r="G252" s="7"/>
-      <c r="L252" s="7"/>
-      <c r="N252" s="12"/>
-    </row>
-    <row r="253" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D253" s="7"/>
-      <c r="G253" s="7"/>
-      <c r="L253" s="7"/>
-      <c r="N253" s="12"/>
-    </row>
-    <row r="254" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D254" s="7"/>
-      <c r="G254" s="7"/>
-      <c r="L254" s="7"/>
-      <c r="N254" s="12"/>
-    </row>
-    <row r="255" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D255" s="7"/>
-      <c r="G255" s="7"/>
-      <c r="L255" s="7"/>
-      <c r="N255" s="12"/>
-    </row>
-    <row r="256" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D256" s="7"/>
-      <c r="G256" s="7"/>
-      <c r="L256" s="7"/>
-      <c r="N256" s="12"/>
-    </row>
-    <row r="257" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D257" s="7"/>
-      <c r="G257" s="7"/>
-      <c r="L257" s="7"/>
-      <c r="N257" s="12"/>
-    </row>
-    <row r="258" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D258" s="7"/>
-      <c r="G258" s="7"/>
-      <c r="L258" s="7"/>
-      <c r="N258" s="12"/>
-    </row>
-    <row r="259" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D259" s="7"/>
-      <c r="G259" s="7"/>
-      <c r="L259" s="7"/>
-      <c r="N259" s="12"/>
-    </row>
-    <row r="260" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D260" s="7"/>
-      <c r="G260" s="7"/>
-      <c r="L260" s="7"/>
-      <c r="N260" s="12"/>
-    </row>
-    <row r="261" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D261" s="7"/>
-      <c r="G261" s="7"/>
-      <c r="L261" s="7"/>
-      <c r="N261" s="12"/>
-    </row>
-    <row r="262" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D262" s="7"/>
-      <c r="G262" s="7"/>
-      <c r="L262" s="7"/>
-      <c r="N262" s="12"/>
-    </row>
-    <row r="263" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D263" s="7"/>
-      <c r="G263" s="7"/>
-      <c r="L263" s="7"/>
-      <c r="N263" s="12"/>
-    </row>
-    <row r="264" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D264" s="7"/>
-      <c r="G264" s="7"/>
-      <c r="L264" s="7"/>
-      <c r="N264" s="12"/>
-    </row>
-    <row r="265" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D265" s="7"/>
-      <c r="G265" s="7"/>
-      <c r="L265" s="7"/>
-      <c r="N265" s="12"/>
-    </row>
-    <row r="266" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D266" s="7"/>
-      <c r="G266" s="7"/>
-      <c r="L266" s="7"/>
-      <c r="N266" s="12"/>
-    </row>
-    <row r="267" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D267" s="7"/>
-      <c r="G267" s="7"/>
-      <c r="L267" s="7"/>
-      <c r="N267" s="12"/>
-    </row>
-    <row r="268" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D268" s="7"/>
-      <c r="G268" s="7"/>
-      <c r="L268" s="7"/>
-      <c r="N268" s="12"/>
-    </row>
-    <row r="269" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D269" s="7"/>
-      <c r="G269" s="7"/>
-      <c r="L269" s="7"/>
-      <c r="N269" s="12"/>
-    </row>
-    <row r="270" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D270" s="7"/>
-      <c r="G270" s="7"/>
-      <c r="L270" s="7"/>
-      <c r="N270" s="12"/>
-    </row>
-    <row r="271" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D271" s="7"/>
-      <c r="G271" s="7"/>
-      <c r="L271" s="7"/>
-      <c r="N271" s="12"/>
-    </row>
-    <row r="272" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D272" s="7"/>
-      <c r="G272" s="7"/>
-      <c r="L272" s="7"/>
-      <c r="N272" s="12"/>
-    </row>
-    <row r="273" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D273" s="7"/>
-      <c r="G273" s="7"/>
-      <c r="L273" s="7"/>
-      <c r="N273" s="12"/>
-    </row>
-    <row r="274" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A224" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C224" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F224" s="10"/>
+      <c r="G224" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H224" s="19">
+        <v>742</v>
+      </c>
+      <c r="I224" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J224" s="10"/>
+      <c r="K224" s="10">
+        <v>1</v>
+      </c>
+      <c r="L224" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M224" s="10">
+        <v>0</v>
+      </c>
+      <c r="N224" s="10">
+        <v>0</v>
+      </c>
+      <c r="O224" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P224" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q224" s="10"/>
+      <c r="R224" s="10"/>
+      <c r="S224" s="10"/>
+      <c r="T224" s="10"/>
+      <c r="U224" s="10"/>
+      <c r="V224" s="10"/>
+    </row>
+    <row r="225" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A225" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C225" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D225" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="E225" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F225" s="10"/>
+      <c r="G225" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H225" s="19">
+        <v>945</v>
+      </c>
+      <c r="I225" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J225" s="10"/>
+      <c r="K225" s="10">
+        <v>1</v>
+      </c>
+      <c r="L225" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M225" s="10">
+        <v>0</v>
+      </c>
+      <c r="N225" s="10">
+        <v>0</v>
+      </c>
+      <c r="O225" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P225" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q225" s="10"/>
+      <c r="R225" s="10"/>
+      <c r="S225" s="10"/>
+      <c r="T225" s="10"/>
+      <c r="U225" s="10"/>
+      <c r="V225" s="10"/>
+    </row>
+    <row r="226" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A226" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F226" s="10"/>
+      <c r="G226" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H226" s="19">
+        <v>959</v>
+      </c>
+      <c r="I226" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J226" s="10"/>
+      <c r="K226" s="10">
+        <v>1</v>
+      </c>
+      <c r="L226" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M226" s="10">
+        <v>0</v>
+      </c>
+      <c r="N226" s="10">
+        <v>0</v>
+      </c>
+      <c r="O226" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P226" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q226" s="10"/>
+      <c r="R226" s="10"/>
+      <c r="S226" s="10"/>
+      <c r="T226" s="10"/>
+      <c r="U226" s="10"/>
+      <c r="V226" s="10"/>
+    </row>
+    <row r="227" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A227" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C227" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F227" s="10"/>
+      <c r="G227" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H227" s="19">
+        <v>184</v>
+      </c>
+      <c r="I227" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J227" s="10"/>
+      <c r="K227" s="10">
+        <v>1</v>
+      </c>
+      <c r="L227" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M227" s="10">
+        <v>0</v>
+      </c>
+      <c r="N227" s="10">
+        <v>0</v>
+      </c>
+      <c r="O227" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="P227" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q227" s="10"/>
+      <c r="R227" s="10"/>
+      <c r="S227" s="10"/>
+      <c r="T227" s="10"/>
+      <c r="U227" s="10"/>
+      <c r="V227" s="10"/>
+    </row>
+    <row r="228" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A228" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F228" s="10"/>
+      <c r="G228" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H228" s="19">
+        <v>217</v>
+      </c>
+      <c r="I228" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J228" s="10"/>
+      <c r="K228" s="10">
+        <v>50</v>
+      </c>
+      <c r="L228" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M228" s="10">
+        <v>0</v>
+      </c>
+      <c r="N228" s="10">
+        <v>0</v>
+      </c>
+      <c r="O228" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P228" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q228" s="10"/>
+      <c r="R228" s="10"/>
+      <c r="S228" s="10"/>
+      <c r="T228" s="10"/>
+      <c r="U228" s="10"/>
+      <c r="V228" s="10"/>
+    </row>
+    <row r="229" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A229" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="D229" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E229" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F229" s="10"/>
+      <c r="G229" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H229" s="19">
+        <v>184</v>
+      </c>
+      <c r="I229" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J229" s="10"/>
+      <c r="K229" s="10">
+        <v>28</v>
+      </c>
+      <c r="L229" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M229" s="10">
+        <v>0</v>
+      </c>
+      <c r="N229" s="10">
+        <v>0</v>
+      </c>
+      <c r="O229" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P229" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q229" s="10"/>
+      <c r="R229" s="10"/>
+      <c r="S229" s="10"/>
+      <c r="T229" s="10"/>
+      <c r="U229" s="10"/>
+      <c r="V229" s="10"/>
+    </row>
+    <row r="230" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A230" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="D230" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F230" s="10"/>
+      <c r="G230" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H230" s="19">
+        <v>184</v>
+      </c>
+      <c r="I230" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J230" s="10"/>
+      <c r="K230" s="10">
+        <v>25</v>
+      </c>
+      <c r="L230" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M230" s="10">
+        <v>0</v>
+      </c>
+      <c r="N230" s="10">
+        <v>0</v>
+      </c>
+      <c r="O230" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P230" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q230" s="10"/>
+      <c r="R230" s="10"/>
+      <c r="S230" s="10"/>
+      <c r="T230" s="10"/>
+      <c r="U230" s="10"/>
+      <c r="V230" s="10"/>
+    </row>
+    <row r="231" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A231" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C231" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D231" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F231" s="10"/>
+      <c r="G231" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H231" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="I231" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J231" s="10"/>
+      <c r="K231" s="10">
+        <v>1</v>
+      </c>
+      <c r="L231" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M231" s="10">
+        <v>0</v>
+      </c>
+      <c r="N231" s="10">
+        <v>0</v>
+      </c>
+      <c r="O231" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="P231" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="Q231" s="10"/>
+      <c r="R231" s="10"/>
+      <c r="S231" s="10"/>
+      <c r="T231" s="10"/>
+      <c r="U231" s="10"/>
+      <c r="V231" s="10"/>
+    </row>
+    <row r="232" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A232" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C232" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="D232" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="E232" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="F232" s="10"/>
+      <c r="G232" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H232" s="19" t="s">
+        <v>813</v>
+      </c>
+      <c r="I232" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J232" s="10"/>
+      <c r="K232" s="10">
+        <v>1</v>
+      </c>
+      <c r="L232" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M232" s="10">
+        <v>0</v>
+      </c>
+      <c r="N232" s="10">
+        <v>0</v>
+      </c>
+      <c r="O232" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P232" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q232" s="10"/>
+      <c r="R232" s="10"/>
+      <c r="S232" s="10"/>
+      <c r="T232" s="10"/>
+      <c r="U232" s="10"/>
+      <c r="V232" s="10"/>
+    </row>
+    <row r="233" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A233" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C233" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="F233" s="10"/>
+      <c r="G233" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H233" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="I233" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J233" s="10"/>
+      <c r="K233" s="10">
+        <v>1</v>
+      </c>
+      <c r="L233" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M233" s="10">
+        <v>0</v>
+      </c>
+      <c r="N233" s="10">
+        <v>0</v>
+      </c>
+      <c r="O233" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P233" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q233" s="10"/>
+      <c r="R233" s="10"/>
+      <c r="S233" s="10"/>
+      <c r="T233" s="10"/>
+      <c r="U233" s="10"/>
+      <c r="V233" s="10"/>
+    </row>
+    <row r="234" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A234" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="D234" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="E234" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F234" s="10"/>
+      <c r="G234" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H234" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="I234" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J234" s="10"/>
+      <c r="K234" s="10">
+        <v>1</v>
+      </c>
+      <c r="L234" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M234" s="10">
+        <v>0</v>
+      </c>
+      <c r="N234" s="10">
+        <v>0</v>
+      </c>
+      <c r="O234" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P234" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q234" s="10"/>
+      <c r="R234" s="10"/>
+      <c r="S234" s="10"/>
+      <c r="T234" s="10"/>
+      <c r="U234" s="10"/>
+      <c r="V234" s="10"/>
+    </row>
+    <row r="235" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A235" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B235" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="D235" s="40" t="s">
+        <v>818</v>
+      </c>
+      <c r="E235" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="F235" s="40"/>
+      <c r="G235" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H235" s="42" t="s">
+        <v>518</v>
+      </c>
+      <c r="I235" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="J235" s="40"/>
+      <c r="K235" s="40">
+        <v>1</v>
+      </c>
+      <c r="L235" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="M235" s="40">
+        <v>0</v>
+      </c>
+      <c r="N235" s="40">
+        <v>0</v>
+      </c>
+      <c r="O235" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="P235" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q235" s="40"/>
+      <c r="R235" s="40"/>
+      <c r="S235" s="40"/>
+      <c r="T235" s="40"/>
+      <c r="U235" s="40"/>
+      <c r="V235" s="40"/>
+      <c r="W235" s="41"/>
+      <c r="X235" s="41"/>
+    </row>
+    <row r="236" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A236" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E236" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F236" s="10"/>
+      <c r="G236" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H236" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="I236" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J236" s="10"/>
+      <c r="K236" s="10">
+        <v>1</v>
+      </c>
+      <c r="L236" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M236" s="10">
+        <v>0</v>
+      </c>
+      <c r="N236" s="10">
+        <v>0</v>
+      </c>
+      <c r="O236" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P236" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q236" s="10"/>
+      <c r="R236" s="10"/>
+      <c r="S236" s="10"/>
+      <c r="T236" s="10"/>
+      <c r="U236" s="10"/>
+      <c r="V236" s="10"/>
+    </row>
+    <row r="237" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A237" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B237" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C237" s="10" t="s">
+        <v>832</v>
+      </c>
+      <c r="D237" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="E237" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="F237" s="40"/>
+      <c r="G237" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H237" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="I237" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="J237" s="40"/>
+      <c r="K237" s="40">
+        <v>1</v>
+      </c>
+      <c r="L237" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="M237" s="40">
+        <v>0</v>
+      </c>
+      <c r="N237" s="40">
+        <v>0</v>
+      </c>
+      <c r="O237" s="40" t="s">
+        <v>738</v>
+      </c>
+      <c r="P237" s="40" t="s">
+        <v>738</v>
+      </c>
+      <c r="Q237" s="40"/>
+      <c r="R237" s="40"/>
+      <c r="S237" s="40"/>
+      <c r="T237" s="40"/>
+      <c r="U237" s="40"/>
+      <c r="V237" s="40"/>
+    </row>
+    <row r="238" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A238" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B238" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="D238" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="E238" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="F238" s="40"/>
+      <c r="G238" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="H238" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="I238" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="J238" s="40"/>
+      <c r="K238" s="40">
+        <v>1</v>
+      </c>
+      <c r="L238" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="M238" s="40">
+        <v>0</v>
+      </c>
+      <c r="N238" s="40">
+        <v>0</v>
+      </c>
+      <c r="O238" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="P238" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q238" s="40"/>
+      <c r="R238" s="40"/>
+      <c r="S238" s="40"/>
+      <c r="T238" s="40"/>
+      <c r="U238" s="40"/>
+      <c r="V238" s="40"/>
+      <c r="W238" s="41"/>
+      <c r="X238" s="41"/>
+    </row>
+    <row r="239" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A239" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C239" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="E239" s="10" t="s">
+        <v>821</v>
+      </c>
+      <c r="F239" s="10"/>
+      <c r="G239" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H239" s="19" t="s">
+        <v>822</v>
+      </c>
+      <c r="I239" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J239" s="10"/>
+      <c r="K239" s="10">
+        <v>1</v>
+      </c>
+      <c r="L239" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M239" s="10">
+        <v>0</v>
+      </c>
+      <c r="N239" s="10">
+        <v>0</v>
+      </c>
+      <c r="O239" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P239" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q239" s="10"/>
+      <c r="R239" s="10"/>
+      <c r="S239" s="10"/>
+      <c r="T239" s="10"/>
+      <c r="U239" s="10"/>
+      <c r="V239" s="10"/>
+    </row>
+    <row r="240" spans="1:24" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A240" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="D240" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="F240" s="10"/>
+      <c r="G240" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H240" s="19">
+        <v>230</v>
+      </c>
+      <c r="I240" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="J240" s="10"/>
+      <c r="K240" s="10">
+        <v>1</v>
+      </c>
+      <c r="L240" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M240" s="10">
+        <v>0</v>
+      </c>
+      <c r="N240" s="10">
+        <v>0</v>
+      </c>
+      <c r="O240" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P240" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q240" s="10"/>
+      <c r="R240" s="10"/>
+      <c r="S240" s="10"/>
+      <c r="T240" s="10"/>
+      <c r="U240" s="10"/>
+      <c r="V240" s="10"/>
+    </row>
+    <row r="241" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A241" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C241" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D241" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="E241" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="F241" s="10"/>
+      <c r="G241" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H241" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="I241" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J241" s="10"/>
+      <c r="K241" s="10">
+        <v>6</v>
+      </c>
+      <c r="L241" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M241" s="10">
+        <v>0</v>
+      </c>
+      <c r="N241" s="10">
+        <v>0</v>
+      </c>
+      <c r="O241" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="P241" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q241" s="10"/>
+      <c r="R241" s="10"/>
+      <c r="S241" s="10"/>
+      <c r="T241" s="10"/>
+      <c r="U241" s="10"/>
+      <c r="V241" s="10"/>
+    </row>
+    <row r="242" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A242" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F242" s="10"/>
+      <c r="G242" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H242" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="I242" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J242" s="10"/>
+      <c r="K242" s="10">
+        <v>6</v>
+      </c>
+      <c r="L242" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M242" s="10">
+        <v>0</v>
+      </c>
+      <c r="N242" s="10">
+        <v>0</v>
+      </c>
+      <c r="O242" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="P242" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q242" s="10"/>
+      <c r="R242" s="10"/>
+      <c r="S242" s="10"/>
+      <c r="T242" s="10"/>
+      <c r="U242" s="10"/>
+      <c r="V242" s="10"/>
+    </row>
+    <row r="243" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A243" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C243" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="D243" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="E243" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F243" s="10"/>
+      <c r="G243" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H243" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="I243" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J243" s="10"/>
+      <c r="K243" s="10">
+        <v>6</v>
+      </c>
+      <c r="L243" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M243" s="10">
+        <v>0</v>
+      </c>
+      <c r="N243" s="10">
+        <v>0</v>
+      </c>
+      <c r="O243" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P243" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q243" s="10"/>
+      <c r="R243" s="10"/>
+      <c r="S243" s="10"/>
+      <c r="T243" s="10"/>
+      <c r="U243" s="10"/>
+      <c r="V243" s="10"/>
+    </row>
+    <row r="244" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A244" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="E244" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F244" s="10"/>
+      <c r="G244" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H244" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="I244" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J244" s="10"/>
+      <c r="K244" s="10">
+        <v>6</v>
+      </c>
+      <c r="L244" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M244" s="10">
+        <v>0</v>
+      </c>
+      <c r="N244" s="10">
+        <v>0</v>
+      </c>
+      <c r="O244" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="P244" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q244" s="10"/>
+      <c r="R244" s="10"/>
+      <c r="S244" s="10"/>
+      <c r="T244" s="10"/>
+      <c r="U244" s="10"/>
+      <c r="V244" s="10"/>
+    </row>
+    <row r="245" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A245" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C245" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E245" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F245" s="10"/>
+      <c r="G245" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H245" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="I245" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J245" s="10"/>
+      <c r="K245" s="10">
+        <v>6</v>
+      </c>
+      <c r="L245" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M245" s="10">
+        <v>0</v>
+      </c>
+      <c r="N245" s="10">
+        <v>0</v>
+      </c>
+      <c r="O245" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P245" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q245" s="10"/>
+      <c r="R245" s="10"/>
+      <c r="S245" s="10"/>
+      <c r="T245" s="10"/>
+      <c r="U245" s="10"/>
+      <c r="V245" s="10"/>
+    </row>
+    <row r="246" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A246" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F246" s="10"/>
+      <c r="G246" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H246" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="I246" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J246" s="10"/>
+      <c r="K246" s="10">
+        <v>6</v>
+      </c>
+      <c r="L246" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M246" s="10">
+        <v>0</v>
+      </c>
+      <c r="N246" s="10">
+        <v>0</v>
+      </c>
+      <c r="O246" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="P246" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="Q246" s="10"/>
+      <c r="R246" s="10"/>
+      <c r="S246" s="10"/>
+      <c r="T246" s="10"/>
+      <c r="U246" s="10"/>
+      <c r="V246" s="10"/>
+    </row>
+    <row r="247" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A247" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C247" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="E247" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F247" s="10"/>
+      <c r="G247" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H247" s="19">
+        <v>810</v>
+      </c>
+      <c r="I247" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J247" s="10"/>
+      <c r="K247" s="10">
+        <v>6</v>
+      </c>
+      <c r="L247" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M247" s="10">
+        <v>0</v>
+      </c>
+      <c r="N247" s="10">
+        <v>0</v>
+      </c>
+      <c r="O247" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P247" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q247" s="10"/>
+      <c r="R247" s="10"/>
+      <c r="S247" s="10"/>
+      <c r="T247" s="10"/>
+      <c r="U247" s="10"/>
+      <c r="V247" s="10"/>
+    </row>
+    <row r="248" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A248" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C248" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F248" s="10"/>
+      <c r="G248" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H248" s="19">
+        <v>384</v>
+      </c>
+      <c r="I248" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J248" s="10"/>
+      <c r="K248" s="10">
+        <v>6</v>
+      </c>
+      <c r="L248" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M248" s="10">
+        <v>0</v>
+      </c>
+      <c r="N248" s="10">
+        <v>0</v>
+      </c>
+      <c r="O248" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P248" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q248" s="10"/>
+      <c r="R248" s="10"/>
+      <c r="S248" s="10"/>
+      <c r="T248" s="10"/>
+      <c r="U248" s="10"/>
+      <c r="V248" s="10"/>
+    </row>
+    <row r="249" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A249" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C249" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E249" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F249" s="10"/>
+      <c r="G249" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H249" s="19">
+        <v>161</v>
+      </c>
+      <c r="I249" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J249" s="10"/>
+      <c r="K249" s="10">
+        <v>1</v>
+      </c>
+      <c r="L249" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M249" s="10">
+        <v>0</v>
+      </c>
+      <c r="N249" s="10">
+        <v>0</v>
+      </c>
+      <c r="O249" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="P249" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q249" s="10"/>
+      <c r="R249" s="10"/>
+      <c r="S249" s="10"/>
+      <c r="T249" s="10"/>
+      <c r="U249" s="10"/>
+      <c r="V249" s="10"/>
+    </row>
+    <row r="250" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A250" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F250" s="10"/>
+      <c r="G250" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H250" s="19">
+        <v>742</v>
+      </c>
+      <c r="I250" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J250" s="10"/>
+      <c r="K250" s="10">
+        <v>1</v>
+      </c>
+      <c r="L250" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M250" s="10">
+        <v>0</v>
+      </c>
+      <c r="N250" s="10">
+        <v>0</v>
+      </c>
+      <c r="O250" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P250" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q250" s="10"/>
+      <c r="R250" s="10"/>
+      <c r="S250" s="10"/>
+      <c r="T250" s="10"/>
+      <c r="U250" s="10"/>
+      <c r="V250" s="10"/>
+    </row>
+    <row r="251" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A251" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C251" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F251" s="10"/>
+      <c r="G251" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H251" s="19">
+        <v>945</v>
+      </c>
+      <c r="I251" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J251" s="10"/>
+      <c r="K251" s="10">
+        <v>1</v>
+      </c>
+      <c r="L251" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M251" s="10">
+        <v>0</v>
+      </c>
+      <c r="N251" s="10">
+        <v>0</v>
+      </c>
+      <c r="O251" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P251" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q251" s="10"/>
+      <c r="R251" s="10"/>
+      <c r="S251" s="10"/>
+      <c r="T251" s="10"/>
+      <c r="U251" s="10"/>
+      <c r="V251" s="10"/>
+    </row>
+    <row r="252" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A252" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F252" s="10"/>
+      <c r="G252" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H252" s="19">
+        <v>959</v>
+      </c>
+      <c r="I252" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J252" s="10"/>
+      <c r="K252" s="10">
+        <v>1</v>
+      </c>
+      <c r="L252" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M252" s="10">
+        <v>0</v>
+      </c>
+      <c r="N252" s="10">
+        <v>0</v>
+      </c>
+      <c r="O252" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="P252" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q252" s="10"/>
+      <c r="R252" s="10"/>
+      <c r="S252" s="10"/>
+      <c r="T252" s="10"/>
+      <c r="U252" s="10"/>
+      <c r="V252" s="10"/>
+    </row>
+    <row r="253" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A253" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C253" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F253" s="10"/>
+      <c r="G253" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H253" s="19">
+        <v>184</v>
+      </c>
+      <c r="I253" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J253" s="10"/>
+      <c r="K253" s="10">
+        <v>1</v>
+      </c>
+      <c r="L253" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M253" s="10">
+        <v>0</v>
+      </c>
+      <c r="N253" s="10">
+        <v>0</v>
+      </c>
+      <c r="O253" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="P253" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q253" s="10"/>
+      <c r="R253" s="10"/>
+      <c r="S253" s="10"/>
+      <c r="T253" s="10"/>
+      <c r="U253" s="10"/>
+      <c r="V253" s="10"/>
+    </row>
+    <row r="254" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A254" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F254" s="10"/>
+      <c r="G254" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H254" s="19">
+        <v>217</v>
+      </c>
+      <c r="I254" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J254" s="10"/>
+      <c r="K254" s="10">
+        <v>50</v>
+      </c>
+      <c r="L254" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M254" s="10">
+        <v>0</v>
+      </c>
+      <c r="N254" s="10">
+        <v>0</v>
+      </c>
+      <c r="O254" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P254" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q254" s="10"/>
+      <c r="R254" s="10"/>
+      <c r="S254" s="10"/>
+      <c r="T254" s="10"/>
+      <c r="U254" s="10"/>
+      <c r="V254" s="10"/>
+    </row>
+    <row r="255" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A255" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C255" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F255" s="10"/>
+      <c r="G255" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H255" s="19">
+        <v>184</v>
+      </c>
+      <c r="I255" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J255" s="10"/>
+      <c r="K255" s="10">
+        <v>28</v>
+      </c>
+      <c r="L255" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M255" s="10">
+        <v>0</v>
+      </c>
+      <c r="N255" s="10">
+        <v>0</v>
+      </c>
+      <c r="O255" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P255" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q255" s="10"/>
+      <c r="R255" s="10"/>
+      <c r="S255" s="10"/>
+      <c r="T255" s="10"/>
+      <c r="U255" s="10"/>
+      <c r="V255" s="10"/>
+    </row>
+    <row r="256" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A256" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F256" s="10"/>
+      <c r="G256" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H256" s="19">
+        <v>184</v>
+      </c>
+      <c r="I256" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J256" s="10"/>
+      <c r="K256" s="10">
+        <v>25</v>
+      </c>
+      <c r="L256" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M256" s="10">
+        <v>0</v>
+      </c>
+      <c r="N256" s="10">
+        <v>0</v>
+      </c>
+      <c r="O256" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P256" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q256" s="10"/>
+      <c r="R256" s="10"/>
+      <c r="S256" s="10"/>
+      <c r="T256" s="10"/>
+      <c r="U256" s="10"/>
+      <c r="V256" s="10"/>
+    </row>
+    <row r="257" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A257" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>826</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="F257" s="10"/>
+      <c r="G257" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H257" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="I257" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J257" s="10"/>
+      <c r="K257" s="10">
+        <v>1</v>
+      </c>
+      <c r="L257" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M257" s="10">
+        <v>0</v>
+      </c>
+      <c r="N257" s="10">
+        <v>0</v>
+      </c>
+      <c r="O257" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="P257" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="Q257" s="10"/>
+      <c r="R257" s="10"/>
+      <c r="S257" s="10"/>
+      <c r="T257" s="10"/>
+      <c r="U257" s="10"/>
+      <c r="V257" s="10"/>
+    </row>
+    <row r="258" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A258" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>828</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="F258" s="10"/>
+      <c r="G258" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H258" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="I258" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J258" s="10"/>
+      <c r="K258" s="10">
+        <v>1</v>
+      </c>
+      <c r="L258" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M258" s="10"/>
+      <c r="N258" s="10"/>
+      <c r="O258" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="P258" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q258" s="10"/>
+      <c r="R258" s="10"/>
+      <c r="S258" s="10"/>
+      <c r="T258" s="10"/>
+      <c r="U258" s="10"/>
+      <c r="V258" s="10"/>
+    </row>
+    <row r="259" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A259" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C259" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="D259" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F259" s="10"/>
+      <c r="G259" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H259" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="I259" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J259" s="10"/>
+      <c r="K259" s="10">
+        <v>1</v>
+      </c>
+      <c r="L259" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M259" s="10">
+        <v>0</v>
+      </c>
+      <c r="N259" s="10">
+        <v>0</v>
+      </c>
+      <c r="O259" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P259" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="10"/>
+      <c r="S259" s="10"/>
+      <c r="T259" s="10"/>
+      <c r="U259" s="10"/>
+      <c r="V259" s="10"/>
+    </row>
+    <row r="260" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A260" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F260" s="10"/>
+      <c r="G260" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H260" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="I260" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J260" s="10"/>
+      <c r="K260" s="10">
+        <v>1</v>
+      </c>
+      <c r="L260" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M260" s="10">
+        <v>0</v>
+      </c>
+      <c r="N260" s="10">
+        <v>0</v>
+      </c>
+      <c r="O260" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P260" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q260" s="10"/>
+      <c r="R260" s="10"/>
+      <c r="S260" s="10"/>
+      <c r="T260" s="10"/>
+      <c r="U260" s="10"/>
+      <c r="V260" s="10"/>
+    </row>
+    <row r="261" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A261" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B261" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C261" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="D261" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="E261" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="F261" s="40"/>
+      <c r="G261" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H261" s="42" t="s">
+        <v>518</v>
+      </c>
+      <c r="I261" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="J261" s="40"/>
+      <c r="K261" s="40">
+        <v>1</v>
+      </c>
+      <c r="L261" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="M261" s="40">
+        <v>0</v>
+      </c>
+      <c r="N261" s="40">
+        <v>0</v>
+      </c>
+      <c r="O261" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="P261" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q261" s="40"/>
+      <c r="R261" s="40"/>
+      <c r="S261" s="40"/>
+      <c r="T261" s="40"/>
+      <c r="U261" s="40"/>
+      <c r="V261" s="40"/>
+    </row>
+    <row r="262" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A262" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="D262" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E262" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F262" s="10"/>
+      <c r="G262" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H262" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="I262" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J262" s="10"/>
+      <c r="K262" s="10">
+        <v>1</v>
+      </c>
+      <c r="L262" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M262" s="10"/>
+      <c r="N262" s="10"/>
+      <c r="O262" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="P262" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q262" s="10"/>
+      <c r="R262" s="10"/>
+      <c r="S262" s="10"/>
+      <c r="T262" s="10"/>
+      <c r="U262" s="10"/>
+      <c r="V262" s="10"/>
+    </row>
+    <row r="263" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A263" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="B263" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="D263" s="40" t="s">
+        <v>820</v>
+      </c>
+      <c r="E263" s="40" t="s">
+        <v>831</v>
+      </c>
+      <c r="F263" s="40"/>
+      <c r="G263" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H263" s="42" t="s">
+        <v>822</v>
+      </c>
+      <c r="I263" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="J263" s="40"/>
+      <c r="K263" s="40">
+        <v>1</v>
+      </c>
+      <c r="L263" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="M263" s="40">
+        <v>0</v>
+      </c>
+      <c r="N263" s="40">
+        <v>0</v>
+      </c>
+      <c r="O263" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="P263" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q263" s="40"/>
+      <c r="R263" s="40"/>
+      <c r="S263" s="40"/>
+      <c r="T263" s="40"/>
+      <c r="U263" s="40"/>
+      <c r="V263" s="40"/>
+    </row>
+    <row r="264" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A264" s="10"/>
+      <c r="B264" s="10"/>
+      <c r="C264" s="10"/>
+      <c r="D264" s="10"/>
+      <c r="E264" s="10"/>
+      <c r="F264" s="10"/>
+      <c r="G264" s="10"/>
+      <c r="H264" s="19"/>
+      <c r="I264" s="10"/>
+      <c r="J264" s="10"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="10"/>
+      <c r="M264" s="10"/>
+      <c r="N264" s="10"/>
+      <c r="P264" s="10"/>
+      <c r="Q264" s="10"/>
+      <c r="R264" s="10"/>
+      <c r="S264" s="10"/>
+      <c r="T264" s="10"/>
+      <c r="U264" s="10"/>
+      <c r="V264" s="10"/>
+    </row>
+    <row r="265" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A265" s="10"/>
+      <c r="B265" s="10"/>
+      <c r="C265" s="10"/>
+      <c r="D265" s="10"/>
+      <c r="E265" s="10"/>
+      <c r="F265" s="10"/>
+      <c r="G265" s="10"/>
+      <c r="H265" s="19"/>
+      <c r="I265" s="10"/>
+      <c r="J265" s="10"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="10"/>
+      <c r="M265" s="10"/>
+      <c r="N265" s="10"/>
+      <c r="P265" s="10"/>
+      <c r="Q265" s="10"/>
+      <c r="R265" s="10"/>
+      <c r="S265" s="10"/>
+      <c r="T265" s="10"/>
+      <c r="U265" s="10"/>
+      <c r="V265" s="10"/>
+    </row>
+    <row r="266" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A266" s="10"/>
+      <c r="B266" s="10"/>
+      <c r="C266" s="10"/>
+      <c r="D266" s="10"/>
+      <c r="E266" s="10"/>
+      <c r="F266" s="10"/>
+      <c r="G266" s="10"/>
+      <c r="H266" s="19"/>
+      <c r="I266" s="10"/>
+      <c r="J266" s="10"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="10"/>
+      <c r="M266" s="10"/>
+      <c r="N266" s="10"/>
+      <c r="P266" s="10"/>
+      <c r="Q266" s="10"/>
+      <c r="R266" s="10"/>
+      <c r="S266" s="10"/>
+      <c r="T266" s="10"/>
+      <c r="U266" s="10"/>
+      <c r="V266" s="10"/>
+    </row>
+    <row r="267" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A267" s="10"/>
+      <c r="B267" s="10"/>
+      <c r="C267" s="10"/>
+      <c r="D267" s="10"/>
+      <c r="E267" s="10"/>
+      <c r="F267" s="10"/>
+      <c r="G267" s="10"/>
+      <c r="H267" s="19"/>
+      <c r="I267" s="10"/>
+      <c r="J267" s="10"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="10"/>
+      <c r="M267" s="10"/>
+      <c r="N267" s="10"/>
+      <c r="P267" s="10"/>
+      <c r="Q267" s="10"/>
+      <c r="R267" s="10"/>
+      <c r="S267" s="10"/>
+      <c r="T267" s="10"/>
+      <c r="U267" s="10"/>
+      <c r="V267" s="10"/>
+    </row>
+    <row r="268" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A268" s="10"/>
+      <c r="B268" s="10"/>
+      <c r="C268" s="10"/>
+      <c r="D268" s="10"/>
+      <c r="E268" s="10"/>
+      <c r="F268" s="10"/>
+      <c r="G268" s="10"/>
+      <c r="H268" s="19"/>
+      <c r="I268" s="10"/>
+      <c r="J268" s="10"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="10"/>
+      <c r="M268" s="10"/>
+      <c r="N268" s="10"/>
+      <c r="P268" s="10"/>
+      <c r="Q268" s="10"/>
+      <c r="R268" s="10"/>
+      <c r="S268" s="10"/>
+      <c r="T268" s="10"/>
+      <c r="U268" s="10"/>
+      <c r="V268" s="10"/>
+    </row>
+    <row r="269" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A269" s="10"/>
+      <c r="B269" s="10"/>
+      <c r="C269" s="10"/>
+      <c r="D269" s="10"/>
+      <c r="E269" s="10"/>
+      <c r="F269" s="10"/>
+      <c r="G269" s="10"/>
+      <c r="H269" s="19"/>
+      <c r="I269" s="10"/>
+      <c r="J269" s="10"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="10"/>
+      <c r="M269" s="10"/>
+      <c r="N269" s="10"/>
+      <c r="P269" s="10"/>
+      <c r="Q269" s="10"/>
+      <c r="R269" s="10"/>
+      <c r="S269" s="10"/>
+      <c r="T269" s="10"/>
+      <c r="U269" s="10"/>
+      <c r="V269" s="10"/>
+    </row>
+    <row r="270" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A270" s="10"/>
+      <c r="B270" s="10"/>
+      <c r="C270" s="10"/>
+      <c r="D270" s="10"/>
+      <c r="E270" s="10"/>
+      <c r="F270" s="10"/>
+      <c r="G270" s="10"/>
+      <c r="H270" s="19"/>
+      <c r="I270" s="10"/>
+      <c r="J270" s="10"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="10"/>
+      <c r="M270" s="10"/>
+      <c r="N270" s="10"/>
+      <c r="P270" s="10"/>
+      <c r="Q270" s="10"/>
+      <c r="R270" s="10"/>
+      <c r="S270" s="10"/>
+      <c r="T270" s="10"/>
+      <c r="U270" s="10"/>
+      <c r="V270" s="10"/>
+    </row>
+    <row r="271" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A271" s="10"/>
+      <c r="B271" s="10"/>
+      <c r="C271" s="10"/>
+      <c r="D271" s="10"/>
+      <c r="E271" s="10"/>
+      <c r="F271" s="10"/>
+      <c r="G271" s="10"/>
+      <c r="H271" s="19"/>
+      <c r="I271" s="10"/>
+      <c r="J271" s="10"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="10"/>
+      <c r="M271" s="10"/>
+      <c r="N271" s="10"/>
+      <c r="P271" s="10"/>
+      <c r="Q271" s="10"/>
+      <c r="R271" s="10"/>
+      <c r="S271" s="10"/>
+      <c r="T271" s="10"/>
+      <c r="U271" s="10"/>
+      <c r="V271" s="10"/>
+    </row>
+    <row r="272" spans="1:22" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A272" s="10"/>
+      <c r="B272" s="10"/>
+      <c r="C272" s="10"/>
+      <c r="D272" s="10"/>
+      <c r="E272" s="10"/>
+      <c r="F272" s="10"/>
+      <c r="G272" s="10"/>
+      <c r="H272" s="19"/>
+      <c r="I272" s="10"/>
+      <c r="J272" s="10"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="10"/>
+      <c r="M272" s="10"/>
+      <c r="N272" s="10"/>
+      <c r="P272" s="10"/>
+      <c r="Q272" s="10"/>
+      <c r="R272" s="10"/>
+      <c r="S272" s="10"/>
+      <c r="T272" s="10"/>
+      <c r="U272" s="10"/>
+      <c r="V272" s="10"/>
+    </row>
+    <row r="273" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A273" s="10"/>
+      <c r="B273" s="10"/>
+      <c r="C273" s="10"/>
+      <c r="D273" s="10"/>
+      <c r="E273" s="10"/>
+      <c r="F273" s="10"/>
+      <c r="G273" s="10"/>
+      <c r="H273" s="19"/>
+      <c r="I273" s="10"/>
+      <c r="J273" s="10"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="10"/>
+      <c r="M273" s="10"/>
+      <c r="N273" s="10"/>
+      <c r="P273" s="10"/>
+      <c r="Q273" s="10"/>
+      <c r="R273" s="10"/>
+      <c r="S273" s="10"/>
+      <c r="T273" s="10"/>
+      <c r="U273" s="10"/>
+    </row>
+    <row r="274" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D274" s="7"/>
       <c r="G274" s="7"/>
       <c r="L274" s="7"/>
       <c r="N274" s="12"/>
     </row>
-    <row r="275" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D275" s="7"/>
       <c r="G275" s="7"/>
       <c r="L275" s="7"/>
       <c r="N275" s="12"/>
     </row>
-    <row r="276" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D276" s="7"/>
       <c r="G276" s="7"/>
       <c r="L276" s="7"/>
       <c r="N276" s="12"/>
     </row>
-    <row r="277" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D277" s="7"/>
       <c r="G277" s="7"/>
       <c r="L277" s="7"/>
       <c r="N277" s="12"/>
     </row>
-    <row r="278" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D278" s="7"/>
       <c r="G278" s="7"/>
       <c r="L278" s="7"/>
       <c r="N278" s="12"/>
     </row>
-    <row r="279" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D279" s="7"/>
       <c r="G279" s="7"/>
       <c r="L279" s="7"/>
       <c r="N279" s="12"/>
     </row>
-    <row r="280" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D280" s="7"/>
       <c r="G280" s="7"/>
       <c r="L280" s="7"/>
       <c r="N280" s="12"/>
     </row>
-    <row r="281" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D281" s="7"/>
       <c r="G281" s="7"/>
       <c r="L281" s="7"/>
       <c r="N281" s="12"/>
     </row>
-    <row r="282" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D282" s="7"/>
       <c r="G282" s="7"/>
       <c r="L282" s="7"/>
       <c r="N282" s="12"/>
     </row>
-    <row r="283" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D283" s="7"/>
       <c r="G283" s="7"/>
       <c r="L283" s="7"/>
       <c r="N283" s="12"/>
     </row>
-    <row r="284" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D284" s="7"/>
       <c r="G284" s="7"/>
       <c r="L284" s="7"/>
       <c r="N284" s="12"/>
     </row>
-    <row r="285" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D285" s="7"/>
       <c r="G285" s="7"/>
       <c r="L285" s="7"/>
       <c r="N285" s="12"/>
     </row>
-    <row r="286" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D286" s="7"/>
       <c r="G286" s="7"/>
       <c r="L286" s="7"/>
       <c r="N286" s="12"/>
     </row>
-    <row r="287" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D287" s="7"/>
       <c r="G287" s="7"/>
       <c r="L287" s="7"/>
       <c r="N287" s="12"/>
     </row>
-    <row r="288" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D288" s="7"/>
       <c r="G288" s="7"/>
       <c r="L288" s="7"/>
@@ -16625,36 +19168,6 @@
       <c r="G563" s="7"/>
       <c r="L563" s="7"/>
       <c r="N563" s="12"/>
-    </row>
-    <row r="564" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D564" s="7"/>
-      <c r="G564" s="7"/>
-      <c r="L564" s="7"/>
-      <c r="N564" s="12"/>
-    </row>
-    <row r="565" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D565" s="7"/>
-      <c r="G565" s="7"/>
-      <c r="L565" s="7"/>
-      <c r="N565" s="12"/>
-    </row>
-    <row r="566" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D566" s="7"/>
-      <c r="G566" s="7"/>
-      <c r="L566" s="7"/>
-      <c r="N566" s="12"/>
-    </row>
-    <row r="567" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D567" s="7"/>
-      <c r="G567" s="7"/>
-      <c r="L567" s="7"/>
-      <c r="N567" s="12"/>
-    </row>
-    <row r="568" spans="4:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D568" s="7"/>
-      <c r="G568" s="7"/>
-      <c r="L568" s="7"/>
-      <c r="N568" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A5809D1-7C6A-5740-822E-8049BC0B6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3A2794-0A7F-4544-B95B-934D2C571FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Итоговый расчет с монтажом" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$263</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'СПРАВОЧНИК -3'!$A$1:$Q$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -19453,10 +19453,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q998"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" style="10" customWidth="1"/>
@@ -19482,8 +19482,8 @@
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
       <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="30"/>
@@ -19493,15 +19493,15 @@
       <c r="P1" s="30"/>
       <c r="Q1" s="30"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="10" t="s">
         <v>483</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>46</v>
+      <c r="C2" s="24" t="s">
+        <v>687</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>585</v>
@@ -19509,8 +19509,6 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -19520,7 +19518,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10" t="s">
         <v>520</v>
       </c>
@@ -19536,8 +19534,6 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -19547,7 +19543,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10" t="s">
         <v>101</v>
       </c>
@@ -19563,8 +19559,6 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -19590,8 +19584,6 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -19601,7 +19593,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>472</v>
       </c>
@@ -19617,8 +19609,6 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -19628,7 +19618,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10" t="s">
         <v>475</v>
       </c>
@@ -19644,8 +19634,6 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
@@ -19655,7 +19643,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
@@ -19671,8 +19659,6 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -19682,7 +19668,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
         <v>222</v>
       </c>
@@ -19698,8 +19684,6 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -19709,7 +19693,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10" t="s">
         <v>517</v>
       </c>
@@ -19725,8 +19709,6 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -19736,7 +19718,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10" t="s">
         <v>285</v>
       </c>
@@ -19752,8 +19734,6 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
@@ -19763,7 +19743,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10" t="s">
         <v>108</v>
       </c>
@@ -19779,8 +19759,6 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
@@ -19790,7 +19768,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
         <v>249</v>
       </c>
@@ -19806,8 +19784,6 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
@@ -19817,7 +19793,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
         <v>489</v>
       </c>
@@ -19833,8 +19809,6 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
@@ -19844,7 +19818,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
         <v>431</v>
       </c>
@@ -19860,8 +19834,6 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
@@ -19871,7 +19843,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
         <v>492</v>
       </c>
@@ -19887,8 +19859,6 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -19898,7 +19868,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10" t="s">
         <v>496</v>
       </c>
@@ -19914,8 +19884,6 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -19925,7 +19893,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10" t="s">
         <v>636</v>
       </c>
@@ -19941,8 +19909,6 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
@@ -19952,7 +19918,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -19968,8 +19934,6 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -19979,7 +19943,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
         <v>469</v>
       </c>
@@ -19995,8 +19959,6 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
@@ -20006,7 +19968,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10" t="s">
         <v>447</v>
       </c>
@@ -20022,8 +19984,6 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -20033,7 +19993,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10" t="s">
         <v>182</v>
       </c>
@@ -20049,8 +20009,6 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
@@ -20060,7 +20018,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10" t="s">
         <v>499</v>
       </c>
@@ -20076,8 +20034,6 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
@@ -20087,7 +20043,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="10" t="s">
         <v>199</v>
       </c>
@@ -20103,8 +20059,6 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
@@ -20114,7 +20068,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10" t="s">
         <v>203</v>
       </c>
@@ -20130,8 +20084,6 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
@@ -20141,7 +20093,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
         <v>413</v>
       </c>
@@ -20157,8 +20109,6 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
@@ -20168,7 +20118,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10" t="s">
         <v>503</v>
       </c>
@@ -20184,8 +20134,6 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
@@ -20195,7 +20143,7 @@
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
         <v>445</v>
       </c>
@@ -20211,8 +20159,6 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
@@ -20222,7 +20168,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10" t="s">
         <v>502</v>
       </c>
@@ -20238,8 +20184,6 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
@@ -20249,7 +20193,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10" t="s">
         <v>504</v>
       </c>
@@ -20265,8 +20209,6 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
@@ -20276,7 +20218,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10" t="s">
         <v>451</v>
       </c>
@@ -20292,8 +20234,6 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
@@ -20303,7 +20243,7 @@
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10" t="s">
         <v>486</v>
       </c>
@@ -20319,8 +20259,6 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
@@ -20330,7 +20268,7 @@
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10" t="s">
         <v>506</v>
       </c>
@@ -20346,8 +20284,6 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
@@ -20357,7 +20293,7 @@
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10" t="s">
         <v>423</v>
       </c>
@@ -20373,8 +20309,6 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
@@ -20384,7 +20318,7 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10" t="s">
         <v>132</v>
       </c>
@@ -20400,8 +20334,6 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
@@ -20411,7 +20343,7 @@
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10" t="s">
         <v>276</v>
       </c>
@@ -20427,8 +20359,6 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
@@ -20438,7 +20368,7 @@
       <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10" t="s">
         <v>456</v>
       </c>
@@ -20454,8 +20384,6 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
@@ -20465,7 +20393,7 @@
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10" t="s">
         <v>453</v>
       </c>
@@ -20481,8 +20409,6 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
@@ -20492,7 +20418,7 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10" t="s">
         <v>507</v>
       </c>
@@ -20508,8 +20434,6 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
@@ -20519,7 +20443,7 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10" t="s">
         <v>137</v>
       </c>
@@ -20535,8 +20459,6 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
@@ -20546,7 +20468,7 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10" t="s">
         <v>188</v>
       </c>
@@ -20562,8 +20484,6 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
@@ -20573,7 +20493,7 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10" t="s">
         <v>510</v>
       </c>
@@ -20589,8 +20509,6 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
@@ -20600,7 +20518,7 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10" t="s">
         <v>42</v>
       </c>
@@ -20616,8 +20534,6 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
@@ -20627,7 +20543,7 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10" t="s">
         <v>515</v>
       </c>
@@ -20643,8 +20559,6 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -20654,7 +20568,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10" t="s">
         <v>38</v>
       </c>
@@ -20670,8 +20584,6 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
@@ -20681,7 +20593,7 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10" t="s">
         <v>435</v>
       </c>
@@ -20697,8 +20609,6 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
@@ -20708,7 +20618,7 @@
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10" t="s">
         <v>525</v>
       </c>
@@ -20721,8 +20631,6 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
@@ -20738,8 +20646,6 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
@@ -20755,8 +20661,6 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
@@ -20772,8 +20676,6 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
@@ -20789,8 +20691,6 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
@@ -20806,8 +20706,6 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
@@ -20823,8 +20721,6 @@
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
@@ -20840,8 +20736,6 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
@@ -20857,8 +20751,6 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
@@ -20874,8 +20766,6 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
@@ -20891,8 +20781,6 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
@@ -20908,8 +20796,6 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
@@ -20925,8 +20811,6 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
@@ -20942,8 +20826,6 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
@@ -20959,8 +20841,6 @@
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
@@ -20976,8 +20856,6 @@
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
@@ -20993,8 +20871,6 @@
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
@@ -21010,8 +20886,6 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
@@ -21027,8 +20901,6 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
@@ -21044,8 +20916,6 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
@@ -21061,8 +20931,6 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
@@ -21078,8 +20946,6 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
@@ -21095,8 +20961,6 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
@@ -21112,8 +20976,6 @@
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
@@ -21129,8 +20991,6 @@
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
@@ -21146,8 +21006,6 @@
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
@@ -21163,8 +21021,6 @@
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
@@ -21180,8 +21036,6 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
@@ -21197,8 +21051,6 @@
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
@@ -21214,8 +21066,6 @@
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
@@ -21231,8 +21081,6 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
@@ -21248,8 +21096,6 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
@@ -21265,8 +21111,6 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
@@ -21282,8 +21126,6 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
@@ -21299,8 +21141,6 @@
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
@@ -21316,8 +21156,6 @@
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
@@ -21333,8 +21171,6 @@
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
@@ -21350,8 +21186,6 @@
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
@@ -21367,8 +21201,6 @@
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
@@ -21384,8 +21216,6 @@
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
@@ -21401,8 +21231,6 @@
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
@@ -21418,8 +21246,6 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
@@ -21435,8 +21261,6 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
@@ -21452,8 +21276,6 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
       <c r="J90" s="6"/>
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
@@ -21469,8 +21291,6 @@
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
@@ -21486,8 +21306,6 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
@@ -21503,8 +21321,6 @@
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
@@ -21520,8 +21336,6 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
@@ -21537,8 +21351,6 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
@@ -21554,8 +21366,6 @@
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
@@ -21571,8 +21381,6 @@
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
@@ -21588,8 +21396,6 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
@@ -21605,8 +21411,6 @@
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
@@ -21622,8 +21426,6 @@
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
@@ -21639,8 +21441,6 @@
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
@@ -21656,8 +21456,6 @@
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
@@ -21673,8 +21471,6 @@
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
@@ -21690,8 +21486,6 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
@@ -21707,8 +21501,6 @@
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
       <c r="J105" s="6"/>
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
@@ -21724,8 +21516,6 @@
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
@@ -21741,8 +21531,6 @@
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
@@ -21758,8 +21546,6 @@
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
@@ -21775,8 +21561,6 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
       <c r="J109" s="6"/>
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
@@ -21792,8 +21576,6 @@
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
@@ -21809,8 +21591,6 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
@@ -21826,8 +21606,6 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
       <c r="J112" s="6"/>
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
@@ -21843,8 +21621,6 @@
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
       <c r="J113" s="6"/>
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
@@ -21860,8 +21636,6 @@
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
@@ -21877,8 +21651,6 @@
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
@@ -21894,8 +21666,6 @@
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
@@ -21911,8 +21681,6 @@
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
       <c r="J117" s="6"/>
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
@@ -21928,8 +21696,6 @@
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
@@ -21945,8 +21711,6 @@
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
       <c r="J119" s="6"/>
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
@@ -21962,8 +21726,6 @@
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
       <c r="J120" s="6"/>
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
@@ -21979,8 +21741,6 @@
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
       <c r="J121" s="6"/>
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
@@ -21996,8 +21756,6 @@
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
@@ -22013,8 +21771,6 @@
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
@@ -22030,8 +21786,6 @@
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
       <c r="J124" s="6"/>
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
@@ -22047,8 +21801,6 @@
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
       <c r="J125" s="6"/>
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
@@ -22064,8 +21816,6 @@
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
       <c r="J126" s="6"/>
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
@@ -22081,8 +21831,6 @@
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
       <c r="J127" s="6"/>
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
@@ -22098,8 +21846,6 @@
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
       <c r="J128" s="6"/>
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
@@ -22115,8 +21861,6 @@
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
       <c r="J129" s="6"/>
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
@@ -22132,8 +21876,6 @@
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
       <c r="J130" s="6"/>
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
@@ -22149,8 +21891,6 @@
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
       <c r="J131" s="6"/>
       <c r="K131" s="6"/>
       <c r="L131" s="6"/>
@@ -22166,8 +21906,6 @@
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
@@ -22183,8 +21921,6 @@
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
       <c r="J133" s="6"/>
       <c r="K133" s="6"/>
       <c r="L133" s="6"/>
@@ -22200,8 +21936,6 @@
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
       <c r="J134" s="6"/>
       <c r="K134" s="6"/>
       <c r="L134" s="6"/>
@@ -22217,8 +21951,6 @@
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
       <c r="J135" s="6"/>
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
@@ -22234,8 +21966,6 @@
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
@@ -22251,8 +21981,6 @@
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
       <c r="L137" s="6"/>
@@ -22268,8 +21996,6 @@
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
       <c r="J138" s="6"/>
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
@@ -22285,8 +22011,6 @@
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
       <c r="J139" s="6"/>
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
@@ -22302,8 +22026,6 @@
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
@@ -22319,8 +22041,6 @@
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
@@ -22336,8 +22056,6 @@
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
       <c r="J142" s="6"/>
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
@@ -22353,8 +22071,6 @@
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
@@ -22370,8 +22086,6 @@
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
       <c r="J144" s="6"/>
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
@@ -22387,8 +22101,6 @@
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
       <c r="J145" s="6"/>
       <c r="K145" s="6"/>
       <c r="L145" s="6"/>
@@ -22404,8 +22116,6 @@
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
       <c r="J146" s="6"/>
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
@@ -22421,8 +22131,6 @@
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
       <c r="J147" s="6"/>
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
@@ -22438,8 +22146,6 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
       <c r="J148" s="6"/>
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
@@ -22455,8 +22161,6 @@
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
@@ -22472,8 +22176,6 @@
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
       <c r="J150" s="6"/>
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
@@ -22489,8 +22191,6 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
       <c r="J151" s="6"/>
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
@@ -22506,8 +22206,6 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
@@ -22523,8 +22221,6 @@
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
@@ -22540,8 +22236,6 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
       <c r="J154" s="6"/>
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
@@ -22557,8 +22251,6 @@
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
       <c r="J155" s="6"/>
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
@@ -22574,8 +22266,6 @@
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
@@ -22591,8 +22281,6 @@
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
@@ -22608,8 +22296,6 @@
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
@@ -22625,8 +22311,6 @@
       <c r="E159" s="6"/>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
       <c r="J159" s="6"/>
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
@@ -22642,8 +22326,6 @@
       <c r="E160" s="6"/>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
@@ -22659,8 +22341,6 @@
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
@@ -22676,8 +22356,6 @@
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
@@ -22693,8 +22371,6 @@
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
       <c r="J163" s="6"/>
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
@@ -22710,8 +22386,6 @@
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
       <c r="J164" s="6"/>
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
@@ -22727,8 +22401,6 @@
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
       <c r="J165" s="6"/>
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
@@ -22744,8 +22416,6 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
       <c r="J166" s="6"/>
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
@@ -22761,8 +22431,6 @@
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
       <c r="J167" s="6"/>
       <c r="K167" s="6"/>
       <c r="L167" s="6"/>
@@ -22778,8 +22446,6 @@
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
       <c r="J168" s="6"/>
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
@@ -22795,8 +22461,6 @@
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
       <c r="J169" s="6"/>
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
@@ -22812,8 +22476,6 @@
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
@@ -22829,8 +22491,6 @@
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
       <c r="J171" s="6"/>
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
@@ -22846,8 +22506,6 @@
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
       <c r="J172" s="6"/>
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
@@ -22863,8 +22521,6 @@
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
       <c r="J173" s="6"/>
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
@@ -22880,8 +22536,6 @@
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
@@ -22897,8 +22551,6 @@
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
@@ -22914,8 +22566,6 @@
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
       <c r="J176" s="6"/>
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
@@ -22931,8 +22581,6 @@
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
       <c r="J177" s="6"/>
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
@@ -22948,8 +22596,6 @@
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
@@ -22965,8 +22611,6 @@
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
       <c r="J179" s="6"/>
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
@@ -22982,8 +22626,6 @@
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
@@ -22999,8 +22641,6 @@
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
@@ -23016,8 +22656,6 @@
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
@@ -23033,8 +22671,6 @@
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
@@ -23050,8 +22686,6 @@
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
@@ -23067,8 +22701,6 @@
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
@@ -23084,8 +22716,6 @@
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
@@ -23101,8 +22731,6 @@
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
@@ -23118,8 +22746,6 @@
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
@@ -23135,8 +22761,6 @@
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
@@ -23152,8 +22776,6 @@
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
@@ -23169,8 +22791,6 @@
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
@@ -23186,8 +22806,6 @@
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
@@ -23203,8 +22821,6 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
@@ -23220,8 +22836,6 @@
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
@@ -23237,8 +22851,6 @@
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
@@ -23254,8 +22866,6 @@
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
@@ -23271,8 +22881,6 @@
       <c r="E197" s="6"/>
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
@@ -23288,8 +22896,6 @@
       <c r="E198" s="6"/>
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
@@ -23305,8 +22911,6 @@
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
@@ -23322,8 +22926,6 @@
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
@@ -23339,8 +22941,6 @@
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
@@ -23356,8 +22956,6 @@
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
@@ -23373,8 +22971,6 @@
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
@@ -23390,8 +22986,6 @@
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
@@ -23407,8 +23001,6 @@
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
@@ -23424,8 +23016,6 @@
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
       <c r="J206" s="6"/>
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
@@ -23441,8 +23031,6 @@
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
       <c r="J207" s="6"/>
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
@@ -23458,8 +23046,6 @@
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
       <c r="J208" s="6"/>
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
@@ -23475,8 +23061,6 @@
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
       <c r="J209" s="6"/>
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
@@ -23492,8 +23076,6 @@
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
-      <c r="I210" s="6"/>
       <c r="J210" s="6"/>
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
@@ -23509,8 +23091,6 @@
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
-      <c r="I211" s="6"/>
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
@@ -23526,8 +23106,6 @@
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
-      <c r="I212" s="6"/>
       <c r="J212" s="6"/>
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
@@ -23543,8 +23121,6 @@
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
       <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
@@ -23560,8 +23136,6 @@
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
-      <c r="I214" s="6"/>
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
@@ -23577,8 +23151,6 @@
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
       <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
-      <c r="I215" s="6"/>
       <c r="J215" s="6"/>
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
@@ -23594,8 +23166,6 @@
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
       <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-      <c r="I216" s="6"/>
       <c r="J216" s="6"/>
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
@@ -23611,8 +23181,6 @@
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
       <c r="G217" s="6"/>
-      <c r="H217" s="6"/>
-      <c r="I217" s="6"/>
       <c r="J217" s="6"/>
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
@@ -23628,8 +23196,6 @@
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
       <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
@@ -23645,8 +23211,6 @@
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
       <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
@@ -23662,8 +23226,6 @@
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
       <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
       <c r="J220" s="6"/>
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
@@ -23679,8 +23241,6 @@
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
       <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
       <c r="J221" s="6"/>
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
@@ -23696,8 +23256,6 @@
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
       <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
-      <c r="I222" s="6"/>
       <c r="J222" s="6"/>
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
@@ -23713,8 +23271,6 @@
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
       <c r="G223" s="6"/>
-      <c r="H223" s="6"/>
-      <c r="I223" s="6"/>
       <c r="J223" s="6"/>
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
@@ -23730,8 +23286,6 @@
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
       <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
-      <c r="I224" s="6"/>
       <c r="J224" s="6"/>
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
@@ -23747,8 +23301,6 @@
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
       <c r="G225" s="6"/>
-      <c r="H225" s="6"/>
-      <c r="I225" s="6"/>
       <c r="J225" s="6"/>
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
@@ -23764,8 +23316,6 @@
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
       <c r="G226" s="6"/>
-      <c r="H226" s="6"/>
-      <c r="I226" s="6"/>
       <c r="J226" s="6"/>
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
@@ -23781,8 +23331,6 @@
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
       <c r="G227" s="6"/>
-      <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
       <c r="J227" s="6"/>
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
@@ -23798,8 +23346,6 @@
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
       <c r="G228" s="6"/>
-      <c r="H228" s="6"/>
-      <c r="I228" s="6"/>
       <c r="J228" s="6"/>
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
@@ -23815,8 +23361,6 @@
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
       <c r="G229" s="6"/>
-      <c r="H229" s="6"/>
-      <c r="I229" s="6"/>
       <c r="J229" s="6"/>
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
@@ -23832,8 +23376,6 @@
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
       <c r="G230" s="6"/>
-      <c r="H230" s="6"/>
-      <c r="I230" s="6"/>
       <c r="J230" s="6"/>
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
@@ -23849,8 +23391,6 @@
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
       <c r="G231" s="6"/>
-      <c r="H231" s="6"/>
-      <c r="I231" s="6"/>
       <c r="J231" s="6"/>
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
@@ -23866,8 +23406,6 @@
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
       <c r="G232" s="6"/>
-      <c r="H232" s="6"/>
-      <c r="I232" s="6"/>
       <c r="J232" s="6"/>
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
@@ -23883,8 +23421,6 @@
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
       <c r="G233" s="6"/>
-      <c r="H233" s="6"/>
-      <c r="I233" s="6"/>
       <c r="J233" s="6"/>
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
@@ -23900,8 +23436,6 @@
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
       <c r="G234" s="6"/>
-      <c r="H234" s="6"/>
-      <c r="I234" s="6"/>
       <c r="J234" s="6"/>
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
@@ -23917,8 +23451,6 @@
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
       <c r="G235" s="6"/>
-      <c r="H235" s="6"/>
-      <c r="I235" s="6"/>
       <c r="J235" s="6"/>
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
@@ -23934,8 +23466,6 @@
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
       <c r="G236" s="6"/>
-      <c r="H236" s="6"/>
-      <c r="I236" s="6"/>
       <c r="J236" s="6"/>
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
@@ -23951,8 +23481,6 @@
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
       <c r="G237" s="6"/>
-      <c r="H237" s="6"/>
-      <c r="I237" s="6"/>
       <c r="J237" s="6"/>
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
@@ -23968,8 +23496,6 @@
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
       <c r="G238" s="6"/>
-      <c r="H238" s="6"/>
-      <c r="I238" s="6"/>
       <c r="J238" s="6"/>
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
@@ -23985,8 +23511,6 @@
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
       <c r="G239" s="6"/>
-      <c r="H239" s="6"/>
-      <c r="I239" s="6"/>
       <c r="J239" s="6"/>
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
@@ -24002,8 +23526,6 @@
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
       <c r="G240" s="6"/>
-      <c r="H240" s="6"/>
-      <c r="I240" s="6"/>
       <c r="J240" s="6"/>
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
@@ -24019,8 +23541,6 @@
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
       <c r="G241" s="6"/>
-      <c r="H241" s="6"/>
-      <c r="I241" s="6"/>
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
@@ -24036,8 +23556,6 @@
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
       <c r="G242" s="6"/>
-      <c r="H242" s="6"/>
-      <c r="I242" s="6"/>
       <c r="J242" s="6"/>
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
@@ -24053,8 +23571,6 @@
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
       <c r="G243" s="6"/>
-      <c r="H243" s="6"/>
-      <c r="I243" s="6"/>
       <c r="J243" s="6"/>
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
@@ -24070,8 +23586,6 @@
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
       <c r="G244" s="6"/>
-      <c r="H244" s="6"/>
-      <c r="I244" s="6"/>
       <c r="J244" s="6"/>
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
@@ -24087,8 +23601,6 @@
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
       <c r="G245" s="6"/>
-      <c r="H245" s="6"/>
-      <c r="I245" s="6"/>
       <c r="J245" s="6"/>
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
@@ -24104,8 +23616,6 @@
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
       <c r="G246" s="6"/>
-      <c r="H246" s="6"/>
-      <c r="I246" s="6"/>
       <c r="J246" s="6"/>
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
@@ -24121,8 +23631,6 @@
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
       <c r="G247" s="6"/>
-      <c r="H247" s="6"/>
-      <c r="I247" s="6"/>
       <c r="J247" s="6"/>
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
@@ -24138,8 +23646,6 @@
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
       <c r="G248" s="6"/>
-      <c r="H248" s="6"/>
-      <c r="I248" s="6"/>
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
@@ -24155,8 +23661,6 @@
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
       <c r="G249" s="6"/>
-      <c r="H249" s="6"/>
-      <c r="I249" s="6"/>
       <c r="J249" s="6"/>
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
@@ -24172,8 +23676,6 @@
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
       <c r="G250" s="6"/>
-      <c r="H250" s="6"/>
-      <c r="I250" s="6"/>
       <c r="J250" s="6"/>
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
@@ -24189,8 +23691,6 @@
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
       <c r="G251" s="6"/>
-      <c r="H251" s="6"/>
-      <c r="I251" s="6"/>
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
@@ -24206,8 +23706,6 @@
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
       <c r="G252" s="6"/>
-      <c r="H252" s="6"/>
-      <c r="I252" s="6"/>
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
@@ -24223,8 +23721,6 @@
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
       <c r="G253" s="6"/>
-      <c r="H253" s="6"/>
-      <c r="I253" s="6"/>
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
@@ -24240,8 +23736,6 @@
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
       <c r="G254" s="6"/>
-      <c r="H254" s="6"/>
-      <c r="I254" s="6"/>
       <c r="J254" s="6"/>
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
@@ -24257,8 +23751,6 @@
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
       <c r="G255" s="6"/>
-      <c r="H255" s="6"/>
-      <c r="I255" s="6"/>
       <c r="J255" s="6"/>
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
@@ -24274,8 +23766,6 @@
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
       <c r="G256" s="6"/>
-      <c r="H256" s="6"/>
-      <c r="I256" s="6"/>
       <c r="J256" s="6"/>
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
@@ -24291,8 +23781,6 @@
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
       <c r="G257" s="6"/>
-      <c r="H257" s="6"/>
-      <c r="I257" s="6"/>
       <c r="J257" s="6"/>
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
@@ -24308,8 +23796,6 @@
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
       <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
-      <c r="I258" s="6"/>
       <c r="J258" s="6"/>
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
@@ -24325,8 +23811,6 @@
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
       <c r="G259" s="6"/>
-      <c r="H259" s="6"/>
-      <c r="I259" s="6"/>
       <c r="J259" s="6"/>
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
@@ -24342,8 +23826,6 @@
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
       <c r="G260" s="6"/>
-      <c r="H260" s="6"/>
-      <c r="I260" s="6"/>
       <c r="J260" s="6"/>
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
@@ -24359,8 +23841,6 @@
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
       <c r="G261" s="6"/>
-      <c r="H261" s="6"/>
-      <c r="I261" s="6"/>
       <c r="J261" s="6"/>
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
@@ -24376,8 +23856,6 @@
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
       <c r="G262" s="6"/>
-      <c r="H262" s="6"/>
-      <c r="I262" s="6"/>
       <c r="J262" s="6"/>
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
@@ -24393,8 +23871,6 @@
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
       <c r="G263" s="6"/>
-      <c r="H263" s="6"/>
-      <c r="I263" s="6"/>
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
@@ -24410,8 +23886,6 @@
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
       <c r="G264" s="6"/>
-      <c r="H264" s="6"/>
-      <c r="I264" s="6"/>
       <c r="J264" s="6"/>
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
@@ -24427,8 +23901,6 @@
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
       <c r="G265" s="6"/>
-      <c r="H265" s="6"/>
-      <c r="I265" s="6"/>
       <c r="J265" s="6"/>
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
@@ -24444,8 +23916,6 @@
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
       <c r="G266" s="6"/>
-      <c r="H266" s="6"/>
-      <c r="I266" s="6"/>
       <c r="J266" s="6"/>
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
@@ -24461,8 +23931,6 @@
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
       <c r="G267" s="6"/>
-      <c r="H267" s="6"/>
-      <c r="I267" s="6"/>
       <c r="J267" s="6"/>
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
@@ -24478,8 +23946,6 @@
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
       <c r="G268" s="6"/>
-      <c r="H268" s="6"/>
-      <c r="I268" s="6"/>
       <c r="J268" s="6"/>
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
@@ -24495,8 +23961,6 @@
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
       <c r="G269" s="6"/>
-      <c r="H269" s="6"/>
-      <c r="I269" s="6"/>
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
@@ -24512,8 +23976,6 @@
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
       <c r="G270" s="6"/>
-      <c r="H270" s="6"/>
-      <c r="I270" s="6"/>
       <c r="J270" s="6"/>
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
@@ -24529,8 +23991,6 @@
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
       <c r="G271" s="6"/>
-      <c r="H271" s="6"/>
-      <c r="I271" s="6"/>
       <c r="J271" s="6"/>
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
@@ -24546,8 +24006,6 @@
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
       <c r="G272" s="6"/>
-      <c r="H272" s="6"/>
-      <c r="I272" s="6"/>
       <c r="J272" s="6"/>
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
@@ -24563,8 +24021,6 @@
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
       <c r="G273" s="6"/>
-      <c r="H273" s="6"/>
-      <c r="I273" s="6"/>
       <c r="J273" s="6"/>
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
@@ -24580,8 +24036,6 @@
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
       <c r="G274" s="6"/>
-      <c r="H274" s="6"/>
-      <c r="I274" s="6"/>
       <c r="J274" s="6"/>
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
@@ -24597,8 +24051,6 @@
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
       <c r="G275" s="6"/>
-      <c r="H275" s="6"/>
-      <c r="I275" s="6"/>
       <c r="J275" s="6"/>
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
@@ -24614,8 +24066,6 @@
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
       <c r="G276" s="6"/>
-      <c r="H276" s="6"/>
-      <c r="I276" s="6"/>
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
@@ -24631,8 +24081,6 @@
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
       <c r="G277" s="6"/>
-      <c r="H277" s="6"/>
-      <c r="I277" s="6"/>
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
@@ -24648,8 +24096,6 @@
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
       <c r="G278" s="6"/>
-      <c r="H278" s="6"/>
-      <c r="I278" s="6"/>
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
@@ -24665,8 +24111,6 @@
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
       <c r="G279" s="6"/>
-      <c r="H279" s="6"/>
-      <c r="I279" s="6"/>
       <c r="J279" s="6"/>
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
@@ -24682,8 +24126,6 @@
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
       <c r="G280" s="6"/>
-      <c r="H280" s="6"/>
-      <c r="I280" s="6"/>
       <c r="J280" s="6"/>
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
@@ -24699,8 +24141,6 @@
       <c r="E281" s="6"/>
       <c r="F281" s="6"/>
       <c r="G281" s="6"/>
-      <c r="H281" s="6"/>
-      <c r="I281" s="6"/>
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
@@ -24716,8 +24156,6 @@
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
       <c r="G282" s="6"/>
-      <c r="H282" s="6"/>
-      <c r="I282" s="6"/>
       <c r="J282" s="6"/>
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
@@ -24733,8 +24171,6 @@
       <c r="E283" s="6"/>
       <c r="F283" s="6"/>
       <c r="G283" s="6"/>
-      <c r="H283" s="6"/>
-      <c r="I283" s="6"/>
       <c r="J283" s="6"/>
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
@@ -24750,8 +24186,6 @@
       <c r="E284" s="6"/>
       <c r="F284" s="6"/>
       <c r="G284" s="6"/>
-      <c r="H284" s="6"/>
-      <c r="I284" s="6"/>
       <c r="J284" s="6"/>
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
@@ -24767,8 +24201,6 @@
       <c r="E285" s="6"/>
       <c r="F285" s="6"/>
       <c r="G285" s="6"/>
-      <c r="H285" s="6"/>
-      <c r="I285" s="6"/>
       <c r="J285" s="6"/>
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
@@ -24784,8 +24216,6 @@
       <c r="E286" s="6"/>
       <c r="F286" s="6"/>
       <c r="G286" s="6"/>
-      <c r="H286" s="6"/>
-      <c r="I286" s="6"/>
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
@@ -24801,8 +24231,6 @@
       <c r="E287" s="6"/>
       <c r="F287" s="6"/>
       <c r="G287" s="6"/>
-      <c r="H287" s="6"/>
-      <c r="I287" s="6"/>
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
@@ -24818,8 +24246,6 @@
       <c r="E288" s="6"/>
       <c r="F288" s="6"/>
       <c r="G288" s="6"/>
-      <c r="H288" s="6"/>
-      <c r="I288" s="6"/>
       <c r="J288" s="6"/>
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
@@ -24835,8 +24261,6 @@
       <c r="E289" s="6"/>
       <c r="F289" s="6"/>
       <c r="G289" s="6"/>
-      <c r="H289" s="6"/>
-      <c r="I289" s="6"/>
       <c r="J289" s="6"/>
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
@@ -24852,8 +24276,6 @@
       <c r="E290" s="6"/>
       <c r="F290" s="6"/>
       <c r="G290" s="6"/>
-      <c r="H290" s="6"/>
-      <c r="I290" s="6"/>
       <c r="J290" s="6"/>
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
@@ -24869,8 +24291,6 @@
       <c r="E291" s="6"/>
       <c r="F291" s="6"/>
       <c r="G291" s="6"/>
-      <c r="H291" s="6"/>
-      <c r="I291" s="6"/>
       <c r="J291" s="6"/>
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
@@ -24886,8 +24306,6 @@
       <c r="E292" s="6"/>
       <c r="F292" s="6"/>
       <c r="G292" s="6"/>
-      <c r="H292" s="6"/>
-      <c r="I292" s="6"/>
       <c r="J292" s="6"/>
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
@@ -24903,8 +24321,6 @@
       <c r="E293" s="6"/>
       <c r="F293" s="6"/>
       <c r="G293" s="6"/>
-      <c r="H293" s="6"/>
-      <c r="I293" s="6"/>
       <c r="J293" s="6"/>
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
@@ -24920,8 +24336,6 @@
       <c r="E294" s="6"/>
       <c r="F294" s="6"/>
       <c r="G294" s="6"/>
-      <c r="H294" s="6"/>
-      <c r="I294" s="6"/>
       <c r="J294" s="6"/>
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
@@ -24937,8 +24351,6 @@
       <c r="E295" s="6"/>
       <c r="F295" s="6"/>
       <c r="G295" s="6"/>
-      <c r="H295" s="6"/>
-      <c r="I295" s="6"/>
       <c r="J295" s="6"/>
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
@@ -24954,8 +24366,6 @@
       <c r="E296" s="6"/>
       <c r="F296" s="6"/>
       <c r="G296" s="6"/>
-      <c r="H296" s="6"/>
-      <c r="I296" s="6"/>
       <c r="J296" s="6"/>
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
@@ -24971,8 +24381,6 @@
       <c r="E297" s="6"/>
       <c r="F297" s="6"/>
       <c r="G297" s="6"/>
-      <c r="H297" s="6"/>
-      <c r="I297" s="6"/>
       <c r="J297" s="6"/>
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
@@ -24988,8 +24396,6 @@
       <c r="E298" s="6"/>
       <c r="F298" s="6"/>
       <c r="G298" s="6"/>
-      <c r="H298" s="6"/>
-      <c r="I298" s="6"/>
       <c r="J298" s="6"/>
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
@@ -25005,8 +24411,6 @@
       <c r="E299" s="6"/>
       <c r="F299" s="6"/>
       <c r="G299" s="6"/>
-      <c r="H299" s="6"/>
-      <c r="I299" s="6"/>
       <c r="J299" s="6"/>
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
@@ -25022,8 +24426,6 @@
       <c r="E300" s="6"/>
       <c r="F300" s="6"/>
       <c r="G300" s="6"/>
-      <c r="H300" s="6"/>
-      <c r="I300" s="6"/>
       <c r="J300" s="6"/>
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
@@ -25039,8 +24441,6 @@
       <c r="E301" s="6"/>
       <c r="F301" s="6"/>
       <c r="G301" s="6"/>
-      <c r="H301" s="6"/>
-      <c r="I301" s="6"/>
       <c r="J301" s="6"/>
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
@@ -25056,8 +24456,6 @@
       <c r="E302" s="6"/>
       <c r="F302" s="6"/>
       <c r="G302" s="6"/>
-      <c r="H302" s="6"/>
-      <c r="I302" s="6"/>
       <c r="J302" s="6"/>
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
@@ -25073,8 +24471,6 @@
       <c r="E303" s="6"/>
       <c r="F303" s="6"/>
       <c r="G303" s="6"/>
-      <c r="H303" s="6"/>
-      <c r="I303" s="6"/>
       <c r="J303" s="6"/>
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
@@ -25090,8 +24486,6 @@
       <c r="E304" s="6"/>
       <c r="F304" s="6"/>
       <c r="G304" s="6"/>
-      <c r="H304" s="6"/>
-      <c r="I304" s="6"/>
       <c r="J304" s="6"/>
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
@@ -25107,8 +24501,6 @@
       <c r="E305" s="6"/>
       <c r="F305" s="6"/>
       <c r="G305" s="6"/>
-      <c r="H305" s="6"/>
-      <c r="I305" s="6"/>
       <c r="J305" s="6"/>
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
@@ -25124,8 +24516,6 @@
       <c r="E306" s="6"/>
       <c r="F306" s="6"/>
       <c r="G306" s="6"/>
-      <c r="H306" s="6"/>
-      <c r="I306" s="6"/>
       <c r="J306" s="6"/>
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
@@ -25141,8 +24531,6 @@
       <c r="E307" s="6"/>
       <c r="F307" s="6"/>
       <c r="G307" s="6"/>
-      <c r="H307" s="6"/>
-      <c r="I307" s="6"/>
       <c r="J307" s="6"/>
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
@@ -25158,8 +24546,6 @@
       <c r="E308" s="6"/>
       <c r="F308" s="6"/>
       <c r="G308" s="6"/>
-      <c r="H308" s="6"/>
-      <c r="I308" s="6"/>
       <c r="J308" s="6"/>
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
@@ -25175,8 +24561,6 @@
       <c r="E309" s="6"/>
       <c r="F309" s="6"/>
       <c r="G309" s="6"/>
-      <c r="H309" s="6"/>
-      <c r="I309" s="6"/>
       <c r="J309" s="6"/>
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
@@ -25192,8 +24576,6 @@
       <c r="E310" s="6"/>
       <c r="F310" s="6"/>
       <c r="G310" s="6"/>
-      <c r="H310" s="6"/>
-      <c r="I310" s="6"/>
       <c r="J310" s="6"/>
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
@@ -25209,8 +24591,6 @@
       <c r="E311" s="6"/>
       <c r="F311" s="6"/>
       <c r="G311" s="6"/>
-      <c r="H311" s="6"/>
-      <c r="I311" s="6"/>
       <c r="J311" s="6"/>
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
@@ -25226,8 +24606,6 @@
       <c r="E312" s="6"/>
       <c r="F312" s="6"/>
       <c r="G312" s="6"/>
-      <c r="H312" s="6"/>
-      <c r="I312" s="6"/>
       <c r="J312" s="6"/>
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
@@ -25243,8 +24621,6 @@
       <c r="E313" s="6"/>
       <c r="F313" s="6"/>
       <c r="G313" s="6"/>
-      <c r="H313" s="6"/>
-      <c r="I313" s="6"/>
       <c r="J313" s="6"/>
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
@@ -25260,8 +24636,6 @@
       <c r="E314" s="6"/>
       <c r="F314" s="6"/>
       <c r="G314" s="6"/>
-      <c r="H314" s="6"/>
-      <c r="I314" s="6"/>
       <c r="J314" s="6"/>
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
@@ -25277,8 +24651,6 @@
       <c r="E315" s="6"/>
       <c r="F315" s="6"/>
       <c r="G315" s="6"/>
-      <c r="H315" s="6"/>
-      <c r="I315" s="6"/>
       <c r="J315" s="6"/>
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
@@ -25294,8 +24666,6 @@
       <c r="E316" s="6"/>
       <c r="F316" s="6"/>
       <c r="G316" s="6"/>
-      <c r="H316" s="6"/>
-      <c r="I316" s="6"/>
       <c r="J316" s="6"/>
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
@@ -25311,8 +24681,6 @@
       <c r="E317" s="6"/>
       <c r="F317" s="6"/>
       <c r="G317" s="6"/>
-      <c r="H317" s="6"/>
-      <c r="I317" s="6"/>
       <c r="J317" s="6"/>
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
@@ -25328,8 +24696,6 @@
       <c r="E318" s="6"/>
       <c r="F318" s="6"/>
       <c r="G318" s="6"/>
-      <c r="H318" s="6"/>
-      <c r="I318" s="6"/>
       <c r="J318" s="6"/>
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
@@ -25345,8 +24711,6 @@
       <c r="E319" s="6"/>
       <c r="F319" s="6"/>
       <c r="G319" s="6"/>
-      <c r="H319" s="6"/>
-      <c r="I319" s="6"/>
       <c r="J319" s="6"/>
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
@@ -25362,8 +24726,6 @@
       <c r="E320" s="6"/>
       <c r="F320" s="6"/>
       <c r="G320" s="6"/>
-      <c r="H320" s="6"/>
-      <c r="I320" s="6"/>
       <c r="J320" s="6"/>
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
@@ -25379,8 +24741,6 @@
       <c r="E321" s="6"/>
       <c r="F321" s="6"/>
       <c r="G321" s="6"/>
-      <c r="H321" s="6"/>
-      <c r="I321" s="6"/>
       <c r="J321" s="6"/>
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
@@ -25396,8 +24756,6 @@
       <c r="E322" s="6"/>
       <c r="F322" s="6"/>
       <c r="G322" s="6"/>
-      <c r="H322" s="6"/>
-      <c r="I322" s="6"/>
       <c r="J322" s="6"/>
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
@@ -25413,8 +24771,6 @@
       <c r="E323" s="6"/>
       <c r="F323" s="6"/>
       <c r="G323" s="6"/>
-      <c r="H323" s="6"/>
-      <c r="I323" s="6"/>
       <c r="J323" s="6"/>
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
@@ -25430,8 +24786,6 @@
       <c r="E324" s="6"/>
       <c r="F324" s="6"/>
       <c r="G324" s="6"/>
-      <c r="H324" s="6"/>
-      <c r="I324" s="6"/>
       <c r="J324" s="6"/>
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
@@ -25447,8 +24801,6 @@
       <c r="E325" s="6"/>
       <c r="F325" s="6"/>
       <c r="G325" s="6"/>
-      <c r="H325" s="6"/>
-      <c r="I325" s="6"/>
       <c r="J325" s="6"/>
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
@@ -25464,8 +24816,6 @@
       <c r="E326" s="6"/>
       <c r="F326" s="6"/>
       <c r="G326" s="6"/>
-      <c r="H326" s="6"/>
-      <c r="I326" s="6"/>
       <c r="J326" s="6"/>
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
@@ -25481,8 +24831,6 @@
       <c r="E327" s="6"/>
       <c r="F327" s="6"/>
       <c r="G327" s="6"/>
-      <c r="H327" s="6"/>
-      <c r="I327" s="6"/>
       <c r="J327" s="6"/>
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
@@ -25498,8 +24846,6 @@
       <c r="E328" s="6"/>
       <c r="F328" s="6"/>
       <c r="G328" s="6"/>
-      <c r="H328" s="6"/>
-      <c r="I328" s="6"/>
       <c r="J328" s="6"/>
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
@@ -25515,8 +24861,6 @@
       <c r="E329" s="6"/>
       <c r="F329" s="6"/>
       <c r="G329" s="6"/>
-      <c r="H329" s="6"/>
-      <c r="I329" s="6"/>
       <c r="J329" s="6"/>
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
@@ -25532,8 +24876,6 @@
       <c r="E330" s="6"/>
       <c r="F330" s="6"/>
       <c r="G330" s="6"/>
-      <c r="H330" s="6"/>
-      <c r="I330" s="6"/>
       <c r="J330" s="6"/>
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
@@ -25549,8 +24891,6 @@
       <c r="E331" s="6"/>
       <c r="F331" s="6"/>
       <c r="G331" s="6"/>
-      <c r="H331" s="6"/>
-      <c r="I331" s="6"/>
       <c r="J331" s="6"/>
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
@@ -25566,8 +24906,6 @@
       <c r="E332" s="6"/>
       <c r="F332" s="6"/>
       <c r="G332" s="6"/>
-      <c r="H332" s="6"/>
-      <c r="I332" s="6"/>
       <c r="J332" s="6"/>
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
@@ -25583,8 +24921,6 @@
       <c r="E333" s="6"/>
       <c r="F333" s="6"/>
       <c r="G333" s="6"/>
-      <c r="H333" s="6"/>
-      <c r="I333" s="6"/>
       <c r="J333" s="6"/>
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
@@ -25600,8 +24936,6 @@
       <c r="E334" s="6"/>
       <c r="F334" s="6"/>
       <c r="G334" s="6"/>
-      <c r="H334" s="6"/>
-      <c r="I334" s="6"/>
       <c r="J334" s="6"/>
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
@@ -25617,8 +24951,6 @@
       <c r="E335" s="6"/>
       <c r="F335" s="6"/>
       <c r="G335" s="6"/>
-      <c r="H335" s="6"/>
-      <c r="I335" s="6"/>
       <c r="J335" s="6"/>
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
@@ -25634,8 +24966,6 @@
       <c r="E336" s="6"/>
       <c r="F336" s="6"/>
       <c r="G336" s="6"/>
-      <c r="H336" s="6"/>
-      <c r="I336" s="6"/>
       <c r="J336" s="6"/>
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
@@ -25651,8 +24981,6 @@
       <c r="E337" s="6"/>
       <c r="F337" s="6"/>
       <c r="G337" s="6"/>
-      <c r="H337" s="6"/>
-      <c r="I337" s="6"/>
       <c r="J337" s="6"/>
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
@@ -25668,8 +24996,6 @@
       <c r="E338" s="6"/>
       <c r="F338" s="6"/>
       <c r="G338" s="6"/>
-      <c r="H338" s="6"/>
-      <c r="I338" s="6"/>
       <c r="J338" s="6"/>
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
@@ -25685,8 +25011,6 @@
       <c r="E339" s="6"/>
       <c r="F339" s="6"/>
       <c r="G339" s="6"/>
-      <c r="H339" s="6"/>
-      <c r="I339" s="6"/>
       <c r="J339" s="6"/>
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
@@ -25702,8 +25026,6 @@
       <c r="E340" s="6"/>
       <c r="F340" s="6"/>
       <c r="G340" s="6"/>
-      <c r="H340" s="6"/>
-      <c r="I340" s="6"/>
       <c r="J340" s="6"/>
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
@@ -25719,8 +25041,6 @@
       <c r="E341" s="6"/>
       <c r="F341" s="6"/>
       <c r="G341" s="6"/>
-      <c r="H341" s="6"/>
-      <c r="I341" s="6"/>
       <c r="J341" s="6"/>
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
@@ -25736,8 +25056,6 @@
       <c r="E342" s="6"/>
       <c r="F342" s="6"/>
       <c r="G342" s="6"/>
-      <c r="H342" s="6"/>
-      <c r="I342" s="6"/>
       <c r="J342" s="6"/>
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
@@ -25753,8 +25071,6 @@
       <c r="E343" s="6"/>
       <c r="F343" s="6"/>
       <c r="G343" s="6"/>
-      <c r="H343" s="6"/>
-      <c r="I343" s="6"/>
       <c r="J343" s="6"/>
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
@@ -25770,8 +25086,6 @@
       <c r="E344" s="6"/>
       <c r="F344" s="6"/>
       <c r="G344" s="6"/>
-      <c r="H344" s="6"/>
-      <c r="I344" s="6"/>
       <c r="J344" s="6"/>
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
@@ -25787,8 +25101,6 @@
       <c r="E345" s="6"/>
       <c r="F345" s="6"/>
       <c r="G345" s="6"/>
-      <c r="H345" s="6"/>
-      <c r="I345" s="6"/>
       <c r="J345" s="6"/>
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
@@ -25804,8 +25116,6 @@
       <c r="E346" s="6"/>
       <c r="F346" s="6"/>
       <c r="G346" s="6"/>
-      <c r="H346" s="6"/>
-      <c r="I346" s="6"/>
       <c r="J346" s="6"/>
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
@@ -25821,8 +25131,6 @@
       <c r="E347" s="6"/>
       <c r="F347" s="6"/>
       <c r="G347" s="6"/>
-      <c r="H347" s="6"/>
-      <c r="I347" s="6"/>
       <c r="J347" s="6"/>
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
@@ -25838,8 +25146,6 @@
       <c r="E348" s="6"/>
       <c r="F348" s="6"/>
       <c r="G348" s="6"/>
-      <c r="H348" s="6"/>
-      <c r="I348" s="6"/>
       <c r="J348" s="6"/>
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
@@ -25855,8 +25161,6 @@
       <c r="E349" s="6"/>
       <c r="F349" s="6"/>
       <c r="G349" s="6"/>
-      <c r="H349" s="6"/>
-      <c r="I349" s="6"/>
       <c r="J349" s="6"/>
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
@@ -25872,8 +25176,6 @@
       <c r="E350" s="6"/>
       <c r="F350" s="6"/>
       <c r="G350" s="6"/>
-      <c r="H350" s="6"/>
-      <c r="I350" s="6"/>
       <c r="J350" s="6"/>
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
@@ -25889,8 +25191,6 @@
       <c r="E351" s="6"/>
       <c r="F351" s="6"/>
       <c r="G351" s="6"/>
-      <c r="H351" s="6"/>
-      <c r="I351" s="6"/>
       <c r="J351" s="6"/>
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
@@ -25906,8 +25206,6 @@
       <c r="E352" s="6"/>
       <c r="F352" s="6"/>
       <c r="G352" s="6"/>
-      <c r="H352" s="6"/>
-      <c r="I352" s="6"/>
       <c r="J352" s="6"/>
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
@@ -25923,8 +25221,6 @@
       <c r="E353" s="6"/>
       <c r="F353" s="6"/>
       <c r="G353" s="6"/>
-      <c r="H353" s="6"/>
-      <c r="I353" s="6"/>
       <c r="J353" s="6"/>
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
@@ -25940,8 +25236,6 @@
       <c r="E354" s="6"/>
       <c r="F354" s="6"/>
       <c r="G354" s="6"/>
-      <c r="H354" s="6"/>
-      <c r="I354" s="6"/>
       <c r="J354" s="6"/>
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
@@ -25957,8 +25251,6 @@
       <c r="E355" s="6"/>
       <c r="F355" s="6"/>
       <c r="G355" s="6"/>
-      <c r="H355" s="6"/>
-      <c r="I355" s="6"/>
       <c r="J355" s="6"/>
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
@@ -25974,8 +25266,6 @@
       <c r="E356" s="6"/>
       <c r="F356" s="6"/>
       <c r="G356" s="6"/>
-      <c r="H356" s="6"/>
-      <c r="I356" s="6"/>
       <c r="J356" s="6"/>
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
@@ -25991,8 +25281,6 @@
       <c r="E357" s="6"/>
       <c r="F357" s="6"/>
       <c r="G357" s="6"/>
-      <c r="H357" s="6"/>
-      <c r="I357" s="6"/>
       <c r="J357" s="6"/>
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
@@ -26008,8 +25296,6 @@
       <c r="E358" s="6"/>
       <c r="F358" s="6"/>
       <c r="G358" s="6"/>
-      <c r="H358" s="6"/>
-      <c r="I358" s="6"/>
       <c r="J358" s="6"/>
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
@@ -26025,8 +25311,6 @@
       <c r="E359" s="6"/>
       <c r="F359" s="6"/>
       <c r="G359" s="6"/>
-      <c r="H359" s="6"/>
-      <c r="I359" s="6"/>
       <c r="J359" s="6"/>
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
@@ -26042,8 +25326,6 @@
       <c r="E360" s="6"/>
       <c r="F360" s="6"/>
       <c r="G360" s="6"/>
-      <c r="H360" s="6"/>
-      <c r="I360" s="6"/>
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
@@ -26059,8 +25341,6 @@
       <c r="E361" s="6"/>
       <c r="F361" s="6"/>
       <c r="G361" s="6"/>
-      <c r="H361" s="6"/>
-      <c r="I361" s="6"/>
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
@@ -26076,8 +25356,6 @@
       <c r="E362" s="6"/>
       <c r="F362" s="6"/>
       <c r="G362" s="6"/>
-      <c r="H362" s="6"/>
-      <c r="I362" s="6"/>
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
@@ -26093,8 +25371,6 @@
       <c r="E363" s="6"/>
       <c r="F363" s="6"/>
       <c r="G363" s="6"/>
-      <c r="H363" s="6"/>
-      <c r="I363" s="6"/>
       <c r="J363" s="6"/>
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
@@ -26110,8 +25386,6 @@
       <c r="E364" s="6"/>
       <c r="F364" s="6"/>
       <c r="G364" s="6"/>
-      <c r="H364" s="6"/>
-      <c r="I364" s="6"/>
       <c r="J364" s="6"/>
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
@@ -26127,8 +25401,6 @@
       <c r="E365" s="6"/>
       <c r="F365" s="6"/>
       <c r="G365" s="6"/>
-      <c r="H365" s="6"/>
-      <c r="I365" s="6"/>
       <c r="J365" s="6"/>
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
@@ -26144,8 +25416,6 @@
       <c r="E366" s="6"/>
       <c r="F366" s="6"/>
       <c r="G366" s="6"/>
-      <c r="H366" s="6"/>
-      <c r="I366" s="6"/>
       <c r="J366" s="6"/>
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
@@ -26161,8 +25431,6 @@
       <c r="E367" s="6"/>
       <c r="F367" s="6"/>
       <c r="G367" s="6"/>
-      <c r="H367" s="6"/>
-      <c r="I367" s="6"/>
       <c r="J367" s="6"/>
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
@@ -26178,8 +25446,6 @@
       <c r="E368" s="6"/>
       <c r="F368" s="6"/>
       <c r="G368" s="6"/>
-      <c r="H368" s="6"/>
-      <c r="I368" s="6"/>
       <c r="J368" s="6"/>
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
@@ -26195,8 +25461,6 @@
       <c r="E369" s="6"/>
       <c r="F369" s="6"/>
       <c r="G369" s="6"/>
-      <c r="H369" s="6"/>
-      <c r="I369" s="6"/>
       <c r="J369" s="6"/>
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
@@ -26212,8 +25476,6 @@
       <c r="E370" s="6"/>
       <c r="F370" s="6"/>
       <c r="G370" s="6"/>
-      <c r="H370" s="6"/>
-      <c r="I370" s="6"/>
       <c r="J370" s="6"/>
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
@@ -26229,8 +25491,6 @@
       <c r="E371" s="6"/>
       <c r="F371" s="6"/>
       <c r="G371" s="6"/>
-      <c r="H371" s="6"/>
-      <c r="I371" s="6"/>
       <c r="J371" s="6"/>
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
@@ -26246,8 +25506,6 @@
       <c r="E372" s="6"/>
       <c r="F372" s="6"/>
       <c r="G372" s="6"/>
-      <c r="H372" s="6"/>
-      <c r="I372" s="6"/>
       <c r="J372" s="6"/>
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
@@ -26263,8 +25521,6 @@
       <c r="E373" s="6"/>
       <c r="F373" s="6"/>
       <c r="G373" s="6"/>
-      <c r="H373" s="6"/>
-      <c r="I373" s="6"/>
       <c r="J373" s="6"/>
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
@@ -26280,8 +25536,6 @@
       <c r="E374" s="6"/>
       <c r="F374" s="6"/>
       <c r="G374" s="6"/>
-      <c r="H374" s="6"/>
-      <c r="I374" s="6"/>
       <c r="J374" s="6"/>
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
@@ -26297,8 +25551,6 @@
       <c r="E375" s="6"/>
       <c r="F375" s="6"/>
       <c r="G375" s="6"/>
-      <c r="H375" s="6"/>
-      <c r="I375" s="6"/>
       <c r="J375" s="6"/>
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
@@ -26314,8 +25566,6 @@
       <c r="E376" s="6"/>
       <c r="F376" s="6"/>
       <c r="G376" s="6"/>
-      <c r="H376" s="6"/>
-      <c r="I376" s="6"/>
       <c r="J376" s="6"/>
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
@@ -26331,8 +25581,6 @@
       <c r="E377" s="6"/>
       <c r="F377" s="6"/>
       <c r="G377" s="6"/>
-      <c r="H377" s="6"/>
-      <c r="I377" s="6"/>
       <c r="J377" s="6"/>
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
@@ -26348,8 +25596,6 @@
       <c r="E378" s="6"/>
       <c r="F378" s="6"/>
       <c r="G378" s="6"/>
-      <c r="H378" s="6"/>
-      <c r="I378" s="6"/>
       <c r="J378" s="6"/>
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
@@ -26365,8 +25611,6 @@
       <c r="E379" s="6"/>
       <c r="F379" s="6"/>
       <c r="G379" s="6"/>
-      <c r="H379" s="6"/>
-      <c r="I379" s="6"/>
       <c r="J379" s="6"/>
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
@@ -26382,8 +25626,6 @@
       <c r="E380" s="6"/>
       <c r="F380" s="6"/>
       <c r="G380" s="6"/>
-      <c r="H380" s="6"/>
-      <c r="I380" s="6"/>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
@@ -26399,8 +25641,6 @@
       <c r="E381" s="6"/>
       <c r="F381" s="6"/>
       <c r="G381" s="6"/>
-      <c r="H381" s="6"/>
-      <c r="I381" s="6"/>
       <c r="J381" s="6"/>
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
@@ -26416,8 +25656,6 @@
       <c r="E382" s="6"/>
       <c r="F382" s="6"/>
       <c r="G382" s="6"/>
-      <c r="H382" s="6"/>
-      <c r="I382" s="6"/>
       <c r="J382" s="6"/>
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
@@ -26433,8 +25671,6 @@
       <c r="E383" s="6"/>
       <c r="F383" s="6"/>
       <c r="G383" s="6"/>
-      <c r="H383" s="6"/>
-      <c r="I383" s="6"/>
       <c r="J383" s="6"/>
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
@@ -26450,8 +25686,6 @@
       <c r="E384" s="6"/>
       <c r="F384" s="6"/>
       <c r="G384" s="6"/>
-      <c r="H384" s="6"/>
-      <c r="I384" s="6"/>
       <c r="J384" s="6"/>
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
@@ -26467,8 +25701,6 @@
       <c r="E385" s="6"/>
       <c r="F385" s="6"/>
       <c r="G385" s="6"/>
-      <c r="H385" s="6"/>
-      <c r="I385" s="6"/>
       <c r="J385" s="6"/>
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
@@ -26484,8 +25716,6 @@
       <c r="E386" s="6"/>
       <c r="F386" s="6"/>
       <c r="G386" s="6"/>
-      <c r="H386" s="6"/>
-      <c r="I386" s="6"/>
       <c r="J386" s="6"/>
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
@@ -26501,8 +25731,6 @@
       <c r="E387" s="6"/>
       <c r="F387" s="6"/>
       <c r="G387" s="6"/>
-      <c r="H387" s="6"/>
-      <c r="I387" s="6"/>
       <c r="J387" s="6"/>
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
@@ -26518,8 +25746,6 @@
       <c r="E388" s="6"/>
       <c r="F388" s="6"/>
       <c r="G388" s="6"/>
-      <c r="H388" s="6"/>
-      <c r="I388" s="6"/>
       <c r="J388" s="6"/>
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
@@ -26535,8 +25761,6 @@
       <c r="E389" s="6"/>
       <c r="F389" s="6"/>
       <c r="G389" s="6"/>
-      <c r="H389" s="6"/>
-      <c r="I389" s="6"/>
       <c r="J389" s="6"/>
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
@@ -26552,8 +25776,6 @@
       <c r="E390" s="6"/>
       <c r="F390" s="6"/>
       <c r="G390" s="6"/>
-      <c r="H390" s="6"/>
-      <c r="I390" s="6"/>
       <c r="J390" s="6"/>
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
@@ -26569,8 +25791,6 @@
       <c r="E391" s="6"/>
       <c r="F391" s="6"/>
       <c r="G391" s="6"/>
-      <c r="H391" s="6"/>
-      <c r="I391" s="6"/>
       <c r="J391" s="6"/>
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
@@ -26586,8 +25806,6 @@
       <c r="E392" s="6"/>
       <c r="F392" s="6"/>
       <c r="G392" s="6"/>
-      <c r="H392" s="6"/>
-      <c r="I392" s="6"/>
       <c r="J392" s="6"/>
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
@@ -26603,8 +25821,6 @@
       <c r="E393" s="6"/>
       <c r="F393" s="6"/>
       <c r="G393" s="6"/>
-      <c r="H393" s="6"/>
-      <c r="I393" s="6"/>
       <c r="J393" s="6"/>
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
@@ -26620,8 +25836,6 @@
       <c r="E394" s="6"/>
       <c r="F394" s="6"/>
       <c r="G394" s="6"/>
-      <c r="H394" s="6"/>
-      <c r="I394" s="6"/>
       <c r="J394" s="6"/>
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
@@ -26637,8 +25851,6 @@
       <c r="E395" s="6"/>
       <c r="F395" s="6"/>
       <c r="G395" s="6"/>
-      <c r="H395" s="6"/>
-      <c r="I395" s="6"/>
       <c r="J395" s="6"/>
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
@@ -26654,8 +25866,6 @@
       <c r="E396" s="6"/>
       <c r="F396" s="6"/>
       <c r="G396" s="6"/>
-      <c r="H396" s="6"/>
-      <c r="I396" s="6"/>
       <c r="J396" s="6"/>
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
@@ -26671,8 +25881,6 @@
       <c r="E397" s="6"/>
       <c r="F397" s="6"/>
       <c r="G397" s="6"/>
-      <c r="H397" s="6"/>
-      <c r="I397" s="6"/>
       <c r="J397" s="6"/>
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
@@ -26688,8 +25896,6 @@
       <c r="E398" s="6"/>
       <c r="F398" s="6"/>
       <c r="G398" s="6"/>
-      <c r="H398" s="6"/>
-      <c r="I398" s="6"/>
       <c r="J398" s="6"/>
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
@@ -26705,8 +25911,6 @@
       <c r="E399" s="6"/>
       <c r="F399" s="6"/>
       <c r="G399" s="6"/>
-      <c r="H399" s="6"/>
-      <c r="I399" s="6"/>
       <c r="J399" s="6"/>
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
@@ -26722,8 +25926,6 @@
       <c r="E400" s="6"/>
       <c r="F400" s="6"/>
       <c r="G400" s="6"/>
-      <c r="H400" s="6"/>
-      <c r="I400" s="6"/>
       <c r="J400" s="6"/>
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
@@ -26739,8 +25941,6 @@
       <c r="E401" s="6"/>
       <c r="F401" s="6"/>
       <c r="G401" s="6"/>
-      <c r="H401" s="6"/>
-      <c r="I401" s="6"/>
       <c r="J401" s="6"/>
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
@@ -26756,8 +25956,6 @@
       <c r="E402" s="6"/>
       <c r="F402" s="6"/>
       <c r="G402" s="6"/>
-      <c r="H402" s="6"/>
-      <c r="I402" s="6"/>
       <c r="J402" s="6"/>
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
@@ -26773,8 +25971,6 @@
       <c r="E403" s="6"/>
       <c r="F403" s="6"/>
       <c r="G403" s="6"/>
-      <c r="H403" s="6"/>
-      <c r="I403" s="6"/>
       <c r="J403" s="6"/>
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
@@ -26790,8 +25986,6 @@
       <c r="E404" s="6"/>
       <c r="F404" s="6"/>
       <c r="G404" s="6"/>
-      <c r="H404" s="6"/>
-      <c r="I404" s="6"/>
       <c r="J404" s="6"/>
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
@@ -26807,8 +26001,6 @@
       <c r="E405" s="6"/>
       <c r="F405" s="6"/>
       <c r="G405" s="6"/>
-      <c r="H405" s="6"/>
-      <c r="I405" s="6"/>
       <c r="J405" s="6"/>
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
@@ -26824,8 +26016,6 @@
       <c r="E406" s="6"/>
       <c r="F406" s="6"/>
       <c r="G406" s="6"/>
-      <c r="H406" s="6"/>
-      <c r="I406" s="6"/>
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
@@ -26841,8 +26031,6 @@
       <c r="E407" s="6"/>
       <c r="F407" s="6"/>
       <c r="G407" s="6"/>
-      <c r="H407" s="6"/>
-      <c r="I407" s="6"/>
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
@@ -26858,8 +26046,6 @@
       <c r="E408" s="6"/>
       <c r="F408" s="6"/>
       <c r="G408" s="6"/>
-      <c r="H408" s="6"/>
-      <c r="I408" s="6"/>
       <c r="J408" s="6"/>
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
@@ -26875,8 +26061,6 @@
       <c r="E409" s="6"/>
       <c r="F409" s="6"/>
       <c r="G409" s="6"/>
-      <c r="H409" s="6"/>
-      <c r="I409" s="6"/>
       <c r="J409" s="6"/>
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
@@ -26892,8 +26076,6 @@
       <c r="E410" s="6"/>
       <c r="F410" s="6"/>
       <c r="G410" s="6"/>
-      <c r="H410" s="6"/>
-      <c r="I410" s="6"/>
       <c r="J410" s="6"/>
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
@@ -26909,8 +26091,6 @@
       <c r="E411" s="6"/>
       <c r="F411" s="6"/>
       <c r="G411" s="6"/>
-      <c r="H411" s="6"/>
-      <c r="I411" s="6"/>
       <c r="J411" s="6"/>
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
@@ -26926,8 +26106,6 @@
       <c r="E412" s="6"/>
       <c r="F412" s="6"/>
       <c r="G412" s="6"/>
-      <c r="H412" s="6"/>
-      <c r="I412" s="6"/>
       <c r="J412" s="6"/>
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
@@ -26943,8 +26121,6 @@
       <c r="E413" s="6"/>
       <c r="F413" s="6"/>
       <c r="G413" s="6"/>
-      <c r="H413" s="6"/>
-      <c r="I413" s="6"/>
       <c r="J413" s="6"/>
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
@@ -26960,8 +26136,6 @@
       <c r="E414" s="6"/>
       <c r="F414" s="6"/>
       <c r="G414" s="6"/>
-      <c r="H414" s="6"/>
-      <c r="I414" s="6"/>
       <c r="J414" s="6"/>
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
@@ -26977,8 +26151,6 @@
       <c r="E415" s="6"/>
       <c r="F415" s="6"/>
       <c r="G415" s="6"/>
-      <c r="H415" s="6"/>
-      <c r="I415" s="6"/>
       <c r="J415" s="6"/>
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
@@ -26994,8 +26166,6 @@
       <c r="E416" s="6"/>
       <c r="F416" s="6"/>
       <c r="G416" s="6"/>
-      <c r="H416" s="6"/>
-      <c r="I416" s="6"/>
       <c r="J416" s="6"/>
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
@@ -27011,8 +26181,6 @@
       <c r="E417" s="6"/>
       <c r="F417" s="6"/>
       <c r="G417" s="6"/>
-      <c r="H417" s="6"/>
-      <c r="I417" s="6"/>
       <c r="J417" s="6"/>
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
@@ -27028,8 +26196,6 @@
       <c r="E418" s="6"/>
       <c r="F418" s="6"/>
       <c r="G418" s="6"/>
-      <c r="H418" s="6"/>
-      <c r="I418" s="6"/>
       <c r="J418" s="6"/>
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
@@ -27045,8 +26211,6 @@
       <c r="E419" s="6"/>
       <c r="F419" s="6"/>
       <c r="G419" s="6"/>
-      <c r="H419" s="6"/>
-      <c r="I419" s="6"/>
       <c r="J419" s="6"/>
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
@@ -27062,8 +26226,6 @@
       <c r="E420" s="6"/>
       <c r="F420" s="6"/>
       <c r="G420" s="6"/>
-      <c r="H420" s="6"/>
-      <c r="I420" s="6"/>
       <c r="J420" s="6"/>
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
@@ -27079,8 +26241,6 @@
       <c r="E421" s="6"/>
       <c r="F421" s="6"/>
       <c r="G421" s="6"/>
-      <c r="H421" s="6"/>
-      <c r="I421" s="6"/>
       <c r="J421" s="6"/>
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
@@ -27096,8 +26256,6 @@
       <c r="E422" s="6"/>
       <c r="F422" s="6"/>
       <c r="G422" s="6"/>
-      <c r="H422" s="6"/>
-      <c r="I422" s="6"/>
       <c r="J422" s="6"/>
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
@@ -27113,8 +26271,6 @@
       <c r="E423" s="6"/>
       <c r="F423" s="6"/>
       <c r="G423" s="6"/>
-      <c r="H423" s="6"/>
-      <c r="I423" s="6"/>
       <c r="J423" s="6"/>
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
@@ -27130,8 +26286,6 @@
       <c r="E424" s="6"/>
       <c r="F424" s="6"/>
       <c r="G424" s="6"/>
-      <c r="H424" s="6"/>
-      <c r="I424" s="6"/>
       <c r="J424" s="6"/>
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
@@ -27147,8 +26301,6 @@
       <c r="E425" s="6"/>
       <c r="F425" s="6"/>
       <c r="G425" s="6"/>
-      <c r="H425" s="6"/>
-      <c r="I425" s="6"/>
       <c r="J425" s="6"/>
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
@@ -27164,8 +26316,6 @@
       <c r="E426" s="6"/>
       <c r="F426" s="6"/>
       <c r="G426" s="6"/>
-      <c r="H426" s="6"/>
-      <c r="I426" s="6"/>
       <c r="J426" s="6"/>
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
@@ -27181,8 +26331,6 @@
       <c r="E427" s="6"/>
       <c r="F427" s="6"/>
       <c r="G427" s="6"/>
-      <c r="H427" s="6"/>
-      <c r="I427" s="6"/>
       <c r="J427" s="6"/>
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
@@ -27198,8 +26346,6 @@
       <c r="E428" s="6"/>
       <c r="F428" s="6"/>
       <c r="G428" s="6"/>
-      <c r="H428" s="6"/>
-      <c r="I428" s="6"/>
       <c r="J428" s="6"/>
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
@@ -27215,8 +26361,6 @@
       <c r="E429" s="6"/>
       <c r="F429" s="6"/>
       <c r="G429" s="6"/>
-      <c r="H429" s="6"/>
-      <c r="I429" s="6"/>
       <c r="J429" s="6"/>
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
@@ -27232,8 +26376,6 @@
       <c r="E430" s="6"/>
       <c r="F430" s="6"/>
       <c r="G430" s="6"/>
-      <c r="H430" s="6"/>
-      <c r="I430" s="6"/>
       <c r="J430" s="6"/>
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
@@ -27249,8 +26391,6 @@
       <c r="E431" s="6"/>
       <c r="F431" s="6"/>
       <c r="G431" s="6"/>
-      <c r="H431" s="6"/>
-      <c r="I431" s="6"/>
       <c r="J431" s="6"/>
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
@@ -27266,8 +26406,6 @@
       <c r="E432" s="6"/>
       <c r="F432" s="6"/>
       <c r="G432" s="6"/>
-      <c r="H432" s="6"/>
-      <c r="I432" s="6"/>
       <c r="J432" s="6"/>
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
@@ -27283,8 +26421,6 @@
       <c r="E433" s="6"/>
       <c r="F433" s="6"/>
       <c r="G433" s="6"/>
-      <c r="H433" s="6"/>
-      <c r="I433" s="6"/>
       <c r="J433" s="6"/>
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
@@ -27300,8 +26436,6 @@
       <c r="E434" s="6"/>
       <c r="F434" s="6"/>
       <c r="G434" s="6"/>
-      <c r="H434" s="6"/>
-      <c r="I434" s="6"/>
       <c r="J434" s="6"/>
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
@@ -27317,8 +26451,6 @@
       <c r="E435" s="6"/>
       <c r="F435" s="6"/>
       <c r="G435" s="6"/>
-      <c r="H435" s="6"/>
-      <c r="I435" s="6"/>
       <c r="J435" s="6"/>
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
@@ -27334,8 +26466,6 @@
       <c r="E436" s="6"/>
       <c r="F436" s="6"/>
       <c r="G436" s="6"/>
-      <c r="H436" s="6"/>
-      <c r="I436" s="6"/>
       <c r="J436" s="6"/>
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
@@ -27351,8 +26481,6 @@
       <c r="E437" s="6"/>
       <c r="F437" s="6"/>
       <c r="G437" s="6"/>
-      <c r="H437" s="6"/>
-      <c r="I437" s="6"/>
       <c r="J437" s="6"/>
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
@@ -27368,8 +26496,6 @@
       <c r="E438" s="6"/>
       <c r="F438" s="6"/>
       <c r="G438" s="6"/>
-      <c r="H438" s="6"/>
-      <c r="I438" s="6"/>
       <c r="J438" s="6"/>
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
@@ -27385,8 +26511,6 @@
       <c r="E439" s="6"/>
       <c r="F439" s="6"/>
       <c r="G439" s="6"/>
-      <c r="H439" s="6"/>
-      <c r="I439" s="6"/>
       <c r="J439" s="6"/>
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
@@ -27402,8 +26526,6 @@
       <c r="E440" s="6"/>
       <c r="F440" s="6"/>
       <c r="G440" s="6"/>
-      <c r="H440" s="6"/>
-      <c r="I440" s="6"/>
       <c r="J440" s="6"/>
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
@@ -27419,8 +26541,6 @@
       <c r="E441" s="6"/>
       <c r="F441" s="6"/>
       <c r="G441" s="6"/>
-      <c r="H441" s="6"/>
-      <c r="I441" s="6"/>
       <c r="J441" s="6"/>
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
@@ -27436,8 +26556,6 @@
       <c r="E442" s="6"/>
       <c r="F442" s="6"/>
       <c r="G442" s="6"/>
-      <c r="H442" s="6"/>
-      <c r="I442" s="6"/>
       <c r="J442" s="6"/>
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
@@ -27453,8 +26571,6 @@
       <c r="E443" s="6"/>
       <c r="F443" s="6"/>
       <c r="G443" s="6"/>
-      <c r="H443" s="6"/>
-      <c r="I443" s="6"/>
       <c r="J443" s="6"/>
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
@@ -27470,8 +26586,6 @@
       <c r="E444" s="6"/>
       <c r="F444" s="6"/>
       <c r="G444" s="6"/>
-      <c r="H444" s="6"/>
-      <c r="I444" s="6"/>
       <c r="J444" s="6"/>
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
@@ -27487,8 +26601,6 @@
       <c r="E445" s="6"/>
       <c r="F445" s="6"/>
       <c r="G445" s="6"/>
-      <c r="H445" s="6"/>
-      <c r="I445" s="6"/>
       <c r="J445" s="6"/>
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
@@ -27504,8 +26616,6 @@
       <c r="E446" s="6"/>
       <c r="F446" s="6"/>
       <c r="G446" s="6"/>
-      <c r="H446" s="6"/>
-      <c r="I446" s="6"/>
       <c r="J446" s="6"/>
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
@@ -27521,8 +26631,6 @@
       <c r="E447" s="6"/>
       <c r="F447" s="6"/>
       <c r="G447" s="6"/>
-      <c r="H447" s="6"/>
-      <c r="I447" s="6"/>
       <c r="J447" s="6"/>
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
@@ -27538,8 +26646,6 @@
       <c r="E448" s="6"/>
       <c r="F448" s="6"/>
       <c r="G448" s="6"/>
-      <c r="H448" s="6"/>
-      <c r="I448" s="6"/>
       <c r="J448" s="6"/>
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
@@ -27555,8 +26661,6 @@
       <c r="E449" s="6"/>
       <c r="F449" s="6"/>
       <c r="G449" s="6"/>
-      <c r="H449" s="6"/>
-      <c r="I449" s="6"/>
       <c r="J449" s="6"/>
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
@@ -27572,8 +26676,6 @@
       <c r="E450" s="6"/>
       <c r="F450" s="6"/>
       <c r="G450" s="6"/>
-      <c r="H450" s="6"/>
-      <c r="I450" s="6"/>
       <c r="J450" s="6"/>
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
@@ -27589,8 +26691,6 @@
       <c r="E451" s="6"/>
       <c r="F451" s="6"/>
       <c r="G451" s="6"/>
-      <c r="H451" s="6"/>
-      <c r="I451" s="6"/>
       <c r="J451" s="6"/>
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
@@ -27606,8 +26706,6 @@
       <c r="E452" s="6"/>
       <c r="F452" s="6"/>
       <c r="G452" s="6"/>
-      <c r="H452" s="6"/>
-      <c r="I452" s="6"/>
       <c r="J452" s="6"/>
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
@@ -27623,8 +26721,6 @@
       <c r="E453" s="6"/>
       <c r="F453" s="6"/>
       <c r="G453" s="6"/>
-      <c r="H453" s="6"/>
-      <c r="I453" s="6"/>
       <c r="J453" s="6"/>
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
@@ -27640,8 +26736,6 @@
       <c r="E454" s="6"/>
       <c r="F454" s="6"/>
       <c r="G454" s="6"/>
-      <c r="H454" s="6"/>
-      <c r="I454" s="6"/>
       <c r="J454" s="6"/>
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
@@ -27657,8 +26751,6 @@
       <c r="E455" s="6"/>
       <c r="F455" s="6"/>
       <c r="G455" s="6"/>
-      <c r="H455" s="6"/>
-      <c r="I455" s="6"/>
       <c r="J455" s="6"/>
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
@@ -27674,8 +26766,6 @@
       <c r="E456" s="6"/>
       <c r="F456" s="6"/>
       <c r="G456" s="6"/>
-      <c r="H456" s="6"/>
-      <c r="I456" s="6"/>
       <c r="J456" s="6"/>
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
@@ -27691,8 +26781,6 @@
       <c r="E457" s="6"/>
       <c r="F457" s="6"/>
       <c r="G457" s="6"/>
-      <c r="H457" s="6"/>
-      <c r="I457" s="6"/>
       <c r="J457" s="6"/>
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
@@ -27708,8 +26796,6 @@
       <c r="E458" s="6"/>
       <c r="F458" s="6"/>
       <c r="G458" s="6"/>
-      <c r="H458" s="6"/>
-      <c r="I458" s="6"/>
       <c r="J458" s="6"/>
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
@@ -27725,8 +26811,6 @@
       <c r="E459" s="6"/>
       <c r="F459" s="6"/>
       <c r="G459" s="6"/>
-      <c r="H459" s="6"/>
-      <c r="I459" s="6"/>
       <c r="J459" s="6"/>
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
@@ -27742,8 +26826,6 @@
       <c r="E460" s="6"/>
       <c r="F460" s="6"/>
       <c r="G460" s="6"/>
-      <c r="H460" s="6"/>
-      <c r="I460" s="6"/>
       <c r="J460" s="6"/>
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
@@ -27759,8 +26841,6 @@
       <c r="E461" s="6"/>
       <c r="F461" s="6"/>
       <c r="G461" s="6"/>
-      <c r="H461" s="6"/>
-      <c r="I461" s="6"/>
       <c r="J461" s="6"/>
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
@@ -27776,8 +26856,6 @@
       <c r="E462" s="6"/>
       <c r="F462" s="6"/>
       <c r="G462" s="6"/>
-      <c r="H462" s="6"/>
-      <c r="I462" s="6"/>
       <c r="J462" s="6"/>
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
@@ -27793,8 +26871,6 @@
       <c r="E463" s="6"/>
       <c r="F463" s="6"/>
       <c r="G463" s="6"/>
-      <c r="H463" s="6"/>
-      <c r="I463" s="6"/>
       <c r="J463" s="6"/>
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
@@ -27810,8 +26886,6 @@
       <c r="E464" s="6"/>
       <c r="F464" s="6"/>
       <c r="G464" s="6"/>
-      <c r="H464" s="6"/>
-      <c r="I464" s="6"/>
       <c r="J464" s="6"/>
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
@@ -27827,8 +26901,6 @@
       <c r="E465" s="6"/>
       <c r="F465" s="6"/>
       <c r="G465" s="6"/>
-      <c r="H465" s="6"/>
-      <c r="I465" s="6"/>
       <c r="J465" s="6"/>
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
@@ -27844,8 +26916,6 @@
       <c r="E466" s="6"/>
       <c r="F466" s="6"/>
       <c r="G466" s="6"/>
-      <c r="H466" s="6"/>
-      <c r="I466" s="6"/>
       <c r="J466" s="6"/>
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
@@ -27861,8 +26931,6 @@
       <c r="E467" s="6"/>
       <c r="F467" s="6"/>
       <c r="G467" s="6"/>
-      <c r="H467" s="6"/>
-      <c r="I467" s="6"/>
       <c r="J467" s="6"/>
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
@@ -27878,8 +26946,6 @@
       <c r="E468" s="6"/>
       <c r="F468" s="6"/>
       <c r="G468" s="6"/>
-      <c r="H468" s="6"/>
-      <c r="I468" s="6"/>
       <c r="J468" s="6"/>
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
@@ -27895,8 +26961,6 @@
       <c r="E469" s="6"/>
       <c r="F469" s="6"/>
       <c r="G469" s="6"/>
-      <c r="H469" s="6"/>
-      <c r="I469" s="6"/>
       <c r="J469" s="6"/>
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
@@ -27912,8 +26976,6 @@
       <c r="E470" s="6"/>
       <c r="F470" s="6"/>
       <c r="G470" s="6"/>
-      <c r="H470" s="6"/>
-      <c r="I470" s="6"/>
       <c r="J470" s="6"/>
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
@@ -27929,8 +26991,6 @@
       <c r="E471" s="6"/>
       <c r="F471" s="6"/>
       <c r="G471" s="6"/>
-      <c r="H471" s="6"/>
-      <c r="I471" s="6"/>
       <c r="J471" s="6"/>
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
@@ -27946,8 +27006,6 @@
       <c r="E472" s="6"/>
       <c r="F472" s="6"/>
       <c r="G472" s="6"/>
-      <c r="H472" s="6"/>
-      <c r="I472" s="6"/>
       <c r="J472" s="6"/>
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
@@ -27963,8 +27021,6 @@
       <c r="E473" s="6"/>
       <c r="F473" s="6"/>
       <c r="G473" s="6"/>
-      <c r="H473" s="6"/>
-      <c r="I473" s="6"/>
       <c r="J473" s="6"/>
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
@@ -27980,8 +27036,6 @@
       <c r="E474" s="6"/>
       <c r="F474" s="6"/>
       <c r="G474" s="6"/>
-      <c r="H474" s="6"/>
-      <c r="I474" s="6"/>
       <c r="J474" s="6"/>
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
@@ -27997,8 +27051,6 @@
       <c r="E475" s="6"/>
       <c r="F475" s="6"/>
       <c r="G475" s="6"/>
-      <c r="H475" s="6"/>
-      <c r="I475" s="6"/>
       <c r="J475" s="6"/>
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
@@ -28014,8 +27066,6 @@
       <c r="E476" s="6"/>
       <c r="F476" s="6"/>
       <c r="G476" s="6"/>
-      <c r="H476" s="6"/>
-      <c r="I476" s="6"/>
       <c r="J476" s="6"/>
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
@@ -28031,8 +27081,6 @@
       <c r="E477" s="6"/>
       <c r="F477" s="6"/>
       <c r="G477" s="6"/>
-      <c r="H477" s="6"/>
-      <c r="I477" s="6"/>
       <c r="J477" s="6"/>
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
@@ -28048,8 +27096,6 @@
       <c r="E478" s="6"/>
       <c r="F478" s="6"/>
       <c r="G478" s="6"/>
-      <c r="H478" s="6"/>
-      <c r="I478" s="6"/>
       <c r="J478" s="6"/>
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
@@ -28065,8 +27111,6 @@
       <c r="E479" s="6"/>
       <c r="F479" s="6"/>
       <c r="G479" s="6"/>
-      <c r="H479" s="6"/>
-      <c r="I479" s="6"/>
       <c r="J479" s="6"/>
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
@@ -28082,8 +27126,6 @@
       <c r="E480" s="6"/>
       <c r="F480" s="6"/>
       <c r="G480" s="6"/>
-      <c r="H480" s="6"/>
-      <c r="I480" s="6"/>
       <c r="J480" s="6"/>
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
@@ -28099,8 +27141,6 @@
       <c r="E481" s="6"/>
       <c r="F481" s="6"/>
       <c r="G481" s="6"/>
-      <c r="H481" s="6"/>
-      <c r="I481" s="6"/>
       <c r="J481" s="6"/>
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
@@ -28116,8 +27156,6 @@
       <c r="E482" s="6"/>
       <c r="F482" s="6"/>
       <c r="G482" s="6"/>
-      <c r="H482" s="6"/>
-      <c r="I482" s="6"/>
       <c r="J482" s="6"/>
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
@@ -28133,8 +27171,6 @@
       <c r="E483" s="6"/>
       <c r="F483" s="6"/>
       <c r="G483" s="6"/>
-      <c r="H483" s="6"/>
-      <c r="I483" s="6"/>
       <c r="J483" s="6"/>
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
@@ -28150,8 +27186,6 @@
       <c r="E484" s="6"/>
       <c r="F484" s="6"/>
       <c r="G484" s="6"/>
-      <c r="H484" s="6"/>
-      <c r="I484" s="6"/>
       <c r="J484" s="6"/>
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
@@ -28167,8 +27201,6 @@
       <c r="E485" s="6"/>
       <c r="F485" s="6"/>
       <c r="G485" s="6"/>
-      <c r="H485" s="6"/>
-      <c r="I485" s="6"/>
       <c r="J485" s="6"/>
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
@@ -28184,8 +27216,6 @@
       <c r="E486" s="6"/>
       <c r="F486" s="6"/>
       <c r="G486" s="6"/>
-      <c r="H486" s="6"/>
-      <c r="I486" s="6"/>
       <c r="J486" s="6"/>
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
@@ -28201,8 +27231,6 @@
       <c r="E487" s="6"/>
       <c r="F487" s="6"/>
       <c r="G487" s="6"/>
-      <c r="H487" s="6"/>
-      <c r="I487" s="6"/>
       <c r="J487" s="6"/>
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
@@ -28218,8 +27246,6 @@
       <c r="E488" s="6"/>
       <c r="F488" s="6"/>
       <c r="G488" s="6"/>
-      <c r="H488" s="6"/>
-      <c r="I488" s="6"/>
       <c r="J488" s="6"/>
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
@@ -28235,8 +27261,6 @@
       <c r="E489" s="6"/>
       <c r="F489" s="6"/>
       <c r="G489" s="6"/>
-      <c r="H489" s="6"/>
-      <c r="I489" s="6"/>
       <c r="J489" s="6"/>
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
@@ -28252,8 +27276,6 @@
       <c r="E490" s="6"/>
       <c r="F490" s="6"/>
       <c r="G490" s="6"/>
-      <c r="H490" s="6"/>
-      <c r="I490" s="6"/>
       <c r="J490" s="6"/>
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
@@ -28269,8 +27291,6 @@
       <c r="E491" s="6"/>
       <c r="F491" s="6"/>
       <c r="G491" s="6"/>
-      <c r="H491" s="6"/>
-      <c r="I491" s="6"/>
       <c r="J491" s="6"/>
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
@@ -28286,8 +27306,6 @@
       <c r="E492" s="6"/>
       <c r="F492" s="6"/>
       <c r="G492" s="6"/>
-      <c r="H492" s="6"/>
-      <c r="I492" s="6"/>
       <c r="J492" s="6"/>
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
@@ -28303,8 +27321,6 @@
       <c r="E493" s="6"/>
       <c r="F493" s="6"/>
       <c r="G493" s="6"/>
-      <c r="H493" s="6"/>
-      <c r="I493" s="6"/>
       <c r="J493" s="6"/>
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
@@ -28320,8 +27336,6 @@
       <c r="E494" s="6"/>
       <c r="F494" s="6"/>
       <c r="G494" s="6"/>
-      <c r="H494" s="6"/>
-      <c r="I494" s="6"/>
       <c r="J494" s="6"/>
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
@@ -28337,8 +27351,6 @@
       <c r="E495" s="6"/>
       <c r="F495" s="6"/>
       <c r="G495" s="6"/>
-      <c r="H495" s="6"/>
-      <c r="I495" s="6"/>
       <c r="J495" s="6"/>
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
@@ -28354,8 +27366,6 @@
       <c r="E496" s="6"/>
       <c r="F496" s="6"/>
       <c r="G496" s="6"/>
-      <c r="H496" s="6"/>
-      <c r="I496" s="6"/>
       <c r="J496" s="6"/>
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
@@ -28371,8 +27381,6 @@
       <c r="E497" s="6"/>
       <c r="F497" s="6"/>
       <c r="G497" s="6"/>
-      <c r="H497" s="6"/>
-      <c r="I497" s="6"/>
       <c r="J497" s="6"/>
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
@@ -28388,8 +27396,6 @@
       <c r="E498" s="6"/>
       <c r="F498" s="6"/>
       <c r="G498" s="6"/>
-      <c r="H498" s="6"/>
-      <c r="I498" s="6"/>
       <c r="J498" s="6"/>
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
@@ -28405,8 +27411,6 @@
       <c r="E499" s="6"/>
       <c r="F499" s="6"/>
       <c r="G499" s="6"/>
-      <c r="H499" s="6"/>
-      <c r="I499" s="6"/>
       <c r="J499" s="6"/>
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
@@ -28422,8 +27426,6 @@
       <c r="E500" s="6"/>
       <c r="F500" s="6"/>
       <c r="G500" s="6"/>
-      <c r="H500" s="6"/>
-      <c r="I500" s="6"/>
       <c r="J500" s="6"/>
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
@@ -28439,8 +27441,6 @@
       <c r="E501" s="6"/>
       <c r="F501" s="6"/>
       <c r="G501" s="6"/>
-      <c r="H501" s="6"/>
-      <c r="I501" s="6"/>
       <c r="J501" s="6"/>
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
@@ -28456,8 +27456,6 @@
       <c r="E502" s="6"/>
       <c r="F502" s="6"/>
       <c r="G502" s="6"/>
-      <c r="H502" s="6"/>
-      <c r="I502" s="6"/>
       <c r="J502" s="6"/>
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
@@ -28473,8 +27471,6 @@
       <c r="E503" s="6"/>
       <c r="F503" s="6"/>
       <c r="G503" s="6"/>
-      <c r="H503" s="6"/>
-      <c r="I503" s="6"/>
       <c r="J503" s="6"/>
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
@@ -28490,8 +27486,6 @@
       <c r="E504" s="6"/>
       <c r="F504" s="6"/>
       <c r="G504" s="6"/>
-      <c r="H504" s="6"/>
-      <c r="I504" s="6"/>
       <c r="J504" s="6"/>
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
@@ -28507,8 +27501,6 @@
       <c r="E505" s="6"/>
       <c r="F505" s="6"/>
       <c r="G505" s="6"/>
-      <c r="H505" s="6"/>
-      <c r="I505" s="6"/>
       <c r="J505" s="6"/>
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
@@ -28524,8 +27516,6 @@
       <c r="E506" s="6"/>
       <c r="F506" s="6"/>
       <c r="G506" s="6"/>
-      <c r="H506" s="6"/>
-      <c r="I506" s="6"/>
       <c r="J506" s="6"/>
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
@@ -28541,8 +27531,6 @@
       <c r="E507" s="6"/>
       <c r="F507" s="6"/>
       <c r="G507" s="6"/>
-      <c r="H507" s="6"/>
-      <c r="I507" s="6"/>
       <c r="J507" s="6"/>
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
@@ -28558,8 +27546,6 @@
       <c r="E508" s="6"/>
       <c r="F508" s="6"/>
       <c r="G508" s="6"/>
-      <c r="H508" s="6"/>
-      <c r="I508" s="6"/>
       <c r="J508" s="6"/>
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
@@ -28575,8 +27561,6 @@
       <c r="E509" s="6"/>
       <c r="F509" s="6"/>
       <c r="G509" s="6"/>
-      <c r="H509" s="6"/>
-      <c r="I509" s="6"/>
       <c r="J509" s="6"/>
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
@@ -28592,8 +27576,6 @@
       <c r="E510" s="6"/>
       <c r="F510" s="6"/>
       <c r="G510" s="6"/>
-      <c r="H510" s="6"/>
-      <c r="I510" s="6"/>
       <c r="J510" s="6"/>
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
@@ -28609,8 +27591,6 @@
       <c r="E511" s="6"/>
       <c r="F511" s="6"/>
       <c r="G511" s="6"/>
-      <c r="H511" s="6"/>
-      <c r="I511" s="6"/>
       <c r="J511" s="6"/>
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
@@ -28626,8 +27606,6 @@
       <c r="E512" s="6"/>
       <c r="F512" s="6"/>
       <c r="G512" s="6"/>
-      <c r="H512" s="6"/>
-      <c r="I512" s="6"/>
       <c r="J512" s="6"/>
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
@@ -28643,8 +27621,6 @@
       <c r="E513" s="6"/>
       <c r="F513" s="6"/>
       <c r="G513" s="6"/>
-      <c r="H513" s="6"/>
-      <c r="I513" s="6"/>
       <c r="J513" s="6"/>
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
@@ -28660,8 +27636,6 @@
       <c r="E514" s="6"/>
       <c r="F514" s="6"/>
       <c r="G514" s="6"/>
-      <c r="H514" s="6"/>
-      <c r="I514" s="6"/>
       <c r="J514" s="6"/>
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
@@ -28677,8 +27651,6 @@
       <c r="E515" s="6"/>
       <c r="F515" s="6"/>
       <c r="G515" s="6"/>
-      <c r="H515" s="6"/>
-      <c r="I515" s="6"/>
       <c r="J515" s="6"/>
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
@@ -28694,8 +27666,6 @@
       <c r="E516" s="6"/>
       <c r="F516" s="6"/>
       <c r="G516" s="6"/>
-      <c r="H516" s="6"/>
-      <c r="I516" s="6"/>
       <c r="J516" s="6"/>
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
@@ -28711,8 +27681,6 @@
       <c r="E517" s="6"/>
       <c r="F517" s="6"/>
       <c r="G517" s="6"/>
-      <c r="H517" s="6"/>
-      <c r="I517" s="6"/>
       <c r="J517" s="6"/>
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
@@ -28728,8 +27696,6 @@
       <c r="E518" s="6"/>
       <c r="F518" s="6"/>
       <c r="G518" s="6"/>
-      <c r="H518" s="6"/>
-      <c r="I518" s="6"/>
       <c r="J518" s="6"/>
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
@@ -28745,8 +27711,6 @@
       <c r="E519" s="6"/>
       <c r="F519" s="6"/>
       <c r="G519" s="6"/>
-      <c r="H519" s="6"/>
-      <c r="I519" s="6"/>
       <c r="J519" s="6"/>
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
@@ -28762,8 +27726,6 @@
       <c r="E520" s="6"/>
       <c r="F520" s="6"/>
       <c r="G520" s="6"/>
-      <c r="H520" s="6"/>
-      <c r="I520" s="6"/>
       <c r="J520" s="6"/>
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
@@ -28779,8 +27741,6 @@
       <c r="E521" s="6"/>
       <c r="F521" s="6"/>
       <c r="G521" s="6"/>
-      <c r="H521" s="6"/>
-      <c r="I521" s="6"/>
       <c r="J521" s="6"/>
       <c r="K521" s="6"/>
       <c r="L521" s="6"/>
@@ -28796,8 +27756,6 @@
       <c r="E522" s="6"/>
       <c r="F522" s="6"/>
       <c r="G522" s="6"/>
-      <c r="H522" s="6"/>
-      <c r="I522" s="6"/>
       <c r="J522" s="6"/>
       <c r="K522" s="6"/>
       <c r="L522" s="6"/>
@@ -28813,8 +27771,6 @@
       <c r="E523" s="6"/>
       <c r="F523" s="6"/>
       <c r="G523" s="6"/>
-      <c r="H523" s="6"/>
-      <c r="I523" s="6"/>
       <c r="J523" s="6"/>
       <c r="K523" s="6"/>
       <c r="L523" s="6"/>
@@ -28830,8 +27786,6 @@
       <c r="E524" s="6"/>
       <c r="F524" s="6"/>
       <c r="G524" s="6"/>
-      <c r="H524" s="6"/>
-      <c r="I524" s="6"/>
       <c r="J524" s="6"/>
       <c r="K524" s="6"/>
       <c r="L524" s="6"/>
@@ -28847,8 +27801,6 @@
       <c r="E525" s="6"/>
       <c r="F525" s="6"/>
       <c r="G525" s="6"/>
-      <c r="H525" s="6"/>
-      <c r="I525" s="6"/>
       <c r="J525" s="6"/>
       <c r="K525" s="6"/>
       <c r="L525" s="6"/>
@@ -28864,8 +27816,6 @@
       <c r="E526" s="6"/>
       <c r="F526" s="6"/>
       <c r="G526" s="6"/>
-      <c r="H526" s="6"/>
-      <c r="I526" s="6"/>
       <c r="J526" s="6"/>
       <c r="K526" s="6"/>
       <c r="L526" s="6"/>
@@ -28881,8 +27831,6 @@
       <c r="E527" s="6"/>
       <c r="F527" s="6"/>
       <c r="G527" s="6"/>
-      <c r="H527" s="6"/>
-      <c r="I527" s="6"/>
       <c r="J527" s="6"/>
       <c r="K527" s="6"/>
       <c r="L527" s="6"/>
@@ -28898,8 +27846,6 @@
       <c r="E528" s="6"/>
       <c r="F528" s="6"/>
       <c r="G528" s="6"/>
-      <c r="H528" s="6"/>
-      <c r="I528" s="6"/>
       <c r="J528" s="6"/>
       <c r="K528" s="6"/>
       <c r="L528" s="6"/>
@@ -28915,8 +27861,6 @@
       <c r="E529" s="6"/>
       <c r="F529" s="6"/>
       <c r="G529" s="6"/>
-      <c r="H529" s="6"/>
-      <c r="I529" s="6"/>
       <c r="J529" s="6"/>
       <c r="K529" s="6"/>
       <c r="L529" s="6"/>
@@ -28932,8 +27876,6 @@
       <c r="E530" s="6"/>
       <c r="F530" s="6"/>
       <c r="G530" s="6"/>
-      <c r="H530" s="6"/>
-      <c r="I530" s="6"/>
       <c r="J530" s="6"/>
       <c r="K530" s="6"/>
       <c r="L530" s="6"/>
@@ -28949,8 +27891,6 @@
       <c r="E531" s="6"/>
       <c r="F531" s="6"/>
       <c r="G531" s="6"/>
-      <c r="H531" s="6"/>
-      <c r="I531" s="6"/>
       <c r="J531" s="6"/>
       <c r="K531" s="6"/>
       <c r="L531" s="6"/>
@@ -28966,8 +27906,6 @@
       <c r="E532" s="6"/>
       <c r="F532" s="6"/>
       <c r="G532" s="6"/>
-      <c r="H532" s="6"/>
-      <c r="I532" s="6"/>
       <c r="J532" s="6"/>
       <c r="K532" s="6"/>
       <c r="L532" s="6"/>
@@ -28983,8 +27921,6 @@
       <c r="E533" s="6"/>
       <c r="F533" s="6"/>
       <c r="G533" s="6"/>
-      <c r="H533" s="6"/>
-      <c r="I533" s="6"/>
       <c r="J533" s="6"/>
       <c r="K533" s="6"/>
       <c r="L533" s="6"/>
@@ -29000,8 +27936,6 @@
       <c r="E534" s="6"/>
       <c r="F534" s="6"/>
       <c r="G534" s="6"/>
-      <c r="H534" s="6"/>
-      <c r="I534" s="6"/>
       <c r="J534" s="6"/>
       <c r="K534" s="6"/>
       <c r="L534" s="6"/>
@@ -29017,8 +27951,6 @@
       <c r="E535" s="6"/>
       <c r="F535" s="6"/>
       <c r="G535" s="6"/>
-      <c r="H535" s="6"/>
-      <c r="I535" s="6"/>
       <c r="J535" s="6"/>
       <c r="K535" s="6"/>
       <c r="L535" s="6"/>
@@ -29034,8 +27966,6 @@
       <c r="E536" s="6"/>
       <c r="F536" s="6"/>
       <c r="G536" s="6"/>
-      <c r="H536" s="6"/>
-      <c r="I536" s="6"/>
       <c r="J536" s="6"/>
       <c r="K536" s="6"/>
       <c r="L536" s="6"/>
@@ -29051,8 +27981,6 @@
       <c r="E537" s="6"/>
       <c r="F537" s="6"/>
       <c r="G537" s="6"/>
-      <c r="H537" s="6"/>
-      <c r="I537" s="6"/>
       <c r="J537" s="6"/>
       <c r="K537" s="6"/>
       <c r="L537" s="6"/>
@@ -29068,8 +27996,6 @@
       <c r="E538" s="6"/>
       <c r="F538" s="6"/>
       <c r="G538" s="6"/>
-      <c r="H538" s="6"/>
-      <c r="I538" s="6"/>
       <c r="J538" s="6"/>
       <c r="K538" s="6"/>
       <c r="L538" s="6"/>
@@ -29085,8 +28011,6 @@
       <c r="E539" s="6"/>
       <c r="F539" s="6"/>
       <c r="G539" s="6"/>
-      <c r="H539" s="6"/>
-      <c r="I539" s="6"/>
       <c r="J539" s="6"/>
       <c r="K539" s="6"/>
       <c r="L539" s="6"/>
@@ -29102,8 +28026,6 @@
       <c r="E540" s="6"/>
       <c r="F540" s="6"/>
       <c r="G540" s="6"/>
-      <c r="H540" s="6"/>
-      <c r="I540" s="6"/>
       <c r="J540" s="6"/>
       <c r="K540" s="6"/>
       <c r="L540" s="6"/>
@@ -29119,8 +28041,6 @@
       <c r="E541" s="6"/>
       <c r="F541" s="6"/>
       <c r="G541" s="6"/>
-      <c r="H541" s="6"/>
-      <c r="I541" s="6"/>
       <c r="J541" s="6"/>
       <c r="K541" s="6"/>
       <c r="L541" s="6"/>
@@ -29136,8 +28056,6 @@
       <c r="E542" s="6"/>
       <c r="F542" s="6"/>
       <c r="G542" s="6"/>
-      <c r="H542" s="6"/>
-      <c r="I542" s="6"/>
       <c r="J542" s="6"/>
       <c r="K542" s="6"/>
       <c r="L542" s="6"/>
@@ -29153,8 +28071,6 @@
       <c r="E543" s="6"/>
       <c r="F543" s="6"/>
       <c r="G543" s="6"/>
-      <c r="H543" s="6"/>
-      <c r="I543" s="6"/>
       <c r="J543" s="6"/>
       <c r="K543" s="6"/>
       <c r="L543" s="6"/>
@@ -29170,8 +28086,6 @@
       <c r="E544" s="6"/>
       <c r="F544" s="6"/>
       <c r="G544" s="6"/>
-      <c r="H544" s="6"/>
-      <c r="I544" s="6"/>
       <c r="J544" s="6"/>
       <c r="K544" s="6"/>
       <c r="L544" s="6"/>
@@ -29187,8 +28101,6 @@
       <c r="E545" s="6"/>
       <c r="F545" s="6"/>
       <c r="G545" s="6"/>
-      <c r="H545" s="6"/>
-      <c r="I545" s="6"/>
       <c r="J545" s="6"/>
       <c r="K545" s="6"/>
       <c r="L545" s="6"/>
@@ -29204,8 +28116,6 @@
       <c r="E546" s="6"/>
       <c r="F546" s="6"/>
       <c r="G546" s="6"/>
-      <c r="H546" s="6"/>
-      <c r="I546" s="6"/>
       <c r="J546" s="6"/>
       <c r="K546" s="6"/>
       <c r="L546" s="6"/>
@@ -29221,8 +28131,6 @@
       <c r="E547" s="6"/>
       <c r="F547" s="6"/>
       <c r="G547" s="6"/>
-      <c r="H547" s="6"/>
-      <c r="I547" s="6"/>
       <c r="J547" s="6"/>
       <c r="K547" s="6"/>
       <c r="L547" s="6"/>
@@ -29238,8 +28146,6 @@
       <c r="E548" s="6"/>
       <c r="F548" s="6"/>
       <c r="G548" s="6"/>
-      <c r="H548" s="6"/>
-      <c r="I548" s="6"/>
       <c r="J548" s="6"/>
       <c r="K548" s="6"/>
       <c r="L548" s="6"/>
@@ -29255,8 +28161,6 @@
       <c r="E549" s="6"/>
       <c r="F549" s="6"/>
       <c r="G549" s="6"/>
-      <c r="H549" s="6"/>
-      <c r="I549" s="6"/>
       <c r="J549" s="6"/>
       <c r="K549" s="6"/>
       <c r="L549" s="6"/>
@@ -29272,8 +28176,6 @@
       <c r="E550" s="6"/>
       <c r="F550" s="6"/>
       <c r="G550" s="6"/>
-      <c r="H550" s="6"/>
-      <c r="I550" s="6"/>
       <c r="J550" s="6"/>
       <c r="K550" s="6"/>
       <c r="L550" s="6"/>
@@ -29289,8 +28191,6 @@
       <c r="E551" s="6"/>
       <c r="F551" s="6"/>
       <c r="G551" s="6"/>
-      <c r="H551" s="6"/>
-      <c r="I551" s="6"/>
       <c r="J551" s="6"/>
       <c r="K551" s="6"/>
       <c r="L551" s="6"/>
@@ -29306,8 +28206,6 @@
       <c r="E552" s="6"/>
       <c r="F552" s="6"/>
       <c r="G552" s="6"/>
-      <c r="H552" s="6"/>
-      <c r="I552" s="6"/>
       <c r="J552" s="6"/>
       <c r="K552" s="6"/>
       <c r="L552" s="6"/>
@@ -29323,8 +28221,6 @@
       <c r="E553" s="6"/>
       <c r="F553" s="6"/>
       <c r="G553" s="6"/>
-      <c r="H553" s="6"/>
-      <c r="I553" s="6"/>
       <c r="J553" s="6"/>
       <c r="K553" s="6"/>
       <c r="L553" s="6"/>
@@ -29340,8 +28236,6 @@
       <c r="E554" s="6"/>
       <c r="F554" s="6"/>
       <c r="G554" s="6"/>
-      <c r="H554" s="6"/>
-      <c r="I554" s="6"/>
       <c r="J554" s="6"/>
       <c r="K554" s="6"/>
       <c r="L554" s="6"/>
@@ -29357,8 +28251,6 @@
       <c r="E555" s="6"/>
       <c r="F555" s="6"/>
       <c r="G555" s="6"/>
-      <c r="H555" s="6"/>
-      <c r="I555" s="6"/>
       <c r="J555" s="6"/>
       <c r="K555" s="6"/>
       <c r="L555" s="6"/>
@@ -29374,8 +28266,6 @@
       <c r="E556" s="6"/>
       <c r="F556" s="6"/>
       <c r="G556" s="6"/>
-      <c r="H556" s="6"/>
-      <c r="I556" s="6"/>
       <c r="J556" s="6"/>
       <c r="K556" s="6"/>
       <c r="L556" s="6"/>
@@ -29391,8 +28281,6 @@
       <c r="E557" s="6"/>
       <c r="F557" s="6"/>
       <c r="G557" s="6"/>
-      <c r="H557" s="6"/>
-      <c r="I557" s="6"/>
       <c r="J557" s="6"/>
       <c r="K557" s="6"/>
       <c r="L557" s="6"/>
@@ -29408,8 +28296,6 @@
       <c r="E558" s="6"/>
       <c r="F558" s="6"/>
       <c r="G558" s="6"/>
-      <c r="H558" s="6"/>
-      <c r="I558" s="6"/>
       <c r="J558" s="6"/>
       <c r="K558" s="6"/>
       <c r="L558" s="6"/>
@@ -29425,8 +28311,6 @@
       <c r="E559" s="6"/>
       <c r="F559" s="6"/>
       <c r="G559" s="6"/>
-      <c r="H559" s="6"/>
-      <c r="I559" s="6"/>
       <c r="J559" s="6"/>
       <c r="K559" s="6"/>
       <c r="L559" s="6"/>
@@ -29442,8 +28326,6 @@
       <c r="E560" s="6"/>
       <c r="F560" s="6"/>
       <c r="G560" s="6"/>
-      <c r="H560" s="6"/>
-      <c r="I560" s="6"/>
       <c r="J560" s="6"/>
       <c r="K560" s="6"/>
       <c r="L560" s="6"/>
@@ -29459,8 +28341,6 @@
       <c r="E561" s="6"/>
       <c r="F561" s="6"/>
       <c r="G561" s="6"/>
-      <c r="H561" s="6"/>
-      <c r="I561" s="6"/>
       <c r="J561" s="6"/>
       <c r="K561" s="6"/>
       <c r="L561" s="6"/>
@@ -29476,8 +28356,6 @@
       <c r="E562" s="6"/>
       <c r="F562" s="6"/>
       <c r="G562" s="6"/>
-      <c r="H562" s="6"/>
-      <c r="I562" s="6"/>
       <c r="J562" s="6"/>
       <c r="K562" s="6"/>
       <c r="L562" s="6"/>
@@ -29493,8 +28371,6 @@
       <c r="E563" s="6"/>
       <c r="F563" s="6"/>
       <c r="G563" s="6"/>
-      <c r="H563" s="6"/>
-      <c r="I563" s="6"/>
       <c r="J563" s="6"/>
       <c r="K563" s="6"/>
       <c r="L563" s="6"/>
@@ -29510,8 +28386,6 @@
       <c r="E564" s="6"/>
       <c r="F564" s="6"/>
       <c r="G564" s="6"/>
-      <c r="H564" s="6"/>
-      <c r="I564" s="6"/>
       <c r="J564" s="6"/>
       <c r="K564" s="6"/>
       <c r="L564" s="6"/>
@@ -29527,8 +28401,6 @@
       <c r="E565" s="6"/>
       <c r="F565" s="6"/>
       <c r="G565" s="6"/>
-      <c r="H565" s="6"/>
-      <c r="I565" s="6"/>
       <c r="J565" s="6"/>
       <c r="K565" s="6"/>
       <c r="L565" s="6"/>
@@ -29544,8 +28416,6 @@
       <c r="E566" s="6"/>
       <c r="F566" s="6"/>
       <c r="G566" s="6"/>
-      <c r="H566" s="6"/>
-      <c r="I566" s="6"/>
       <c r="J566" s="6"/>
       <c r="K566" s="6"/>
       <c r="L566" s="6"/>
@@ -29561,8 +28431,6 @@
       <c r="E567" s="6"/>
       <c r="F567" s="6"/>
       <c r="G567" s="6"/>
-      <c r="H567" s="6"/>
-      <c r="I567" s="6"/>
       <c r="J567" s="6"/>
       <c r="K567" s="6"/>
       <c r="L567" s="6"/>
@@ -29578,8 +28446,6 @@
       <c r="E568" s="6"/>
       <c r="F568" s="6"/>
       <c r="G568" s="6"/>
-      <c r="H568" s="6"/>
-      <c r="I568" s="6"/>
       <c r="J568" s="6"/>
       <c r="K568" s="6"/>
       <c r="L568" s="6"/>
@@ -29595,8 +28461,6 @@
       <c r="E569" s="6"/>
       <c r="F569" s="6"/>
       <c r="G569" s="6"/>
-      <c r="H569" s="6"/>
-      <c r="I569" s="6"/>
       <c r="J569" s="6"/>
       <c r="K569" s="6"/>
       <c r="L569" s="6"/>
@@ -29612,8 +28476,6 @@
       <c r="E570" s="6"/>
       <c r="F570" s="6"/>
       <c r="G570" s="6"/>
-      <c r="H570" s="6"/>
-      <c r="I570" s="6"/>
       <c r="J570" s="6"/>
       <c r="K570" s="6"/>
       <c r="L570" s="6"/>
@@ -29629,8 +28491,6 @@
       <c r="E571" s="6"/>
       <c r="F571" s="6"/>
       <c r="G571" s="6"/>
-      <c r="H571" s="6"/>
-      <c r="I571" s="6"/>
       <c r="J571" s="6"/>
       <c r="K571" s="6"/>
       <c r="L571" s="6"/>
@@ -29646,8 +28506,6 @@
       <c r="E572" s="6"/>
       <c r="F572" s="6"/>
       <c r="G572" s="6"/>
-      <c r="H572" s="6"/>
-      <c r="I572" s="6"/>
       <c r="J572" s="6"/>
       <c r="K572" s="6"/>
       <c r="L572" s="6"/>
@@ -29663,8 +28521,6 @@
       <c r="E573" s="6"/>
       <c r="F573" s="6"/>
       <c r="G573" s="6"/>
-      <c r="H573" s="6"/>
-      <c r="I573" s="6"/>
       <c r="J573" s="6"/>
       <c r="K573" s="6"/>
       <c r="L573" s="6"/>
@@ -29680,8 +28536,6 @@
       <c r="E574" s="6"/>
       <c r="F574" s="6"/>
       <c r="G574" s="6"/>
-      <c r="H574" s="6"/>
-      <c r="I574" s="6"/>
       <c r="J574" s="6"/>
       <c r="K574" s="6"/>
       <c r="L574" s="6"/>
@@ -29697,8 +28551,6 @@
       <c r="E575" s="6"/>
       <c r="F575" s="6"/>
       <c r="G575" s="6"/>
-      <c r="H575" s="6"/>
-      <c r="I575" s="6"/>
       <c r="J575" s="6"/>
       <c r="K575" s="6"/>
       <c r="L575" s="6"/>
@@ -29714,8 +28566,6 @@
       <c r="E576" s="6"/>
       <c r="F576" s="6"/>
       <c r="G576" s="6"/>
-      <c r="H576" s="6"/>
-      <c r="I576" s="6"/>
       <c r="J576" s="6"/>
       <c r="K576" s="6"/>
       <c r="L576" s="6"/>
@@ -29731,8 +28581,6 @@
       <c r="E577" s="6"/>
       <c r="F577" s="6"/>
       <c r="G577" s="6"/>
-      <c r="H577" s="6"/>
-      <c r="I577" s="6"/>
       <c r="J577" s="6"/>
       <c r="K577" s="6"/>
       <c r="L577" s="6"/>
@@ -29748,8 +28596,6 @@
       <c r="E578" s="6"/>
       <c r="F578" s="6"/>
       <c r="G578" s="6"/>
-      <c r="H578" s="6"/>
-      <c r="I578" s="6"/>
       <c r="J578" s="6"/>
       <c r="K578" s="6"/>
       <c r="L578" s="6"/>
@@ -29765,8 +28611,6 @@
       <c r="E579" s="6"/>
       <c r="F579" s="6"/>
       <c r="G579" s="6"/>
-      <c r="H579" s="6"/>
-      <c r="I579" s="6"/>
       <c r="J579" s="6"/>
       <c r="K579" s="6"/>
       <c r="L579" s="6"/>
@@ -29782,8 +28626,6 @@
       <c r="E580" s="6"/>
       <c r="F580" s="6"/>
       <c r="G580" s="6"/>
-      <c r="H580" s="6"/>
-      <c r="I580" s="6"/>
       <c r="J580" s="6"/>
       <c r="K580" s="6"/>
       <c r="L580" s="6"/>
@@ -29799,8 +28641,6 @@
       <c r="E581" s="6"/>
       <c r="F581" s="6"/>
       <c r="G581" s="6"/>
-      <c r="H581" s="6"/>
-      <c r="I581" s="6"/>
       <c r="J581" s="6"/>
       <c r="K581" s="6"/>
       <c r="L581" s="6"/>
@@ -29816,8 +28656,6 @@
       <c r="E582" s="6"/>
       <c r="F582" s="6"/>
       <c r="G582" s="6"/>
-      <c r="H582" s="6"/>
-      <c r="I582" s="6"/>
       <c r="J582" s="6"/>
       <c r="K582" s="6"/>
       <c r="L582" s="6"/>
@@ -29833,8 +28671,6 @@
       <c r="E583" s="6"/>
       <c r="F583" s="6"/>
       <c r="G583" s="6"/>
-      <c r="H583" s="6"/>
-      <c r="I583" s="6"/>
       <c r="J583" s="6"/>
       <c r="K583" s="6"/>
       <c r="L583" s="6"/>
@@ -29850,8 +28686,6 @@
       <c r="E584" s="6"/>
       <c r="F584" s="6"/>
       <c r="G584" s="6"/>
-      <c r="H584" s="6"/>
-      <c r="I584" s="6"/>
       <c r="J584" s="6"/>
       <c r="K584" s="6"/>
       <c r="L584" s="6"/>
@@ -29867,8 +28701,6 @@
       <c r="E585" s="6"/>
       <c r="F585" s="6"/>
       <c r="G585" s="6"/>
-      <c r="H585" s="6"/>
-      <c r="I585" s="6"/>
       <c r="J585" s="6"/>
       <c r="K585" s="6"/>
       <c r="L585" s="6"/>
@@ -29884,8 +28716,6 @@
       <c r="E586" s="6"/>
       <c r="F586" s="6"/>
       <c r="G586" s="6"/>
-      <c r="H586" s="6"/>
-      <c r="I586" s="6"/>
       <c r="J586" s="6"/>
       <c r="K586" s="6"/>
       <c r="L586" s="6"/>
@@ -29901,8 +28731,6 @@
       <c r="E587" s="6"/>
       <c r="F587" s="6"/>
       <c r="G587" s="6"/>
-      <c r="H587" s="6"/>
-      <c r="I587" s="6"/>
       <c r="J587" s="6"/>
       <c r="K587" s="6"/>
       <c r="L587" s="6"/>
@@ -29918,8 +28746,6 @@
       <c r="E588" s="6"/>
       <c r="F588" s="6"/>
       <c r="G588" s="6"/>
-      <c r="H588" s="6"/>
-      <c r="I588" s="6"/>
       <c r="J588" s="6"/>
       <c r="K588" s="6"/>
       <c r="L588" s="6"/>
@@ -29935,8 +28761,6 @@
       <c r="E589" s="6"/>
       <c r="F589" s="6"/>
       <c r="G589" s="6"/>
-      <c r="H589" s="6"/>
-      <c r="I589" s="6"/>
       <c r="J589" s="6"/>
       <c r="K589" s="6"/>
       <c r="L589" s="6"/>
@@ -29952,8 +28776,6 @@
       <c r="E590" s="6"/>
       <c r="F590" s="6"/>
       <c r="G590" s="6"/>
-      <c r="H590" s="6"/>
-      <c r="I590" s="6"/>
       <c r="J590" s="6"/>
       <c r="K590" s="6"/>
       <c r="L590" s="6"/>
@@ -29969,8 +28791,6 @@
       <c r="E591" s="6"/>
       <c r="F591" s="6"/>
       <c r="G591" s="6"/>
-      <c r="H591" s="6"/>
-      <c r="I591" s="6"/>
       <c r="J591" s="6"/>
       <c r="K591" s="6"/>
       <c r="L591" s="6"/>
@@ -29986,8 +28806,6 @@
       <c r="E592" s="6"/>
       <c r="F592" s="6"/>
       <c r="G592" s="6"/>
-      <c r="H592" s="6"/>
-      <c r="I592" s="6"/>
       <c r="J592" s="6"/>
       <c r="K592" s="6"/>
       <c r="L592" s="6"/>
@@ -30003,8 +28821,6 @@
       <c r="E593" s="6"/>
       <c r="F593" s="6"/>
       <c r="G593" s="6"/>
-      <c r="H593" s="6"/>
-      <c r="I593" s="6"/>
       <c r="J593" s="6"/>
       <c r="K593" s="6"/>
       <c r="L593" s="6"/>
@@ -30020,8 +28836,6 @@
       <c r="E594" s="6"/>
       <c r="F594" s="6"/>
       <c r="G594" s="6"/>
-      <c r="H594" s="6"/>
-      <c r="I594" s="6"/>
       <c r="J594" s="6"/>
       <c r="K594" s="6"/>
       <c r="L594" s="6"/>
@@ -30037,8 +28851,6 @@
       <c r="E595" s="6"/>
       <c r="F595" s="6"/>
       <c r="G595" s="6"/>
-      <c r="H595" s="6"/>
-      <c r="I595" s="6"/>
       <c r="J595" s="6"/>
       <c r="K595" s="6"/>
       <c r="L595" s="6"/>
@@ -30054,8 +28866,6 @@
       <c r="E596" s="6"/>
       <c r="F596" s="6"/>
       <c r="G596" s="6"/>
-      <c r="H596" s="6"/>
-      <c r="I596" s="6"/>
       <c r="J596" s="6"/>
       <c r="K596" s="6"/>
       <c r="L596" s="6"/>
@@ -30071,8 +28881,6 @@
       <c r="E597" s="6"/>
       <c r="F597" s="6"/>
       <c r="G597" s="6"/>
-      <c r="H597" s="6"/>
-      <c r="I597" s="6"/>
       <c r="J597" s="6"/>
       <c r="K597" s="6"/>
       <c r="L597" s="6"/>
@@ -30088,8 +28896,6 @@
       <c r="E598" s="6"/>
       <c r="F598" s="6"/>
       <c r="G598" s="6"/>
-      <c r="H598" s="6"/>
-      <c r="I598" s="6"/>
       <c r="J598" s="6"/>
       <c r="K598" s="6"/>
       <c r="L598" s="6"/>
@@ -30105,8 +28911,6 @@
       <c r="E599" s="6"/>
       <c r="F599" s="6"/>
       <c r="G599" s="6"/>
-      <c r="H599" s="6"/>
-      <c r="I599" s="6"/>
       <c r="J599" s="6"/>
       <c r="K599" s="6"/>
       <c r="L599" s="6"/>
@@ -30122,8 +28926,6 @@
       <c r="E600" s="6"/>
       <c r="F600" s="6"/>
       <c r="G600" s="6"/>
-      <c r="H600" s="6"/>
-      <c r="I600" s="6"/>
       <c r="J600" s="6"/>
       <c r="K600" s="6"/>
       <c r="L600" s="6"/>
@@ -30139,8 +28941,6 @@
       <c r="E601" s="6"/>
       <c r="F601" s="6"/>
       <c r="G601" s="6"/>
-      <c r="H601" s="6"/>
-      <c r="I601" s="6"/>
       <c r="J601" s="6"/>
       <c r="K601" s="6"/>
       <c r="L601" s="6"/>
@@ -30156,8 +28956,6 @@
       <c r="E602" s="6"/>
       <c r="F602" s="6"/>
       <c r="G602" s="6"/>
-      <c r="H602" s="6"/>
-      <c r="I602" s="6"/>
       <c r="J602" s="6"/>
       <c r="K602" s="6"/>
       <c r="L602" s="6"/>
@@ -30173,8 +28971,6 @@
       <c r="E603" s="6"/>
       <c r="F603" s="6"/>
       <c r="G603" s="6"/>
-      <c r="H603" s="6"/>
-      <c r="I603" s="6"/>
       <c r="J603" s="6"/>
       <c r="K603" s="6"/>
       <c r="L603" s="6"/>
@@ -30190,8 +28986,6 @@
       <c r="E604" s="6"/>
       <c r="F604" s="6"/>
       <c r="G604" s="6"/>
-      <c r="H604" s="6"/>
-      <c r="I604" s="6"/>
       <c r="J604" s="6"/>
       <c r="K604" s="6"/>
       <c r="L604" s="6"/>
@@ -30207,8 +29001,6 @@
       <c r="E605" s="6"/>
       <c r="F605" s="6"/>
       <c r="G605" s="6"/>
-      <c r="H605" s="6"/>
-      <c r="I605" s="6"/>
       <c r="J605" s="6"/>
       <c r="K605" s="6"/>
       <c r="L605" s="6"/>
@@ -30224,8 +29016,6 @@
       <c r="E606" s="6"/>
       <c r="F606" s="6"/>
       <c r="G606" s="6"/>
-      <c r="H606" s="6"/>
-      <c r="I606" s="6"/>
       <c r="J606" s="6"/>
       <c r="K606" s="6"/>
       <c r="L606" s="6"/>
@@ -30241,8 +29031,6 @@
       <c r="E607" s="6"/>
       <c r="F607" s="6"/>
       <c r="G607" s="6"/>
-      <c r="H607" s="6"/>
-      <c r="I607" s="6"/>
       <c r="J607" s="6"/>
       <c r="K607" s="6"/>
       <c r="L607" s="6"/>
@@ -30258,8 +29046,6 @@
       <c r="E608" s="6"/>
       <c r="F608" s="6"/>
       <c r="G608" s="6"/>
-      <c r="H608" s="6"/>
-      <c r="I608" s="6"/>
       <c r="J608" s="6"/>
       <c r="K608" s="6"/>
       <c r="L608" s="6"/>
@@ -30275,8 +29061,6 @@
       <c r="E609" s="6"/>
       <c r="F609" s="6"/>
       <c r="G609" s="6"/>
-      <c r="H609" s="6"/>
-      <c r="I609" s="6"/>
       <c r="J609" s="6"/>
       <c r="K609" s="6"/>
       <c r="L609" s="6"/>
@@ -30292,8 +29076,6 @@
       <c r="E610" s="6"/>
       <c r="F610" s="6"/>
       <c r="G610" s="6"/>
-      <c r="H610" s="6"/>
-      <c r="I610" s="6"/>
       <c r="J610" s="6"/>
       <c r="K610" s="6"/>
       <c r="L610" s="6"/>
@@ -30309,8 +29091,6 @@
       <c r="E611" s="6"/>
       <c r="F611" s="6"/>
       <c r="G611" s="6"/>
-      <c r="H611" s="6"/>
-      <c r="I611" s="6"/>
       <c r="J611" s="6"/>
       <c r="K611" s="6"/>
       <c r="L611" s="6"/>
@@ -30326,8 +29106,6 @@
       <c r="E612" s="6"/>
       <c r="F612" s="6"/>
       <c r="G612" s="6"/>
-      <c r="H612" s="6"/>
-      <c r="I612" s="6"/>
       <c r="J612" s="6"/>
       <c r="K612" s="6"/>
       <c r="L612" s="6"/>
@@ -30343,8 +29121,6 @@
       <c r="E613" s="6"/>
       <c r="F613" s="6"/>
       <c r="G613" s="6"/>
-      <c r="H613" s="6"/>
-      <c r="I613" s="6"/>
       <c r="J613" s="6"/>
       <c r="K613" s="6"/>
       <c r="L613" s="6"/>
@@ -30360,8 +29136,6 @@
       <c r="E614" s="6"/>
       <c r="F614" s="6"/>
       <c r="G614" s="6"/>
-      <c r="H614" s="6"/>
-      <c r="I614" s="6"/>
       <c r="J614" s="6"/>
       <c r="K614" s="6"/>
       <c r="L614" s="6"/>
@@ -30377,8 +29151,6 @@
       <c r="E615" s="6"/>
       <c r="F615" s="6"/>
       <c r="G615" s="6"/>
-      <c r="H615" s="6"/>
-      <c r="I615" s="6"/>
       <c r="J615" s="6"/>
       <c r="K615" s="6"/>
       <c r="L615" s="6"/>
@@ -30394,8 +29166,6 @@
       <c r="E616" s="6"/>
       <c r="F616" s="6"/>
       <c r="G616" s="6"/>
-      <c r="H616" s="6"/>
-      <c r="I616" s="6"/>
       <c r="J616" s="6"/>
       <c r="K616" s="6"/>
       <c r="L616" s="6"/>
@@ -30411,8 +29181,6 @@
       <c r="E617" s="6"/>
       <c r="F617" s="6"/>
       <c r="G617" s="6"/>
-      <c r="H617" s="6"/>
-      <c r="I617" s="6"/>
       <c r="J617" s="6"/>
       <c r="K617" s="6"/>
       <c r="L617" s="6"/>
@@ -30428,8 +29196,6 @@
       <c r="E618" s="6"/>
       <c r="F618" s="6"/>
       <c r="G618" s="6"/>
-      <c r="H618" s="6"/>
-      <c r="I618" s="6"/>
       <c r="J618" s="6"/>
       <c r="K618" s="6"/>
       <c r="L618" s="6"/>
@@ -30445,8 +29211,6 @@
       <c r="E619" s="6"/>
       <c r="F619" s="6"/>
       <c r="G619" s="6"/>
-      <c r="H619" s="6"/>
-      <c r="I619" s="6"/>
       <c r="J619" s="6"/>
       <c r="K619" s="6"/>
       <c r="L619" s="6"/>
@@ -30462,8 +29226,6 @@
       <c r="E620" s="6"/>
       <c r="F620" s="6"/>
       <c r="G620" s="6"/>
-      <c r="H620" s="6"/>
-      <c r="I620" s="6"/>
       <c r="J620" s="6"/>
       <c r="K620" s="6"/>
       <c r="L620" s="6"/>
@@ -30479,8 +29241,6 @@
       <c r="E621" s="6"/>
       <c r="F621" s="6"/>
       <c r="G621" s="6"/>
-      <c r="H621" s="6"/>
-      <c r="I621" s="6"/>
       <c r="J621" s="6"/>
       <c r="K621" s="6"/>
       <c r="L621" s="6"/>
@@ -30496,8 +29256,6 @@
       <c r="E622" s="6"/>
       <c r="F622" s="6"/>
       <c r="G622" s="6"/>
-      <c r="H622" s="6"/>
-      <c r="I622" s="6"/>
       <c r="J622" s="6"/>
       <c r="K622" s="6"/>
       <c r="L622" s="6"/>
@@ -30513,8 +29271,6 @@
       <c r="E623" s="6"/>
       <c r="F623" s="6"/>
       <c r="G623" s="6"/>
-      <c r="H623" s="6"/>
-      <c r="I623" s="6"/>
       <c r="J623" s="6"/>
       <c r="K623" s="6"/>
       <c r="L623" s="6"/>
@@ -30530,8 +29286,6 @@
       <c r="E624" s="6"/>
       <c r="F624" s="6"/>
       <c r="G624" s="6"/>
-      <c r="H624" s="6"/>
-      <c r="I624" s="6"/>
       <c r="J624" s="6"/>
       <c r="K624" s="6"/>
       <c r="L624" s="6"/>
@@ -30547,8 +29301,6 @@
       <c r="E625" s="6"/>
       <c r="F625" s="6"/>
       <c r="G625" s="6"/>
-      <c r="H625" s="6"/>
-      <c r="I625" s="6"/>
       <c r="J625" s="6"/>
       <c r="K625" s="6"/>
       <c r="L625" s="6"/>
@@ -30564,8 +29316,6 @@
       <c r="E626" s="6"/>
       <c r="F626" s="6"/>
       <c r="G626" s="6"/>
-      <c r="H626" s="6"/>
-      <c r="I626" s="6"/>
       <c r="J626" s="6"/>
       <c r="K626" s="6"/>
       <c r="L626" s="6"/>
@@ -30581,8 +29331,6 @@
       <c r="E627" s="6"/>
       <c r="F627" s="6"/>
       <c r="G627" s="6"/>
-      <c r="H627" s="6"/>
-      <c r="I627" s="6"/>
       <c r="J627" s="6"/>
       <c r="K627" s="6"/>
       <c r="L627" s="6"/>
@@ -30598,8 +29346,6 @@
       <c r="E628" s="6"/>
       <c r="F628" s="6"/>
       <c r="G628" s="6"/>
-      <c r="H628" s="6"/>
-      <c r="I628" s="6"/>
       <c r="J628" s="6"/>
       <c r="K628" s="6"/>
       <c r="L628" s="6"/>
@@ -30615,8 +29361,6 @@
       <c r="E629" s="6"/>
       <c r="F629" s="6"/>
       <c r="G629" s="6"/>
-      <c r="H629" s="6"/>
-      <c r="I629" s="6"/>
       <c r="J629" s="6"/>
       <c r="K629" s="6"/>
       <c r="L629" s="6"/>
@@ -30632,8 +29376,6 @@
       <c r="E630" s="6"/>
       <c r="F630" s="6"/>
       <c r="G630" s="6"/>
-      <c r="H630" s="6"/>
-      <c r="I630" s="6"/>
       <c r="J630" s="6"/>
       <c r="K630" s="6"/>
       <c r="L630" s="6"/>
@@ -30649,8 +29391,6 @@
       <c r="E631" s="6"/>
       <c r="F631" s="6"/>
       <c r="G631" s="6"/>
-      <c r="H631" s="6"/>
-      <c r="I631" s="6"/>
       <c r="J631" s="6"/>
       <c r="K631" s="6"/>
       <c r="L631" s="6"/>
@@ -30666,8 +29406,6 @@
       <c r="E632" s="6"/>
       <c r="F632" s="6"/>
       <c r="G632" s="6"/>
-      <c r="H632" s="6"/>
-      <c r="I632" s="6"/>
       <c r="J632" s="6"/>
       <c r="K632" s="6"/>
       <c r="L632" s="6"/>
@@ -30683,8 +29421,6 @@
       <c r="E633" s="6"/>
       <c r="F633" s="6"/>
       <c r="G633" s="6"/>
-      <c r="H633" s="6"/>
-      <c r="I633" s="6"/>
       <c r="J633" s="6"/>
       <c r="K633" s="6"/>
       <c r="L633" s="6"/>
@@ -30700,8 +29436,6 @@
       <c r="E634" s="6"/>
       <c r="F634" s="6"/>
       <c r="G634" s="6"/>
-      <c r="H634" s="6"/>
-      <c r="I634" s="6"/>
       <c r="J634" s="6"/>
       <c r="K634" s="6"/>
       <c r="L634" s="6"/>
@@ -30717,8 +29451,6 @@
       <c r="E635" s="6"/>
       <c r="F635" s="6"/>
       <c r="G635" s="6"/>
-      <c r="H635" s="6"/>
-      <c r="I635" s="6"/>
       <c r="J635" s="6"/>
       <c r="K635" s="6"/>
       <c r="L635" s="6"/>
@@ -30734,8 +29466,6 @@
       <c r="E636" s="6"/>
       <c r="F636" s="6"/>
       <c r="G636" s="6"/>
-      <c r="H636" s="6"/>
-      <c r="I636" s="6"/>
       <c r="J636" s="6"/>
       <c r="K636" s="6"/>
       <c r="L636" s="6"/>
@@ -30751,8 +29481,6 @@
       <c r="E637" s="6"/>
       <c r="F637" s="6"/>
       <c r="G637" s="6"/>
-      <c r="H637" s="6"/>
-      <c r="I637" s="6"/>
       <c r="J637" s="6"/>
       <c r="K637" s="6"/>
       <c r="L637" s="6"/>
@@ -30768,8 +29496,6 @@
       <c r="E638" s="6"/>
       <c r="F638" s="6"/>
       <c r="G638" s="6"/>
-      <c r="H638" s="6"/>
-      <c r="I638" s="6"/>
       <c r="J638" s="6"/>
       <c r="K638" s="6"/>
       <c r="L638" s="6"/>
@@ -30785,8 +29511,6 @@
       <c r="E639" s="6"/>
       <c r="F639" s="6"/>
       <c r="G639" s="6"/>
-      <c r="H639" s="6"/>
-      <c r="I639" s="6"/>
       <c r="J639" s="6"/>
       <c r="K639" s="6"/>
       <c r="L639" s="6"/>
@@ -30802,8 +29526,6 @@
       <c r="E640" s="6"/>
       <c r="F640" s="6"/>
       <c r="G640" s="6"/>
-      <c r="H640" s="6"/>
-      <c r="I640" s="6"/>
       <c r="J640" s="6"/>
       <c r="K640" s="6"/>
       <c r="L640" s="6"/>
@@ -30819,8 +29541,6 @@
       <c r="E641" s="6"/>
       <c r="F641" s="6"/>
       <c r="G641" s="6"/>
-      <c r="H641" s="6"/>
-      <c r="I641" s="6"/>
       <c r="J641" s="6"/>
       <c r="K641" s="6"/>
       <c r="L641" s="6"/>
@@ -30836,8 +29556,6 @@
       <c r="E642" s="6"/>
       <c r="F642" s="6"/>
       <c r="G642" s="6"/>
-      <c r="H642" s="6"/>
-      <c r="I642" s="6"/>
       <c r="J642" s="6"/>
       <c r="K642" s="6"/>
       <c r="L642" s="6"/>
@@ -30853,8 +29571,6 @@
       <c r="E643" s="6"/>
       <c r="F643" s="6"/>
       <c r="G643" s="6"/>
-      <c r="H643" s="6"/>
-      <c r="I643" s="6"/>
       <c r="J643" s="6"/>
       <c r="K643" s="6"/>
       <c r="L643" s="6"/>
@@ -30870,8 +29586,6 @@
       <c r="E644" s="6"/>
       <c r="F644" s="6"/>
       <c r="G644" s="6"/>
-      <c r="H644" s="6"/>
-      <c r="I644" s="6"/>
       <c r="J644" s="6"/>
       <c r="K644" s="6"/>
       <c r="L644" s="6"/>
@@ -30887,8 +29601,6 @@
       <c r="E645" s="6"/>
       <c r="F645" s="6"/>
       <c r="G645" s="6"/>
-      <c r="H645" s="6"/>
-      <c r="I645" s="6"/>
       <c r="J645" s="6"/>
       <c r="K645" s="6"/>
       <c r="L645" s="6"/>
@@ -30904,8 +29616,6 @@
       <c r="E646" s="6"/>
       <c r="F646" s="6"/>
       <c r="G646" s="6"/>
-      <c r="H646" s="6"/>
-      <c r="I646" s="6"/>
       <c r="J646" s="6"/>
       <c r="K646" s="6"/>
       <c r="L646" s="6"/>
@@ -30921,8 +29631,6 @@
       <c r="E647" s="6"/>
       <c r="F647" s="6"/>
       <c r="G647" s="6"/>
-      <c r="H647" s="6"/>
-      <c r="I647" s="6"/>
       <c r="J647" s="6"/>
       <c r="K647" s="6"/>
       <c r="L647" s="6"/>
@@ -30938,8 +29646,6 @@
       <c r="E648" s="6"/>
       <c r="F648" s="6"/>
       <c r="G648" s="6"/>
-      <c r="H648" s="6"/>
-      <c r="I648" s="6"/>
       <c r="J648" s="6"/>
       <c r="K648" s="6"/>
       <c r="L648" s="6"/>
@@ -30955,8 +29661,6 @@
       <c r="E649" s="6"/>
       <c r="F649" s="6"/>
       <c r="G649" s="6"/>
-      <c r="H649" s="6"/>
-      <c r="I649" s="6"/>
       <c r="J649" s="6"/>
       <c r="K649" s="6"/>
       <c r="L649" s="6"/>
@@ -30972,8 +29676,6 @@
       <c r="E650" s="6"/>
       <c r="F650" s="6"/>
       <c r="G650" s="6"/>
-      <c r="H650" s="6"/>
-      <c r="I650" s="6"/>
       <c r="J650" s="6"/>
       <c r="K650" s="6"/>
       <c r="L650" s="6"/>
@@ -30989,8 +29691,6 @@
       <c r="E651" s="6"/>
       <c r="F651" s="6"/>
       <c r="G651" s="6"/>
-      <c r="H651" s="6"/>
-      <c r="I651" s="6"/>
       <c r="J651" s="6"/>
       <c r="K651" s="6"/>
       <c r="L651" s="6"/>
@@ -31006,8 +29706,6 @@
       <c r="E652" s="6"/>
       <c r="F652" s="6"/>
       <c r="G652" s="6"/>
-      <c r="H652" s="6"/>
-      <c r="I652" s="6"/>
       <c r="J652" s="6"/>
       <c r="K652" s="6"/>
       <c r="L652" s="6"/>
@@ -31023,8 +29721,6 @@
       <c r="E653" s="6"/>
       <c r="F653" s="6"/>
       <c r="G653" s="6"/>
-      <c r="H653" s="6"/>
-      <c r="I653" s="6"/>
       <c r="J653" s="6"/>
       <c r="K653" s="6"/>
       <c r="L653" s="6"/>
@@ -31040,8 +29736,6 @@
       <c r="E654" s="6"/>
       <c r="F654" s="6"/>
       <c r="G654" s="6"/>
-      <c r="H654" s="6"/>
-      <c r="I654" s="6"/>
       <c r="J654" s="6"/>
       <c r="K654" s="6"/>
       <c r="L654" s="6"/>
@@ -31057,8 +29751,6 @@
       <c r="E655" s="6"/>
       <c r="F655" s="6"/>
       <c r="G655" s="6"/>
-      <c r="H655" s="6"/>
-      <c r="I655" s="6"/>
       <c r="J655" s="6"/>
       <c r="K655" s="6"/>
       <c r="L655" s="6"/>
@@ -31074,8 +29766,6 @@
       <c r="E656" s="6"/>
       <c r="F656" s="6"/>
       <c r="G656" s="6"/>
-      <c r="H656" s="6"/>
-      <c r="I656" s="6"/>
       <c r="J656" s="6"/>
       <c r="K656" s="6"/>
       <c r="L656" s="6"/>
@@ -31091,8 +29781,6 @@
       <c r="E657" s="6"/>
       <c r="F657" s="6"/>
       <c r="G657" s="6"/>
-      <c r="H657" s="6"/>
-      <c r="I657" s="6"/>
       <c r="J657" s="6"/>
       <c r="K657" s="6"/>
       <c r="L657" s="6"/>
@@ -31108,8 +29796,6 @@
       <c r="E658" s="6"/>
       <c r="F658" s="6"/>
       <c r="G658" s="6"/>
-      <c r="H658" s="6"/>
-      <c r="I658" s="6"/>
       <c r="J658" s="6"/>
       <c r="K658" s="6"/>
       <c r="L658" s="6"/>
@@ -31125,8 +29811,6 @@
       <c r="E659" s="6"/>
       <c r="F659" s="6"/>
       <c r="G659" s="6"/>
-      <c r="H659" s="6"/>
-      <c r="I659" s="6"/>
       <c r="J659" s="6"/>
       <c r="K659" s="6"/>
       <c r="L659" s="6"/>
@@ -31142,8 +29826,6 @@
       <c r="E660" s="6"/>
       <c r="F660" s="6"/>
       <c r="G660" s="6"/>
-      <c r="H660" s="6"/>
-      <c r="I660" s="6"/>
       <c r="J660" s="6"/>
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
@@ -31159,8 +29841,6 @@
       <c r="E661" s="6"/>
       <c r="F661" s="6"/>
       <c r="G661" s="6"/>
-      <c r="H661" s="6"/>
-      <c r="I661" s="6"/>
       <c r="J661" s="6"/>
       <c r="K661" s="6"/>
       <c r="L661" s="6"/>
@@ -31176,8 +29856,6 @@
       <c r="E662" s="6"/>
       <c r="F662" s="6"/>
       <c r="G662" s="6"/>
-      <c r="H662" s="6"/>
-      <c r="I662" s="6"/>
       <c r="J662" s="6"/>
       <c r="K662" s="6"/>
       <c r="L662" s="6"/>
@@ -31193,8 +29871,6 @@
       <c r="E663" s="6"/>
       <c r="F663" s="6"/>
       <c r="G663" s="6"/>
-      <c r="H663" s="6"/>
-      <c r="I663" s="6"/>
       <c r="J663" s="6"/>
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
@@ -31210,8 +29886,6 @@
       <c r="E664" s="6"/>
       <c r="F664" s="6"/>
       <c r="G664" s="6"/>
-      <c r="H664" s="6"/>
-      <c r="I664" s="6"/>
       <c r="J664" s="6"/>
       <c r="K664" s="6"/>
       <c r="L664" s="6"/>
@@ -31227,8 +29901,6 @@
       <c r="E665" s="6"/>
       <c r="F665" s="6"/>
       <c r="G665" s="6"/>
-      <c r="H665" s="6"/>
-      <c r="I665" s="6"/>
       <c r="J665" s="6"/>
       <c r="K665" s="6"/>
       <c r="L665" s="6"/>
@@ -31244,8 +29916,6 @@
       <c r="E666" s="6"/>
       <c r="F666" s="6"/>
       <c r="G666" s="6"/>
-      <c r="H666" s="6"/>
-      <c r="I666" s="6"/>
       <c r="J666" s="6"/>
       <c r="K666" s="6"/>
       <c r="L666" s="6"/>
@@ -31261,8 +29931,6 @@
       <c r="E667" s="6"/>
       <c r="F667" s="6"/>
       <c r="G667" s="6"/>
-      <c r="H667" s="6"/>
-      <c r="I667" s="6"/>
       <c r="J667" s="6"/>
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
@@ -31278,8 +29946,6 @@
       <c r="E668" s="6"/>
       <c r="F668" s="6"/>
       <c r="G668" s="6"/>
-      <c r="H668" s="6"/>
-      <c r="I668" s="6"/>
       <c r="J668" s="6"/>
       <c r="K668" s="6"/>
       <c r="L668" s="6"/>
@@ -31295,8 +29961,6 @@
       <c r="E669" s="6"/>
       <c r="F669" s="6"/>
       <c r="G669" s="6"/>
-      <c r="H669" s="6"/>
-      <c r="I669" s="6"/>
       <c r="J669" s="6"/>
       <c r="K669" s="6"/>
       <c r="L669" s="6"/>
@@ -31312,8 +29976,6 @@
       <c r="E670" s="6"/>
       <c r="F670" s="6"/>
       <c r="G670" s="6"/>
-      <c r="H670" s="6"/>
-      <c r="I670" s="6"/>
       <c r="J670" s="6"/>
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
@@ -31329,8 +29991,6 @@
       <c r="E671" s="6"/>
       <c r="F671" s="6"/>
       <c r="G671" s="6"/>
-      <c r="H671" s="6"/>
-      <c r="I671" s="6"/>
       <c r="J671" s="6"/>
       <c r="K671" s="6"/>
       <c r="L671" s="6"/>
@@ -31346,8 +30006,6 @@
       <c r="E672" s="6"/>
       <c r="F672" s="6"/>
       <c r="G672" s="6"/>
-      <c r="H672" s="6"/>
-      <c r="I672" s="6"/>
       <c r="J672" s="6"/>
       <c r="K672" s="6"/>
       <c r="L672" s="6"/>
@@ -31363,8 +30021,6 @@
       <c r="E673" s="6"/>
       <c r="F673" s="6"/>
       <c r="G673" s="6"/>
-      <c r="H673" s="6"/>
-      <c r="I673" s="6"/>
       <c r="J673" s="6"/>
       <c r="K673" s="6"/>
       <c r="L673" s="6"/>
@@ -31380,8 +30036,6 @@
       <c r="E674" s="6"/>
       <c r="F674" s="6"/>
       <c r="G674" s="6"/>
-      <c r="H674" s="6"/>
-      <c r="I674" s="6"/>
       <c r="J674" s="6"/>
       <c r="K674" s="6"/>
       <c r="L674" s="6"/>
@@ -31397,8 +30051,6 @@
       <c r="E675" s="6"/>
       <c r="F675" s="6"/>
       <c r="G675" s="6"/>
-      <c r="H675" s="6"/>
-      <c r="I675" s="6"/>
       <c r="J675" s="6"/>
       <c r="K675" s="6"/>
       <c r="L675" s="6"/>
@@ -31414,8 +30066,6 @@
       <c r="E676" s="6"/>
       <c r="F676" s="6"/>
       <c r="G676" s="6"/>
-      <c r="H676" s="6"/>
-      <c r="I676" s="6"/>
       <c r="J676" s="6"/>
       <c r="K676" s="6"/>
       <c r="L676" s="6"/>
@@ -31431,8 +30081,6 @@
       <c r="E677" s="6"/>
       <c r="F677" s="6"/>
       <c r="G677" s="6"/>
-      <c r="H677" s="6"/>
-      <c r="I677" s="6"/>
       <c r="J677" s="6"/>
       <c r="K677" s="6"/>
       <c r="L677" s="6"/>
@@ -31448,8 +30096,6 @@
       <c r="E678" s="6"/>
       <c r="F678" s="6"/>
       <c r="G678" s="6"/>
-      <c r="H678" s="6"/>
-      <c r="I678" s="6"/>
       <c r="J678" s="6"/>
       <c r="K678" s="6"/>
       <c r="L678" s="6"/>
@@ -31465,8 +30111,6 @@
       <c r="E679" s="6"/>
       <c r="F679" s="6"/>
       <c r="G679" s="6"/>
-      <c r="H679" s="6"/>
-      <c r="I679" s="6"/>
       <c r="J679" s="6"/>
       <c r="K679" s="6"/>
       <c r="L679" s="6"/>
@@ -31482,8 +30126,6 @@
       <c r="E680" s="6"/>
       <c r="F680" s="6"/>
       <c r="G680" s="6"/>
-      <c r="H680" s="6"/>
-      <c r="I680" s="6"/>
       <c r="J680" s="6"/>
       <c r="K680" s="6"/>
       <c r="L680" s="6"/>
@@ -31499,8 +30141,6 @@
       <c r="E681" s="6"/>
       <c r="F681" s="6"/>
       <c r="G681" s="6"/>
-      <c r="H681" s="6"/>
-      <c r="I681" s="6"/>
       <c r="J681" s="6"/>
       <c r="K681" s="6"/>
       <c r="L681" s="6"/>
@@ -31516,8 +30156,6 @@
       <c r="E682" s="6"/>
       <c r="F682" s="6"/>
       <c r="G682" s="6"/>
-      <c r="H682" s="6"/>
-      <c r="I682" s="6"/>
       <c r="J682" s="6"/>
       <c r="K682" s="6"/>
       <c r="L682" s="6"/>
@@ -31533,8 +30171,6 @@
       <c r="E683" s="6"/>
       <c r="F683" s="6"/>
       <c r="G683" s="6"/>
-      <c r="H683" s="6"/>
-      <c r="I683" s="6"/>
       <c r="J683" s="6"/>
       <c r="K683" s="6"/>
       <c r="L683" s="6"/>
@@ -31550,8 +30186,6 @@
       <c r="E684" s="6"/>
       <c r="F684" s="6"/>
       <c r="G684" s="6"/>
-      <c r="H684" s="6"/>
-      <c r="I684" s="6"/>
       <c r="J684" s="6"/>
       <c r="K684" s="6"/>
       <c r="L684" s="6"/>
@@ -31567,8 +30201,6 @@
       <c r="E685" s="6"/>
       <c r="F685" s="6"/>
       <c r="G685" s="6"/>
-      <c r="H685" s="6"/>
-      <c r="I685" s="6"/>
       <c r="J685" s="6"/>
       <c r="K685" s="6"/>
       <c r="L685" s="6"/>
@@ -31584,8 +30216,6 @@
       <c r="E686" s="6"/>
       <c r="F686" s="6"/>
       <c r="G686" s="6"/>
-      <c r="H686" s="6"/>
-      <c r="I686" s="6"/>
       <c r="J686" s="6"/>
       <c r="K686" s="6"/>
       <c r="L686" s="6"/>
@@ -31601,8 +30231,6 @@
       <c r="E687" s="6"/>
       <c r="F687" s="6"/>
       <c r="G687" s="6"/>
-      <c r="H687" s="6"/>
-      <c r="I687" s="6"/>
       <c r="J687" s="6"/>
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
@@ -31618,8 +30246,6 @@
       <c r="E688" s="6"/>
       <c r="F688" s="6"/>
       <c r="G688" s="6"/>
-      <c r="H688" s="6"/>
-      <c r="I688" s="6"/>
       <c r="J688" s="6"/>
       <c r="K688" s="6"/>
       <c r="L688" s="6"/>
@@ -31635,8 +30261,6 @@
       <c r="E689" s="6"/>
       <c r="F689" s="6"/>
       <c r="G689" s="6"/>
-      <c r="H689" s="6"/>
-      <c r="I689" s="6"/>
       <c r="J689" s="6"/>
       <c r="K689" s="6"/>
       <c r="L689" s="6"/>
@@ -31652,8 +30276,6 @@
       <c r="E690" s="6"/>
       <c r="F690" s="6"/>
       <c r="G690" s="6"/>
-      <c r="H690" s="6"/>
-      <c r="I690" s="6"/>
       <c r="J690" s="6"/>
       <c r="K690" s="6"/>
       <c r="L690" s="6"/>
@@ -31669,8 +30291,6 @@
       <c r="E691" s="6"/>
       <c r="F691" s="6"/>
       <c r="G691" s="6"/>
-      <c r="H691" s="6"/>
-      <c r="I691" s="6"/>
       <c r="J691" s="6"/>
       <c r="K691" s="6"/>
       <c r="L691" s="6"/>
@@ -31686,8 +30306,6 @@
       <c r="E692" s="6"/>
       <c r="F692" s="6"/>
       <c r="G692" s="6"/>
-      <c r="H692" s="6"/>
-      <c r="I692" s="6"/>
       <c r="J692" s="6"/>
       <c r="K692" s="6"/>
       <c r="L692" s="6"/>
@@ -31703,8 +30321,6 @@
       <c r="E693" s="6"/>
       <c r="F693" s="6"/>
       <c r="G693" s="6"/>
-      <c r="H693" s="6"/>
-      <c r="I693" s="6"/>
       <c r="J693" s="6"/>
       <c r="K693" s="6"/>
       <c r="L693" s="6"/>
@@ -31720,8 +30336,6 @@
       <c r="E694" s="6"/>
       <c r="F694" s="6"/>
       <c r="G694" s="6"/>
-      <c r="H694" s="6"/>
-      <c r="I694" s="6"/>
       <c r="J694" s="6"/>
       <c r="K694" s="6"/>
       <c r="L694" s="6"/>
@@ -31737,8 +30351,6 @@
       <c r="E695" s="6"/>
       <c r="F695" s="6"/>
       <c r="G695" s="6"/>
-      <c r="H695" s="6"/>
-      <c r="I695" s="6"/>
       <c r="J695" s="6"/>
       <c r="K695" s="6"/>
       <c r="L695" s="6"/>
@@ -31754,8 +30366,6 @@
       <c r="E696" s="6"/>
       <c r="F696" s="6"/>
       <c r="G696" s="6"/>
-      <c r="H696" s="6"/>
-      <c r="I696" s="6"/>
       <c r="J696" s="6"/>
       <c r="K696" s="6"/>
       <c r="L696" s="6"/>
@@ -31771,8 +30381,6 @@
       <c r="E697" s="6"/>
       <c r="F697" s="6"/>
       <c r="G697" s="6"/>
-      <c r="H697" s="6"/>
-      <c r="I697" s="6"/>
       <c r="J697" s="6"/>
       <c r="K697" s="6"/>
       <c r="L697" s="6"/>
@@ -31788,8 +30396,6 @@
       <c r="E698" s="6"/>
       <c r="F698" s="6"/>
       <c r="G698" s="6"/>
-      <c r="H698" s="6"/>
-      <c r="I698" s="6"/>
       <c r="J698" s="6"/>
       <c r="K698" s="6"/>
       <c r="L698" s="6"/>
@@ -31805,8 +30411,6 @@
       <c r="E699" s="6"/>
       <c r="F699" s="6"/>
       <c r="G699" s="6"/>
-      <c r="H699" s="6"/>
-      <c r="I699" s="6"/>
       <c r="J699" s="6"/>
       <c r="K699" s="6"/>
       <c r="L699" s="6"/>
@@ -31822,8 +30426,6 @@
       <c r="E700" s="6"/>
       <c r="F700" s="6"/>
       <c r="G700" s="6"/>
-      <c r="H700" s="6"/>
-      <c r="I700" s="6"/>
       <c r="J700" s="6"/>
       <c r="K700" s="6"/>
       <c r="L700" s="6"/>
@@ -31839,8 +30441,6 @@
       <c r="E701" s="6"/>
       <c r="F701" s="6"/>
       <c r="G701" s="6"/>
-      <c r="H701" s="6"/>
-      <c r="I701" s="6"/>
       <c r="J701" s="6"/>
       <c r="K701" s="6"/>
       <c r="L701" s="6"/>
@@ -31856,8 +30456,6 @@
       <c r="E702" s="6"/>
       <c r="F702" s="6"/>
       <c r="G702" s="6"/>
-      <c r="H702" s="6"/>
-      <c r="I702" s="6"/>
       <c r="J702" s="6"/>
       <c r="K702" s="6"/>
       <c r="L702" s="6"/>
@@ -31873,8 +30471,6 @@
       <c r="E703" s="6"/>
       <c r="F703" s="6"/>
       <c r="G703" s="6"/>
-      <c r="H703" s="6"/>
-      <c r="I703" s="6"/>
       <c r="J703" s="6"/>
       <c r="K703" s="6"/>
       <c r="L703" s="6"/>
@@ -31890,8 +30486,6 @@
       <c r="E704" s="6"/>
       <c r="F704" s="6"/>
       <c r="G704" s="6"/>
-      <c r="H704" s="6"/>
-      <c r="I704" s="6"/>
       <c r="J704" s="6"/>
       <c r="K704" s="6"/>
       <c r="L704" s="6"/>
@@ -31907,8 +30501,6 @@
       <c r="E705" s="6"/>
       <c r="F705" s="6"/>
       <c r="G705" s="6"/>
-      <c r="H705" s="6"/>
-      <c r="I705" s="6"/>
       <c r="J705" s="6"/>
       <c r="K705" s="6"/>
       <c r="L705" s="6"/>
@@ -31924,8 +30516,6 @@
       <c r="E706" s="6"/>
       <c r="F706" s="6"/>
       <c r="G706" s="6"/>
-      <c r="H706" s="6"/>
-      <c r="I706" s="6"/>
       <c r="J706" s="6"/>
       <c r="K706" s="6"/>
       <c r="L706" s="6"/>
@@ -31941,8 +30531,6 @@
       <c r="E707" s="6"/>
       <c r="F707" s="6"/>
       <c r="G707" s="6"/>
-      <c r="H707" s="6"/>
-      <c r="I707" s="6"/>
       <c r="J707" s="6"/>
       <c r="K707" s="6"/>
       <c r="L707" s="6"/>
@@ -31958,8 +30546,6 @@
       <c r="E708" s="6"/>
       <c r="F708" s="6"/>
       <c r="G708" s="6"/>
-      <c r="H708" s="6"/>
-      <c r="I708" s="6"/>
       <c r="J708" s="6"/>
       <c r="K708" s="6"/>
       <c r="L708" s="6"/>
@@ -31975,8 +30561,6 @@
       <c r="E709" s="6"/>
       <c r="F709" s="6"/>
       <c r="G709" s="6"/>
-      <c r="H709" s="6"/>
-      <c r="I709" s="6"/>
       <c r="J709" s="6"/>
       <c r="K709" s="6"/>
       <c r="L709" s="6"/>
@@ -31992,8 +30576,6 @@
       <c r="E710" s="6"/>
       <c r="F710" s="6"/>
       <c r="G710" s="6"/>
-      <c r="H710" s="6"/>
-      <c r="I710" s="6"/>
       <c r="J710" s="6"/>
       <c r="K710" s="6"/>
       <c r="L710" s="6"/>
@@ -32009,8 +30591,6 @@
       <c r="E711" s="6"/>
       <c r="F711" s="6"/>
       <c r="G711" s="6"/>
-      <c r="H711" s="6"/>
-      <c r="I711" s="6"/>
       <c r="J711" s="6"/>
       <c r="K711" s="6"/>
       <c r="L711" s="6"/>
@@ -32026,8 +30606,6 @@
       <c r="E712" s="6"/>
       <c r="F712" s="6"/>
       <c r="G712" s="6"/>
-      <c r="H712" s="6"/>
-      <c r="I712" s="6"/>
       <c r="J712" s="6"/>
       <c r="K712" s="6"/>
       <c r="L712" s="6"/>
@@ -32043,8 +30621,6 @@
       <c r="E713" s="6"/>
       <c r="F713" s="6"/>
       <c r="G713" s="6"/>
-      <c r="H713" s="6"/>
-      <c r="I713" s="6"/>
       <c r="J713" s="6"/>
       <c r="K713" s="6"/>
       <c r="L713" s="6"/>
@@ -32060,8 +30636,6 @@
       <c r="E714" s="6"/>
       <c r="F714" s="6"/>
       <c r="G714" s="6"/>
-      <c r="H714" s="6"/>
-      <c r="I714" s="6"/>
       <c r="J714" s="6"/>
       <c r="K714" s="6"/>
       <c r="L714" s="6"/>
@@ -32077,8 +30651,6 @@
       <c r="E715" s="6"/>
       <c r="F715" s="6"/>
       <c r="G715" s="6"/>
-      <c r="H715" s="6"/>
-      <c r="I715" s="6"/>
       <c r="J715" s="6"/>
       <c r="K715" s="6"/>
       <c r="L715" s="6"/>
@@ -32094,8 +30666,6 @@
       <c r="E716" s="6"/>
       <c r="F716" s="6"/>
       <c r="G716" s="6"/>
-      <c r="H716" s="6"/>
-      <c r="I716" s="6"/>
       <c r="J716" s="6"/>
       <c r="K716" s="6"/>
       <c r="L716" s="6"/>
@@ -32111,8 +30681,6 @@
       <c r="E717" s="6"/>
       <c r="F717" s="6"/>
       <c r="G717" s="6"/>
-      <c r="H717" s="6"/>
-      <c r="I717" s="6"/>
       <c r="J717" s="6"/>
       <c r="K717" s="6"/>
       <c r="L717" s="6"/>
@@ -32128,8 +30696,6 @@
       <c r="E718" s="6"/>
       <c r="F718" s="6"/>
       <c r="G718" s="6"/>
-      <c r="H718" s="6"/>
-      <c r="I718" s="6"/>
       <c r="J718" s="6"/>
       <c r="K718" s="6"/>
       <c r="L718" s="6"/>
@@ -32145,8 +30711,6 @@
       <c r="E719" s="6"/>
       <c r="F719" s="6"/>
       <c r="G719" s="6"/>
-      <c r="H719" s="6"/>
-      <c r="I719" s="6"/>
       <c r="J719" s="6"/>
       <c r="K719" s="6"/>
       <c r="L719" s="6"/>
@@ -32162,8 +30726,6 @@
       <c r="E720" s="6"/>
       <c r="F720" s="6"/>
       <c r="G720" s="6"/>
-      <c r="H720" s="6"/>
-      <c r="I720" s="6"/>
       <c r="J720" s="6"/>
       <c r="K720" s="6"/>
       <c r="L720" s="6"/>
@@ -32179,8 +30741,6 @@
       <c r="E721" s="6"/>
       <c r="F721" s="6"/>
       <c r="G721" s="6"/>
-      <c r="H721" s="6"/>
-      <c r="I721" s="6"/>
       <c r="J721" s="6"/>
       <c r="K721" s="6"/>
       <c r="L721" s="6"/>
@@ -32196,8 +30756,6 @@
       <c r="E722" s="6"/>
       <c r="F722" s="6"/>
       <c r="G722" s="6"/>
-      <c r="H722" s="6"/>
-      <c r="I722" s="6"/>
       <c r="J722" s="6"/>
       <c r="K722" s="6"/>
       <c r="L722" s="6"/>
@@ -32213,8 +30771,6 @@
       <c r="E723" s="6"/>
       <c r="F723" s="6"/>
       <c r="G723" s="6"/>
-      <c r="H723" s="6"/>
-      <c r="I723" s="6"/>
       <c r="J723" s="6"/>
       <c r="K723" s="6"/>
       <c r="L723" s="6"/>
@@ -32230,8 +30786,6 @@
       <c r="E724" s="6"/>
       <c r="F724" s="6"/>
       <c r="G724" s="6"/>
-      <c r="H724" s="6"/>
-      <c r="I724" s="6"/>
       <c r="J724" s="6"/>
       <c r="K724" s="6"/>
       <c r="L724" s="6"/>
@@ -32247,8 +30801,6 @@
       <c r="E725" s="6"/>
       <c r="F725" s="6"/>
       <c r="G725" s="6"/>
-      <c r="H725" s="6"/>
-      <c r="I725" s="6"/>
       <c r="J725" s="6"/>
       <c r="K725" s="6"/>
       <c r="L725" s="6"/>
@@ -32264,8 +30816,6 @@
       <c r="E726" s="6"/>
       <c r="F726" s="6"/>
       <c r="G726" s="6"/>
-      <c r="H726" s="6"/>
-      <c r="I726" s="6"/>
       <c r="J726" s="6"/>
       <c r="K726" s="6"/>
       <c r="L726" s="6"/>
@@ -32281,8 +30831,6 @@
       <c r="E727" s="6"/>
       <c r="F727" s="6"/>
       <c r="G727" s="6"/>
-      <c r="H727" s="6"/>
-      <c r="I727" s="6"/>
       <c r="J727" s="6"/>
       <c r="K727" s="6"/>
       <c r="L727" s="6"/>
@@ -32298,8 +30846,6 @@
       <c r="E728" s="6"/>
       <c r="F728" s="6"/>
       <c r="G728" s="6"/>
-      <c r="H728" s="6"/>
-      <c r="I728" s="6"/>
       <c r="J728" s="6"/>
       <c r="K728" s="6"/>
       <c r="L728" s="6"/>
@@ -32315,8 +30861,6 @@
       <c r="E729" s="6"/>
       <c r="F729" s="6"/>
       <c r="G729" s="6"/>
-      <c r="H729" s="6"/>
-      <c r="I729" s="6"/>
       <c r="J729" s="6"/>
       <c r="K729" s="6"/>
       <c r="L729" s="6"/>
@@ -32332,8 +30876,6 @@
       <c r="E730" s="6"/>
       <c r="F730" s="6"/>
       <c r="G730" s="6"/>
-      <c r="H730" s="6"/>
-      <c r="I730" s="6"/>
       <c r="J730" s="6"/>
       <c r="K730" s="6"/>
       <c r="L730" s="6"/>
@@ -32349,8 +30891,6 @@
       <c r="E731" s="6"/>
       <c r="F731" s="6"/>
       <c r="G731" s="6"/>
-      <c r="H731" s="6"/>
-      <c r="I731" s="6"/>
       <c r="J731" s="6"/>
       <c r="K731" s="6"/>
       <c r="L731" s="6"/>
@@ -32366,8 +30906,6 @@
       <c r="E732" s="6"/>
       <c r="F732" s="6"/>
       <c r="G732" s="6"/>
-      <c r="H732" s="6"/>
-      <c r="I732" s="6"/>
       <c r="J732" s="6"/>
       <c r="K732" s="6"/>
       <c r="L732" s="6"/>
@@ -32383,8 +30921,6 @@
       <c r="E733" s="6"/>
       <c r="F733" s="6"/>
       <c r="G733" s="6"/>
-      <c r="H733" s="6"/>
-      <c r="I733" s="6"/>
       <c r="J733" s="6"/>
       <c r="K733" s="6"/>
       <c r="L733" s="6"/>
@@ -32400,8 +30936,6 @@
       <c r="E734" s="6"/>
       <c r="F734" s="6"/>
       <c r="G734" s="6"/>
-      <c r="H734" s="6"/>
-      <c r="I734" s="6"/>
       <c r="J734" s="6"/>
       <c r="K734" s="6"/>
       <c r="L734" s="6"/>
@@ -32417,8 +30951,6 @@
       <c r="E735" s="6"/>
       <c r="F735" s="6"/>
       <c r="G735" s="6"/>
-      <c r="H735" s="6"/>
-      <c r="I735" s="6"/>
       <c r="J735" s="6"/>
       <c r="K735" s="6"/>
       <c r="L735" s="6"/>
@@ -32434,8 +30966,6 @@
       <c r="E736" s="6"/>
       <c r="F736" s="6"/>
       <c r="G736" s="6"/>
-      <c r="H736" s="6"/>
-      <c r="I736" s="6"/>
       <c r="J736" s="6"/>
       <c r="K736" s="6"/>
       <c r="L736" s="6"/>
@@ -32451,8 +30981,6 @@
       <c r="E737" s="6"/>
       <c r="F737" s="6"/>
       <c r="G737" s="6"/>
-      <c r="H737" s="6"/>
-      <c r="I737" s="6"/>
       <c r="J737" s="6"/>
       <c r="K737" s="6"/>
       <c r="L737" s="6"/>
@@ -32468,8 +30996,6 @@
       <c r="E738" s="6"/>
       <c r="F738" s="6"/>
       <c r="G738" s="6"/>
-      <c r="H738" s="6"/>
-      <c r="I738" s="6"/>
       <c r="J738" s="6"/>
       <c r="K738" s="6"/>
       <c r="L738" s="6"/>
@@ -32485,8 +31011,6 @@
       <c r="E739" s="6"/>
       <c r="F739" s="6"/>
       <c r="G739" s="6"/>
-      <c r="H739" s="6"/>
-      <c r="I739" s="6"/>
       <c r="J739" s="6"/>
       <c r="K739" s="6"/>
       <c r="L739" s="6"/>
@@ -32502,8 +31026,6 @@
       <c r="E740" s="6"/>
       <c r="F740" s="6"/>
       <c r="G740" s="6"/>
-      <c r="H740" s="6"/>
-      <c r="I740" s="6"/>
       <c r="J740" s="6"/>
       <c r="K740" s="6"/>
       <c r="L740" s="6"/>
@@ -32519,8 +31041,6 @@
       <c r="E741" s="6"/>
       <c r="F741" s="6"/>
       <c r="G741" s="6"/>
-      <c r="H741" s="6"/>
-      <c r="I741" s="6"/>
       <c r="J741" s="6"/>
       <c r="K741" s="6"/>
       <c r="L741" s="6"/>
@@ -32536,8 +31056,6 @@
       <c r="E742" s="6"/>
       <c r="F742" s="6"/>
       <c r="G742" s="6"/>
-      <c r="H742" s="6"/>
-      <c r="I742" s="6"/>
       <c r="J742" s="6"/>
       <c r="K742" s="6"/>
       <c r="L742" s="6"/>
@@ -32553,8 +31071,6 @@
       <c r="E743" s="6"/>
       <c r="F743" s="6"/>
       <c r="G743" s="6"/>
-      <c r="H743" s="6"/>
-      <c r="I743" s="6"/>
       <c r="J743" s="6"/>
       <c r="K743" s="6"/>
       <c r="L743" s="6"/>
@@ -32570,8 +31086,6 @@
       <c r="E744" s="6"/>
       <c r="F744" s="6"/>
       <c r="G744" s="6"/>
-      <c r="H744" s="6"/>
-      <c r="I744" s="6"/>
       <c r="J744" s="6"/>
       <c r="K744" s="6"/>
       <c r="L744" s="6"/>
@@ -32587,8 +31101,6 @@
       <c r="E745" s="6"/>
       <c r="F745" s="6"/>
       <c r="G745" s="6"/>
-      <c r="H745" s="6"/>
-      <c r="I745" s="6"/>
       <c r="J745" s="6"/>
       <c r="K745" s="6"/>
       <c r="L745" s="6"/>
@@ -32604,8 +31116,6 @@
       <c r="E746" s="6"/>
       <c r="F746" s="6"/>
       <c r="G746" s="6"/>
-      <c r="H746" s="6"/>
-      <c r="I746" s="6"/>
       <c r="J746" s="6"/>
       <c r="K746" s="6"/>
       <c r="L746" s="6"/>
@@ -32621,8 +31131,6 @@
       <c r="E747" s="6"/>
       <c r="F747" s="6"/>
       <c r="G747" s="6"/>
-      <c r="H747" s="6"/>
-      <c r="I747" s="6"/>
       <c r="J747" s="6"/>
       <c r="K747" s="6"/>
       <c r="L747" s="6"/>
@@ -32638,8 +31146,6 @@
       <c r="E748" s="6"/>
       <c r="F748" s="6"/>
       <c r="G748" s="6"/>
-      <c r="H748" s="6"/>
-      <c r="I748" s="6"/>
       <c r="J748" s="6"/>
       <c r="K748" s="6"/>
       <c r="L748" s="6"/>
@@ -32655,8 +31161,6 @@
       <c r="E749" s="6"/>
       <c r="F749" s="6"/>
       <c r="G749" s="6"/>
-      <c r="H749" s="6"/>
-      <c r="I749" s="6"/>
       <c r="J749" s="6"/>
       <c r="K749" s="6"/>
       <c r="L749" s="6"/>
@@ -32672,8 +31176,6 @@
       <c r="E750" s="6"/>
       <c r="F750" s="6"/>
       <c r="G750" s="6"/>
-      <c r="H750" s="6"/>
-      <c r="I750" s="6"/>
       <c r="J750" s="6"/>
       <c r="K750" s="6"/>
       <c r="L750" s="6"/>
@@ -32689,8 +31191,6 @@
       <c r="E751" s="6"/>
       <c r="F751" s="6"/>
       <c r="G751" s="6"/>
-      <c r="H751" s="6"/>
-      <c r="I751" s="6"/>
       <c r="J751" s="6"/>
       <c r="K751" s="6"/>
       <c r="L751" s="6"/>
@@ -32706,8 +31206,6 @@
       <c r="E752" s="6"/>
       <c r="F752" s="6"/>
       <c r="G752" s="6"/>
-      <c r="H752" s="6"/>
-      <c r="I752" s="6"/>
       <c r="J752" s="6"/>
       <c r="K752" s="6"/>
       <c r="L752" s="6"/>
@@ -32723,8 +31221,6 @@
       <c r="E753" s="6"/>
       <c r="F753" s="6"/>
       <c r="G753" s="6"/>
-      <c r="H753" s="6"/>
-      <c r="I753" s="6"/>
       <c r="J753" s="6"/>
       <c r="K753" s="6"/>
       <c r="L753" s="6"/>
@@ -32740,8 +31236,6 @@
       <c r="E754" s="6"/>
       <c r="F754" s="6"/>
       <c r="G754" s="6"/>
-      <c r="H754" s="6"/>
-      <c r="I754" s="6"/>
       <c r="J754" s="6"/>
       <c r="K754" s="6"/>
       <c r="L754" s="6"/>
@@ -32757,8 +31251,6 @@
       <c r="E755" s="6"/>
       <c r="F755" s="6"/>
       <c r="G755" s="6"/>
-      <c r="H755" s="6"/>
-      <c r="I755" s="6"/>
       <c r="J755" s="6"/>
       <c r="K755" s="6"/>
       <c r="L755" s="6"/>
@@ -32774,8 +31266,6 @@
       <c r="E756" s="6"/>
       <c r="F756" s="6"/>
       <c r="G756" s="6"/>
-      <c r="H756" s="6"/>
-      <c r="I756" s="6"/>
       <c r="J756" s="6"/>
       <c r="K756" s="6"/>
       <c r="L756" s="6"/>
@@ -32791,8 +31281,6 @@
       <c r="E757" s="6"/>
       <c r="F757" s="6"/>
       <c r="G757" s="6"/>
-      <c r="H757" s="6"/>
-      <c r="I757" s="6"/>
       <c r="J757" s="6"/>
       <c r="K757" s="6"/>
       <c r="L757" s="6"/>
@@ -32808,8 +31296,6 @@
       <c r="E758" s="6"/>
       <c r="F758" s="6"/>
       <c r="G758" s="6"/>
-      <c r="H758" s="6"/>
-      <c r="I758" s="6"/>
       <c r="J758" s="6"/>
       <c r="K758" s="6"/>
       <c r="L758" s="6"/>
@@ -32825,8 +31311,6 @@
       <c r="E759" s="6"/>
       <c r="F759" s="6"/>
       <c r="G759" s="6"/>
-      <c r="H759" s="6"/>
-      <c r="I759" s="6"/>
       <c r="J759" s="6"/>
       <c r="K759" s="6"/>
       <c r="L759" s="6"/>
@@ -32842,8 +31326,6 @@
       <c r="E760" s="6"/>
       <c r="F760" s="6"/>
       <c r="G760" s="6"/>
-      <c r="H760" s="6"/>
-      <c r="I760" s="6"/>
       <c r="J760" s="6"/>
       <c r="K760" s="6"/>
       <c r="L760" s="6"/>
@@ -32859,8 +31341,6 @@
       <c r="E761" s="6"/>
       <c r="F761" s="6"/>
       <c r="G761" s="6"/>
-      <c r="H761" s="6"/>
-      <c r="I761" s="6"/>
       <c r="J761" s="6"/>
       <c r="K761" s="6"/>
       <c r="L761" s="6"/>
@@ -32876,8 +31356,6 @@
       <c r="E762" s="6"/>
       <c r="F762" s="6"/>
       <c r="G762" s="6"/>
-      <c r="H762" s="6"/>
-      <c r="I762" s="6"/>
       <c r="J762" s="6"/>
       <c r="K762" s="6"/>
       <c r="L762" s="6"/>
@@ -32893,8 +31371,6 @@
       <c r="E763" s="6"/>
       <c r="F763" s="6"/>
       <c r="G763" s="6"/>
-      <c r="H763" s="6"/>
-      <c r="I763" s="6"/>
       <c r="J763" s="6"/>
       <c r="K763" s="6"/>
       <c r="L763" s="6"/>
@@ -32910,8 +31386,6 @@
       <c r="E764" s="6"/>
       <c r="F764" s="6"/>
       <c r="G764" s="6"/>
-      <c r="H764" s="6"/>
-      <c r="I764" s="6"/>
       <c r="J764" s="6"/>
       <c r="K764" s="6"/>
       <c r="L764" s="6"/>
@@ -32927,8 +31401,6 @@
       <c r="E765" s="6"/>
       <c r="F765" s="6"/>
       <c r="G765" s="6"/>
-      <c r="H765" s="6"/>
-      <c r="I765" s="6"/>
       <c r="J765" s="6"/>
       <c r="K765" s="6"/>
       <c r="L765" s="6"/>
@@ -32944,8 +31416,6 @@
       <c r="E766" s="6"/>
       <c r="F766" s="6"/>
       <c r="G766" s="6"/>
-      <c r="H766" s="6"/>
-      <c r="I766" s="6"/>
       <c r="J766" s="6"/>
       <c r="K766" s="6"/>
       <c r="L766" s="6"/>
@@ -32961,8 +31431,6 @@
       <c r="E767" s="6"/>
       <c r="F767" s="6"/>
       <c r="G767" s="6"/>
-      <c r="H767" s="6"/>
-      <c r="I767" s="6"/>
       <c r="J767" s="6"/>
       <c r="K767" s="6"/>
       <c r="L767" s="6"/>
@@ -32978,8 +31446,6 @@
       <c r="E768" s="6"/>
       <c r="F768" s="6"/>
       <c r="G768" s="6"/>
-      <c r="H768" s="6"/>
-      <c r="I768" s="6"/>
       <c r="J768" s="6"/>
       <c r="K768" s="6"/>
       <c r="L768" s="6"/>
@@ -32995,8 +31461,6 @@
       <c r="E769" s="6"/>
       <c r="F769" s="6"/>
       <c r="G769" s="6"/>
-      <c r="H769" s="6"/>
-      <c r="I769" s="6"/>
       <c r="J769" s="6"/>
       <c r="K769" s="6"/>
       <c r="L769" s="6"/>
@@ -33012,8 +31476,6 @@
       <c r="E770" s="6"/>
       <c r="F770" s="6"/>
       <c r="G770" s="6"/>
-      <c r="H770" s="6"/>
-      <c r="I770" s="6"/>
       <c r="J770" s="6"/>
       <c r="K770" s="6"/>
       <c r="L770" s="6"/>
@@ -33029,8 +31491,6 @@
       <c r="E771" s="6"/>
       <c r="F771" s="6"/>
       <c r="G771" s="6"/>
-      <c r="H771" s="6"/>
-      <c r="I771" s="6"/>
       <c r="J771" s="6"/>
       <c r="K771" s="6"/>
       <c r="L771" s="6"/>
@@ -33046,8 +31506,6 @@
       <c r="E772" s="6"/>
       <c r="F772" s="6"/>
       <c r="G772" s="6"/>
-      <c r="H772" s="6"/>
-      <c r="I772" s="6"/>
       <c r="J772" s="6"/>
       <c r="K772" s="6"/>
       <c r="L772" s="6"/>
@@ -33063,8 +31521,6 @@
       <c r="E773" s="6"/>
       <c r="F773" s="6"/>
       <c r="G773" s="6"/>
-      <c r="H773" s="6"/>
-      <c r="I773" s="6"/>
       <c r="J773" s="6"/>
       <c r="K773" s="6"/>
       <c r="L773" s="6"/>
@@ -33080,8 +31536,6 @@
       <c r="E774" s="6"/>
       <c r="F774" s="6"/>
       <c r="G774" s="6"/>
-      <c r="H774" s="6"/>
-      <c r="I774" s="6"/>
       <c r="J774" s="6"/>
       <c r="K774" s="6"/>
       <c r="L774" s="6"/>
@@ -33097,8 +31551,6 @@
       <c r="E775" s="6"/>
       <c r="F775" s="6"/>
       <c r="G775" s="6"/>
-      <c r="H775" s="6"/>
-      <c r="I775" s="6"/>
       <c r="J775" s="6"/>
       <c r="K775" s="6"/>
       <c r="L775" s="6"/>
@@ -33114,8 +31566,6 @@
       <c r="E776" s="6"/>
       <c r="F776" s="6"/>
       <c r="G776" s="6"/>
-      <c r="H776" s="6"/>
-      <c r="I776" s="6"/>
       <c r="J776" s="6"/>
       <c r="K776" s="6"/>
       <c r="L776" s="6"/>
@@ -33131,8 +31581,6 @@
       <c r="E777" s="6"/>
       <c r="F777" s="6"/>
       <c r="G777" s="6"/>
-      <c r="H777" s="6"/>
-      <c r="I777" s="6"/>
       <c r="J777" s="6"/>
       <c r="K777" s="6"/>
       <c r="L777" s="6"/>
@@ -33148,8 +31596,6 @@
       <c r="E778" s="6"/>
       <c r="F778" s="6"/>
       <c r="G778" s="6"/>
-      <c r="H778" s="6"/>
-      <c r="I778" s="6"/>
       <c r="J778" s="6"/>
       <c r="K778" s="6"/>
       <c r="L778" s="6"/>
@@ -33165,8 +31611,6 @@
       <c r="E779" s="6"/>
       <c r="F779" s="6"/>
       <c r="G779" s="6"/>
-      <c r="H779" s="6"/>
-      <c r="I779" s="6"/>
       <c r="J779" s="6"/>
       <c r="K779" s="6"/>
       <c r="L779" s="6"/>
@@ -33182,8 +31626,6 @@
       <c r="E780" s="6"/>
       <c r="F780" s="6"/>
       <c r="G780" s="6"/>
-      <c r="H780" s="6"/>
-      <c r="I780" s="6"/>
       <c r="J780" s="6"/>
       <c r="K780" s="6"/>
       <c r="L780" s="6"/>
@@ -33199,8 +31641,6 @@
       <c r="E781" s="6"/>
       <c r="F781" s="6"/>
       <c r="G781" s="6"/>
-      <c r="H781" s="6"/>
-      <c r="I781" s="6"/>
       <c r="J781" s="6"/>
       <c r="K781" s="6"/>
       <c r="L781" s="6"/>
@@ -33216,8 +31656,6 @@
       <c r="E782" s="6"/>
       <c r="F782" s="6"/>
       <c r="G782" s="6"/>
-      <c r="H782" s="6"/>
-      <c r="I782" s="6"/>
       <c r="J782" s="6"/>
       <c r="K782" s="6"/>
       <c r="L782" s="6"/>
@@ -33233,8 +31671,6 @@
       <c r="E783" s="6"/>
       <c r="F783" s="6"/>
       <c r="G783" s="6"/>
-      <c r="H783" s="6"/>
-      <c r="I783" s="6"/>
       <c r="J783" s="6"/>
       <c r="K783" s="6"/>
       <c r="L783" s="6"/>
@@ -33250,8 +31686,6 @@
       <c r="E784" s="6"/>
       <c r="F784" s="6"/>
       <c r="G784" s="6"/>
-      <c r="H784" s="6"/>
-      <c r="I784" s="6"/>
       <c r="J784" s="6"/>
       <c r="K784" s="6"/>
       <c r="L784" s="6"/>
@@ -33267,8 +31701,6 @@
       <c r="E785" s="6"/>
       <c r="F785" s="6"/>
       <c r="G785" s="6"/>
-      <c r="H785" s="6"/>
-      <c r="I785" s="6"/>
       <c r="J785" s="6"/>
       <c r="K785" s="6"/>
       <c r="L785" s="6"/>
@@ -33284,8 +31716,6 @@
       <c r="E786" s="6"/>
       <c r="F786" s="6"/>
       <c r="G786" s="6"/>
-      <c r="H786" s="6"/>
-      <c r="I786" s="6"/>
       <c r="J786" s="6"/>
       <c r="K786" s="6"/>
       <c r="L786" s="6"/>
@@ -33301,8 +31731,6 @@
       <c r="E787" s="6"/>
       <c r="F787" s="6"/>
       <c r="G787" s="6"/>
-      <c r="H787" s="6"/>
-      <c r="I787" s="6"/>
       <c r="J787" s="6"/>
       <c r="K787" s="6"/>
       <c r="L787" s="6"/>
@@ -33318,8 +31746,6 @@
       <c r="E788" s="6"/>
       <c r="F788" s="6"/>
       <c r="G788" s="6"/>
-      <c r="H788" s="6"/>
-      <c r="I788" s="6"/>
       <c r="J788" s="6"/>
       <c r="K788" s="6"/>
       <c r="L788" s="6"/>
@@ -33335,8 +31761,6 @@
       <c r="E789" s="6"/>
       <c r="F789" s="6"/>
       <c r="G789" s="6"/>
-      <c r="H789" s="6"/>
-      <c r="I789" s="6"/>
       <c r="J789" s="6"/>
       <c r="K789" s="6"/>
       <c r="L789" s="6"/>
@@ -33352,8 +31776,6 @@
       <c r="E790" s="6"/>
       <c r="F790" s="6"/>
       <c r="G790" s="6"/>
-      <c r="H790" s="6"/>
-      <c r="I790" s="6"/>
       <c r="J790" s="6"/>
       <c r="K790" s="6"/>
       <c r="L790" s="6"/>
@@ -33369,8 +31791,6 @@
       <c r="E791" s="6"/>
       <c r="F791" s="6"/>
       <c r="G791" s="6"/>
-      <c r="H791" s="6"/>
-      <c r="I791" s="6"/>
       <c r="J791" s="6"/>
       <c r="K791" s="6"/>
       <c r="L791" s="6"/>
@@ -33386,8 +31806,6 @@
       <c r="E792" s="6"/>
       <c r="F792" s="6"/>
       <c r="G792" s="6"/>
-      <c r="H792" s="6"/>
-      <c r="I792" s="6"/>
       <c r="J792" s="6"/>
       <c r="K792" s="6"/>
       <c r="L792" s="6"/>
@@ -33403,8 +31821,6 @@
       <c r="E793" s="6"/>
       <c r="F793" s="6"/>
       <c r="G793" s="6"/>
-      <c r="H793" s="6"/>
-      <c r="I793" s="6"/>
       <c r="J793" s="6"/>
       <c r="K793" s="6"/>
       <c r="L793" s="6"/>
@@ -33420,8 +31836,6 @@
       <c r="E794" s="6"/>
       <c r="F794" s="6"/>
       <c r="G794" s="6"/>
-      <c r="H794" s="6"/>
-      <c r="I794" s="6"/>
       <c r="J794" s="6"/>
       <c r="K794" s="6"/>
       <c r="L794" s="6"/>
@@ -33437,8 +31851,6 @@
       <c r="E795" s="6"/>
       <c r="F795" s="6"/>
       <c r="G795" s="6"/>
-      <c r="H795" s="6"/>
-      <c r="I795" s="6"/>
       <c r="J795" s="6"/>
       <c r="K795" s="6"/>
       <c r="L795" s="6"/>
@@ -33454,8 +31866,6 @@
       <c r="E796" s="6"/>
       <c r="F796" s="6"/>
       <c r="G796" s="6"/>
-      <c r="H796" s="6"/>
-      <c r="I796" s="6"/>
       <c r="J796" s="6"/>
       <c r="K796" s="6"/>
       <c r="L796" s="6"/>
@@ -33471,8 +31881,6 @@
       <c r="E797" s="6"/>
       <c r="F797" s="6"/>
       <c r="G797" s="6"/>
-      <c r="H797" s="6"/>
-      <c r="I797" s="6"/>
       <c r="J797" s="6"/>
       <c r="K797" s="6"/>
       <c r="L797" s="6"/>
@@ -33488,8 +31896,6 @@
       <c r="E798" s="6"/>
       <c r="F798" s="6"/>
       <c r="G798" s="6"/>
-      <c r="H798" s="6"/>
-      <c r="I798" s="6"/>
       <c r="J798" s="6"/>
       <c r="K798" s="6"/>
       <c r="L798" s="6"/>
@@ -33505,8 +31911,6 @@
       <c r="E799" s="6"/>
       <c r="F799" s="6"/>
       <c r="G799" s="6"/>
-      <c r="H799" s="6"/>
-      <c r="I799" s="6"/>
       <c r="J799" s="6"/>
       <c r="K799" s="6"/>
       <c r="L799" s="6"/>
@@ -33522,8 +31926,6 @@
       <c r="E800" s="6"/>
       <c r="F800" s="6"/>
       <c r="G800" s="6"/>
-      <c r="H800" s="6"/>
-      <c r="I800" s="6"/>
       <c r="J800" s="6"/>
       <c r="K800" s="6"/>
       <c r="L800" s="6"/>
@@ -33539,8 +31941,6 @@
       <c r="E801" s="6"/>
       <c r="F801" s="6"/>
       <c r="G801" s="6"/>
-      <c r="H801" s="6"/>
-      <c r="I801" s="6"/>
       <c r="J801" s="6"/>
       <c r="K801" s="6"/>
       <c r="L801" s="6"/>
@@ -33556,8 +31956,6 @@
       <c r="E802" s="6"/>
       <c r="F802" s="6"/>
       <c r="G802" s="6"/>
-      <c r="H802" s="6"/>
-      <c r="I802" s="6"/>
       <c r="J802" s="6"/>
       <c r="K802" s="6"/>
       <c r="L802" s="6"/>
@@ -33573,8 +31971,6 @@
       <c r="E803" s="6"/>
       <c r="F803" s="6"/>
       <c r="G803" s="6"/>
-      <c r="H803" s="6"/>
-      <c r="I803" s="6"/>
       <c r="J803" s="6"/>
       <c r="K803" s="6"/>
       <c r="L803" s="6"/>
@@ -33590,8 +31986,6 @@
       <c r="E804" s="6"/>
       <c r="F804" s="6"/>
       <c r="G804" s="6"/>
-      <c r="H804" s="6"/>
-      <c r="I804" s="6"/>
       <c r="J804" s="6"/>
       <c r="K804" s="6"/>
       <c r="L804" s="6"/>
@@ -33607,8 +32001,6 @@
       <c r="E805" s="6"/>
       <c r="F805" s="6"/>
       <c r="G805" s="6"/>
-      <c r="H805" s="6"/>
-      <c r="I805" s="6"/>
       <c r="J805" s="6"/>
       <c r="K805" s="6"/>
       <c r="L805" s="6"/>
@@ -33624,8 +32016,6 @@
       <c r="E806" s="6"/>
       <c r="F806" s="6"/>
       <c r="G806" s="6"/>
-      <c r="H806" s="6"/>
-      <c r="I806" s="6"/>
       <c r="J806" s="6"/>
       <c r="K806" s="6"/>
       <c r="L806" s="6"/>
@@ -33641,8 +32031,6 @@
       <c r="E807" s="6"/>
       <c r="F807" s="6"/>
       <c r="G807" s="6"/>
-      <c r="H807" s="6"/>
-      <c r="I807" s="6"/>
       <c r="J807" s="6"/>
       <c r="K807" s="6"/>
       <c r="L807" s="6"/>
@@ -33658,8 +32046,6 @@
       <c r="E808" s="6"/>
       <c r="F808" s="6"/>
       <c r="G808" s="6"/>
-      <c r="H808" s="6"/>
-      <c r="I808" s="6"/>
       <c r="J808" s="6"/>
       <c r="K808" s="6"/>
       <c r="L808" s="6"/>
@@ -33675,8 +32061,6 @@
       <c r="E809" s="6"/>
       <c r="F809" s="6"/>
       <c r="G809" s="6"/>
-      <c r="H809" s="6"/>
-      <c r="I809" s="6"/>
       <c r="J809" s="6"/>
       <c r="K809" s="6"/>
       <c r="L809" s="6"/>
@@ -33692,8 +32076,6 @@
       <c r="E810" s="6"/>
       <c r="F810" s="6"/>
       <c r="G810" s="6"/>
-      <c r="H810" s="6"/>
-      <c r="I810" s="6"/>
       <c r="J810" s="6"/>
       <c r="K810" s="6"/>
       <c r="L810" s="6"/>
@@ -33709,8 +32091,6 @@
       <c r="E811" s="6"/>
       <c r="F811" s="6"/>
       <c r="G811" s="6"/>
-      <c r="H811" s="6"/>
-      <c r="I811" s="6"/>
       <c r="J811" s="6"/>
       <c r="K811" s="6"/>
       <c r="L811" s="6"/>
@@ -33726,8 +32106,6 @@
       <c r="E812" s="6"/>
       <c r="F812" s="6"/>
       <c r="G812" s="6"/>
-      <c r="H812" s="6"/>
-      <c r="I812" s="6"/>
       <c r="J812" s="6"/>
       <c r="K812" s="6"/>
       <c r="L812" s="6"/>
@@ -33743,8 +32121,6 @@
       <c r="E813" s="6"/>
       <c r="F813" s="6"/>
       <c r="G813" s="6"/>
-      <c r="H813" s="6"/>
-      <c r="I813" s="6"/>
       <c r="J813" s="6"/>
       <c r="K813" s="6"/>
       <c r="L813" s="6"/>
@@ -33760,8 +32136,6 @@
       <c r="E814" s="6"/>
       <c r="F814" s="6"/>
       <c r="G814" s="6"/>
-      <c r="H814" s="6"/>
-      <c r="I814" s="6"/>
       <c r="J814" s="6"/>
       <c r="K814" s="6"/>
       <c r="L814" s="6"/>
@@ -33777,8 +32151,6 @@
       <c r="E815" s="6"/>
       <c r="F815" s="6"/>
       <c r="G815" s="6"/>
-      <c r="H815" s="6"/>
-      <c r="I815" s="6"/>
       <c r="J815" s="6"/>
       <c r="K815" s="6"/>
       <c r="L815" s="6"/>
@@ -33794,8 +32166,6 @@
       <c r="E816" s="6"/>
       <c r="F816" s="6"/>
       <c r="G816" s="6"/>
-      <c r="H816" s="6"/>
-      <c r="I816" s="6"/>
       <c r="J816" s="6"/>
       <c r="K816" s="6"/>
       <c r="L816" s="6"/>
@@ -33811,8 +32181,6 @@
       <c r="E817" s="6"/>
       <c r="F817" s="6"/>
       <c r="G817" s="6"/>
-      <c r="H817" s="6"/>
-      <c r="I817" s="6"/>
       <c r="J817" s="6"/>
       <c r="K817" s="6"/>
       <c r="L817" s="6"/>
@@ -33828,8 +32196,6 @@
       <c r="E818" s="6"/>
       <c r="F818" s="6"/>
       <c r="G818" s="6"/>
-      <c r="H818" s="6"/>
-      <c r="I818" s="6"/>
       <c r="J818" s="6"/>
       <c r="K818" s="6"/>
       <c r="L818" s="6"/>
@@ -33845,8 +32211,6 @@
       <c r="E819" s="6"/>
       <c r="F819" s="6"/>
       <c r="G819" s="6"/>
-      <c r="H819" s="6"/>
-      <c r="I819" s="6"/>
       <c r="J819" s="6"/>
       <c r="K819" s="6"/>
       <c r="L819" s="6"/>
@@ -33862,8 +32226,6 @@
       <c r="E820" s="6"/>
       <c r="F820" s="6"/>
       <c r="G820" s="6"/>
-      <c r="H820" s="6"/>
-      <c r="I820" s="6"/>
       <c r="J820" s="6"/>
       <c r="K820" s="6"/>
       <c r="L820" s="6"/>
@@ -33879,8 +32241,6 @@
       <c r="E821" s="6"/>
       <c r="F821" s="6"/>
       <c r="G821" s="6"/>
-      <c r="H821" s="6"/>
-      <c r="I821" s="6"/>
       <c r="J821" s="6"/>
       <c r="K821" s="6"/>
       <c r="L821" s="6"/>
@@ -33896,8 +32256,6 @@
       <c r="E822" s="6"/>
       <c r="F822" s="6"/>
       <c r="G822" s="6"/>
-      <c r="H822" s="6"/>
-      <c r="I822" s="6"/>
       <c r="J822" s="6"/>
       <c r="K822" s="6"/>
       <c r="L822" s="6"/>
@@ -33913,8 +32271,6 @@
       <c r="E823" s="6"/>
       <c r="F823" s="6"/>
       <c r="G823" s="6"/>
-      <c r="H823" s="6"/>
-      <c r="I823" s="6"/>
       <c r="J823" s="6"/>
       <c r="K823" s="6"/>
       <c r="L823" s="6"/>
@@ -33930,8 +32286,6 @@
       <c r="E824" s="6"/>
       <c r="F824" s="6"/>
       <c r="G824" s="6"/>
-      <c r="H824" s="6"/>
-      <c r="I824" s="6"/>
       <c r="J824" s="6"/>
       <c r="K824" s="6"/>
       <c r="L824" s="6"/>
@@ -33947,8 +32301,6 @@
       <c r="E825" s="6"/>
       <c r="F825" s="6"/>
       <c r="G825" s="6"/>
-      <c r="H825" s="6"/>
-      <c r="I825" s="6"/>
       <c r="J825" s="6"/>
       <c r="K825" s="6"/>
       <c r="L825" s="6"/>
@@ -33964,8 +32316,6 @@
       <c r="E826" s="6"/>
       <c r="F826" s="6"/>
       <c r="G826" s="6"/>
-      <c r="H826" s="6"/>
-      <c r="I826" s="6"/>
       <c r="J826" s="6"/>
       <c r="K826" s="6"/>
       <c r="L826" s="6"/>
@@ -33981,8 +32331,6 @@
       <c r="E827" s="6"/>
       <c r="F827" s="6"/>
       <c r="G827" s="6"/>
-      <c r="H827" s="6"/>
-      <c r="I827" s="6"/>
       <c r="J827" s="6"/>
       <c r="K827" s="6"/>
       <c r="L827" s="6"/>
@@ -33998,8 +32346,6 @@
       <c r="E828" s="6"/>
       <c r="F828" s="6"/>
       <c r="G828" s="6"/>
-      <c r="H828" s="6"/>
-      <c r="I828" s="6"/>
       <c r="J828" s="6"/>
       <c r="K828" s="6"/>
       <c r="L828" s="6"/>
@@ -34015,8 +32361,6 @@
       <c r="E829" s="6"/>
       <c r="F829" s="6"/>
       <c r="G829" s="6"/>
-      <c r="H829" s="6"/>
-      <c r="I829" s="6"/>
       <c r="J829" s="6"/>
       <c r="K829" s="6"/>
       <c r="L829" s="6"/>
@@ -34032,8 +32376,6 @@
       <c r="E830" s="6"/>
       <c r="F830" s="6"/>
       <c r="G830" s="6"/>
-      <c r="H830" s="6"/>
-      <c r="I830" s="6"/>
       <c r="J830" s="6"/>
       <c r="K830" s="6"/>
       <c r="L830" s="6"/>
@@ -34049,8 +32391,6 @@
       <c r="E831" s="6"/>
       <c r="F831" s="6"/>
       <c r="G831" s="6"/>
-      <c r="H831" s="6"/>
-      <c r="I831" s="6"/>
       <c r="J831" s="6"/>
       <c r="K831" s="6"/>
       <c r="L831" s="6"/>
@@ -34066,8 +32406,6 @@
       <c r="E832" s="6"/>
       <c r="F832" s="6"/>
       <c r="G832" s="6"/>
-      <c r="H832" s="6"/>
-      <c r="I832" s="6"/>
       <c r="J832" s="6"/>
       <c r="K832" s="6"/>
       <c r="L832" s="6"/>
@@ -34083,8 +32421,6 @@
       <c r="E833" s="6"/>
       <c r="F833" s="6"/>
       <c r="G833" s="6"/>
-      <c r="H833" s="6"/>
-      <c r="I833" s="6"/>
       <c r="J833" s="6"/>
       <c r="K833" s="6"/>
       <c r="L833" s="6"/>
@@ -34100,8 +32436,6 @@
       <c r="E834" s="6"/>
       <c r="F834" s="6"/>
       <c r="G834" s="6"/>
-      <c r="H834" s="6"/>
-      <c r="I834" s="6"/>
       <c r="J834" s="6"/>
       <c r="K834" s="6"/>
       <c r="L834" s="6"/>
@@ -34117,8 +32451,6 @@
       <c r="E835" s="6"/>
       <c r="F835" s="6"/>
       <c r="G835" s="6"/>
-      <c r="H835" s="6"/>
-      <c r="I835" s="6"/>
       <c r="J835" s="6"/>
       <c r="K835" s="6"/>
       <c r="L835" s="6"/>
@@ -34134,8 +32466,6 @@
       <c r="E836" s="6"/>
       <c r="F836" s="6"/>
       <c r="G836" s="6"/>
-      <c r="H836" s="6"/>
-      <c r="I836" s="6"/>
       <c r="J836" s="6"/>
       <c r="K836" s="6"/>
       <c r="L836" s="6"/>
@@ -34151,8 +32481,6 @@
       <c r="E837" s="6"/>
       <c r="F837" s="6"/>
       <c r="G837" s="6"/>
-      <c r="H837" s="6"/>
-      <c r="I837" s="6"/>
       <c r="J837" s="6"/>
       <c r="K837" s="6"/>
       <c r="L837" s="6"/>
@@ -34168,8 +32496,6 @@
       <c r="E838" s="6"/>
       <c r="F838" s="6"/>
       <c r="G838" s="6"/>
-      <c r="H838" s="6"/>
-      <c r="I838" s="6"/>
       <c r="J838" s="6"/>
       <c r="K838" s="6"/>
       <c r="L838" s="6"/>
@@ -34185,8 +32511,6 @@
       <c r="E839" s="6"/>
       <c r="F839" s="6"/>
       <c r="G839" s="6"/>
-      <c r="H839" s="6"/>
-      <c r="I839" s="6"/>
       <c r="J839" s="6"/>
       <c r="K839" s="6"/>
       <c r="L839" s="6"/>
@@ -34202,8 +32526,6 @@
       <c r="E840" s="6"/>
       <c r="F840" s="6"/>
       <c r="G840" s="6"/>
-      <c r="H840" s="6"/>
-      <c r="I840" s="6"/>
       <c r="J840" s="6"/>
       <c r="K840" s="6"/>
       <c r="L840" s="6"/>
@@ -34219,8 +32541,6 @@
       <c r="E841" s="6"/>
       <c r="F841" s="6"/>
       <c r="G841" s="6"/>
-      <c r="H841" s="6"/>
-      <c r="I841" s="6"/>
       <c r="J841" s="6"/>
       <c r="K841" s="6"/>
       <c r="L841" s="6"/>
@@ -34236,8 +32556,6 @@
       <c r="E842" s="6"/>
       <c r="F842" s="6"/>
       <c r="G842" s="6"/>
-      <c r="H842" s="6"/>
-      <c r="I842" s="6"/>
       <c r="J842" s="6"/>
       <c r="K842" s="6"/>
       <c r="L842" s="6"/>
@@ -34253,8 +32571,6 @@
       <c r="E843" s="6"/>
       <c r="F843" s="6"/>
       <c r="G843" s="6"/>
-      <c r="H843" s="6"/>
-      <c r="I843" s="6"/>
       <c r="J843" s="6"/>
       <c r="K843" s="6"/>
       <c r="L843" s="6"/>
@@ -34270,8 +32586,6 @@
       <c r="E844" s="6"/>
       <c r="F844" s="6"/>
       <c r="G844" s="6"/>
-      <c r="H844" s="6"/>
-      <c r="I844" s="6"/>
       <c r="J844" s="6"/>
       <c r="K844" s="6"/>
       <c r="L844" s="6"/>
@@ -34287,8 +32601,6 @@
       <c r="E845" s="6"/>
       <c r="F845" s="6"/>
       <c r="G845" s="6"/>
-      <c r="H845" s="6"/>
-      <c r="I845" s="6"/>
       <c r="J845" s="6"/>
       <c r="K845" s="6"/>
       <c r="L845" s="6"/>
@@ -34304,8 +32616,6 @@
       <c r="E846" s="6"/>
       <c r="F846" s="6"/>
       <c r="G846" s="6"/>
-      <c r="H846" s="6"/>
-      <c r="I846" s="6"/>
       <c r="J846" s="6"/>
       <c r="K846" s="6"/>
       <c r="L846" s="6"/>
@@ -34321,8 +32631,6 @@
       <c r="E847" s="6"/>
       <c r="F847" s="6"/>
       <c r="G847" s="6"/>
-      <c r="H847" s="6"/>
-      <c r="I847" s="6"/>
       <c r="J847" s="6"/>
       <c r="K847" s="6"/>
       <c r="L847" s="6"/>
@@ -34338,8 +32646,6 @@
       <c r="E848" s="6"/>
       <c r="F848" s="6"/>
       <c r="G848" s="6"/>
-      <c r="H848" s="6"/>
-      <c r="I848" s="6"/>
       <c r="J848" s="6"/>
       <c r="K848" s="6"/>
       <c r="L848" s="6"/>
@@ -34355,8 +32661,6 @@
       <c r="E849" s="6"/>
       <c r="F849" s="6"/>
       <c r="G849" s="6"/>
-      <c r="H849" s="6"/>
-      <c r="I849" s="6"/>
       <c r="J849" s="6"/>
       <c r="K849" s="6"/>
       <c r="L849" s="6"/>
@@ -34372,8 +32676,6 @@
       <c r="E850" s="6"/>
       <c r="F850" s="6"/>
       <c r="G850" s="6"/>
-      <c r="H850" s="6"/>
-      <c r="I850" s="6"/>
       <c r="J850" s="6"/>
       <c r="K850" s="6"/>
       <c r="L850" s="6"/>
@@ -34389,8 +32691,6 @@
       <c r="E851" s="6"/>
       <c r="F851" s="6"/>
       <c r="G851" s="6"/>
-      <c r="H851" s="6"/>
-      <c r="I851" s="6"/>
       <c r="J851" s="6"/>
       <c r="K851" s="6"/>
       <c r="L851" s="6"/>
@@ -34406,8 +32706,6 @@
       <c r="E852" s="6"/>
       <c r="F852" s="6"/>
       <c r="G852" s="6"/>
-      <c r="H852" s="6"/>
-      <c r="I852" s="6"/>
       <c r="J852" s="6"/>
       <c r="K852" s="6"/>
       <c r="L852" s="6"/>
@@ -34423,8 +32721,6 @@
       <c r="E853" s="6"/>
       <c r="F853" s="6"/>
       <c r="G853" s="6"/>
-      <c r="H853" s="6"/>
-      <c r="I853" s="6"/>
       <c r="J853" s="6"/>
       <c r="K853" s="6"/>
       <c r="L853" s="6"/>
@@ -34440,8 +32736,6 @@
       <c r="E854" s="6"/>
       <c r="F854" s="6"/>
       <c r="G854" s="6"/>
-      <c r="H854" s="6"/>
-      <c r="I854" s="6"/>
       <c r="J854" s="6"/>
       <c r="K854" s="6"/>
       <c r="L854" s="6"/>
@@ -34457,8 +32751,6 @@
       <c r="E855" s="6"/>
       <c r="F855" s="6"/>
       <c r="G855" s="6"/>
-      <c r="H855" s="6"/>
-      <c r="I855" s="6"/>
       <c r="J855" s="6"/>
       <c r="K855" s="6"/>
       <c r="L855" s="6"/>
@@ -34474,8 +32766,6 @@
       <c r="E856" s="6"/>
       <c r="F856" s="6"/>
       <c r="G856" s="6"/>
-      <c r="H856" s="6"/>
-      <c r="I856" s="6"/>
       <c r="J856" s="6"/>
       <c r="K856" s="6"/>
       <c r="L856" s="6"/>
@@ -34491,8 +32781,6 @@
       <c r="E857" s="6"/>
       <c r="F857" s="6"/>
       <c r="G857" s="6"/>
-      <c r="H857" s="6"/>
-      <c r="I857" s="6"/>
       <c r="J857" s="6"/>
       <c r="K857" s="6"/>
       <c r="L857" s="6"/>
@@ -34508,8 +32796,6 @@
       <c r="E858" s="6"/>
       <c r="F858" s="6"/>
       <c r="G858" s="6"/>
-      <c r="H858" s="6"/>
-      <c r="I858" s="6"/>
       <c r="J858" s="6"/>
       <c r="K858" s="6"/>
       <c r="L858" s="6"/>
@@ -34525,8 +32811,6 @@
       <c r="E859" s="6"/>
       <c r="F859" s="6"/>
       <c r="G859" s="6"/>
-      <c r="H859" s="6"/>
-      <c r="I859" s="6"/>
       <c r="J859" s="6"/>
       <c r="K859" s="6"/>
       <c r="L859" s="6"/>
@@ -34542,8 +32826,6 @@
       <c r="E860" s="6"/>
       <c r="F860" s="6"/>
       <c r="G860" s="6"/>
-      <c r="H860" s="6"/>
-      <c r="I860" s="6"/>
       <c r="J860" s="6"/>
       <c r="K860" s="6"/>
       <c r="L860" s="6"/>
@@ -34559,8 +32841,6 @@
       <c r="E861" s="6"/>
       <c r="F861" s="6"/>
       <c r="G861" s="6"/>
-      <c r="H861" s="6"/>
-      <c r="I861" s="6"/>
       <c r="J861" s="6"/>
       <c r="K861" s="6"/>
       <c r="L861" s="6"/>
@@ -34576,8 +32856,6 @@
       <c r="E862" s="6"/>
       <c r="F862" s="6"/>
       <c r="G862" s="6"/>
-      <c r="H862" s="6"/>
-      <c r="I862" s="6"/>
       <c r="J862" s="6"/>
       <c r="K862" s="6"/>
       <c r="L862" s="6"/>
@@ -34593,8 +32871,6 @@
       <c r="E863" s="6"/>
       <c r="F863" s="6"/>
       <c r="G863" s="6"/>
-      <c r="H863" s="6"/>
-      <c r="I863" s="6"/>
       <c r="J863" s="6"/>
       <c r="K863" s="6"/>
       <c r="L863" s="6"/>
@@ -34610,8 +32886,6 @@
       <c r="E864" s="6"/>
       <c r="F864" s="6"/>
       <c r="G864" s="6"/>
-      <c r="H864" s="6"/>
-      <c r="I864" s="6"/>
       <c r="J864" s="6"/>
       <c r="K864" s="6"/>
       <c r="L864" s="6"/>
@@ -34627,8 +32901,6 @@
       <c r="E865" s="6"/>
       <c r="F865" s="6"/>
       <c r="G865" s="6"/>
-      <c r="H865" s="6"/>
-      <c r="I865" s="6"/>
       <c r="J865" s="6"/>
       <c r="K865" s="6"/>
       <c r="L865" s="6"/>
@@ -34644,8 +32916,6 @@
       <c r="E866" s="6"/>
       <c r="F866" s="6"/>
       <c r="G866" s="6"/>
-      <c r="H866" s="6"/>
-      <c r="I866" s="6"/>
       <c r="J866" s="6"/>
       <c r="K866" s="6"/>
       <c r="L866" s="6"/>
@@ -34661,8 +32931,6 @@
       <c r="E867" s="6"/>
       <c r="F867" s="6"/>
       <c r="G867" s="6"/>
-      <c r="H867" s="6"/>
-      <c r="I867" s="6"/>
       <c r="J867" s="6"/>
       <c r="K867" s="6"/>
       <c r="L867" s="6"/>
@@ -34678,8 +32946,6 @@
       <c r="E868" s="6"/>
       <c r="F868" s="6"/>
       <c r="G868" s="6"/>
-      <c r="H868" s="6"/>
-      <c r="I868" s="6"/>
       <c r="J868" s="6"/>
       <c r="K868" s="6"/>
       <c r="L868" s="6"/>
@@ -34695,8 +32961,6 @@
       <c r="E869" s="6"/>
       <c r="F869" s="6"/>
       <c r="G869" s="6"/>
-      <c r="H869" s="6"/>
-      <c r="I869" s="6"/>
       <c r="J869" s="6"/>
       <c r="K869" s="6"/>
       <c r="L869" s="6"/>
@@ -34712,8 +32976,6 @@
       <c r="E870" s="6"/>
       <c r="F870" s="6"/>
       <c r="G870" s="6"/>
-      <c r="H870" s="6"/>
-      <c r="I870" s="6"/>
       <c r="J870" s="6"/>
       <c r="K870" s="6"/>
       <c r="L870" s="6"/>
@@ -34729,8 +32991,6 @@
       <c r="E871" s="6"/>
       <c r="F871" s="6"/>
       <c r="G871" s="6"/>
-      <c r="H871" s="6"/>
-      <c r="I871" s="6"/>
       <c r="J871" s="6"/>
       <c r="K871" s="6"/>
       <c r="L871" s="6"/>
@@ -34746,8 +33006,6 @@
       <c r="E872" s="6"/>
       <c r="F872" s="6"/>
       <c r="G872" s="6"/>
-      <c r="H872" s="6"/>
-      <c r="I872" s="6"/>
       <c r="J872" s="6"/>
       <c r="K872" s="6"/>
       <c r="L872" s="6"/>
@@ -34763,8 +33021,6 @@
       <c r="E873" s="6"/>
       <c r="F873" s="6"/>
       <c r="G873" s="6"/>
-      <c r="H873" s="6"/>
-      <c r="I873" s="6"/>
       <c r="J873" s="6"/>
       <c r="K873" s="6"/>
       <c r="L873" s="6"/>
@@ -34780,8 +33036,6 @@
       <c r="E874" s="6"/>
       <c r="F874" s="6"/>
       <c r="G874" s="6"/>
-      <c r="H874" s="6"/>
-      <c r="I874" s="6"/>
       <c r="J874" s="6"/>
       <c r="K874" s="6"/>
       <c r="L874" s="6"/>
@@ -34797,8 +33051,6 @@
       <c r="E875" s="6"/>
       <c r="F875" s="6"/>
       <c r="G875" s="6"/>
-      <c r="H875" s="6"/>
-      <c r="I875" s="6"/>
       <c r="J875" s="6"/>
       <c r="K875" s="6"/>
       <c r="L875" s="6"/>
@@ -34814,8 +33066,6 @@
       <c r="E876" s="6"/>
       <c r="F876" s="6"/>
       <c r="G876" s="6"/>
-      <c r="H876" s="6"/>
-      <c r="I876" s="6"/>
       <c r="J876" s="6"/>
       <c r="K876" s="6"/>
       <c r="L876" s="6"/>
@@ -34831,8 +33081,6 @@
       <c r="E877" s="6"/>
       <c r="F877" s="6"/>
       <c r="G877" s="6"/>
-      <c r="H877" s="6"/>
-      <c r="I877" s="6"/>
       <c r="J877" s="6"/>
       <c r="K877" s="6"/>
       <c r="L877" s="6"/>
@@ -34848,8 +33096,6 @@
       <c r="E878" s="6"/>
       <c r="F878" s="6"/>
       <c r="G878" s="6"/>
-      <c r="H878" s="6"/>
-      <c r="I878" s="6"/>
       <c r="J878" s="6"/>
       <c r="K878" s="6"/>
       <c r="L878" s="6"/>
@@ -34865,8 +33111,6 @@
       <c r="E879" s="6"/>
       <c r="F879" s="6"/>
       <c r="G879" s="6"/>
-      <c r="H879" s="6"/>
-      <c r="I879" s="6"/>
       <c r="J879" s="6"/>
       <c r="K879" s="6"/>
       <c r="L879" s="6"/>
@@ -34882,8 +33126,6 @@
       <c r="E880" s="6"/>
       <c r="F880" s="6"/>
       <c r="G880" s="6"/>
-      <c r="H880" s="6"/>
-      <c r="I880" s="6"/>
       <c r="J880" s="6"/>
       <c r="K880" s="6"/>
       <c r="L880" s="6"/>
@@ -34899,8 +33141,6 @@
       <c r="E881" s="6"/>
       <c r="F881" s="6"/>
       <c r="G881" s="6"/>
-      <c r="H881" s="6"/>
-      <c r="I881" s="6"/>
       <c r="J881" s="6"/>
       <c r="K881" s="6"/>
       <c r="L881" s="6"/>
@@ -34916,8 +33156,6 @@
       <c r="E882" s="6"/>
       <c r="F882" s="6"/>
       <c r="G882" s="6"/>
-      <c r="H882" s="6"/>
-      <c r="I882" s="6"/>
       <c r="J882" s="6"/>
       <c r="K882" s="6"/>
       <c r="L882" s="6"/>
@@ -34933,8 +33171,6 @@
       <c r="E883" s="6"/>
       <c r="F883" s="6"/>
       <c r="G883" s="6"/>
-      <c r="H883" s="6"/>
-      <c r="I883" s="6"/>
       <c r="J883" s="6"/>
       <c r="K883" s="6"/>
       <c r="L883" s="6"/>
@@ -34950,8 +33186,6 @@
       <c r="E884" s="6"/>
       <c r="F884" s="6"/>
       <c r="G884" s="6"/>
-      <c r="H884" s="6"/>
-      <c r="I884" s="6"/>
       <c r="J884" s="6"/>
       <c r="K884" s="6"/>
       <c r="L884" s="6"/>
@@ -34967,8 +33201,6 @@
       <c r="E885" s="6"/>
       <c r="F885" s="6"/>
       <c r="G885" s="6"/>
-      <c r="H885" s="6"/>
-      <c r="I885" s="6"/>
       <c r="J885" s="6"/>
       <c r="K885" s="6"/>
       <c r="L885" s="6"/>
@@ -34984,8 +33216,6 @@
       <c r="E886" s="6"/>
       <c r="F886" s="6"/>
       <c r="G886" s="6"/>
-      <c r="H886" s="6"/>
-      <c r="I886" s="6"/>
       <c r="J886" s="6"/>
       <c r="K886" s="6"/>
       <c r="L886" s="6"/>
@@ -35001,8 +33231,6 @@
       <c r="E887" s="6"/>
       <c r="F887" s="6"/>
       <c r="G887" s="6"/>
-      <c r="H887" s="6"/>
-      <c r="I887" s="6"/>
       <c r="J887" s="6"/>
       <c r="K887" s="6"/>
       <c r="L887" s="6"/>
@@ -35018,8 +33246,6 @@
       <c r="E888" s="6"/>
       <c r="F888" s="6"/>
       <c r="G888" s="6"/>
-      <c r="H888" s="6"/>
-      <c r="I888" s="6"/>
       <c r="J888" s="6"/>
       <c r="K888" s="6"/>
       <c r="L888" s="6"/>
@@ -35035,8 +33261,6 @@
       <c r="E889" s="6"/>
       <c r="F889" s="6"/>
       <c r="G889" s="6"/>
-      <c r="H889" s="6"/>
-      <c r="I889" s="6"/>
       <c r="J889" s="6"/>
       <c r="K889" s="6"/>
       <c r="L889" s="6"/>
@@ -35052,8 +33276,6 @@
       <c r="E890" s="6"/>
       <c r="F890" s="6"/>
       <c r="G890" s="6"/>
-      <c r="H890" s="6"/>
-      <c r="I890" s="6"/>
       <c r="J890" s="6"/>
       <c r="K890" s="6"/>
       <c r="L890" s="6"/>
@@ -35069,8 +33291,6 @@
       <c r="E891" s="6"/>
       <c r="F891" s="6"/>
       <c r="G891" s="6"/>
-      <c r="H891" s="6"/>
-      <c r="I891" s="6"/>
       <c r="J891" s="6"/>
       <c r="K891" s="6"/>
       <c r="L891" s="6"/>
@@ -35086,8 +33306,6 @@
       <c r="E892" s="6"/>
       <c r="F892" s="6"/>
       <c r="G892" s="6"/>
-      <c r="H892" s="6"/>
-      <c r="I892" s="6"/>
       <c r="J892" s="6"/>
       <c r="K892" s="6"/>
       <c r="L892" s="6"/>
@@ -35103,8 +33321,6 @@
       <c r="E893" s="6"/>
       <c r="F893" s="6"/>
       <c r="G893" s="6"/>
-      <c r="H893" s="6"/>
-      <c r="I893" s="6"/>
       <c r="J893" s="6"/>
       <c r="K893" s="6"/>
       <c r="L893" s="6"/>
@@ -35120,8 +33336,6 @@
       <c r="E894" s="6"/>
       <c r="F894" s="6"/>
       <c r="G894" s="6"/>
-      <c r="H894" s="6"/>
-      <c r="I894" s="6"/>
       <c r="J894" s="6"/>
       <c r="K894" s="6"/>
       <c r="L894" s="6"/>
@@ -35137,8 +33351,6 @@
       <c r="E895" s="6"/>
       <c r="F895" s="6"/>
       <c r="G895" s="6"/>
-      <c r="H895" s="6"/>
-      <c r="I895" s="6"/>
       <c r="J895" s="6"/>
       <c r="K895" s="6"/>
       <c r="L895" s="6"/>
@@ -35154,8 +33366,6 @@
       <c r="E896" s="6"/>
       <c r="F896" s="6"/>
       <c r="G896" s="6"/>
-      <c r="H896" s="6"/>
-      <c r="I896" s="6"/>
       <c r="J896" s="6"/>
       <c r="K896" s="6"/>
       <c r="L896" s="6"/>
@@ -35171,8 +33381,6 @@
       <c r="E897" s="6"/>
       <c r="F897" s="6"/>
       <c r="G897" s="6"/>
-      <c r="H897" s="6"/>
-      <c r="I897" s="6"/>
       <c r="J897" s="6"/>
       <c r="K897" s="6"/>
       <c r="L897" s="6"/>
@@ -35188,8 +33396,6 @@
       <c r="E898" s="6"/>
       <c r="F898" s="6"/>
       <c r="G898" s="6"/>
-      <c r="H898" s="6"/>
-      <c r="I898" s="6"/>
       <c r="J898" s="6"/>
       <c r="K898" s="6"/>
       <c r="L898" s="6"/>
@@ -35205,8 +33411,6 @@
       <c r="E899" s="6"/>
       <c r="F899" s="6"/>
       <c r="G899" s="6"/>
-      <c r="H899" s="6"/>
-      <c r="I899" s="6"/>
       <c r="J899" s="6"/>
       <c r="K899" s="6"/>
       <c r="L899" s="6"/>
@@ -35222,8 +33426,6 @@
       <c r="E900" s="6"/>
       <c r="F900" s="6"/>
       <c r="G900" s="6"/>
-      <c r="H900" s="6"/>
-      <c r="I900" s="6"/>
       <c r="J900" s="6"/>
       <c r="K900" s="6"/>
       <c r="L900" s="6"/>
@@ -35239,8 +33441,6 @@
       <c r="E901" s="6"/>
       <c r="F901" s="6"/>
       <c r="G901" s="6"/>
-      <c r="H901" s="6"/>
-      <c r="I901" s="6"/>
       <c r="J901" s="6"/>
       <c r="K901" s="6"/>
       <c r="L901" s="6"/>
@@ -35256,8 +33456,6 @@
       <c r="E902" s="6"/>
       <c r="F902" s="6"/>
       <c r="G902" s="6"/>
-      <c r="H902" s="6"/>
-      <c r="I902" s="6"/>
       <c r="J902" s="6"/>
       <c r="K902" s="6"/>
       <c r="L902" s="6"/>
@@ -35273,8 +33471,6 @@
       <c r="E903" s="6"/>
       <c r="F903" s="6"/>
       <c r="G903" s="6"/>
-      <c r="H903" s="6"/>
-      <c r="I903" s="6"/>
       <c r="J903" s="6"/>
       <c r="K903" s="6"/>
       <c r="L903" s="6"/>
@@ -35290,8 +33486,6 @@
       <c r="E904" s="6"/>
       <c r="F904" s="6"/>
       <c r="G904" s="6"/>
-      <c r="H904" s="6"/>
-      <c r="I904" s="6"/>
       <c r="J904" s="6"/>
       <c r="K904" s="6"/>
       <c r="L904" s="6"/>
@@ -35307,8 +33501,6 @@
       <c r="E905" s="6"/>
       <c r="F905" s="6"/>
       <c r="G905" s="6"/>
-      <c r="H905" s="6"/>
-      <c r="I905" s="6"/>
       <c r="J905" s="6"/>
       <c r="K905" s="6"/>
       <c r="L905" s="6"/>
@@ -35324,8 +33516,6 @@
       <c r="E906" s="6"/>
       <c r="F906" s="6"/>
       <c r="G906" s="6"/>
-      <c r="H906" s="6"/>
-      <c r="I906" s="6"/>
       <c r="J906" s="6"/>
       <c r="K906" s="6"/>
       <c r="L906" s="6"/>
@@ -35341,8 +33531,6 @@
       <c r="E907" s="6"/>
       <c r="F907" s="6"/>
       <c r="G907" s="6"/>
-      <c r="H907" s="6"/>
-      <c r="I907" s="6"/>
       <c r="J907" s="6"/>
       <c r="K907" s="6"/>
       <c r="L907" s="6"/>
@@ -35358,8 +33546,6 @@
       <c r="E908" s="6"/>
       <c r="F908" s="6"/>
       <c r="G908" s="6"/>
-      <c r="H908" s="6"/>
-      <c r="I908" s="6"/>
       <c r="J908" s="6"/>
       <c r="K908" s="6"/>
       <c r="L908" s="6"/>
@@ -35375,8 +33561,6 @@
       <c r="E909" s="6"/>
       <c r="F909" s="6"/>
       <c r="G909" s="6"/>
-      <c r="H909" s="6"/>
-      <c r="I909" s="6"/>
       <c r="J909" s="6"/>
       <c r="K909" s="6"/>
       <c r="L909" s="6"/>
@@ -35392,8 +33576,6 @@
       <c r="E910" s="6"/>
       <c r="F910" s="6"/>
       <c r="G910" s="6"/>
-      <c r="H910" s="6"/>
-      <c r="I910" s="6"/>
       <c r="J910" s="6"/>
       <c r="K910" s="6"/>
       <c r="L910" s="6"/>
@@ -35409,8 +33591,6 @@
       <c r="E911" s="6"/>
       <c r="F911" s="6"/>
       <c r="G911" s="6"/>
-      <c r="H911" s="6"/>
-      <c r="I911" s="6"/>
       <c r="J911" s="6"/>
       <c r="K911" s="6"/>
       <c r="L911" s="6"/>
@@ -35426,8 +33606,6 @@
       <c r="E912" s="6"/>
       <c r="F912" s="6"/>
       <c r="G912" s="6"/>
-      <c r="H912" s="6"/>
-      <c r="I912" s="6"/>
       <c r="J912" s="6"/>
       <c r="K912" s="6"/>
       <c r="L912" s="6"/>
@@ -35443,8 +33621,6 @@
       <c r="E913" s="6"/>
       <c r="F913" s="6"/>
       <c r="G913" s="6"/>
-      <c r="H913" s="6"/>
-      <c r="I913" s="6"/>
       <c r="J913" s="6"/>
       <c r="K913" s="6"/>
       <c r="L913" s="6"/>
@@ -35460,8 +33636,6 @@
       <c r="E914" s="6"/>
       <c r="F914" s="6"/>
       <c r="G914" s="6"/>
-      <c r="H914" s="6"/>
-      <c r="I914" s="6"/>
       <c r="J914" s="6"/>
       <c r="K914" s="6"/>
       <c r="L914" s="6"/>
@@ -35477,8 +33651,6 @@
       <c r="E915" s="6"/>
       <c r="F915" s="6"/>
       <c r="G915" s="6"/>
-      <c r="H915" s="6"/>
-      <c r="I915" s="6"/>
       <c r="J915" s="6"/>
       <c r="K915" s="6"/>
       <c r="L915" s="6"/>
@@ -35494,8 +33666,6 @@
       <c r="E916" s="6"/>
       <c r="F916" s="6"/>
       <c r="G916" s="6"/>
-      <c r="H916" s="6"/>
-      <c r="I916" s="6"/>
       <c r="J916" s="6"/>
       <c r="K916" s="6"/>
       <c r="L916" s="6"/>
@@ -35511,8 +33681,6 @@
       <c r="E917" s="6"/>
       <c r="F917" s="6"/>
       <c r="G917" s="6"/>
-      <c r="H917" s="6"/>
-      <c r="I917" s="6"/>
       <c r="J917" s="6"/>
       <c r="K917" s="6"/>
       <c r="L917" s="6"/>
@@ -35528,8 +33696,6 @@
       <c r="E918" s="6"/>
       <c r="F918" s="6"/>
       <c r="G918" s="6"/>
-      <c r="H918" s="6"/>
-      <c r="I918" s="6"/>
       <c r="J918" s="6"/>
       <c r="K918" s="6"/>
       <c r="L918" s="6"/>
@@ -35545,8 +33711,6 @@
       <c r="E919" s="6"/>
       <c r="F919" s="6"/>
       <c r="G919" s="6"/>
-      <c r="H919" s="6"/>
-      <c r="I919" s="6"/>
       <c r="J919" s="6"/>
       <c r="K919" s="6"/>
       <c r="L919" s="6"/>
@@ -35562,8 +33726,6 @@
       <c r="E920" s="6"/>
       <c r="F920" s="6"/>
       <c r="G920" s="6"/>
-      <c r="H920" s="6"/>
-      <c r="I920" s="6"/>
       <c r="J920" s="6"/>
       <c r="K920" s="6"/>
       <c r="L920" s="6"/>
@@ -35579,8 +33741,6 @@
       <c r="E921" s="6"/>
       <c r="F921" s="6"/>
       <c r="G921" s="6"/>
-      <c r="H921" s="6"/>
-      <c r="I921" s="6"/>
       <c r="J921" s="6"/>
       <c r="K921" s="6"/>
       <c r="L921" s="6"/>
@@ -35596,8 +33756,6 @@
       <c r="E922" s="6"/>
       <c r="F922" s="6"/>
       <c r="G922" s="6"/>
-      <c r="H922" s="6"/>
-      <c r="I922" s="6"/>
       <c r="J922" s="6"/>
       <c r="K922" s="6"/>
       <c r="L922" s="6"/>
@@ -35613,8 +33771,6 @@
       <c r="E923" s="6"/>
       <c r="F923" s="6"/>
       <c r="G923" s="6"/>
-      <c r="H923" s="6"/>
-      <c r="I923" s="6"/>
       <c r="J923" s="6"/>
       <c r="K923" s="6"/>
       <c r="L923" s="6"/>
@@ -35630,8 +33786,6 @@
       <c r="E924" s="6"/>
       <c r="F924" s="6"/>
       <c r="G924" s="6"/>
-      <c r="H924" s="6"/>
-      <c r="I924" s="6"/>
       <c r="J924" s="6"/>
       <c r="K924" s="6"/>
       <c r="L924" s="6"/>
@@ -35647,8 +33801,6 @@
       <c r="E925" s="6"/>
       <c r="F925" s="6"/>
       <c r="G925" s="6"/>
-      <c r="H925" s="6"/>
-      <c r="I925" s="6"/>
       <c r="J925" s="6"/>
       <c r="K925" s="6"/>
       <c r="L925" s="6"/>
@@ -35664,8 +33816,6 @@
       <c r="E926" s="6"/>
       <c r="F926" s="6"/>
       <c r="G926" s="6"/>
-      <c r="H926" s="6"/>
-      <c r="I926" s="6"/>
       <c r="J926" s="6"/>
       <c r="K926" s="6"/>
       <c r="L926" s="6"/>
@@ -35681,8 +33831,6 @@
       <c r="E927" s="6"/>
       <c r="F927" s="6"/>
       <c r="G927" s="6"/>
-      <c r="H927" s="6"/>
-      <c r="I927" s="6"/>
       <c r="J927" s="6"/>
       <c r="K927" s="6"/>
       <c r="L927" s="6"/>
@@ -35698,8 +33846,6 @@
       <c r="E928" s="6"/>
       <c r="F928" s="6"/>
       <c r="G928" s="6"/>
-      <c r="H928" s="6"/>
-      <c r="I928" s="6"/>
       <c r="J928" s="6"/>
       <c r="K928" s="6"/>
       <c r="L928" s="6"/>
@@ -35715,8 +33861,6 @@
       <c r="E929" s="6"/>
       <c r="F929" s="6"/>
       <c r="G929" s="6"/>
-      <c r="H929" s="6"/>
-      <c r="I929" s="6"/>
       <c r="J929" s="6"/>
       <c r="K929" s="6"/>
       <c r="L929" s="6"/>
@@ -35732,8 +33876,6 @@
       <c r="E930" s="6"/>
       <c r="F930" s="6"/>
       <c r="G930" s="6"/>
-      <c r="H930" s="6"/>
-      <c r="I930" s="6"/>
       <c r="J930" s="6"/>
       <c r="K930" s="6"/>
       <c r="L930" s="6"/>
@@ -35749,8 +33891,6 @@
       <c r="E931" s="6"/>
       <c r="F931" s="6"/>
       <c r="G931" s="6"/>
-      <c r="H931" s="6"/>
-      <c r="I931" s="6"/>
       <c r="J931" s="6"/>
       <c r="K931" s="6"/>
       <c r="L931" s="6"/>
@@ -35766,8 +33906,6 @@
       <c r="E932" s="6"/>
       <c r="F932" s="6"/>
       <c r="G932" s="6"/>
-      <c r="H932" s="6"/>
-      <c r="I932" s="6"/>
       <c r="J932" s="6"/>
       <c r="K932" s="6"/>
       <c r="L932" s="6"/>
@@ -35783,8 +33921,6 @@
       <c r="E933" s="6"/>
       <c r="F933" s="6"/>
       <c r="G933" s="6"/>
-      <c r="H933" s="6"/>
-      <c r="I933" s="6"/>
       <c r="J933" s="6"/>
       <c r="K933" s="6"/>
       <c r="L933" s="6"/>
@@ -35800,8 +33936,6 @@
       <c r="E934" s="6"/>
       <c r="F934" s="6"/>
       <c r="G934" s="6"/>
-      <c r="H934" s="6"/>
-      <c r="I934" s="6"/>
       <c r="J934" s="6"/>
       <c r="K934" s="6"/>
       <c r="L934" s="6"/>
@@ -35817,8 +33951,6 @@
       <c r="E935" s="6"/>
       <c r="F935" s="6"/>
       <c r="G935" s="6"/>
-      <c r="H935" s="6"/>
-      <c r="I935" s="6"/>
       <c r="J935" s="6"/>
       <c r="K935" s="6"/>
       <c r="L935" s="6"/>
@@ -35834,8 +33966,6 @@
       <c r="E936" s="6"/>
       <c r="F936" s="6"/>
       <c r="G936" s="6"/>
-      <c r="H936" s="6"/>
-      <c r="I936" s="6"/>
       <c r="J936" s="6"/>
       <c r="K936" s="6"/>
       <c r="L936" s="6"/>
@@ -35851,8 +33981,6 @@
       <c r="E937" s="6"/>
       <c r="F937" s="6"/>
       <c r="G937" s="6"/>
-      <c r="H937" s="6"/>
-      <c r="I937" s="6"/>
       <c r="J937" s="6"/>
       <c r="K937" s="6"/>
       <c r="L937" s="6"/>
@@ -35868,8 +33996,6 @@
       <c r="E938" s="6"/>
       <c r="F938" s="6"/>
       <c r="G938" s="6"/>
-      <c r="H938" s="6"/>
-      <c r="I938" s="6"/>
       <c r="J938" s="6"/>
       <c r="K938" s="6"/>
       <c r="L938" s="6"/>
@@ -35885,8 +34011,6 @@
       <c r="E939" s="6"/>
       <c r="F939" s="6"/>
       <c r="G939" s="6"/>
-      <c r="H939" s="6"/>
-      <c r="I939" s="6"/>
       <c r="J939" s="6"/>
       <c r="K939" s="6"/>
       <c r="L939" s="6"/>
@@ -35902,8 +34026,6 @@
       <c r="E940" s="6"/>
       <c r="F940" s="6"/>
       <c r="G940" s="6"/>
-      <c r="H940" s="6"/>
-      <c r="I940" s="6"/>
       <c r="J940" s="6"/>
       <c r="K940" s="6"/>
       <c r="L940" s="6"/>
@@ -35919,8 +34041,6 @@
       <c r="E941" s="6"/>
       <c r="F941" s="6"/>
       <c r="G941" s="6"/>
-      <c r="H941" s="6"/>
-      <c r="I941" s="6"/>
       <c r="J941" s="6"/>
       <c r="K941" s="6"/>
       <c r="L941" s="6"/>
@@ -35936,8 +34056,6 @@
       <c r="E942" s="6"/>
       <c r="F942" s="6"/>
       <c r="G942" s="6"/>
-      <c r="H942" s="6"/>
-      <c r="I942" s="6"/>
       <c r="J942" s="6"/>
       <c r="K942" s="6"/>
       <c r="L942" s="6"/>
@@ -35953,8 +34071,6 @@
       <c r="E943" s="6"/>
       <c r="F943" s="6"/>
       <c r="G943" s="6"/>
-      <c r="H943" s="6"/>
-      <c r="I943" s="6"/>
       <c r="J943" s="6"/>
       <c r="K943" s="6"/>
       <c r="L943" s="6"/>
@@ -35970,8 +34086,6 @@
       <c r="E944" s="6"/>
       <c r="F944" s="6"/>
       <c r="G944" s="6"/>
-      <c r="H944" s="6"/>
-      <c r="I944" s="6"/>
       <c r="J944" s="6"/>
       <c r="K944" s="6"/>
       <c r="L944" s="6"/>
@@ -35987,8 +34101,6 @@
       <c r="E945" s="6"/>
       <c r="F945" s="6"/>
       <c r="G945" s="6"/>
-      <c r="H945" s="6"/>
-      <c r="I945" s="6"/>
       <c r="J945" s="6"/>
       <c r="K945" s="6"/>
       <c r="L945" s="6"/>
@@ -36004,8 +34116,6 @@
       <c r="E946" s="6"/>
       <c r="F946" s="6"/>
       <c r="G946" s="6"/>
-      <c r="H946" s="6"/>
-      <c r="I946" s="6"/>
       <c r="J946" s="6"/>
       <c r="K946" s="6"/>
       <c r="L946" s="6"/>
@@ -36021,8 +34131,6 @@
       <c r="E947" s="6"/>
       <c r="F947" s="6"/>
       <c r="G947" s="6"/>
-      <c r="H947" s="6"/>
-      <c r="I947" s="6"/>
       <c r="J947" s="6"/>
       <c r="K947" s="6"/>
       <c r="L947" s="6"/>
@@ -36038,8 +34146,6 @@
       <c r="E948" s="6"/>
       <c r="F948" s="6"/>
       <c r="G948" s="6"/>
-      <c r="H948" s="6"/>
-      <c r="I948" s="6"/>
       <c r="J948" s="6"/>
       <c r="K948" s="6"/>
       <c r="L948" s="6"/>
@@ -36055,8 +34161,6 @@
       <c r="E949" s="6"/>
       <c r="F949" s="6"/>
       <c r="G949" s="6"/>
-      <c r="H949" s="6"/>
-      <c r="I949" s="6"/>
       <c r="J949" s="6"/>
       <c r="K949" s="6"/>
       <c r="L949" s="6"/>
@@ -36072,8 +34176,6 @@
       <c r="E950" s="6"/>
       <c r="F950" s="6"/>
       <c r="G950" s="6"/>
-      <c r="H950" s="6"/>
-      <c r="I950" s="6"/>
       <c r="J950" s="6"/>
       <c r="K950" s="6"/>
       <c r="L950" s="6"/>
@@ -36089,8 +34191,6 @@
       <c r="E951" s="6"/>
       <c r="F951" s="6"/>
       <c r="G951" s="6"/>
-      <c r="H951" s="6"/>
-      <c r="I951" s="6"/>
       <c r="J951" s="6"/>
       <c r="K951" s="6"/>
       <c r="L951" s="6"/>
@@ -36106,8 +34206,6 @@
       <c r="E952" s="6"/>
       <c r="F952" s="6"/>
       <c r="G952" s="6"/>
-      <c r="H952" s="6"/>
-      <c r="I952" s="6"/>
       <c r="J952" s="6"/>
       <c r="K952" s="6"/>
       <c r="L952" s="6"/>
@@ -36123,8 +34221,6 @@
       <c r="E953" s="6"/>
       <c r="F953" s="6"/>
       <c r="G953" s="6"/>
-      <c r="H953" s="6"/>
-      <c r="I953" s="6"/>
       <c r="J953" s="6"/>
       <c r="K953" s="6"/>
       <c r="L953" s="6"/>
@@ -36140,8 +34236,6 @@
       <c r="E954" s="6"/>
       <c r="F954" s="6"/>
       <c r="G954" s="6"/>
-      <c r="H954" s="6"/>
-      <c r="I954" s="6"/>
       <c r="J954" s="6"/>
       <c r="K954" s="6"/>
       <c r="L954" s="6"/>
@@ -36157,8 +34251,6 @@
       <c r="E955" s="6"/>
       <c r="F955" s="6"/>
       <c r="G955" s="6"/>
-      <c r="H955" s="6"/>
-      <c r="I955" s="6"/>
       <c r="J955" s="6"/>
       <c r="K955" s="6"/>
       <c r="L955" s="6"/>
@@ -36174,8 +34266,6 @@
       <c r="E956" s="6"/>
       <c r="F956" s="6"/>
       <c r="G956" s="6"/>
-      <c r="H956" s="6"/>
-      <c r="I956" s="6"/>
       <c r="J956" s="6"/>
       <c r="K956" s="6"/>
       <c r="L956" s="6"/>
@@ -36191,8 +34281,6 @@
       <c r="E957" s="6"/>
       <c r="F957" s="6"/>
       <c r="G957" s="6"/>
-      <c r="H957" s="6"/>
-      <c r="I957" s="6"/>
       <c r="J957" s="6"/>
       <c r="K957" s="6"/>
       <c r="L957" s="6"/>
@@ -36208,8 +34296,6 @@
       <c r="E958" s="6"/>
       <c r="F958" s="6"/>
       <c r="G958" s="6"/>
-      <c r="H958" s="6"/>
-      <c r="I958" s="6"/>
       <c r="J958" s="6"/>
       <c r="K958" s="6"/>
       <c r="L958" s="6"/>
@@ -36225,8 +34311,6 @@
       <c r="E959" s="6"/>
       <c r="F959" s="6"/>
       <c r="G959" s="6"/>
-      <c r="H959" s="6"/>
-      <c r="I959" s="6"/>
       <c r="J959" s="6"/>
       <c r="K959" s="6"/>
       <c r="L959" s="6"/>
@@ -36242,8 +34326,6 @@
       <c r="E960" s="6"/>
       <c r="F960" s="6"/>
       <c r="G960" s="6"/>
-      <c r="H960" s="6"/>
-      <c r="I960" s="6"/>
       <c r="J960" s="6"/>
       <c r="K960" s="6"/>
       <c r="L960" s="6"/>
@@ -36259,8 +34341,6 @@
       <c r="E961" s="6"/>
       <c r="F961" s="6"/>
       <c r="G961" s="6"/>
-      <c r="H961" s="6"/>
-      <c r="I961" s="6"/>
       <c r="J961" s="6"/>
       <c r="K961" s="6"/>
       <c r="L961" s="6"/>
@@ -36276,8 +34356,6 @@
       <c r="E962" s="6"/>
       <c r="F962" s="6"/>
       <c r="G962" s="6"/>
-      <c r="H962" s="6"/>
-      <c r="I962" s="6"/>
       <c r="J962" s="6"/>
       <c r="K962" s="6"/>
       <c r="L962" s="6"/>
@@ -36293,8 +34371,6 @@
       <c r="E963" s="6"/>
       <c r="F963" s="6"/>
       <c r="G963" s="6"/>
-      <c r="H963" s="6"/>
-      <c r="I963" s="6"/>
       <c r="J963" s="6"/>
       <c r="K963" s="6"/>
       <c r="L963" s="6"/>
@@ -36310,8 +34386,6 @@
       <c r="E964" s="6"/>
       <c r="F964" s="6"/>
       <c r="G964" s="6"/>
-      <c r="H964" s="6"/>
-      <c r="I964" s="6"/>
       <c r="J964" s="6"/>
       <c r="K964" s="6"/>
       <c r="L964" s="6"/>
@@ -36327,8 +34401,6 @@
       <c r="E965" s="6"/>
       <c r="F965" s="6"/>
       <c r="G965" s="6"/>
-      <c r="H965" s="6"/>
-      <c r="I965" s="6"/>
       <c r="J965" s="6"/>
       <c r="K965" s="6"/>
       <c r="L965" s="6"/>
@@ -36344,8 +34416,6 @@
       <c r="E966" s="6"/>
       <c r="F966" s="6"/>
       <c r="G966" s="6"/>
-      <c r="H966" s="6"/>
-      <c r="I966" s="6"/>
       <c r="J966" s="6"/>
       <c r="K966" s="6"/>
       <c r="L966" s="6"/>
@@ -36361,8 +34431,6 @@
       <c r="E967" s="6"/>
       <c r="F967" s="6"/>
       <c r="G967" s="6"/>
-      <c r="H967" s="6"/>
-      <c r="I967" s="6"/>
       <c r="J967" s="6"/>
       <c r="K967" s="6"/>
       <c r="L967" s="6"/>
@@ -36378,8 +34446,6 @@
       <c r="E968" s="6"/>
       <c r="F968" s="6"/>
       <c r="G968" s="6"/>
-      <c r="H968" s="6"/>
-      <c r="I968" s="6"/>
       <c r="J968" s="6"/>
       <c r="K968" s="6"/>
       <c r="L968" s="6"/>
@@ -36395,8 +34461,6 @@
       <c r="E969" s="6"/>
       <c r="F969" s="6"/>
       <c r="G969" s="6"/>
-      <c r="H969" s="6"/>
-      <c r="I969" s="6"/>
       <c r="J969" s="6"/>
       <c r="K969" s="6"/>
       <c r="L969" s="6"/>
@@ -36412,8 +34476,6 @@
       <c r="E970" s="6"/>
       <c r="F970" s="6"/>
       <c r="G970" s="6"/>
-      <c r="H970" s="6"/>
-      <c r="I970" s="6"/>
       <c r="J970" s="6"/>
       <c r="K970" s="6"/>
       <c r="L970" s="6"/>
@@ -36429,8 +34491,6 @@
       <c r="E971" s="6"/>
       <c r="F971" s="6"/>
       <c r="G971" s="6"/>
-      <c r="H971" s="6"/>
-      <c r="I971" s="6"/>
       <c r="J971" s="6"/>
       <c r="K971" s="6"/>
       <c r="L971" s="6"/>
@@ -36446,8 +34506,6 @@
       <c r="E972" s="6"/>
       <c r="F972" s="6"/>
       <c r="G972" s="6"/>
-      <c r="H972" s="6"/>
-      <c r="I972" s="6"/>
       <c r="J972" s="6"/>
       <c r="K972" s="6"/>
       <c r="L972" s="6"/>
@@ -36463,8 +34521,6 @@
       <c r="E973" s="6"/>
       <c r="F973" s="6"/>
       <c r="G973" s="6"/>
-      <c r="H973" s="6"/>
-      <c r="I973" s="6"/>
       <c r="J973" s="6"/>
       <c r="K973" s="6"/>
       <c r="L973" s="6"/>
@@ -36480,8 +34536,6 @@
       <c r="E974" s="6"/>
       <c r="F974" s="6"/>
       <c r="G974" s="6"/>
-      <c r="H974" s="6"/>
-      <c r="I974" s="6"/>
       <c r="J974" s="6"/>
       <c r="K974" s="6"/>
       <c r="L974" s="6"/>
@@ -36497,8 +34551,6 @@
       <c r="E975" s="6"/>
       <c r="F975" s="6"/>
       <c r="G975" s="6"/>
-      <c r="H975" s="6"/>
-      <c r="I975" s="6"/>
       <c r="J975" s="6"/>
       <c r="K975" s="6"/>
       <c r="L975" s="6"/>
@@ -36514,8 +34566,6 @@
       <c r="E976" s="6"/>
       <c r="F976" s="6"/>
       <c r="G976" s="6"/>
-      <c r="H976" s="6"/>
-      <c r="I976" s="6"/>
       <c r="J976" s="6"/>
       <c r="K976" s="6"/>
       <c r="L976" s="6"/>
@@ -36531,8 +34581,6 @@
       <c r="E977" s="6"/>
       <c r="F977" s="6"/>
       <c r="G977" s="6"/>
-      <c r="H977" s="6"/>
-      <c r="I977" s="6"/>
       <c r="J977" s="6"/>
       <c r="K977" s="6"/>
       <c r="L977" s="6"/>
@@ -36548,8 +34596,6 @@
       <c r="E978" s="6"/>
       <c r="F978" s="6"/>
       <c r="G978" s="6"/>
-      <c r="H978" s="6"/>
-      <c r="I978" s="6"/>
       <c r="J978" s="6"/>
       <c r="K978" s="6"/>
       <c r="L978" s="6"/>
@@ -36565,8 +34611,6 @@
       <c r="E979" s="6"/>
       <c r="F979" s="6"/>
       <c r="G979" s="6"/>
-      <c r="H979" s="6"/>
-      <c r="I979" s="6"/>
       <c r="J979" s="6"/>
       <c r="K979" s="6"/>
       <c r="L979" s="6"/>
@@ -36582,8 +34626,6 @@
       <c r="E980" s="6"/>
       <c r="F980" s="6"/>
       <c r="G980" s="6"/>
-      <c r="H980" s="6"/>
-      <c r="I980" s="6"/>
       <c r="J980" s="6"/>
       <c r="K980" s="6"/>
       <c r="L980" s="6"/>
@@ -36599,8 +34641,6 @@
       <c r="E981" s="6"/>
       <c r="F981" s="6"/>
       <c r="G981" s="6"/>
-      <c r="H981" s="6"/>
-      <c r="I981" s="6"/>
       <c r="J981" s="6"/>
       <c r="K981" s="6"/>
       <c r="L981" s="6"/>
@@ -36616,8 +34656,6 @@
       <c r="E982" s="6"/>
       <c r="F982" s="6"/>
       <c r="G982" s="6"/>
-      <c r="H982" s="6"/>
-      <c r="I982" s="6"/>
       <c r="J982" s="6"/>
       <c r="K982" s="6"/>
       <c r="L982" s="6"/>
@@ -36633,8 +34671,6 @@
       <c r="E983" s="6"/>
       <c r="F983" s="6"/>
       <c r="G983" s="6"/>
-      <c r="H983" s="6"/>
-      <c r="I983" s="6"/>
       <c r="J983" s="6"/>
       <c r="K983" s="6"/>
       <c r="L983" s="6"/>
@@ -36650,8 +34686,6 @@
       <c r="E984" s="6"/>
       <c r="F984" s="6"/>
       <c r="G984" s="6"/>
-      <c r="H984" s="6"/>
-      <c r="I984" s="6"/>
       <c r="J984" s="6"/>
       <c r="K984" s="6"/>
       <c r="L984" s="6"/>
@@ -36667,8 +34701,6 @@
       <c r="E985" s="6"/>
       <c r="F985" s="6"/>
       <c r="G985" s="6"/>
-      <c r="H985" s="6"/>
-      <c r="I985" s="6"/>
       <c r="J985" s="6"/>
       <c r="K985" s="6"/>
       <c r="L985" s="6"/>
@@ -36684,8 +34716,6 @@
       <c r="E986" s="6"/>
       <c r="F986" s="6"/>
       <c r="G986" s="6"/>
-      <c r="H986" s="6"/>
-      <c r="I986" s="6"/>
       <c r="J986" s="6"/>
       <c r="K986" s="6"/>
       <c r="L986" s="6"/>
@@ -36701,8 +34731,6 @@
       <c r="E987" s="6"/>
       <c r="F987" s="6"/>
       <c r="G987" s="6"/>
-      <c r="H987" s="6"/>
-      <c r="I987" s="6"/>
       <c r="J987" s="6"/>
       <c r="K987" s="6"/>
       <c r="L987" s="6"/>
@@ -36718,8 +34746,6 @@
       <c r="E988" s="6"/>
       <c r="F988" s="6"/>
       <c r="G988" s="6"/>
-      <c r="H988" s="6"/>
-      <c r="I988" s="6"/>
       <c r="J988" s="6"/>
       <c r="K988" s="6"/>
       <c r="L988" s="6"/>
@@ -36735,8 +34761,6 @@
       <c r="E989" s="6"/>
       <c r="F989" s="6"/>
       <c r="G989" s="6"/>
-      <c r="H989" s="6"/>
-      <c r="I989" s="6"/>
       <c r="J989" s="6"/>
       <c r="K989" s="6"/>
       <c r="L989" s="6"/>
@@ -36752,8 +34776,6 @@
       <c r="E990" s="6"/>
       <c r="F990" s="6"/>
       <c r="G990" s="6"/>
-      <c r="H990" s="6"/>
-      <c r="I990" s="6"/>
       <c r="J990" s="6"/>
       <c r="K990" s="6"/>
       <c r="L990" s="6"/>
@@ -36769,8 +34791,6 @@
       <c r="E991" s="6"/>
       <c r="F991" s="6"/>
       <c r="G991" s="6"/>
-      <c r="H991" s="6"/>
-      <c r="I991" s="6"/>
       <c r="J991" s="6"/>
       <c r="K991" s="6"/>
       <c r="L991" s="6"/>
@@ -36786,8 +34806,6 @@
       <c r="E992" s="6"/>
       <c r="F992" s="6"/>
       <c r="G992" s="6"/>
-      <c r="H992" s="6"/>
-      <c r="I992" s="6"/>
       <c r="J992" s="6"/>
       <c r="K992" s="6"/>
       <c r="L992" s="6"/>
@@ -36803,8 +34821,6 @@
       <c r="E993" s="6"/>
       <c r="F993" s="6"/>
       <c r="G993" s="6"/>
-      <c r="H993" s="6"/>
-      <c r="I993" s="6"/>
       <c r="J993" s="6"/>
       <c r="K993" s="6"/>
       <c r="L993" s="6"/>
@@ -36820,8 +34836,6 @@
       <c r="E994" s="6"/>
       <c r="F994" s="6"/>
       <c r="G994" s="6"/>
-      <c r="H994" s="6"/>
-      <c r="I994" s="6"/>
       <c r="J994" s="6"/>
       <c r="K994" s="6"/>
       <c r="L994" s="6"/>
@@ -36837,8 +34851,6 @@
       <c r="E995" s="6"/>
       <c r="F995" s="6"/>
       <c r="G995" s="6"/>
-      <c r="H995" s="6"/>
-      <c r="I995" s="6"/>
       <c r="J995" s="6"/>
       <c r="K995" s="6"/>
       <c r="L995" s="6"/>
@@ -36854,8 +34866,6 @@
       <c r="E996" s="6"/>
       <c r="F996" s="6"/>
       <c r="G996" s="6"/>
-      <c r="H996" s="6"/>
-      <c r="I996" s="6"/>
       <c r="J996" s="6"/>
       <c r="K996" s="6"/>
       <c r="L996" s="6"/>
@@ -36871,8 +34881,6 @@
       <c r="E997" s="6"/>
       <c r="F997" s="6"/>
       <c r="G997" s="6"/>
-      <c r="H997" s="6"/>
-      <c r="I997" s="6"/>
       <c r="J997" s="6"/>
       <c r="K997" s="6"/>
       <c r="L997" s="6"/>
@@ -36888,8 +34896,6 @@
       <c r="E998" s="6"/>
       <c r="F998" s="6"/>
       <c r="G998" s="6"/>
-      <c r="H998" s="6"/>
-      <c r="I998" s="6"/>
       <c r="J998" s="6"/>
       <c r="K998" s="6"/>
       <c r="L998" s="6"/>
@@ -36899,14 +34905,10 @@
       <c r="P998" s="6"/>
       <c r="Q998" s="6"/>
     </row>
+    <row r="1000" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I1000"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q47" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Импост двери"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C15D32B-A49D-5944-8084-362A03CDB4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7071ED20-D789-624C-8F10-9DB90FC1B824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="СПРАВОЧНИК -1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$263</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'СПРАВОЧНИК -3'!$A$1:$Q$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'СПРАВОЧНИК -3'!$A$1:$Q$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1591,7 +1591,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1687,6 +1687,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1730,7 +1736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1785,6 +1791,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2007,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z563"/>
@@ -2041,7 +2048,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -2050,13 +2057,13 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -2065,7 +2072,7 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="27" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -2087,7 +2094,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2131,7 +2138,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
@@ -2175,7 +2182,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
@@ -2219,7 +2226,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
@@ -2263,7 +2270,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -2307,7 +2314,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -2351,7 +2358,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
@@ -2395,7 +2402,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -2439,7 +2446,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -2483,7 +2490,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -2527,7 +2534,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2571,7 +2578,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
@@ -2615,7 +2622,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
@@ -2659,7 +2666,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -2703,7 +2710,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:24" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
@@ -2747,7 +2754,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
@@ -2791,7 +2798,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>15</v>
       </c>
@@ -2835,7 +2842,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>63</v>
       </c>
@@ -2879,7 +2886,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>63</v>
       </c>
@@ -2923,7 +2930,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>63</v>
       </c>
@@ -2967,7 +2974,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>63</v>
       </c>
@@ -3011,7 +3018,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>63</v>
       </c>
@@ -3055,7 +3062,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>15</v>
       </c>
@@ -3099,7 +3106,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>15</v>
       </c>
@@ -3143,7 +3150,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>15</v>
       </c>
@@ -3187,7 +3194,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3231,7 +3238,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
         <v>15</v>
       </c>
@@ -3275,7 +3282,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
@@ -3319,7 +3326,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>15</v>
       </c>
@@ -3363,7 +3370,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>15</v>
       </c>
@@ -3407,7 +3414,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -3451,7 +3458,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
         <v>15</v>
       </c>
@@ -3495,7 +3502,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
         <v>15</v>
       </c>
@@ -3539,7 +3546,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
         <v>15</v>
       </c>
@@ -3583,7 +3590,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>63</v>
       </c>
@@ -3627,7 +3634,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
@@ -3671,7 +3678,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>63</v>
       </c>
@@ -3715,7 +3722,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3759,7 +3766,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>63</v>
       </c>
@@ -3803,7 +3810,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>63</v>
       </c>
@@ -3847,7 +3854,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>63</v>
       </c>
@@ -3891,7 +3898,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>63</v>
       </c>
@@ -3935,7 +3942,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>63</v>
       </c>
@@ -3979,7 +3986,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
         <v>63</v>
       </c>
@@ -4023,7 +4030,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
         <v>63</v>
       </c>
@@ -4067,7 +4074,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>63</v>
       </c>
@@ -4111,7 +4118,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>63</v>
       </c>
@@ -4155,7 +4162,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="9" t="s">
         <v>63</v>
       </c>
@@ -4199,7 +4206,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:20" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
         <v>63</v>
       </c>
@@ -4243,7 +4250,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="9" t="s">
         <v>63</v>
       </c>
@@ -4287,7 +4294,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="9" t="s">
         <v>63</v>
       </c>
@@ -4331,7 +4338,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="9" t="s">
         <v>63</v>
       </c>
@@ -4375,7 +4382,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="9" t="s">
         <v>63</v>
       </c>
@@ -4419,7 +4426,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="9" t="s">
         <v>63</v>
       </c>
@@ -4507,7 +4514,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="9" t="s">
         <v>63</v>
       </c>
@@ -4551,7 +4558,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="9" t="s">
         <v>63</v>
       </c>
@@ -4595,7 +4602,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="9" t="s">
         <v>63</v>
       </c>
@@ -4639,7 +4646,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="9" t="s">
         <v>63</v>
       </c>
@@ -4685,7 +4692,7 @@
       <c r="S60" s="11"/>
       <c r="T60" s="11"/>
     </row>
-    <row r="61" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="9" t="s">
         <v>63</v>
       </c>
@@ -4729,7 +4736,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="9" t="s">
         <v>63</v>
       </c>
@@ -4773,7 +4780,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -4817,7 +4824,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="9" t="s">
         <v>63</v>
       </c>
@@ -4861,7 +4868,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="9" t="s">
         <v>63</v>
       </c>
@@ -4905,7 +4912,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="9" t="s">
         <v>63</v>
       </c>
@@ -4949,7 +4956,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
@@ -4993,7 +5000,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
         <v>63</v>
       </c>
@@ -5037,7 +5044,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
         <v>63</v>
       </c>
@@ -5081,7 +5088,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="9" t="s">
         <v>63</v>
       </c>
@@ -5125,7 +5132,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="9" t="s">
         <v>63</v>
       </c>
@@ -5169,7 +5176,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="9" t="s">
         <v>63</v>
       </c>
@@ -5213,7 +5220,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="9" t="s">
         <v>63</v>
       </c>
@@ -5257,7 +5264,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="9" t="s">
         <v>63</v>
       </c>
@@ -5301,7 +5308,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="9" t="s">
         <v>63</v>
       </c>
@@ -5345,7 +5352,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="9" t="s">
         <v>63</v>
       </c>
@@ -5389,7 +5396,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
@@ -5433,7 +5440,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="9" t="s">
         <v>63</v>
       </c>
@@ -5477,7 +5484,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="9" t="s">
         <v>63</v>
       </c>
@@ -5565,7 +5572,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="9" t="s">
         <v>63</v>
       </c>
@@ -5609,7 +5616,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="9" t="s">
         <v>63</v>
       </c>
@@ -5653,7 +5660,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="9" t="s">
         <v>63</v>
       </c>
@@ -5697,7 +5704,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="9" t="s">
         <v>63</v>
       </c>
@@ -5741,7 +5748,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="9" t="s">
         <v>63</v>
       </c>
@@ -5785,7 +5792,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="9" t="s">
         <v>63</v>
       </c>
@@ -5829,7 +5836,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="9" t="s">
         <v>63</v>
       </c>
@@ -5873,7 +5880,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="9" t="s">
         <v>63</v>
       </c>
@@ -5917,7 +5924,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="9" t="s">
         <v>63</v>
       </c>
@@ -5961,7 +5968,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="9" t="s">
         <v>63</v>
       </c>
@@ -6005,7 +6012,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="9" t="s">
         <v>63</v>
       </c>
@@ -6049,7 +6056,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="9" t="s">
         <v>63</v>
       </c>
@@ -6093,7 +6100,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="9" t="s">
         <v>63</v>
       </c>
@@ -6139,7 +6146,7 @@
       <c r="S93" s="11"/>
       <c r="T93" s="11"/>
     </row>
-    <row r="94" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="9" t="s">
         <v>63</v>
       </c>
@@ -6183,7 +6190,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="9" t="s">
         <v>63</v>
       </c>
@@ -6227,7 +6234,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="9" t="s">
         <v>63</v>
       </c>
@@ -6315,7 +6322,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="9" t="s">
         <v>63</v>
       </c>
@@ -6359,7 +6366,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="9" t="s">
         <v>63</v>
       </c>
@@ -6403,7 +6410,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="9" t="s">
         <v>63</v>
       </c>
@@ -6447,7 +6454,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="9" t="s">
         <v>63</v>
       </c>
@@ -6491,7 +6498,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="9" t="s">
         <v>63</v>
       </c>
@@ -6535,7 +6542,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="9" t="s">
         <v>63</v>
       </c>
@@ -6579,7 +6586,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="9" t="s">
         <v>63</v>
       </c>
@@ -6623,7 +6630,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="9" t="s">
         <v>63</v>
       </c>
@@ -6667,7 +6674,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="9" t="s">
         <v>63</v>
       </c>
@@ -6711,7 +6718,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="9" t="s">
         <v>63</v>
       </c>
@@ -6755,7 +6762,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="9" t="s">
         <v>63</v>
       </c>
@@ -6799,7 +6806,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="9" t="s">
         <v>63</v>
       </c>
@@ -6843,7 +6850,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="9" t="s">
         <v>63</v>
       </c>
@@ -6887,7 +6894,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="9" t="s">
         <v>63</v>
       </c>
@@ -6931,7 +6938,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="9" t="s">
         <v>63</v>
       </c>
@@ -6975,7 +6982,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="9" t="s">
         <v>63</v>
       </c>
@@ -7019,7 +7026,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="9" t="s">
         <v>63</v>
       </c>
@@ -7063,7 +7070,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="9" t="s">
         <v>63</v>
       </c>
@@ -7107,7 +7114,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="9" t="s">
         <v>63</v>
       </c>
@@ -7151,7 +7158,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="9" t="s">
         <v>63</v>
       </c>
@@ -7195,7 +7202,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="9" t="s">
         <v>63</v>
       </c>
@@ -7239,7 +7246,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="9" t="s">
         <v>63</v>
       </c>
@@ -7283,7 +7290,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="9" t="s">
         <v>63</v>
       </c>
@@ -7327,7 +7334,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="9" t="s">
         <v>63</v>
       </c>
@@ -7371,7 +7378,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="9" t="s">
         <v>63</v>
       </c>
@@ -7415,7 +7422,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="9" t="s">
         <v>63</v>
       </c>
@@ -7459,7 +7466,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="9" t="s">
         <v>63</v>
       </c>
@@ -7503,7 +7510,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="9" t="s">
         <v>63</v>
       </c>
@@ -7547,7 +7554,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="9" t="s">
         <v>63</v>
       </c>
@@ -7591,7 +7598,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="9" t="s">
         <v>63</v>
       </c>
@@ -7635,7 +7642,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="9" t="s">
         <v>63</v>
       </c>
@@ -7679,7 +7686,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="9" t="s">
         <v>63</v>
       </c>
@@ -7723,7 +7730,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="9" t="s">
         <v>63</v>
       </c>
@@ -7769,7 +7776,7 @@
       <c r="S130" s="11"/>
       <c r="T130" s="11"/>
     </row>
-    <row r="131" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="9" t="s">
         <v>63</v>
       </c>
@@ -7813,7 +7820,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="9" t="s">
         <v>63</v>
       </c>
@@ -7857,7 +7864,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="9" t="s">
         <v>63</v>
       </c>
@@ -7901,7 +7908,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="9" t="s">
         <v>63</v>
       </c>
@@ -7945,7 +7952,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="9" t="s">
         <v>63</v>
       </c>
@@ -7989,7 +7996,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="9" t="s">
         <v>63</v>
       </c>
@@ -8033,7 +8040,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="9" t="s">
         <v>63</v>
       </c>
@@ -8077,7 +8084,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="9" t="s">
         <v>63</v>
       </c>
@@ -8121,7 +8128,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="9" t="s">
         <v>63</v>
       </c>
@@ -8165,7 +8172,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="9" t="s">
         <v>63</v>
       </c>
@@ -8209,7 +8216,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="9" t="s">
         <v>63</v>
       </c>
@@ -8253,7 +8260,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="9" t="s">
         <v>63</v>
       </c>
@@ -8297,7 +8304,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="9" t="s">
         <v>63</v>
       </c>
@@ -8341,7 +8348,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="9" t="s">
         <v>15</v>
       </c>
@@ -8385,7 +8392,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="9" t="s">
         <v>15</v>
       </c>
@@ -8429,7 +8436,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="146" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="9" t="s">
         <v>15</v>
       </c>
@@ -8473,7 +8480,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="147" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="9" t="s">
         <v>15</v>
       </c>
@@ -8522,7 +8529,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" s="25" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:26" s="25" customFormat="1" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="9" t="s">
         <v>325</v>
       </c>
@@ -8577,7 +8584,7 @@
       <c r="Y148" s="9"/>
       <c r="Z148" s="9"/>
     </row>
-    <row r="149" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="9" t="s">
         <v>325</v>
       </c>
@@ -8621,7 +8628,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="9" t="s">
         <v>325</v>
       </c>
@@ -8665,7 +8672,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="151" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="9" t="s">
         <v>325</v>
       </c>
@@ -8709,7 +8716,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="152" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="9" t="s">
         <v>325</v>
       </c>
@@ -8753,7 +8760,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="153" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="9" t="s">
         <v>325</v>
       </c>
@@ -8797,7 +8804,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="154" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="9" t="s">
         <v>325</v>
       </c>
@@ -8841,7 +8848,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="155" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="9" t="s">
         <v>325</v>
       </c>
@@ -8885,7 +8892,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="156" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="9" t="s">
         <v>325</v>
       </c>
@@ -8929,7 +8936,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="157" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="9" t="s">
         <v>325</v>
       </c>
@@ -8973,7 +8980,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="158" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="9" t="s">
         <v>325</v>
       </c>
@@ -9017,7 +9024,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="159" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="9" t="s">
         <v>325</v>
       </c>
@@ -9061,7 +9068,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="160" spans="1:26" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:26" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="9" t="s">
         <v>325</v>
       </c>
@@ -9105,7 +9112,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="9" t="s">
         <v>325</v>
       </c>
@@ -9149,7 +9156,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="9" t="s">
         <v>325</v>
       </c>
@@ -9193,7 +9200,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="9" t="s">
         <v>325</v>
       </c>
@@ -9237,7 +9244,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="9" t="s">
         <v>325</v>
       </c>
@@ -9281,7 +9288,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="9" t="s">
         <v>325</v>
       </c>
@@ -9369,7 +9376,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="9" t="s">
         <v>325</v>
       </c>
@@ -9413,7 +9420,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="9" t="s">
         <v>325</v>
       </c>
@@ -9457,7 +9464,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="9" t="s">
         <v>325</v>
       </c>
@@ -9501,7 +9508,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="9" t="s">
         <v>325</v>
       </c>
@@ -9547,7 +9554,7 @@
       <c r="S170" s="11"/>
       <c r="T170" s="11"/>
     </row>
-    <row r="171" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="9" t="s">
         <v>325</v>
       </c>
@@ -9591,7 +9598,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="9" t="s">
         <v>325</v>
       </c>
@@ -9635,7 +9642,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="9" t="s">
         <v>325</v>
       </c>
@@ -9679,7 +9686,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="9" t="s">
         <v>325</v>
       </c>
@@ -9723,7 +9730,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="9" t="s">
         <v>325</v>
       </c>
@@ -9767,7 +9774,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:20" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="9" t="s">
         <v>325</v>
       </c>
@@ -9811,7 +9818,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="177" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="9" t="s">
         <v>325</v>
       </c>
@@ -9855,7 +9862,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="178" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="9" t="s">
         <v>325</v>
       </c>
@@ -9899,7 +9906,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="179" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="9" t="s">
         <v>325</v>
       </c>
@@ -9943,7 +9950,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="180" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="9" t="s">
         <v>325</v>
       </c>
@@ -9987,7 +9994,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="181" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="9" t="s">
         <v>325</v>
       </c>
@@ -10031,7 +10038,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="9" t="s">
         <v>325</v>
       </c>
@@ -10075,7 +10082,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="9" t="s">
         <v>325</v>
       </c>
@@ -10119,7 +10126,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="9" t="s">
         <v>325</v>
       </c>
@@ -10163,7 +10170,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="9" t="s">
         <v>325</v>
       </c>
@@ -10207,7 +10214,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="9" t="s">
         <v>325</v>
       </c>
@@ -10251,7 +10258,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="187" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="9" t="s">
         <v>325</v>
       </c>
@@ -10295,7 +10302,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="9" t="s">
         <v>325</v>
       </c>
@@ -10339,7 +10346,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="9" t="s">
         <v>325</v>
       </c>
@@ -10383,7 +10390,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="9" t="s">
         <v>325</v>
       </c>
@@ -10471,7 +10478,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="9" t="s">
         <v>325</v>
       </c>
@@ -10515,7 +10522,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="9" t="s">
         <v>325</v>
       </c>
@@ -10559,7 +10566,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="9" t="s">
         <v>325</v>
       </c>
@@ -10603,7 +10610,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="9" t="s">
         <v>325</v>
       </c>
@@ -10647,7 +10654,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="9" t="s">
         <v>325</v>
       </c>
@@ -10691,7 +10698,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="9" t="s">
         <v>325</v>
       </c>
@@ -10735,7 +10742,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="9" t="s">
         <v>325</v>
       </c>
@@ -10779,7 +10786,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="9" t="s">
         <v>325</v>
       </c>
@@ -10823,7 +10830,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="9" t="s">
         <v>325</v>
       </c>
@@ -10868,7 +10875,7 @@
       </c>
       <c r="Y200" s="11"/>
     </row>
-    <row r="201" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="9" t="s">
         <v>325</v>
       </c>
@@ -10913,7 +10920,7 @@
       </c>
       <c r="U201" s="11"/>
     </row>
-    <row r="202" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="9" t="s">
         <v>325</v>
       </c>
@@ -10957,7 +10964,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="9" t="s">
         <v>325</v>
       </c>
@@ -11001,7 +11008,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="9" t="s">
         <v>325</v>
       </c>
@@ -11045,7 +11052,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="9" t="s">
         <v>325</v>
       </c>
@@ -11089,7 +11096,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="9" t="s">
         <v>325</v>
       </c>
@@ -11133,7 +11140,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="9" t="s">
         <v>325</v>
       </c>
@@ -11177,7 +11184,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:25" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="9" t="s">
         <v>325</v>
       </c>
@@ -11221,7 +11228,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="9" t="s">
         <v>325</v>
       </c>
@@ -11265,7 +11272,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="9" t="s">
         <v>325</v>
       </c>
@@ -11309,7 +11316,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="9" t="s">
         <v>325</v>
       </c>
@@ -11353,7 +11360,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="9" t="s">
         <v>325</v>
       </c>
@@ -11397,7 +11404,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="9" t="s">
         <v>325</v>
       </c>
@@ -11441,7 +11448,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="9" t="s">
         <v>325</v>
       </c>
@@ -11485,7 +11492,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="9" t="s">
         <v>325</v>
       </c>
@@ -11529,7 +11536,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="9" t="s">
         <v>325</v>
       </c>
@@ -11573,7 +11580,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="9" t="s">
         <v>325</v>
       </c>
@@ -11617,7 +11624,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="9" t="s">
         <v>325</v>
       </c>
@@ -11661,7 +11668,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="9" t="s">
         <v>325</v>
       </c>
@@ -11705,7 +11712,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="9" t="s">
         <v>325</v>
       </c>
@@ -11749,7 +11756,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="9" t="s">
         <v>325</v>
       </c>
@@ -11793,7 +11800,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="9" t="s">
         <v>325</v>
       </c>
@@ -11837,7 +11844,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="9" t="s">
         <v>325</v>
       </c>
@@ -11881,7 +11888,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="9" t="s">
         <v>325</v>
       </c>
@@ -11925,7 +11932,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="225" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="9" t="s">
         <v>325</v>
       </c>
@@ -11969,7 +11976,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="226" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="9" t="s">
         <v>325</v>
       </c>
@@ -12013,7 +12020,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="227" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="9" t="s">
         <v>325</v>
       </c>
@@ -12101,7 +12108,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="229" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="9" t="s">
         <v>325</v>
       </c>
@@ -12145,7 +12152,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="230" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="9" t="s">
         <v>325</v>
       </c>
@@ -12189,7 +12196,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="231" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="9" t="s">
         <v>325</v>
       </c>
@@ -12233,7 +12240,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="232" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="9" t="s">
         <v>325</v>
       </c>
@@ -12277,7 +12284,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="233" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="9" t="s">
         <v>325</v>
       </c>
@@ -12321,7 +12328,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="234" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="9" t="s">
         <v>325</v>
       </c>
@@ -12365,7 +12372,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="235" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="9" t="s">
         <v>325</v>
       </c>
@@ -12409,7 +12416,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="236" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="9" t="s">
         <v>325</v>
       </c>
@@ -12453,7 +12460,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="237" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="9" t="s">
         <v>325</v>
       </c>
@@ -12497,7 +12504,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="238" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="9" t="s">
         <v>325</v>
       </c>
@@ -12541,7 +12548,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="239" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="9" t="s">
         <v>325</v>
       </c>
@@ -12585,7 +12592,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="240" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="9" t="s">
         <v>325</v>
       </c>
@@ -12629,7 +12636,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="9" t="s">
         <v>325</v>
       </c>
@@ -12673,7 +12680,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="9" t="s">
         <v>325</v>
       </c>
@@ -12717,7 +12724,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="9" t="s">
         <v>325</v>
       </c>
@@ -12761,7 +12768,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="9" t="s">
         <v>325</v>
       </c>
@@ -12805,7 +12812,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="245" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="9" t="s">
         <v>325</v>
       </c>
@@ -12849,7 +12856,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="9" t="s">
         <v>325</v>
       </c>
@@ -12893,7 +12900,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="9" t="s">
         <v>325</v>
       </c>
@@ -12937,7 +12944,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="9" t="s">
         <v>325</v>
       </c>
@@ -12981,7 +12988,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="9" t="s">
         <v>325</v>
       </c>
@@ -13025,7 +13032,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="9" t="s">
         <v>325</v>
       </c>
@@ -13069,7 +13076,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="9" t="s">
         <v>325</v>
       </c>
@@ -13113,7 +13120,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="9" t="s">
         <v>325</v>
       </c>
@@ -13157,7 +13164,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="9" t="s">
         <v>325</v>
       </c>
@@ -13245,7 +13252,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="9" t="s">
         <v>325</v>
       </c>
@@ -13289,7 +13296,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="256" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="9" t="s">
         <v>325</v>
       </c>
@@ -13333,7 +13340,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="9" t="s">
         <v>325</v>
       </c>
@@ -13377,7 +13384,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="9" t="s">
         <v>325</v>
       </c>
@@ -13415,7 +13422,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="259" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="9" t="s">
         <v>325</v>
       </c>
@@ -13459,7 +13466,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="260" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="9" t="s">
         <v>325</v>
       </c>
@@ -13503,7 +13510,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="261" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="9" t="s">
         <v>325</v>
       </c>
@@ -13547,7 +13554,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="9" t="s">
         <v>325</v>
       </c>
@@ -13585,7 +13592,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:15" ht="13" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="9" t="s">
         <v>325</v>
       </c>
@@ -15338,6 +15345,13 @@
       <c r="N563" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z263" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="2-16-0400СТП-00-0500"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15624,7 +15638,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" style="9" customWidth="1"/>
@@ -15904,6 +15918,15 @@
       <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>463</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -15918,13 +15941,13 @@
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -15940,13 +15963,13 @@
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -15962,10 +15985,10 @@
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>463</v>
@@ -15984,13 +16007,13 @@
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -16006,13 +16029,13 @@
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -16028,13 +16051,13 @@
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -16050,13 +16073,13 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -16072,13 +16095,13 @@
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -16094,13 +16117,13 @@
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
-        <v>478</v>
+        <v>35</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -16116,13 +16139,13 @@
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
-        <v>35</v>
+        <v>481</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -16141,10 +16164,10 @@
         <v>481</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -16162,11 +16185,8 @@
       <c r="A25" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>484</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -16182,10 +16202,13 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
-        <v>481</v>
+        <v>487</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>488</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -16201,7 +16224,7 @@
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>488</v>
@@ -16223,13 +16246,13 @@
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
-        <v>490</v>
+        <v>40</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -16245,13 +16268,13 @@
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
-        <v>40</v>
+        <v>491</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -16267,13 +16290,13 @@
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -16292,10 +16315,10 @@
         <v>492</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -16311,13 +16334,13 @@
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -16333,13 +16356,13 @@
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
-        <v>497</v>
+        <v>59</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -16353,15 +16376,15 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>59</v>
+        <v>502</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>501</v>
+        <v>493</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>494</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -16377,13 +16400,13 @@
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
-        <v>502</v>
+        <v>198</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -16399,13 +16422,13 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -16421,13 +16444,13 @@
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -16443,13 +16466,13 @@
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -16465,13 +16488,13 @@
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
-        <v>506</v>
+        <v>342</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>444</v>
+        <v>507</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>419</v>
+        <v>508</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -16487,13 +16510,13 @@
     </row>
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
-        <v>342</v>
+        <v>509</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -16508,15 +16531,7 @@
       <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>511</v>
-      </c>
+      <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -16587,7 +16602,6 @@
     </row>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="J46" s="5"/>
@@ -16601,8 +16615,10 @@
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
+      <c r="I47"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -16617,7 +16633,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
-      <c r="I48"/>
+      <c r="G48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -16642,7 +16658,7 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
     </row>
-    <row r="50" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:17" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -30862,23 +30878,8 @@
       <c r="P997" s="5"/>
       <c r="Q997" s="5"/>
     </row>
-    <row r="998" spans="3:17" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C998" s="5"/>
-      <c r="D998" s="5"/>
-      <c r="E998" s="5"/>
-      <c r="F998" s="5"/>
-      <c r="G998" s="5"/>
-      <c r="J998" s="5"/>
-      <c r="K998" s="5"/>
-      <c r="L998" s="5"/>
-      <c r="M998" s="5"/>
-      <c r="N998" s="5"/>
-      <c r="O998" s="5"/>
-      <c r="P998" s="5"/>
-      <c r="Q998" s="5"/>
-    </row>
-    <row r="1000" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I1000"/>
+    <row r="999" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I999"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0424FDAC-F1C9-A844-A527-A499826C7C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFAC63B3-B6A0-204E-87EE-991F1A70F475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="513">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -1569,16 +1569,19 @@
     <t>4*qty</t>
   </si>
   <si>
-    <t>2∗(width+height)/1000∗qty∗(1+n_impost)</t>
-  </si>
-  <si>
-    <t>4*(sash_w+sash_h)/1000*n_sash*qty</t>
-  </si>
-  <si>
     <t>2∗n_sash_passive∗qty</t>
   </si>
   <si>
     <t>2∗(width+height)/1000∗qty∗(1+n_impost+n_sash)</t>
+  </si>
+  <si>
+    <t>2 * (width + height) / 1000 * qty * (1 + n_impost)</t>
+  </si>
+  <si>
+    <t>4 * (sash_w + sash_h) / 1000 * n_sash * qty</t>
+  </si>
+  <si>
+    <t>2 * (width + height) / 1000 * qty * (1 + n_impost + n_sash)</t>
   </si>
 </sst>
 </file>
@@ -2328,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1">
@@ -4396,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="27" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="13" customHeight="1">
@@ -9340,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="27" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="166" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -9648,7 +9651,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="27" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="173" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -9692,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="27" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="174" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -9736,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="O174" s="27" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="175" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -10529,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="O192" s="27" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -10661,7 +10664,7 @@
         <v>0</v>
       </c>
       <c r="O195" s="27" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="196" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFAC63B3-B6A0-204E-87EE-991F1A70F475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A270D3DA-986E-F54D-9E06-37F84D1AB8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="514">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -1582,6 +1582,9 @@
   </si>
   <si>
     <t>2 * (width + height) / 1000 * qty * (1 + n_impost + n_sash)</t>
+  </si>
+  <si>
+    <t>(width+100)/1000/6*qty</t>
   </si>
 </sst>
 </file>
@@ -2034,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z502"/>
@@ -2114,7 +2117,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1">
+    <row r="2" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1">
+    <row r="3" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1">
+    <row r="4" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
@@ -2246,7 +2249,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1">
+    <row r="5" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" customHeight="1">
+    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" hidden="1" customHeight="1">
       <c r="A6" s="27" t="s">
         <v>15</v>
       </c>
@@ -2334,7 +2337,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1">
+    <row r="7" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1">
+    <row r="8" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1">
+    <row r="9" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1">
+    <row r="10" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1">
+    <row r="11" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -2554,7 +2557,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1">
+    <row r="12" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1">
+    <row r="13" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1">
+    <row r="14" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1">
+    <row r="15" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -2730,7 +2733,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1">
+    <row r="16" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
@@ -2774,7 +2777,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+    <row r="17" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
@@ -2818,7 +2821,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+    <row r="18" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>15</v>
       </c>
@@ -2862,7 +2865,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+    <row r="19" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>63</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1">
+    <row r="20" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>63</v>
       </c>
@@ -2950,7 +2953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1">
+    <row r="21" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>63</v>
       </c>
@@ -2994,7 +2997,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+    <row r="22" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>63</v>
       </c>
@@ -3038,7 +3041,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+    <row r="23" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>63</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1">
+    <row r="24" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>15</v>
       </c>
@@ -3126,7 +3129,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1">
+    <row r="25" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>15</v>
       </c>
@@ -3170,7 +3173,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1">
+    <row r="26" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>15</v>
       </c>
@@ -3214,7 +3217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1">
+    <row r="27" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3258,7 +3261,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1">
+    <row r="28" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>15</v>
       </c>
@@ -3302,7 +3305,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1">
+    <row r="29" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1">
+    <row r="30" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>15</v>
       </c>
@@ -3390,7 +3393,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1">
+    <row r="31" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>15</v>
       </c>
@@ -3434,7 +3437,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1">
+    <row r="32" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -3478,7 +3481,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1">
+    <row r="33" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>15</v>
       </c>
@@ -3522,7 +3525,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1">
+    <row r="34" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>15</v>
       </c>
@@ -3566,7 +3569,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1">
+    <row r="35" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>15</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1">
+    <row r="37" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
@@ -3698,7 +3701,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1">
+    <row r="38" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>63</v>
       </c>
@@ -3742,7 +3745,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1">
+    <row r="39" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3786,7 +3789,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1">
+    <row r="40" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A40" s="9" t="s">
         <v>63</v>
       </c>
@@ -3830,7 +3833,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1">
+    <row r="41" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A41" s="9" t="s">
         <v>63</v>
       </c>
@@ -3874,7 +3877,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1">
+    <row r="42" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>63</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1">
+    <row r="43" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A43" s="9" t="s">
         <v>63</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1">
+    <row r="44" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A44" s="9" t="s">
         <v>63</v>
       </c>
@@ -4006,7 +4009,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1">
+    <row r="45" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A45" s="9" t="s">
         <v>63</v>
       </c>
@@ -4050,7 +4053,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1">
+    <row r="46" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A46" s="9" t="s">
         <v>63</v>
       </c>
@@ -4094,7 +4097,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1">
+    <row r="47" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>63</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1">
+    <row r="48" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A48" s="9" t="s">
         <v>63</v>
       </c>
@@ -4182,7 +4185,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1">
+    <row r="49" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>63</v>
       </c>
@@ -4226,7 +4229,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" customHeight="1">
+    <row r="50" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A50" s="9" t="s">
         <v>63</v>
       </c>
@@ -4270,7 +4273,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13" customHeight="1">
+    <row r="51" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A51" s="9" t="s">
         <v>63</v>
       </c>
@@ -4314,7 +4317,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13" customHeight="1">
+    <row r="52" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A52" s="9" t="s">
         <v>63</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A53" s="27" t="s">
         <v>63</v>
       </c>
@@ -4402,7 +4405,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="13" customHeight="1">
+    <row r="54" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>63</v>
       </c>
@@ -4446,7 +4449,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13" customHeight="1">
+    <row r="55" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>63</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13" customHeight="1">
+    <row r="56" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A56" s="9" t="s">
         <v>63</v>
       </c>
@@ -4534,7 +4537,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13" customHeight="1">
+    <row r="57" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A57" s="9" t="s">
         <v>63</v>
       </c>
@@ -4578,7 +4581,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13" customHeight="1">
+    <row r="58" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>63</v>
       </c>
@@ -4622,7 +4625,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13" customHeight="1">
+    <row r="59" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>63</v>
       </c>
@@ -4666,7 +4669,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13" customHeight="1">
+    <row r="60" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>63</v>
       </c>
@@ -4710,7 +4713,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13" customHeight="1">
+    <row r="61" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A61" s="9" t="s">
         <v>63</v>
       </c>
@@ -4754,7 +4757,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13" customHeight="1">
+    <row r="62" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>63</v>
       </c>
@@ -4798,7 +4801,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13" customHeight="1">
+    <row r="63" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -4842,7 +4845,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13" customHeight="1">
+    <row r="64" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A64" s="9" t="s">
         <v>63</v>
       </c>
@@ -4886,7 +4889,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13" customHeight="1">
+    <row r="65" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A65" s="9" t="s">
         <v>63</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13" customHeight="1">
+    <row r="66" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A66" s="9" t="s">
         <v>63</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13" customHeight="1">
+    <row r="67" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
@@ -5018,7 +5021,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13" customHeight="1">
+    <row r="68" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A68" s="9" t="s">
         <v>63</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="13" customHeight="1">
+    <row r="69" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A69" s="9" t="s">
         <v>63</v>
       </c>
@@ -5106,7 +5109,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13" customHeight="1">
+    <row r="70" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>63</v>
       </c>
@@ -5150,7 +5153,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13" customHeight="1">
+    <row r="71" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>63</v>
       </c>
@@ -5194,7 +5197,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13" customHeight="1">
+    <row r="72" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>63</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13" customHeight="1">
+    <row r="73" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A73" s="9" t="s">
         <v>63</v>
       </c>
@@ -5282,7 +5285,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13" customHeight="1">
+    <row r="74" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A74" s="9" t="s">
         <v>63</v>
       </c>
@@ -5326,7 +5329,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13" customHeight="1">
+    <row r="75" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A75" s="9" t="s">
         <v>63</v>
       </c>
@@ -5370,7 +5373,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="13" customHeight="1">
+    <row r="76" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A76" s="9" t="s">
         <v>63</v>
       </c>
@@ -5414,7 +5417,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="13" customHeight="1">
+    <row r="77" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
@@ -5458,7 +5461,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="13" customHeight="1">
+    <row r="78" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A78" s="9" t="s">
         <v>63</v>
       </c>
@@ -5502,7 +5505,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="13" customHeight="1">
+    <row r="79" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A79" s="9" t="s">
         <v>63</v>
       </c>
@@ -5546,7 +5549,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="13" customHeight="1">
+    <row r="80" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A80" s="9" t="s">
         <v>63</v>
       </c>
@@ -5590,7 +5593,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="13" customHeight="1">
+    <row r="81" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A81" s="9" t="s">
         <v>63</v>
       </c>
@@ -5634,7 +5637,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="13" customHeight="1">
+    <row r="82" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A82" s="9" t="s">
         <v>63</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="13" customHeight="1">
+    <row r="83" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>63</v>
       </c>
@@ -5722,7 +5725,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="13" customHeight="1">
+    <row r="84" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A84" s="9" t="s">
         <v>63</v>
       </c>
@@ -5766,7 +5769,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="13" customHeight="1">
+    <row r="85" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A85" s="9" t="s">
         <v>63</v>
       </c>
@@ -5810,7 +5813,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="13" customHeight="1">
+    <row r="86" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A86" s="9" t="s">
         <v>63</v>
       </c>
@@ -5854,7 +5857,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="13" customHeight="1">
+    <row r="87" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A87" s="9" t="s">
         <v>63</v>
       </c>
@@ -5898,7 +5901,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="13" customHeight="1">
+    <row r="88" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A88" s="9" t="s">
         <v>63</v>
       </c>
@@ -5942,7 +5945,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="13" customHeight="1">
+    <row r="89" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A89" s="9" t="s">
         <v>63</v>
       </c>
@@ -5986,7 +5989,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="13" customHeight="1">
+    <row r="90" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A90" s="9" t="s">
         <v>63</v>
       </c>
@@ -6030,7 +6033,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="13" customHeight="1">
+    <row r="91" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A91" s="9" t="s">
         <v>63</v>
       </c>
@@ -6074,7 +6077,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="13" customHeight="1">
+    <row r="92" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>63</v>
       </c>
@@ -6118,7 +6121,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="13" customHeight="1">
+    <row r="93" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A93" s="9" t="s">
         <v>63</v>
       </c>
@@ -6162,7 +6165,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="13" customHeight="1">
+    <row r="94" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A94" s="9" t="s">
         <v>63</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="13" customHeight="1">
+    <row r="95" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>63</v>
       </c>
@@ -6250,7 +6253,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="13" customHeight="1">
+    <row r="96" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>63</v>
       </c>
@@ -6294,7 +6297,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="13" customHeight="1">
+    <row r="97" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A97" s="9" t="s">
         <v>63</v>
       </c>
@@ -6338,7 +6341,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="13" customHeight="1">
+    <row r="98" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A98" s="9" t="s">
         <v>63</v>
       </c>
@@ -6382,7 +6385,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="13" customHeight="1">
+    <row r="99" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A99" s="9" t="s">
         <v>63</v>
       </c>
@@ -6426,7 +6429,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="13" customHeight="1">
+    <row r="100" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A100" s="9" t="s">
         <v>63</v>
       </c>
@@ -6470,7 +6473,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="13" customHeight="1">
+    <row r="101" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A101" s="9" t="s">
         <v>63</v>
       </c>
@@ -6514,7 +6517,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="13" customHeight="1">
+    <row r="102" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A102" s="9" t="s">
         <v>63</v>
       </c>
@@ -6558,7 +6561,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="13" customHeight="1">
+    <row r="103" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A103" s="9" t="s">
         <v>63</v>
       </c>
@@ -6602,7 +6605,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="13" customHeight="1">
+    <row r="104" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A104" s="9" t="s">
         <v>63</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="13" customHeight="1">
+    <row r="105" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A105" s="9" t="s">
         <v>63</v>
       </c>
@@ -6690,7 +6693,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="13" customHeight="1">
+    <row r="106" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A106" s="9" t="s">
         <v>63</v>
       </c>
@@ -6734,7 +6737,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="13" customHeight="1">
+    <row r="107" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A107" s="9" t="s">
         <v>63</v>
       </c>
@@ -6778,7 +6781,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="13" customHeight="1">
+    <row r="108" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A108" s="9" t="s">
         <v>63</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="13" customHeight="1">
+    <row r="109" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A109" s="9" t="s">
         <v>63</v>
       </c>
@@ -6866,7 +6869,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="13" customHeight="1">
+    <row r="110" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>63</v>
       </c>
@@ -6910,7 +6913,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="13" customHeight="1">
+    <row r="111" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A111" s="9" t="s">
         <v>63</v>
       </c>
@@ -6954,7 +6957,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="13" customHeight="1">
+    <row r="112" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A112" s="9" t="s">
         <v>63</v>
       </c>
@@ -6998,7 +7001,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="13" customHeight="1">
+    <row r="113" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A113" s="9" t="s">
         <v>63</v>
       </c>
@@ -7042,7 +7045,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="13" customHeight="1">
+    <row r="114" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>63</v>
       </c>
@@ -7086,7 +7089,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="13" customHeight="1">
+    <row r="115" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A115" s="9" t="s">
         <v>63</v>
       </c>
@@ -7130,7 +7133,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="13" customHeight="1">
+    <row r="116" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A116" s="9" t="s">
         <v>63</v>
       </c>
@@ -7174,7 +7177,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="13" customHeight="1">
+    <row r="117" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A117" s="9" t="s">
         <v>63</v>
       </c>
@@ -7218,7 +7221,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="13" customHeight="1">
+    <row r="118" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A118" s="9" t="s">
         <v>63</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="13" customHeight="1">
+    <row r="119" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A119" s="9" t="s">
         <v>63</v>
       </c>
@@ -7306,7 +7309,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="13" customHeight="1">
+    <row r="120" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A120" s="9" t="s">
         <v>63</v>
       </c>
@@ -7350,7 +7353,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="13" customHeight="1">
+    <row r="121" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A121" s="9" t="s">
         <v>63</v>
       </c>
@@ -7394,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="13" customHeight="1">
+    <row r="122" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A122" s="9" t="s">
         <v>63</v>
       </c>
@@ -7438,7 +7441,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="13" customHeight="1">
+    <row r="123" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A123" s="9" t="s">
         <v>63</v>
       </c>
@@ -7482,7 +7485,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="13" customHeight="1">
+    <row r="124" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A124" s="9" t="s">
         <v>63</v>
       </c>
@@ -7526,7 +7529,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="13" customHeight="1">
+    <row r="125" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A125" s="9" t="s">
         <v>15</v>
       </c>
@@ -7570,7 +7573,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="13" customHeight="1">
+    <row r="126" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A126" s="9" t="s">
         <v>15</v>
       </c>
@@ -7614,7 +7617,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="13" customHeight="1">
+    <row r="127" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A127" s="9" t="s">
         <v>15</v>
       </c>
@@ -7658,7 +7661,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="13" customHeight="1">
+    <row r="128" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A128" s="9" t="s">
         <v>15</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="13" customHeight="1">
+    <row r="129" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>324</v>
       </c>
@@ -7746,7 +7749,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A130" s="27" t="s">
         <v>324</v>
       </c>
@@ -7790,7 +7793,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:26" ht="13" customHeight="1">
+    <row r="131" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A131" s="9" t="s">
         <v>324</v>
       </c>
@@ -7834,7 +7837,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A132" s="27" t="s">
         <v>324</v>
       </c>
@@ -7878,7 +7881,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="13" customHeight="1">
+    <row r="133" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A133" s="9" t="s">
         <v>324</v>
       </c>
@@ -7922,7 +7925,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="13" customHeight="1">
+    <row r="134" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A134" s="9" t="s">
         <v>324</v>
       </c>
@@ -7971,7 +7974,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" customHeight="1">
+    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A135" s="9" t="s">
         <v>324</v>
       </c>
@@ -8026,7 +8029,7 @@
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
     </row>
-    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A136" s="27" t="s">
         <v>324</v>
       </c>
@@ -8070,7 +8073,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="13" customHeight="1">
+    <row r="137" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A137" s="9" t="s">
         <v>324</v>
       </c>
@@ -8114,7 +8117,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="13" customHeight="1">
+    <row r="138" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A138" s="9" t="s">
         <v>324</v>
       </c>
@@ -8158,7 +8161,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="13" customHeight="1">
+    <row r="139" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A139" s="9" t="s">
         <v>324</v>
       </c>
@@ -8202,7 +8205,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="13" customHeight="1">
+    <row r="140" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A140" s="9" t="s">
         <v>324</v>
       </c>
@@ -8246,7 +8249,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="13" customHeight="1">
+    <row r="141" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A141" s="9" t="s">
         <v>324</v>
       </c>
@@ -8290,7 +8293,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="13" customHeight="1">
+    <row r="142" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A142" s="9" t="s">
         <v>324</v>
       </c>
@@ -8334,7 +8337,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="13" customHeight="1">
+    <row r="143" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A143" s="9" t="s">
         <v>324</v>
       </c>
@@ -8378,7 +8381,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="144" spans="1:26" ht="13" customHeight="1">
+    <row r="144" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A144" s="9" t="s">
         <v>324</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="13" customHeight="1">
+    <row r="145" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A145" s="9" t="s">
         <v>324</v>
       </c>
@@ -8466,7 +8469,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="13" customHeight="1">
+    <row r="146" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A146" s="9" t="s">
         <v>324</v>
       </c>
@@ -8510,7 +8513,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="13" customHeight="1">
+    <row r="147" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A147" s="9" t="s">
         <v>324</v>
       </c>
@@ -8554,7 +8557,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="13" customHeight="1">
+    <row r="148" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A148" s="9" t="s">
         <v>324</v>
       </c>
@@ -8598,7 +8601,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="13" customHeight="1">
+    <row r="149" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A149" s="9" t="s">
         <v>324</v>
       </c>
@@ -8642,7 +8645,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="13" customHeight="1">
+    <row r="150" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A150" s="9" t="s">
         <v>324</v>
       </c>
@@ -8686,7 +8689,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="13" customHeight="1">
+    <row r="151" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A151" s="9" t="s">
         <v>324</v>
       </c>
@@ -8730,7 +8733,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A152" s="27" t="s">
         <v>324</v>
       </c>
@@ -8774,7 +8777,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="13" customHeight="1">
+    <row r="153" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A153" s="9" t="s">
         <v>324</v>
       </c>
@@ -8818,7 +8821,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="13" customHeight="1">
+    <row r="154" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A154" s="9" t="s">
         <v>324</v>
       </c>
@@ -8862,7 +8865,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A155" s="27" t="s">
         <v>324</v>
       </c>
@@ -8906,7 +8909,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="13" customHeight="1">
+    <row r="156" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A156" s="9" t="s">
         <v>324</v>
       </c>
@@ -8950,7 +8953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A157" s="27" t="s">
         <v>324</v>
       </c>
@@ -8994,7 +8997,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A158" s="27" t="s">
         <v>324</v>
       </c>
@@ -9038,7 +9041,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A159" s="27" t="s">
         <v>324</v>
       </c>
@@ -9123,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="O160" s="27" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A161" s="27" t="s">
         <v>324</v>
       </c>
@@ -9170,7 +9173,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A162" s="27" t="s">
         <v>324</v>
       </c>
@@ -9214,7 +9217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A163" s="27" t="s">
         <v>324</v>
       </c>
@@ -9258,7 +9261,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A164" s="27" t="s">
         <v>324</v>
       </c>
@@ -9302,7 +9305,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A165" s="27" t="s">
         <v>324</v>
       </c>
@@ -9346,7 +9349,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A166" s="27" t="s">
         <v>324</v>
       </c>
@@ -9390,7 +9393,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A167" s="27" t="s">
         <v>324</v>
       </c>
@@ -9434,7 +9437,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A168" s="27" t="s">
         <v>324</v>
       </c>
@@ -9478,7 +9481,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A169" s="27" t="s">
         <v>324</v>
       </c>
@@ -9522,7 +9525,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A170" s="27" t="s">
         <v>324</v>
       </c>
@@ -9566,7 +9569,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A171" s="27" t="s">
         <v>324</v>
       </c>
@@ -9610,7 +9613,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A172" s="27" t="s">
         <v>324</v>
       </c>
@@ -9654,7 +9657,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A173" s="27" t="s">
         <v>324</v>
       </c>
@@ -9698,7 +9701,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A174" s="27" t="s">
         <v>324</v>
       </c>
@@ -9742,7 +9745,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A175" s="27" t="s">
         <v>324</v>
       </c>
@@ -9786,7 +9789,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A176" s="27" t="s">
         <v>324</v>
       </c>
@@ -9830,7 +9833,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A177" s="27" t="s">
         <v>324</v>
       </c>
@@ -9874,7 +9877,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A178" s="27" t="s">
         <v>324</v>
       </c>
@@ -9918,7 +9921,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A179" s="27" t="s">
         <v>324</v>
       </c>
@@ -9962,7 +9965,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A180" s="27" t="s">
         <v>324</v>
       </c>
@@ -10006,7 +10009,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A181" s="27" t="s">
         <v>324</v>
       </c>
@@ -10050,7 +10053,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="182" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="182" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A182" s="27" t="s">
         <v>324</v>
       </c>
@@ -10094,7 +10097,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="13" customHeight="1">
+    <row r="183" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A183" s="9" t="s">
         <v>324</v>
       </c>
@@ -10138,7 +10141,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="13" customHeight="1">
+    <row r="184" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A184" s="9" t="s">
         <v>324</v>
       </c>
@@ -10182,7 +10185,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="13" customHeight="1">
+    <row r="185" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A185" s="9" t="s">
         <v>324</v>
       </c>
@@ -10226,7 +10229,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="13" customHeight="1">
+    <row r="186" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A186" s="9" t="s">
         <v>324</v>
       </c>
@@ -10271,7 +10274,7 @@
       </c>
       <c r="U186" s="11"/>
     </row>
-    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A187" s="27" t="s">
         <v>324</v>
       </c>
@@ -10315,7 +10318,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A188" s="27" t="s">
         <v>324</v>
       </c>
@@ -10359,7 +10362,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A189" s="27" t="s">
         <v>324</v>
       </c>
@@ -10403,7 +10406,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A190" s="27" t="s">
         <v>324</v>
       </c>
@@ -10447,7 +10450,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A191" s="27" t="s">
         <v>324</v>
       </c>
@@ -10491,7 +10494,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A192" s="27" t="s">
         <v>324</v>
       </c>
@@ -10535,7 +10538,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A193" s="27" t="s">
         <v>324</v>
       </c>
@@ -10579,7 +10582,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="194" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="194" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A194" s="27" t="s">
         <v>324</v>
       </c>
@@ -10623,7 +10626,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A195" s="27" t="s">
         <v>324</v>
       </c>
@@ -10667,7 +10670,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A196" s="27" t="s">
         <v>324</v>
       </c>
@@ -10711,7 +10714,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="197" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="197" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A197" s="27" t="s">
         <v>324</v>
       </c>
@@ -12554,6 +12557,13 @@
       <c r="N502" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z197" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="45 Профиль порога компланарной двери NEW"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A270D3DA-986E-F54D-9E06-37F84D1AB8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E60010-A29F-5141-BC66-364E2C9DBCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="515">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -1563,9 +1563,6 @@
     <t>4*(1+n_sash)*qty</t>
   </si>
   <si>
-    <t>n_imp_hor∗1∗qty</t>
-  </si>
-  <si>
     <t>4*qty</t>
   </si>
   <si>
@@ -1585,6 +1582,12 @@
   </si>
   <si>
     <t>(width+100)/1000/6*qty</t>
+  </si>
+  <si>
+    <t>(2∗(width+height)+4∗(sash_w+sash_h)∗n_sash)/1000∗qty</t>
+  </si>
+  <si>
+    <t>1*n_sash_active*is_door*qty</t>
   </si>
 </sst>
 </file>
@@ -2334,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="15.75" hidden="1" customHeight="1">
@@ -3613,7 +3616,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1">
+    <row r="36" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>63</v>
       </c>
@@ -4402,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="27" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="13" hidden="1" customHeight="1">
@@ -6825,7 +6828,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="109" spans="1:15" ht="13" customHeight="1">
       <c r="A109" s="9" t="s">
         <v>63</v>
       </c>
@@ -6866,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="13" hidden="1" customHeight="1">
@@ -9085,7 +9088,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A160" s="27" t="s">
         <v>324</v>
       </c>
@@ -9126,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="27" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="161" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9346,7 +9349,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="27" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="166" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9393,7 +9396,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A167" s="27" t="s">
         <v>324</v>
       </c>
@@ -9437,7 +9440,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A168" s="27" t="s">
         <v>324</v>
       </c>
@@ -9477,8 +9480,8 @@
       <c r="N168" s="27">
         <v>0</v>
       </c>
-      <c r="O168" s="27" t="s">
-        <v>506</v>
+      <c r="O168" s="9" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="169" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9522,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="27" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9654,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="173" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9698,7 +9701,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="27" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="174" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -9742,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="O174" s="27" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="175" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -10535,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="O192" s="27" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -10667,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="O195" s="27" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="196" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
@@ -12560,7 +12563,8 @@
   <autoFilter ref="A1:Z197" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="45 Профиль порога компланарной двери NEW"/>
+        <filter val="Соединитель импоста 35 мм (2160.2163)"/>
+        <filter val="Сухарь 32,5 мм (2115) новый дизайн"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E60010-A29F-5141-BC66-364E2C9DBCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25652965-D4F6-8746-A09E-16381BB306A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Итоговый расчет с монтажом" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СПРАВОЧНИК -1'!$A$1:$Z$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'СПРАВОЧНИК -3'!$A$1:$D$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="514">
   <si>
     <t>Тип изделия:</t>
   </si>
@@ -1557,9 +1557,6 @@
     <t>(2∗n_impost+4)∗qty</t>
   </si>
   <si>
-    <t>(4+2*n_impost)*qty</t>
-  </si>
-  <si>
     <t>4*(1+n_sash)*qty</t>
   </si>
   <si>
@@ -1572,15 +1569,6 @@
     <t>2∗(width+height)/1000∗qty∗(1+n_impost+n_sash)</t>
   </si>
   <si>
-    <t>2 * (width + height) / 1000 * qty * (1 + n_impost)</t>
-  </si>
-  <si>
-    <t>4 * (sash_w + sash_h) / 1000 * n_sash * qty</t>
-  </si>
-  <si>
-    <t>2 * (width + height) / 1000 * qty * (1 + n_impost + n_sash)</t>
-  </si>
-  <si>
     <t>(width+100)/1000/6*qty</t>
   </si>
   <si>
@@ -1588,6 +1576,15 @@
   </si>
   <si>
     <t>1*n_sash_active*is_door*qty</t>
+  </si>
+  <si>
+    <t>2∗n_sash_active∗is_door∗qty</t>
+  </si>
+  <si>
+    <t>(4∗n_impost+4)∗qty</t>
+  </si>
+  <si>
+    <t>3∗(sash_w+sash_h)/1000∗n_sash∗qty</t>
   </si>
 </sst>
 </file>
@@ -2040,10 +2037,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z502"/>
+  <dimension ref="A1:Z501"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="9" customWidth="1"/>
@@ -2120,7 +2117,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:24" ht="15.75" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2164,7 +2161,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="3" spans="1:24" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
@@ -2208,7 +2205,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="4" spans="1:24" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
@@ -2252,7 +2249,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="5" spans="1:24" ht="15.75" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
@@ -2296,7 +2293,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" hidden="1" customHeight="1">
+    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="27" t="s">
         <v>15</v>
       </c>
@@ -2337,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -2384,7 +2381,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:24" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
@@ -2428,7 +2425,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="9" spans="1:24" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -2472,7 +2469,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="10" spans="1:24" ht="15.75" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -2516,7 +2513,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="11" spans="1:24" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -2560,7 +2557,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="12" spans="1:24" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2604,7 +2601,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="13" spans="1:24" ht="15.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
@@ -2648,7 +2645,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="14" spans="1:24" ht="15.75" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
@@ -2692,7 +2689,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="15" spans="1:24" ht="15.75" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -2736,7 +2733,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" hidden="1" customHeight="1">
+    <row r="16" spans="1:24" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
@@ -2780,7 +2777,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
@@ -2824,7 +2821,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>15</v>
       </c>
@@ -2868,7 +2865,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="19" spans="1:15" ht="15.75" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>63</v>
       </c>
@@ -2912,7 +2909,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="20" spans="1:15" ht="15.75" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>63</v>
       </c>
@@ -2956,7 +2953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>63</v>
       </c>
@@ -3000,7 +2997,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>63</v>
       </c>
@@ -3044,7 +3041,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>63</v>
       </c>
@@ -3088,7 +3085,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>15</v>
       </c>
@@ -3132,7 +3129,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>15</v>
       </c>
@@ -3176,7 +3173,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>15</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:15" ht="15.75" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3264,7 +3261,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:15" ht="15.75" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>15</v>
       </c>
@@ -3308,7 +3305,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:15" ht="15.75" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
@@ -3352,7 +3349,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:15" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>15</v>
       </c>
@@ -3396,7 +3393,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:15" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>15</v>
       </c>
@@ -3440,7 +3437,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:15" ht="15.75" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -3484,7 +3481,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:15" ht="15.75" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>15</v>
       </c>
@@ -3528,7 +3525,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:15" ht="15.75" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>15</v>
       </c>
@@ -3572,7 +3569,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="35" spans="1:15" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>15</v>
       </c>
@@ -3616,7 +3613,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:15" ht="15.75" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>63</v>
       </c>
@@ -3660,7 +3657,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:15" ht="15.75" customHeight="1">
       <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
@@ -3704,7 +3701,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:15" ht="15.75" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>63</v>
       </c>
@@ -3748,7 +3745,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:15" ht="15.75" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3792,7 +3789,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:15" ht="15.75" customHeight="1">
       <c r="A40" s="9" t="s">
         <v>63</v>
       </c>
@@ -3836,7 +3833,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:15" ht="15.75" customHeight="1">
       <c r="A41" s="9" t="s">
         <v>63</v>
       </c>
@@ -3880,7 +3877,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:15" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>63</v>
       </c>
@@ -3924,7 +3921,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:15" ht="15.75" customHeight="1">
       <c r="A43" s="9" t="s">
         <v>63</v>
       </c>
@@ -3968,7 +3965,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:15" ht="15.75" customHeight="1">
       <c r="A44" s="9" t="s">
         <v>63</v>
       </c>
@@ -4012,7 +4009,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:15" ht="15.75" customHeight="1">
       <c r="A45" s="9" t="s">
         <v>63</v>
       </c>
@@ -4056,7 +4053,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:15" ht="15.75" customHeight="1">
       <c r="A46" s="9" t="s">
         <v>63</v>
       </c>
@@ -4100,7 +4097,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:15" ht="15.75" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>63</v>
       </c>
@@ -4144,7 +4141,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:15" ht="15.75" customHeight="1">
       <c r="A48" s="9" t="s">
         <v>63</v>
       </c>
@@ -4188,7 +4185,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:15" ht="15.75" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>63</v>
       </c>
@@ -4232,7 +4229,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:15" ht="15.75" customHeight="1">
       <c r="A50" s="9" t="s">
         <v>63</v>
       </c>
@@ -4276,7 +4273,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="51" spans="1:15" ht="13" customHeight="1">
       <c r="A51" s="9" t="s">
         <v>63</v>
       </c>
@@ -4320,7 +4317,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="52" spans="1:15" ht="13" customHeight="1">
       <c r="A52" s="9" t="s">
         <v>63</v>
       </c>
@@ -4364,7 +4361,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A53" s="27" t="s">
         <v>63</v>
       </c>
@@ -4405,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="O53" s="27" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="13" hidden="1" customHeight="1">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="13" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>63</v>
       </c>
@@ -4452,7 +4449,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="55" spans="1:15" ht="13" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>63</v>
       </c>
@@ -4496,7 +4493,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="56" spans="1:15" ht="13" customHeight="1">
       <c r="A56" s="9" t="s">
         <v>63</v>
       </c>
@@ -4540,7 +4537,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="57" spans="1:15" ht="13" customHeight="1">
       <c r="A57" s="9" t="s">
         <v>63</v>
       </c>
@@ -4584,7 +4581,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="58" spans="1:15" ht="13" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>63</v>
       </c>
@@ -4628,7 +4625,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="59" spans="1:15" ht="13" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>63</v>
       </c>
@@ -4672,7 +4669,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="60" spans="1:15" ht="13" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>63</v>
       </c>
@@ -4716,7 +4713,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="61" spans="1:15" ht="13" customHeight="1">
       <c r="A61" s="9" t="s">
         <v>63</v>
       </c>
@@ -4760,7 +4757,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="62" spans="1:15" ht="13" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>63</v>
       </c>
@@ -4804,7 +4801,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="63" spans="1:15" ht="13" customHeight="1">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -4848,7 +4845,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="64" spans="1:15" ht="13" customHeight="1">
       <c r="A64" s="9" t="s">
         <v>63</v>
       </c>
@@ -4892,7 +4889,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="65" spans="1:15" ht="13" customHeight="1">
       <c r="A65" s="9" t="s">
         <v>63</v>
       </c>
@@ -4936,7 +4933,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="66" spans="1:15" ht="13" customHeight="1">
       <c r="A66" s="9" t="s">
         <v>63</v>
       </c>
@@ -4980,7 +4977,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="67" spans="1:15" ht="13" customHeight="1">
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
@@ -5024,7 +5021,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="68" spans="1:15" ht="13" customHeight="1">
       <c r="A68" s="9" t="s">
         <v>63</v>
       </c>
@@ -5068,7 +5065,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="69" spans="1:15" ht="13" customHeight="1">
       <c r="A69" s="9" t="s">
         <v>63</v>
       </c>
@@ -5112,7 +5109,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="70" spans="1:15" ht="13" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>63</v>
       </c>
@@ -5156,7 +5153,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="71" spans="1:15" ht="13" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>63</v>
       </c>
@@ -5200,7 +5197,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="72" spans="1:15" ht="13" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>63</v>
       </c>
@@ -5244,7 +5241,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="73" spans="1:15" ht="13" customHeight="1">
       <c r="A73" s="9" t="s">
         <v>63</v>
       </c>
@@ -5288,7 +5285,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="74" spans="1:15" ht="13" customHeight="1">
       <c r="A74" s="9" t="s">
         <v>63</v>
       </c>
@@ -5332,7 +5329,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="75" spans="1:15" ht="13" customHeight="1">
       <c r="A75" s="9" t="s">
         <v>63</v>
       </c>
@@ -5376,7 +5373,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="76" spans="1:15" ht="13" customHeight="1">
       <c r="A76" s="9" t="s">
         <v>63</v>
       </c>
@@ -5420,7 +5417,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="77" spans="1:15" ht="13" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
@@ -5464,7 +5461,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="78" spans="1:15" ht="13" customHeight="1">
       <c r="A78" s="9" t="s">
         <v>63</v>
       </c>
@@ -5508,7 +5505,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="79" spans="1:15" ht="13" customHeight="1">
       <c r="A79" s="9" t="s">
         <v>63</v>
       </c>
@@ -5552,7 +5549,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="80" spans="1:15" ht="13" customHeight="1">
       <c r="A80" s="9" t="s">
         <v>63</v>
       </c>
@@ -5596,7 +5593,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="81" spans="1:15" ht="13" customHeight="1">
       <c r="A81" s="9" t="s">
         <v>63</v>
       </c>
@@ -5640,7 +5637,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="82" spans="1:15" ht="13" customHeight="1">
       <c r="A82" s="9" t="s">
         <v>63</v>
       </c>
@@ -5684,7 +5681,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="83" spans="1:15" ht="13" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>63</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="84" spans="1:15" ht="13" customHeight="1">
       <c r="A84" s="9" t="s">
         <v>63</v>
       </c>
@@ -5772,7 +5769,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="85" spans="1:15" ht="13" customHeight="1">
       <c r="A85" s="9" t="s">
         <v>63</v>
       </c>
@@ -5816,7 +5813,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="86" spans="1:15" ht="13" customHeight="1">
       <c r="A86" s="9" t="s">
         <v>63</v>
       </c>
@@ -5860,7 +5857,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="87" spans="1:15" ht="13" customHeight="1">
       <c r="A87" s="9" t="s">
         <v>63</v>
       </c>
@@ -5904,7 +5901,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="88" spans="1:15" ht="13" customHeight="1">
       <c r="A88" s="9" t="s">
         <v>63</v>
       </c>
@@ -5948,7 +5945,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="89" spans="1:15" ht="13" customHeight="1">
       <c r="A89" s="9" t="s">
         <v>63</v>
       </c>
@@ -5992,7 +5989,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="90" spans="1:15" ht="13" customHeight="1">
       <c r="A90" s="9" t="s">
         <v>63</v>
       </c>
@@ -6036,7 +6033,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="91" spans="1:15" ht="13" customHeight="1">
       <c r="A91" s="9" t="s">
         <v>63</v>
       </c>
@@ -6080,7 +6077,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="92" spans="1:15" ht="13" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>63</v>
       </c>
@@ -6124,7 +6121,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="93" spans="1:15" ht="13" customHeight="1">
       <c r="A93" s="9" t="s">
         <v>63</v>
       </c>
@@ -6168,7 +6165,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="94" spans="1:15" ht="13" customHeight="1">
       <c r="A94" s="9" t="s">
         <v>63</v>
       </c>
@@ -6212,7 +6209,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="95" spans="1:15" ht="13" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>63</v>
       </c>
@@ -6256,7 +6253,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="96" spans="1:15" ht="13" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>63</v>
       </c>
@@ -6300,7 +6297,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="97" spans="1:15" ht="13" customHeight="1">
       <c r="A97" s="9" t="s">
         <v>63</v>
       </c>
@@ -6344,7 +6341,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="98" spans="1:15" ht="13" customHeight="1">
       <c r="A98" s="9" t="s">
         <v>63</v>
       </c>
@@ -6388,7 +6385,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="99" spans="1:15" ht="13" customHeight="1">
       <c r="A99" s="9" t="s">
         <v>63</v>
       </c>
@@ -6432,7 +6429,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="100" spans="1:15" ht="13" customHeight="1">
       <c r="A100" s="9" t="s">
         <v>63</v>
       </c>
@@ -6476,7 +6473,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="101" spans="1:15" ht="13" customHeight="1">
       <c r="A101" s="9" t="s">
         <v>63</v>
       </c>
@@ -6520,7 +6517,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="102" spans="1:15" ht="13" customHeight="1">
       <c r="A102" s="9" t="s">
         <v>63</v>
       </c>
@@ -6564,7 +6561,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="103" spans="1:15" ht="13" customHeight="1">
       <c r="A103" s="9" t="s">
         <v>63</v>
       </c>
@@ -6608,7 +6605,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="104" spans="1:15" ht="13" customHeight="1">
       <c r="A104" s="9" t="s">
         <v>63</v>
       </c>
@@ -6652,7 +6649,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="105" spans="1:15" ht="13" customHeight="1">
       <c r="A105" s="9" t="s">
         <v>63</v>
       </c>
@@ -6696,7 +6693,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="106" spans="1:15" ht="13" customHeight="1">
       <c r="A106" s="9" t="s">
         <v>63</v>
       </c>
@@ -6740,7 +6737,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="107" spans="1:15" ht="13" customHeight="1">
       <c r="A107" s="9" t="s">
         <v>63</v>
       </c>
@@ -6784,7 +6781,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="108" spans="1:15" ht="13" customHeight="1">
       <c r="A108" s="9" t="s">
         <v>63</v>
       </c>
@@ -6869,10 +6866,10 @@
         <v>0</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="13" hidden="1" customHeight="1">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="13" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>63</v>
       </c>
@@ -6916,7 +6913,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="111" spans="1:15" ht="13" customHeight="1">
       <c r="A111" s="9" t="s">
         <v>63</v>
       </c>
@@ -6960,7 +6957,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="112" spans="1:15" ht="13" customHeight="1">
       <c r="A112" s="9" t="s">
         <v>63</v>
       </c>
@@ -7004,7 +7001,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="113" spans="1:15" ht="13" customHeight="1">
       <c r="A113" s="9" t="s">
         <v>63</v>
       </c>
@@ -7048,7 +7045,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="114" spans="1:15" ht="13" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>63</v>
       </c>
@@ -7092,7 +7089,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="115" spans="1:15" ht="13" customHeight="1">
       <c r="A115" s="9" t="s">
         <v>63</v>
       </c>
@@ -7136,7 +7133,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="116" spans="1:15" ht="13" customHeight="1">
       <c r="A116" s="9" t="s">
         <v>63</v>
       </c>
@@ -7180,7 +7177,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="117" spans="1:15" ht="13" customHeight="1">
       <c r="A117" s="9" t="s">
         <v>63</v>
       </c>
@@ -7224,7 +7221,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="118" spans="1:15" ht="13" customHeight="1">
       <c r="A118" s="9" t="s">
         <v>63</v>
       </c>
@@ -7268,7 +7265,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="119" spans="1:15" ht="13" customHeight="1">
       <c r="A119" s="9" t="s">
         <v>63</v>
       </c>
@@ -7312,7 +7309,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="120" spans="1:15" ht="13" customHeight="1">
       <c r="A120" s="9" t="s">
         <v>63</v>
       </c>
@@ -7356,7 +7353,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="121" spans="1:15" ht="13" customHeight="1">
       <c r="A121" s="9" t="s">
         <v>63</v>
       </c>
@@ -7400,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="122" spans="1:15" ht="13" customHeight="1">
       <c r="A122" s="9" t="s">
         <v>63</v>
       </c>
@@ -7444,7 +7441,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="123" spans="1:15" ht="13" customHeight="1">
       <c r="A123" s="9" t="s">
         <v>63</v>
       </c>
@@ -7488,7 +7485,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="124" spans="1:15" ht="13" customHeight="1">
       <c r="A124" s="9" t="s">
         <v>63</v>
       </c>
@@ -7532,7 +7529,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="125" spans="1:15" ht="13" customHeight="1">
       <c r="A125" s="9" t="s">
         <v>15</v>
       </c>
@@ -7576,7 +7573,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="126" spans="1:15" ht="13" customHeight="1">
       <c r="A126" s="9" t="s">
         <v>15</v>
       </c>
@@ -7620,7 +7617,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="127" spans="1:15" ht="13" customHeight="1">
       <c r="A127" s="9" t="s">
         <v>15</v>
       </c>
@@ -7664,7 +7661,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="128" spans="1:15" ht="13" customHeight="1">
       <c r="A128" s="9" t="s">
         <v>15</v>
       </c>
@@ -7708,7 +7705,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="129" spans="1:26" ht="13" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>324</v>
       </c>
@@ -7752,7 +7749,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A130" s="27" t="s">
         <v>324</v>
       </c>
@@ -7796,7 +7793,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="131" spans="1:26" ht="13" customHeight="1">
       <c r="A131" s="9" t="s">
         <v>324</v>
       </c>
@@ -7840,7 +7837,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A132" s="27" t="s">
         <v>324</v>
       </c>
@@ -7884,7 +7881,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="133" spans="1:26" ht="13" customHeight="1">
       <c r="A133" s="9" t="s">
         <v>324</v>
       </c>
@@ -7928,7 +7925,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="134" spans="1:26" ht="13" customHeight="1">
       <c r="A134" s="9" t="s">
         <v>324</v>
       </c>
@@ -7977,7 +7974,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" customHeight="1">
       <c r="A135" s="9" t="s">
         <v>324</v>
       </c>
@@ -8032,7 +8029,7 @@
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
     </row>
-    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A136" s="27" t="s">
         <v>324</v>
       </c>
@@ -8076,7 +8073,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="137" spans="1:26" ht="13" customHeight="1">
       <c r="A137" s="9" t="s">
         <v>324</v>
       </c>
@@ -8120,7 +8117,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="138" spans="1:26" ht="13" customHeight="1">
       <c r="A138" s="9" t="s">
         <v>324</v>
       </c>
@@ -8164,7 +8161,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="139" spans="1:26" ht="13" customHeight="1">
       <c r="A139" s="9" t="s">
         <v>324</v>
       </c>
@@ -8208,7 +8205,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="140" spans="1:26" ht="13" customHeight="1">
       <c r="A140" s="9" t="s">
         <v>324</v>
       </c>
@@ -8252,7 +8249,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="141" spans="1:26" ht="13" customHeight="1">
       <c r="A141" s="9" t="s">
         <v>324</v>
       </c>
@@ -8296,7 +8293,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="142" spans="1:26" ht="13" customHeight="1">
       <c r="A142" s="9" t="s">
         <v>324</v>
       </c>
@@ -8340,7 +8337,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="143" spans="1:26" ht="13" customHeight="1">
       <c r="A143" s="9" t="s">
         <v>324</v>
       </c>
@@ -8384,7 +8381,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="144" spans="1:26" ht="13" hidden="1" customHeight="1">
+    <row r="144" spans="1:26" ht="13" customHeight="1">
       <c r="A144" s="9" t="s">
         <v>324</v>
       </c>
@@ -8428,7 +8425,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="145" spans="1:15" ht="13" customHeight="1">
       <c r="A145" s="9" t="s">
         <v>324</v>
       </c>
@@ -8472,7 +8469,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="146" spans="1:15" ht="13" customHeight="1">
       <c r="A146" s="9" t="s">
         <v>324</v>
       </c>
@@ -8516,7 +8513,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="147" spans="1:15" ht="13" customHeight="1">
       <c r="A147" s="9" t="s">
         <v>324</v>
       </c>
@@ -8560,7 +8557,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="148" spans="1:15" ht="13" customHeight="1">
       <c r="A148" s="9" t="s">
         <v>324</v>
       </c>
@@ -8604,7 +8601,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="149" spans="1:15" ht="13" customHeight="1">
       <c r="A149" s="9" t="s">
         <v>324</v>
       </c>
@@ -8648,7 +8645,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="150" spans="1:15" ht="13" customHeight="1">
       <c r="A150" s="9" t="s">
         <v>324</v>
       </c>
@@ -8692,7 +8689,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="151" spans="1:15" ht="13" customHeight="1">
       <c r="A151" s="9" t="s">
         <v>324</v>
       </c>
@@ -8736,7 +8733,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A152" s="27" t="s">
         <v>324</v>
       </c>
@@ -8780,7 +8777,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="153" spans="1:15" ht="13" customHeight="1">
       <c r="A153" s="9" t="s">
         <v>324</v>
       </c>
@@ -8824,7 +8821,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="154" spans="1:15" ht="13" customHeight="1">
       <c r="A154" s="9" t="s">
         <v>324</v>
       </c>
@@ -8868,7 +8865,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A155" s="27" t="s">
         <v>324</v>
       </c>
@@ -8912,7 +8909,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="13" hidden="1" customHeight="1">
+    <row r="156" spans="1:15" ht="13" customHeight="1">
       <c r="A156" s="9" t="s">
         <v>324</v>
       </c>
@@ -8956,7 +8953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A157" s="27" t="s">
         <v>324</v>
       </c>
@@ -9000,7 +8997,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A158" s="27" t="s">
         <v>324</v>
       </c>
@@ -9044,7 +9041,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A159" s="27" t="s">
         <v>324</v>
       </c>
@@ -9088,7 +9085,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A160" s="27" t="s">
         <v>324</v>
       </c>
@@ -9129,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="O160" s="27" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A161" s="27" t="s">
         <v>324</v>
       </c>
@@ -9176,7 +9173,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A162" s="27" t="s">
         <v>324</v>
       </c>
@@ -9220,7 +9217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A163" s="27" t="s">
         <v>324</v>
       </c>
@@ -9264,7 +9261,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A164" s="27" t="s">
         <v>324</v>
       </c>
@@ -9308,7 +9305,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A165" s="27" t="s">
         <v>324</v>
       </c>
@@ -9316,22 +9313,22 @@
         <v>16</v>
       </c>
       <c r="C165" s="27" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="D165" s="27" t="s">
-        <v>341</v>
+        <v>431</v>
       </c>
       <c r="E165" s="27" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="F165" s="27" t="s">
-        <v>485</v>
+        <v>422</v>
       </c>
       <c r="G165" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H165" s="27">
-        <v>810</v>
+        <v>384</v>
       </c>
       <c r="I165" s="27" t="s">
         <v>19</v>
@@ -9349,10 +9346,10 @@
         <v>0</v>
       </c>
       <c r="O165" s="27" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A166" s="27" t="s">
         <v>324</v>
       </c>
@@ -9360,31 +9357,31 @@
         <v>16</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>142</v>
+        <v>370</v>
       </c>
       <c r="D166" s="27" t="s">
-        <v>431</v>
+        <v>35</v>
       </c>
       <c r="E166" s="27" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="F166" s="27" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="G166" s="27" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H166" s="27">
-        <v>384</v>
+        <v>161</v>
       </c>
       <c r="I166" s="27" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K166" s="27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L166" s="27" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M166" s="27">
         <v>0</v>
@@ -9393,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="27" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="167" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -9404,22 +9401,22 @@
         <v>16</v>
       </c>
       <c r="C167" s="27" t="s">
-        <v>370</v>
+        <v>225</v>
       </c>
       <c r="D167" s="27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E167" s="27" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="F167" s="27" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="G167" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H167" s="27">
-        <v>161</v>
+        <v>742</v>
       </c>
       <c r="I167" s="27" t="s">
         <v>32</v>
@@ -9436,8 +9433,8 @@
       <c r="N167" s="27">
         <v>0</v>
       </c>
-      <c r="O167" s="27" t="s">
-        <v>503</v>
+      <c r="O167" s="9" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
@@ -9448,22 +9445,22 @@
         <v>16</v>
       </c>
       <c r="C168" s="27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D168" s="27" t="s">
         <v>40</v>
       </c>
       <c r="E168" s="27" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F168" s="27" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G168" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H168" s="27">
-        <v>742</v>
+        <v>945</v>
       </c>
       <c r="I168" s="27" t="s">
         <v>32</v>
@@ -9480,11 +9477,11 @@
       <c r="N168" s="27">
         <v>0</v>
       </c>
-      <c r="O168" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+      <c r="O168" s="27" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A169" s="27" t="s">
         <v>324</v>
       </c>
@@ -9492,22 +9489,22 @@
         <v>16</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D169" s="27" t="s">
         <v>40</v>
       </c>
       <c r="E169" s="27" t="s">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="F169" s="27" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G169" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H169" s="27">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="I169" s="27" t="s">
         <v>32</v>
@@ -9525,10 +9522,10 @@
         <v>0</v>
       </c>
       <c r="O169" s="27" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A170" s="27" t="s">
         <v>324</v>
       </c>
@@ -9536,13 +9533,13 @@
         <v>16</v>
       </c>
       <c r="C170" s="27" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="D170" s="27" t="s">
         <v>459</v>
       </c>
       <c r="E170" s="27" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F170" s="27" t="s">
         <v>462</v>
@@ -9551,7 +9548,7 @@
         <v>32</v>
       </c>
       <c r="H170" s="27">
-        <v>959</v>
+        <v>184</v>
       </c>
       <c r="I170" s="27" t="s">
         <v>32</v>
@@ -9572,7 +9569,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A171" s="27" t="s">
         <v>324</v>
       </c>
@@ -9580,31 +9577,31 @@
         <v>16</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="D171" s="27" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="E171" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="F171" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="G171" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" s="27">
+        <v>217</v>
+      </c>
+      <c r="I171" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K171" s="27">
         <v>50</v>
       </c>
-      <c r="F171" s="27" t="s">
-        <v>462</v>
-      </c>
-      <c r="G171" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H171" s="27">
-        <v>184</v>
-      </c>
-      <c r="I171" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K171" s="27">
-        <v>1</v>
-      </c>
       <c r="L171" s="27" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="M171" s="27">
         <v>0</v>
@@ -9613,10 +9610,10 @@
         <v>0</v>
       </c>
       <c r="O171" s="27" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A172" s="27" t="s">
         <v>324</v>
       </c>
@@ -9624,28 +9621,28 @@
         <v>16</v>
       </c>
       <c r="C172" s="27" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="D172" s="27" t="s">
-        <v>480</v>
+        <v>59</v>
       </c>
       <c r="E172" s="27" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="F172" s="27" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="G172" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H172" s="27">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="I172" s="27" t="s">
         <v>19</v>
       </c>
       <c r="K172" s="27">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="L172" s="27" t="s">
         <v>54</v>
@@ -9657,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="O172" s="27" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A173" s="27" t="s">
         <v>324</v>
       </c>
@@ -9668,13 +9665,13 @@
         <v>16</v>
       </c>
       <c r="C173" s="27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D173" s="27" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F173" s="27" t="s">
         <v>478</v>
@@ -9689,7 +9686,7 @@
         <v>19</v>
       </c>
       <c r="K173" s="27">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L173" s="27" t="s">
         <v>54</v>
@@ -9704,7 +9701,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A174" s="27" t="s">
         <v>324</v>
       </c>
@@ -9712,31 +9709,31 @@
         <v>16</v>
       </c>
       <c r="C174" s="27" t="s">
-        <v>373</v>
+        <v>496</v>
       </c>
       <c r="D174" s="27" t="s">
-        <v>199</v>
+        <v>437</v>
       </c>
       <c r="E174" s="27" t="s">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="F174" s="27" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="G174" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H174" s="27">
-        <v>184</v>
+        <v>32</v>
+      </c>
+      <c r="H174" s="31">
+        <v>8959</v>
       </c>
       <c r="I174" s="27" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K174" s="27">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L174" s="27" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M174" s="27">
         <v>0</v>
@@ -9745,10 +9742,10 @@
         <v>0</v>
       </c>
       <c r="O174" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A175" s="27" t="s">
         <v>324</v>
       </c>
@@ -9756,22 +9753,22 @@
         <v>16</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>496</v>
+        <v>375</v>
       </c>
       <c r="D175" s="27" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="E175" s="27" t="s">
-        <v>374</v>
+        <v>153</v>
       </c>
       <c r="F175" s="27" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H175" s="31">
-        <v>8959</v>
+        <v>3429</v>
       </c>
       <c r="I175" s="27" t="s">
         <v>32</v>
@@ -9789,10 +9786,10 @@
         <v>0</v>
       </c>
       <c r="O175" s="27" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A176" s="27" t="s">
         <v>324</v>
       </c>
@@ -9800,13 +9797,13 @@
         <v>16</v>
       </c>
       <c r="C176" s="27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D176" s="27" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="E176" s="27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F176" s="27" t="s">
         <v>423</v>
@@ -9815,7 +9812,7 @@
         <v>32</v>
       </c>
       <c r="H176" s="31">
-        <v>3429</v>
+        <v>3247</v>
       </c>
       <c r="I176" s="27" t="s">
         <v>32</v>
@@ -9836,7 +9833,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A177" s="27" t="s">
         <v>324</v>
       </c>
@@ -9844,13 +9841,13 @@
         <v>16</v>
       </c>
       <c r="C177" s="27" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D177" s="27" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E177" s="27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F177" s="27" t="s">
         <v>423</v>
@@ -9859,7 +9856,7 @@
         <v>32</v>
       </c>
       <c r="H177" s="31">
-        <v>3247</v>
+        <v>2699</v>
       </c>
       <c r="I177" s="27" t="s">
         <v>32</v>
@@ -9877,10 +9874,10 @@
         <v>0</v>
       </c>
       <c r="O177" s="27" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A178" s="27" t="s">
         <v>324</v>
       </c>
@@ -9888,31 +9885,31 @@
         <v>16</v>
       </c>
       <c r="C178" s="27" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D178" s="27" t="s">
-        <v>436</v>
+        <v>159</v>
       </c>
       <c r="E178" s="27" t="s">
-        <v>157</v>
+        <v>378</v>
       </c>
       <c r="F178" s="27" t="s">
         <v>423</v>
       </c>
       <c r="G178" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H178" s="31">
-        <v>2699</v>
+        <v>1336</v>
       </c>
       <c r="I178" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="K178" s="27">
         <v>1</v>
       </c>
       <c r="L178" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="M178" s="27">
         <v>0</v>
@@ -9921,10 +9918,10 @@
         <v>0</v>
       </c>
       <c r="O178" s="27" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A179" s="27" t="s">
         <v>324</v>
       </c>
@@ -9932,31 +9929,31 @@
         <v>16</v>
       </c>
       <c r="C179" s="27" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="D179" s="27" t="s">
-        <v>159</v>
+        <v>437</v>
       </c>
       <c r="E179" s="27" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F179" s="27" t="s">
-        <v>423</v>
+        <v>490</v>
       </c>
       <c r="G179" s="27" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="H179" s="31">
-        <v>1336</v>
+        <v>6136</v>
       </c>
       <c r="I179" s="27" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="K179" s="27">
         <v>1</v>
       </c>
       <c r="L179" s="27" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="M179" s="27">
         <v>0</v>
@@ -9965,33 +9962,33 @@
         <v>0</v>
       </c>
       <c r="O179" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A180" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="B180" s="32" t="s">
+      <c r="B180" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C180" s="27" t="s">
-        <v>495</v>
+        <v>382</v>
       </c>
       <c r="D180" s="27" t="s">
         <v>437</v>
       </c>
       <c r="E180" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F180" s="27" t="s">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="G180" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H180" s="31">
-        <v>6136</v>
+        <v>3800</v>
       </c>
       <c r="I180" s="27" t="s">
         <v>32</v>
@@ -10009,10 +10006,10 @@
         <v>0</v>
       </c>
       <c r="O180" s="27" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A181" s="27" t="s">
         <v>324</v>
       </c>
@@ -10020,13 +10017,13 @@
         <v>16</v>
       </c>
       <c r="C181" s="27" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D181" s="27" t="s">
         <v>437</v>
       </c>
       <c r="E181" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F181" s="27" t="s">
         <v>438</v>
@@ -10035,7 +10032,7 @@
         <v>32</v>
       </c>
       <c r="H181" s="31">
-        <v>3800</v>
+        <v>3323</v>
       </c>
       <c r="I181" s="27" t="s">
         <v>32</v>
@@ -10056,51 +10053,51 @@
         <v>354</v>
       </c>
     </row>
-    <row r="182" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
-      <c r="A182" s="27" t="s">
+    <row r="182" spans="1:21" ht="13" customHeight="1">
+      <c r="A182" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B182" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="D182" s="27" t="s">
+      <c r="B182" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D182" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="E182" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="F182" s="27" t="s">
+      <c r="E182" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F182" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="G182" s="27" t="s">
+      <c r="G182" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H182" s="31">
-        <v>3323</v>
-      </c>
-      <c r="I182" s="27" t="s">
+      <c r="H182" s="8">
+        <v>8959</v>
+      </c>
+      <c r="I182" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K182" s="27">
+      <c r="K182" s="9">
         <v>1</v>
       </c>
-      <c r="L182" s="27" t="s">
+      <c r="L182" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M182" s="27">
-        <v>0</v>
-      </c>
-      <c r="N182" s="27">
-        <v>0</v>
-      </c>
-      <c r="O182" s="27" t="s">
+      <c r="M182" s="9">
+        <v>0</v>
+      </c>
+      <c r="N182" s="9">
+        <v>0</v>
+      </c>
+      <c r="O182" s="9" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="13" hidden="1" customHeight="1">
+    <row r="183" spans="1:21" ht="13" customHeight="1">
       <c r="A183" s="9" t="s">
         <v>324</v>
       </c>
@@ -10108,22 +10105,22 @@
         <v>64</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D183" s="9" t="s">
         <v>437</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="F183" s="9" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
       <c r="G183" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H183" s="8">
-        <v>8959</v>
+        <v>6136</v>
       </c>
       <c r="I183" s="9" t="s">
         <v>32</v>
@@ -10141,10 +10138,10 @@
         <v>0</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="184" spans="1:21" ht="13" hidden="1" customHeight="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21" ht="13" customHeight="1">
       <c r="A184" s="9" t="s">
         <v>324</v>
       </c>
@@ -10152,22 +10149,22 @@
         <v>64</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>495</v>
+        <v>382</v>
       </c>
       <c r="D184" s="9" t="s">
         <v>437</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F184" s="9" t="s">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="G184" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H184" s="8">
-        <v>6136</v>
+        <v>3800</v>
       </c>
       <c r="I184" s="9" t="s">
         <v>32</v>
@@ -10185,10 +10182,10 @@
         <v>0</v>
       </c>
       <c r="O184" s="9" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="185" spans="1:21" ht="13" hidden="1" customHeight="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21" ht="13" customHeight="1">
       <c r="A185" s="9" t="s">
         <v>324</v>
       </c>
@@ -10196,13 +10193,13 @@
         <v>64</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D185" s="9" t="s">
         <v>437</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>438</v>
@@ -10211,7 +10208,7 @@
         <v>32</v>
       </c>
       <c r="H185" s="8">
-        <v>3800</v>
+        <v>3323</v>
       </c>
       <c r="I185" s="9" t="s">
         <v>32</v>
@@ -10231,53 +10228,53 @@
       <c r="O185" s="9" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="186" spans="1:21" ht="13" hidden="1" customHeight="1">
-      <c r="A186" s="9" t="s">
+      <c r="U185" s="11"/>
+    </row>
+    <row r="186" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+      <c r="A186" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="B186" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="D186" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="E186" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F186" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="G186" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H186" s="8">
-        <v>3323</v>
-      </c>
-      <c r="I186" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K186" s="9">
-        <v>1</v>
-      </c>
-      <c r="L186" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M186" s="9">
-        <v>0</v>
-      </c>
-      <c r="N186" s="9">
-        <v>0</v>
-      </c>
-      <c r="O186" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="U186" s="11"/>
-    </row>
-    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+      <c r="B186" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D186" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="E186" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F186" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="G186" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H186" s="31">
+        <v>3086</v>
+      </c>
+      <c r="I186" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K186" s="27">
+        <v>6</v>
+      </c>
+      <c r="L186" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M186" s="27">
+        <v>0</v>
+      </c>
+      <c r="N186" s="27">
+        <v>0</v>
+      </c>
+      <c r="O186" s="27" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A187" s="27" t="s">
         <v>324</v>
       </c>
@@ -10285,22 +10282,22 @@
         <v>16</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D187" s="27" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="E187" s="27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F187" s="27" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="G187" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H187" s="31">
-        <v>3086</v>
+        <v>4078</v>
       </c>
       <c r="I187" s="27" t="s">
         <v>19</v>
@@ -10318,10 +10315,10 @@
         <v>0</v>
       </c>
       <c r="O187" s="27" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A188" s="27" t="s">
         <v>324</v>
       </c>
@@ -10329,28 +10326,28 @@
         <v>16</v>
       </c>
       <c r="C188" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D188" s="27" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="E188" s="27" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="F188" s="27" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="G188" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H188" s="31">
-        <v>4078</v>
+        <v>2186</v>
       </c>
       <c r="I188" s="27" t="s">
         <v>19</v>
       </c>
       <c r="K188" s="27">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L188" s="27" t="s">
         <v>20</v>
@@ -10362,10 +10359,10 @@
         <v>0</v>
       </c>
       <c r="O188" s="27" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A189" s="27" t="s">
         <v>324</v>
       </c>
@@ -10373,28 +10370,28 @@
         <v>16</v>
       </c>
       <c r="C189" s="27" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D189" s="27" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="E189" s="27" t="s">
-        <v>107</v>
+        <v>411</v>
       </c>
       <c r="F189" s="27" t="s">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="G189" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H189" s="31">
-        <v>2186</v>
+        <v>3435</v>
       </c>
       <c r="I189" s="27" t="s">
         <v>19</v>
       </c>
       <c r="K189" s="27">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L189" s="27" t="s">
         <v>20</v>
@@ -10406,10 +10403,10 @@
         <v>0</v>
       </c>
       <c r="O189" s="27" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A190" s="27" t="s">
         <v>324</v>
       </c>
@@ -10417,22 +10414,22 @@
         <v>16</v>
       </c>
       <c r="C190" s="27" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D190" s="27" t="s">
-        <v>448</v>
+        <v>330</v>
       </c>
       <c r="E190" s="27" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F190" s="27" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="G190" s="27" t="s">
         <v>19</v>
       </c>
       <c r="H190" s="31">
-        <v>3435</v>
+        <v>4029</v>
       </c>
       <c r="I190" s="27" t="s">
         <v>19</v>
@@ -10450,10 +10447,10 @@
         <v>0</v>
       </c>
       <c r="O190" s="27" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A191" s="27" t="s">
         <v>324</v>
       </c>
@@ -10461,22 +10458,22 @@
         <v>16</v>
       </c>
       <c r="C191" s="27" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D191" s="27" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E191" s="27" t="s">
-        <v>413</v>
+        <v>141</v>
       </c>
       <c r="F191" s="27" t="s">
-        <v>426</v>
+        <v>485</v>
       </c>
       <c r="G191" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H191" s="31">
-        <v>4029</v>
+      <c r="H191" s="27">
+        <v>810</v>
       </c>
       <c r="I191" s="27" t="s">
         <v>19</v>
@@ -10494,10 +10491,10 @@
         <v>0</v>
       </c>
       <c r="O191" s="27" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A192" s="27" t="s">
         <v>324</v>
       </c>
@@ -10505,31 +10502,31 @@
         <v>16</v>
       </c>
       <c r="C192" s="27" t="s">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="D192" s="27" t="s">
-        <v>341</v>
+        <v>437</v>
       </c>
       <c r="E192" s="27" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F192" s="27" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="G192" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H192" s="27">
-        <v>810</v>
+        <v>32</v>
+      </c>
+      <c r="H192" s="31">
+        <v>8959</v>
       </c>
       <c r="I192" s="27" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K192" s="27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L192" s="27" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M192" s="27">
         <v>0</v>
@@ -10538,10 +10535,10 @@
         <v>0</v>
       </c>
       <c r="O192" s="27" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A193" s="27" t="s">
         <v>324</v>
       </c>
@@ -10549,22 +10546,22 @@
         <v>16</v>
       </c>
       <c r="C193" s="27" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="D193" s="27" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="E193" s="27" t="s">
-        <v>149</v>
+        <v>416</v>
       </c>
       <c r="F193" s="27" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H193" s="31">
-        <v>8959</v>
+        <v>3429</v>
       </c>
       <c r="I193" s="27" t="s">
         <v>32</v>
@@ -10582,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="O193" s="27" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A194" s="27" t="s">
         <v>324</v>
       </c>
@@ -10593,22 +10590,22 @@
         <v>16</v>
       </c>
       <c r="C194" s="27" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D194" s="27" t="s">
-        <v>425</v>
+        <v>481</v>
       </c>
       <c r="E194" s="27" t="s">
-        <v>416</v>
+        <v>69</v>
       </c>
       <c r="F194" s="27" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="G194" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H194" s="31">
-        <v>3429</v>
+        <v>2505</v>
       </c>
       <c r="I194" s="27" t="s">
         <v>32</v>
@@ -10626,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="O194" s="27" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A195" s="27" t="s">
         <v>324</v>
       </c>
@@ -10637,31 +10634,31 @@
         <v>16</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D195" s="27" t="s">
-        <v>481</v>
+        <v>428</v>
       </c>
       <c r="E195" s="27" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="F195" s="27" t="s">
-        <v>482</v>
+        <v>429</v>
       </c>
       <c r="G195" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H195" s="31">
-        <v>2505</v>
+        <v>2448</v>
       </c>
       <c r="I195" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="K195" s="27">
         <v>1</v>
       </c>
       <c r="L195" s="27" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="M195" s="27">
         <v>0</v>
@@ -10670,10 +10667,10 @@
         <v>0</v>
       </c>
       <c r="O195" s="27" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
       <c r="A196" s="27" t="s">
         <v>324</v>
       </c>
@@ -10681,22 +10678,22 @@
         <v>16</v>
       </c>
       <c r="C196" s="27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D196" s="27" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>109</v>
+        <v>418</v>
       </c>
       <c r="F196" s="27" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G196" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="H196" s="31">
-        <v>2448</v>
+      <c r="H196" s="27">
+        <v>230</v>
       </c>
       <c r="I196" s="27" t="s">
         <v>79</v>
@@ -10713,53 +10710,14 @@
       <c r="N196" s="27">
         <v>0</v>
       </c>
-      <c r="O196" s="27" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
-      <c r="A197" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="B197" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" s="27" t="s">
-        <v>417</v>
-      </c>
-      <c r="D197" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="E197" s="27" t="s">
-        <v>418</v>
-      </c>
-      <c r="F197" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="G197" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="H197" s="27">
-        <v>230</v>
-      </c>
-      <c r="I197" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="K197" s="27">
-        <v>1</v>
-      </c>
-      <c r="L197" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="M197" s="27">
-        <v>0</v>
-      </c>
-      <c r="N197" s="27">
-        <v>0</v>
-      </c>
-      <c r="O197" s="30" t="s">
+      <c r="O196" s="30" t="s">
         <v>497</v>
       </c>
+    </row>
+    <row r="197" spans="1:15" ht="13" customHeight="1">
+      <c r="G197" s="9"/>
+      <c r="H197" s="9"/>
+      <c r="I197" s="9"/>
     </row>
     <row r="198" spans="1:15" ht="13" customHeight="1">
       <c r="G198" s="9"/>
@@ -10870,12 +10828,12 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="9"/>
+      <c r="T219"/>
     </row>
     <row r="220" spans="7:20" ht="13" customHeight="1">
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="9"/>
-      <c r="T220"/>
     </row>
     <row r="221" spans="7:20" ht="13" customHeight="1">
       <c r="G221" s="9"/>
@@ -10923,9 +10881,10 @@
       <c r="I229" s="9"/>
     </row>
     <row r="230" spans="4:14" ht="13" customHeight="1">
-      <c r="G230" s="9"/>
-      <c r="H230" s="9"/>
-      <c r="I230" s="9"/>
+      <c r="D230" s="6"/>
+      <c r="G230" s="6"/>
+      <c r="L230" s="6"/>
+      <c r="N230" s="10"/>
     </row>
     <row r="231" spans="4:14" ht="13" customHeight="1">
       <c r="D231" s="6"/>
@@ -12553,21 +12512,7 @@
       <c r="L501" s="6"/>
       <c r="N501" s="10"/>
     </row>
-    <row r="502" spans="4:14" ht="13" customHeight="1">
-      <c r="D502" s="6"/>
-      <c r="G502" s="6"/>
-      <c r="L502" s="6"/>
-      <c r="N502" s="10"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z197" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Соединитель импоста 35 мм (2160.2163)"/>
-        <filter val="Сухарь 32,5 мм (2115) новый дизайн"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/axis_pro_gf.xlsx
+++ b/axis_pro_gf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gulmira/Documents/Axis web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25652965-D4F6-8746-A09E-16381BB306A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80A723F-AB21-AB42-987F-16CC3C02103D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1557,15 +1557,6 @@
     <t>(2∗n_impost+4)∗qty</t>
   </si>
   <si>
-    <t>4*(1+n_sash)*qty</t>
-  </si>
-  <si>
-    <t>4*qty</t>
-  </si>
-  <si>
-    <t>2∗n_sash_passive∗qty</t>
-  </si>
-  <si>
     <t>2∗(width+height)/1000∗qty∗(1+n_impost+n_sash)</t>
   </si>
   <si>
@@ -1578,13 +1569,22 @@
     <t>1*n_sash_active*is_door*qty</t>
   </si>
   <si>
-    <t>2∗n_sash_active∗is_door∗qty</t>
-  </si>
-  <si>
-    <t>(4∗n_impost+4)∗qty</t>
-  </si>
-  <si>
-    <t>3∗(sash_w+sash_h)/1000∗n_sash∗qty</t>
+    <t>(2 * n_impost + 4) * qty</t>
+  </si>
+  <si>
+    <t>2 * n_sash_active * is_door * qty</t>
+  </si>
+  <si>
+    <t>(4 + 2 * n_impost) * qty</t>
+  </si>
+  <si>
+    <t>4 * (1 + n_sash) * qty</t>
+  </si>
+  <si>
+    <t>3 * (sash_w + sash_h) / 1000 * n_sash * qty</t>
+  </si>
+  <si>
+    <t>(2 * (width + height) + 4 * (sash_w + sash_h) * n_sash) / 1000 * qty</t>
   </si>
 </sst>
 </file>
@@ -2037,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z501"/>
@@ -2117,7 +2117,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1">
+    <row r="2" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1">
+    <row r="3" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1">
+    <row r="4" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1">
+    <row r="5" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" customHeight="1">
+    <row r="6" spans="1:24" s="27" customFormat="1" ht="15.75" hidden="1" customHeight="1">
       <c r="A6" s="27" t="s">
         <v>15</v>
       </c>
@@ -2334,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1">
+    <row r="8" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1">
+    <row r="9" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1">
+    <row r="10" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1">
+    <row r="11" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1">
+    <row r="12" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1">
+    <row r="13" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1">
+    <row r="14" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1">
+    <row r="15" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1">
+    <row r="16" spans="1:24" ht="15.75" hidden="1" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+    <row r="17" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+    <row r="18" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>15</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+    <row r="19" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>63</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1">
+    <row r="20" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>63</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1">
+    <row r="21" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>63</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+    <row r="22" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>63</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+    <row r="23" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>63</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1">
+    <row r="24" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>15</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1">
+    <row r="25" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>15</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1">
+    <row r="26" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>15</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1">
+    <row r="27" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1">
+    <row r="28" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>15</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1">
+    <row r="29" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>15</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1">
+    <row r="30" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>15</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1">
+    <row r="31" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>15</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1">
+    <row r="32" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1">
+    <row r="33" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>15</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1">
+    <row r="34" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>15</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1">
+    <row r="35" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>15</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1">
+    <row r="36" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>63</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1">
+    <row r="37" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1">
+    <row r="38" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>63</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1">
+    <row r="39" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1">
+    <row r="40" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A40" s="9" t="s">
         <v>63</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1">
+    <row r="41" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A41" s="9" t="s">
         <v>63</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1">
+    <row r="42" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>63</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1">
+    <row r="43" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A43" s="9" t="s">
         <v>63</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1">
+    <row r="44" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A44" s="9" t="s">
         <v>63</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1">
+    <row r="45" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A45" s="9" t="s">
         <v>63</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1">
+    <row r="46" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A46" s="9" t="s">
         <v>63</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1">
+    <row r="47" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>63</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1">
+    <row r="48" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A48" s="9" t="s">
         <v>63</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1">
+    <row r="49" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>63</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" customHeight="1">
+    <row r="50" spans="1:15" ht="15.75" hidden="1" customHeight="1">
       <c r="A50" s="9" t="s">
         <v>63</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13" customHeight="1">
+    <row r="51" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A51" s="9" t="s">
         <v>63</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13" customHeight="1">
+    <row r="52" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A52" s="9" t="s">
         <v>63</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="53" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A53" s="27" t="s">
         <v>63</v>
       </c>
@@ -4402,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="O53" s="27" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="13" customHeight="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>63</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13" customHeight="1">
+    <row r="55" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>63</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13" customHeight="1">
+    <row r="56" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A56" s="9" t="s">
         <v>63</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13" customHeight="1">
+    <row r="57" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A57" s="9" t="s">
         <v>63</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13" customHeight="1">
+    <row r="58" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>63</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13" customHeight="1">
+    <row r="59" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>63</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13" customHeight="1">
+    <row r="60" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>63</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13" customHeight="1">
+    <row r="61" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A61" s="9" t="s">
         <v>63</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13" customHeight="1">
+    <row r="62" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>63</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13" customHeight="1">
+    <row r="63" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13" customHeight="1">
+    <row r="64" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A64" s="9" t="s">
         <v>63</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13" customHeight="1">
+    <row r="65" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A65" s="9" t="s">
         <v>63</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13" customHeight="1">
+    <row r="66" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A66" s="9" t="s">
         <v>63</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13" customHeight="1">
+    <row r="67" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13" customHeight="1">
+    <row r="68" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A68" s="9" t="s">
         <v>63</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="13" customHeight="1">
+    <row r="69" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A69" s="9" t="s">
         <v>63</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13" customHeight="1">
+    <row r="70" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>63</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13" customHeight="1">
+    <row r="71" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>63</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13" customHeight="1">
+    <row r="72" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>63</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13" customHeight="1">
+    <row r="73" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A73" s="9" t="s">
         <v>63</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13" customHeight="1">
+    <row r="74" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A74" s="9" t="s">
         <v>63</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13" customHeight="1">
+    <row r="75" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A75" s="9" t="s">
         <v>63</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="13" customHeight="1">
+    <row r="76" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A76" s="9" t="s">
         <v>63</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="13" customHeight="1">
+    <row r="77" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="13" customHeight="1">
+    <row r="78" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A78" s="9" t="s">
         <v>63</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="13" customHeight="1">
+    <row r="79" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A79" s="9" t="s">
         <v>63</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="13" customHeight="1">
+    <row r="80" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A80" s="9" t="s">
         <v>63</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="13" customHeight="1">
+    <row r="81" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A81" s="9" t="s">
         <v>63</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="13" customHeight="1">
+    <row r="82" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A82" s="9" t="s">
         <v>63</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="13" customHeight="1">
+    <row r="83" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>63</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="13" customHeight="1">
+    <row r="84" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A84" s="9" t="s">
         <v>63</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="13" customHeight="1">
+    <row r="85" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A85" s="9" t="s">
         <v>63</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="13" customHeight="1">
+    <row r="86" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A86" s="9" t="s">
         <v>63</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="13" customHeight="1">
+    <row r="87" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A87" s="9" t="s">
         <v>63</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="13" customHeight="1">
+    <row r="88" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A88" s="9" t="s">
         <v>63</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="13" customHeight="1">
+    <row r="89" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A89" s="9" t="s">
         <v>63</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="13" customHeight="1">
+    <row r="90" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A90" s="9" t="s">
         <v>63</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="13" customHeight="1">
+    <row r="91" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A91" s="9" t="s">
         <v>63</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="13" customHeight="1">
+    <row r="92" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>63</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="13" customHeight="1">
+    <row r="93" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A93" s="9" t="s">
         <v>63</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="13" customHeight="1">
+    <row r="94" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A94" s="9" t="s">
         <v>63</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="13" customHeight="1">
+    <row r="95" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>63</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="13" customHeight="1">
+    <row r="96" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>63</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="13" customHeight="1">
+    <row r="97" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A97" s="9" t="s">
         <v>63</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="13" customHeight="1">
+    <row r="98" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A98" s="9" t="s">
         <v>63</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="13" customHeight="1">
+    <row r="99" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A99" s="9" t="s">
         <v>63</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="13" customHeight="1">
+    <row r="100" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A100" s="9" t="s">
         <v>63</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="13" customHeight="1">
+    <row r="101" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A101" s="9" t="s">
         <v>63</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="13" customHeight="1">
+    <row r="102" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A102" s="9" t="s">
         <v>63</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="13" customHeight="1">
+    <row r="103" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A103" s="9" t="s">
         <v>63</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="13" customHeight="1">
+    <row r="104" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A104" s="9" t="s">
         <v>63</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="13" customHeight="1">
+    <row r="105" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A105" s="9" t="s">
         <v>63</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="13" customHeight="1">
+    <row r="106" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A106" s="9" t="s">
         <v>63</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="13" customHeight="1">
+    <row r="107" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A107" s="9" t="s">
         <v>63</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="13" customHeight="1">
+    <row r="108" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A108" s="9" t="s">
         <v>63</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="13" customHeight="1">
+    <row r="109" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A109" s="9" t="s">
         <v>63</v>
       </c>
@@ -6866,10 +6866,10 @@
         <v>0</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="13" customHeight="1">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>63</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="13" customHeight="1">
+    <row r="111" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A111" s="9" t="s">
         <v>63</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="13" customHeight="1">
+    <row r="112" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A112" s="9" t="s">
         <v>63</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="13" customHeight="1">
+    <row r="113" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A113" s="9" t="s">
         <v>63</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="13" customHeight="1">
+    <row r="114" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>63</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="13" customHeight="1">
+    <row r="115" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A115" s="9" t="s">
         <v>63</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="13" customHeight="1">
+    <row r="116" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A116" s="9" t="s">
         <v>63</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="13" customHeight="1">
+    <row r="117" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A117" s="9" t="s">
         <v>63</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="13" customHeight="1">
+    <row r="118" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A118" s="9" t="s">
         <v>63</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="13" customHeight="1">
+    <row r="119" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A119" s="9" t="s">
         <v>63</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="13" customHeight="1">
+    <row r="120" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A120" s="9" t="s">
         <v>63</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="13" customHeight="1">
+    <row r="121" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A121" s="9" t="s">
         <v>63</v>
       </c>
@@ -7397,7 +7397,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="13" customHeight="1">
+    <row r="122" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A122" s="9" t="s">
         <v>63</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="13" customHeight="1">
+    <row r="123" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A123" s="9" t="s">
         <v>63</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="13" customHeight="1">
+    <row r="124" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A124" s="9" t="s">
         <v>63</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="13" customHeight="1">
+    <row r="125" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A125" s="9" t="s">
         <v>15</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="13" customHeight="1">
+    <row r="126" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A126" s="9" t="s">
         <v>15</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="13" customHeight="1">
+    <row r="127" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A127" s="9" t="s">
         <v>15</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="13" customHeight="1">
+    <row r="128" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A128" s="9" t="s">
         <v>15</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="13" customHeight="1">
+    <row r="129" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>324</v>
       </c>
@@ -7749,7 +7749,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="130" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A130" s="27" t="s">
         <v>324</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:26" ht="13" customHeight="1">
+    <row r="131" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A131" s="9" t="s">
         <v>324</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="132" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A132" s="27" t="s">
         <v>324</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="13" customHeight="1">
+    <row r="133" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A133" s="9" t="s">
         <v>324</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="13" customHeight="1">
+    <row r="134" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A134" s="9" t="s">
         <v>324</v>
       </c>
@@ -7974,7 +7974,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" customHeight="1">
+    <row r="135" spans="1:26" s="25" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A135" s="9" t="s">
         <v>324</v>
       </c>
@@ -8029,7 +8029,7 @@
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
     </row>
-    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="136" spans="1:26" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A136" s="27" t="s">
         <v>324</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="13" customHeight="1">
+    <row r="137" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A137" s="9" t="s">
         <v>324</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="13" customHeight="1">
+    <row r="138" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A138" s="9" t="s">
         <v>324</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="13" customHeight="1">
+    <row r="139" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A139" s="9" t="s">
         <v>324</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="13" customHeight="1">
+    <row r="140" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A140" s="9" t="s">
         <v>324</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="13" customHeight="1">
+    <row r="141" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A141" s="9" t="s">
         <v>324</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="13" customHeight="1">
+    <row r="142" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A142" s="9" t="s">
         <v>324</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="13" customHeight="1">
+    <row r="143" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A143" s="9" t="s">
         <v>324</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="144" spans="1:26" ht="13" customHeight="1">
+    <row r="144" spans="1:26" ht="13" hidden="1" customHeight="1">
       <c r="A144" s="9" t="s">
         <v>324</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="13" customHeight="1">
+    <row r="145" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A145" s="9" t="s">
         <v>324</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="13" customHeight="1">
+    <row r="146" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A146" s="9" t="s">
         <v>324</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="13" customHeight="1">
+    <row r="147" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A147" s="9" t="s">
         <v>324</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="13" customHeight="1">
+    <row r="148" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A148" s="9" t="s">
         <v>324</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="13" customHeight="1">
+    <row r="149" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A149" s="9" t="s">
         <v>324</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="13" customHeight="1">
+    <row r="150" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A150" s="9" t="s">
         <v>324</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="13" customHeight="1">
+    <row r="151" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A151" s="9" t="s">
         <v>324</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="152" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A152" s="27" t="s">
         <v>324</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="13" customHeight="1">
+    <row r="153" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A153" s="9" t="s">
         <v>324</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="13" customHeight="1">
+    <row r="154" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A154" s="9" t="s">
         <v>324</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="155" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A155" s="27" t="s">
         <v>324</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="13" customHeight="1">
+    <row r="156" spans="1:15" ht="13" hidden="1" customHeight="1">
       <c r="A156" s="9" t="s">
         <v>324</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="157" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A157" s="27" t="s">
         <v>324</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="158" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A158" s="27" t="s">
         <v>324</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="159" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A159" s="27" t="s">
         <v>324</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="160" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A160" s="27" t="s">
         <v>324</v>
       </c>
@@ -9126,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="O160" s="27" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A161" s="27" t="s">
         <v>324</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="162" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A162" s="27" t="s">
         <v>324</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="163" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A163" s="27" t="s">
         <v>324</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="164" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A164" s="27" t="s">
         <v>324</v>
       </c>
@@ -9305,7 +9305,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="165" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A165" s="27" t="s">
         <v>324</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="166" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A166" s="27" t="s">
         <v>324</v>
       </c>
@@ -9390,10 +9390,10 @@
         <v>0</v>
       </c>
       <c r="O166" s="27" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A167" s="27" t="s">
         <v>324</v>
       </c>
@@ -9433,11 +9433,11 @@
       <c r="N167" s="27">
         <v>0</v>
       </c>
-      <c r="O167" s="9" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+      <c r="O167" s="27" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A168" s="27" t="s">
         <v>324</v>
       </c>
@@ -9478,10 +9478,10 @@
         <v>0</v>
       </c>
       <c r="O168" s="27" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A169" s="27" t="s">
         <v>324</v>
       </c>
@@ -9522,10 +9522,10 @@
         <v>0</v>
       </c>
       <c r="O169" s="27" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A170" s="27" t="s">
         <v>324</v>
       </c>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="O170" s="27" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A171" s="27" t="s">
         <v>324</v>
       </c>
@@ -9610,10 +9610,10 @@
         <v>0</v>
       </c>
       <c r="O171" s="27" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A172" s="27" t="s">
         <v>324</v>
       </c>
@@ -9654,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="O172" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A173" s="27" t="s">
         <v>324</v>
       </c>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="O173" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A174" s="27" t="s">
         <v>324</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="175" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A175" s="27" t="s">
         <v>324</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="176" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A176" s="27" t="s">
         <v>324</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="177" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A177" s="27" t="s">
         <v>324</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="178" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A178" s="27" t="s">
         <v>324</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="179" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A179" s="27" t="s">
         <v>324</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="180" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A180" s="27" t="s">
         <v>324</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="181" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A181" s="27" t="s">
         <v>324</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="13" customHeight="1">
+    <row r="182" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A182" s="9" t="s">
         <v>324</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="13" customHeight="1">
+    <row r="183" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A183" s="9" t="s">
         <v>324</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="13" customHeight="1">
+    <row r="184" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A184" s="9" t="s">
         <v>324</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="13" customHeight="1">
+    <row r="185" spans="1:21" ht="13" hidden="1" customHeight="1">
       <c r="A185" s="9" t="s">
         <v>324</v>
       </c>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="U185" s="11"/>
     </row>
-    <row r="186" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="186" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A186" s="27" t="s">
         <v>324</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="187" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A187" s="27" t="s">
         <v>324</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="188" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A188" s="27" t="s">
         <v>324</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="189" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A189" s="27" t="s">
         <v>324</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="190" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A190" s="27" t="s">
         <v>324</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="191" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A191" s="27" t="s">
         <v>324</v>
       </c>
@@ -10491,10 +10491,10 @@
         <v>0</v>
       </c>
       <c r="O191" s="27" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A192" s="27" t="s">
         <v>324</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="193" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A193" s="27" t="s">
         <v>324</v>
       </c>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="O194" s="27" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A195" s="27" t="s">
         <v>324</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" customHeight="1">
+    <row r="196" spans="1:15" s="27" customFormat="1" ht="13" hidden="1" customHeight="1">
       <c r="A196" s="27" t="s">
         <v>324</v>
       </c>
@@ -12513,6 +12513,23 @@
       <c r="N501" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z196" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Тамбур"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ALG 2030-45C"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Фиксатор пассивной створки накладной 220*2*8 мм ELEMENTIS с ответной планкой RAL 9016"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
